--- a/testcases.xlsx
+++ b/testcases.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\energinet.local\endk_funktion\Dynsim\13_Medarbejdermapper\CVL\MTB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCDA9812-C775-4754-AF79-27435F9726B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18450" windowHeight="10785" tabRatio="822"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="8" r:id="rId1"/>
@@ -398,7 +397,7 @@
     <definedName name="sel_ures" localSheetId="10">'[1]Area values'!$H$27</definedName>
     <definedName name="sel_ures">'Area values'!$H$27</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -419,7 +418,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5279" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5279" uniqueCount="850">
   <si>
     <t>Range</t>
   </si>
@@ -3309,11 +3308,26 @@
   <si>
     <t>Under construction</t>
   </si>
+  <si>
+    <t>DCC_SS_flatrun_Q1</t>
+  </si>
+  <si>
+    <t>DCC_SS_flatrun_Q2</t>
+  </si>
+  <si>
+    <t>DCC_SS_flatrun_Q3</t>
+  </si>
+  <si>
+    <t>DCC_SS_flatrun_Q4</t>
+  </si>
+  <si>
+    <t>DCC_SS_flatrun_Q5</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -5137,6 +5151,20 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5150,6 +5178,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5188,6 +5222,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5215,34 +5252,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="20 % - Farve3" xfId="1" builtinId="38"/>
+    <cellStyle name="20% - Accent3" xfId="1" builtinId="38"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Procent" xfId="2" builtinId="5"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5266,7 +5280,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Settings"/>
@@ -5501,7 +5515,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Settings"/>
@@ -5795,14 +5809,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00847C"/>
   </sheetPr>
   <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="7.7109375" style="3" customWidth="1"/>
@@ -5942,16 +5956,16 @@
         <v>326</v>
       </c>
       <c r="H8" s="137"/>
-      <c r="I8" s="346" t="s">
+      <c r="I8" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="J8" s="346"/>
-      <c r="K8" s="346"/>
-      <c r="L8" s="346" t="s">
+      <c r="J8" s="352"/>
+      <c r="K8" s="352"/>
+      <c r="L8" s="352" t="s">
         <v>341</v>
       </c>
-      <c r="M8" s="346"/>
-      <c r="N8" s="347"/>
+      <c r="M8" s="352"/>
+      <c r="N8" s="353"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
@@ -6310,11 +6324,11 @@
     <mergeCell ref="L8:N8"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25">
       <formula1>0.1</formula1>
       <formula2>999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" showInputMessage="1" showErrorMessage="1" sqref="B24" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="decimal" showInputMessage="1" showErrorMessage="1" sqref="B24">
       <formula1>1</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
@@ -6327,13 +6341,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E27D541C-B9E7-4263-9D37-D42E488ADEAF}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Area values'!$L$2:$L$3</xm:f>
           </x14:formula1>
           <xm:sqref>B3</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{68154F19-57F4-4F30-85E4-87753927D7D5}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Area values'!$K$2:$K$6</xm:f>
           </x14:formula1>
@@ -6346,7 +6360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF02525E"/>
   </sheetPr>
@@ -6379,7 +6393,7 @@
       <c r="B2" s="314" t="s">
         <v>357</v>
       </c>
-      <c r="C2" s="366" t="s">
+      <c r="C2" s="375" t="s">
         <v>795</v>
       </c>
       <c r="D2" s="305" t="s">
@@ -6393,7 +6407,7 @@
       <c r="B3" s="314" t="s">
         <v>358</v>
       </c>
-      <c r="C3" s="366"/>
+      <c r="C3" s="375"/>
       <c r="D3" s="306" t="s">
         <v>796</v>
       </c>
@@ -6405,7 +6419,7 @@
       <c r="B4" s="314" t="s">
         <v>359</v>
       </c>
-      <c r="C4" s="366"/>
+      <c r="C4" s="375"/>
       <c r="D4" s="307" t="s">
         <v>11</v>
       </c>
@@ -6417,7 +6431,7 @@
       <c r="B5" s="314" t="s">
         <v>360</v>
       </c>
-      <c r="C5" s="366"/>
+      <c r="C5" s="375"/>
       <c r="D5" s="307" t="s">
         <v>11</v>
       </c>
@@ -6429,7 +6443,7 @@
       <c r="B6" s="316" t="s">
         <v>361</v>
       </c>
-      <c r="C6" s="367"/>
+      <c r="C6" s="376"/>
       <c r="D6" s="308" t="s">
         <v>11</v>
       </c>
@@ -6441,7 +6455,7 @@
       <c r="B7" s="252" t="s">
         <v>239</v>
       </c>
-      <c r="C7" s="368" t="s">
+      <c r="C7" s="377" t="s">
         <v>797</v>
       </c>
       <c r="D7" s="309" t="s">
@@ -6455,7 +6469,7 @@
       <c r="B8" s="248" t="s">
         <v>240</v>
       </c>
-      <c r="C8" s="366"/>
+      <c r="C8" s="375"/>
       <c r="D8" s="307" t="s">
         <v>11</v>
       </c>
@@ -6467,7 +6481,7 @@
       <c r="B9" s="248" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="366"/>
+      <c r="C9" s="375"/>
       <c r="D9" s="307" t="s">
         <v>11</v>
       </c>
@@ -6479,7 +6493,7 @@
       <c r="B10" s="248" t="s">
         <v>242</v>
       </c>
-      <c r="C10" s="366"/>
+      <c r="C10" s="375"/>
       <c r="D10" s="307" t="s">
         <v>11</v>
       </c>
@@ -6491,7 +6505,7 @@
       <c r="B11" s="248" t="s">
         <v>243</v>
       </c>
-      <c r="C11" s="366"/>
+      <c r="C11" s="375"/>
       <c r="D11" s="307" t="s">
         <v>11</v>
       </c>
@@ -6503,7 +6517,7 @@
       <c r="B12" s="248" t="s">
         <v>244</v>
       </c>
-      <c r="C12" s="366"/>
+      <c r="C12" s="375"/>
       <c r="D12" s="307" t="s">
         <v>11</v>
       </c>
@@ -6515,7 +6529,7 @@
       <c r="B13" s="248" t="s">
         <v>245</v>
       </c>
-      <c r="C13" s="366"/>
+      <c r="C13" s="375"/>
       <c r="D13" s="307" t="s">
         <v>11</v>
       </c>
@@ -6527,7 +6541,7 @@
       <c r="B14" s="248" t="s">
         <v>246</v>
       </c>
-      <c r="C14" s="366"/>
+      <c r="C14" s="375"/>
       <c r="D14" s="307" t="s">
         <v>11</v>
       </c>
@@ -6539,7 +6553,7 @@
       <c r="B15" s="248" t="s">
         <v>247</v>
       </c>
-      <c r="C15" s="366"/>
+      <c r="C15" s="375"/>
       <c r="D15" s="307" t="s">
         <v>11</v>
       </c>
@@ -6551,7 +6565,7 @@
       <c r="B16" s="248" t="s">
         <v>248</v>
       </c>
-      <c r="C16" s="366"/>
+      <c r="C16" s="375"/>
       <c r="D16" s="307" t="s">
         <v>11</v>
       </c>
@@ -6563,7 +6577,7 @@
       <c r="B17" s="248" t="s">
         <v>249</v>
       </c>
-      <c r="C17" s="366"/>
+      <c r="C17" s="375"/>
       <c r="D17" s="307" t="s">
         <v>11</v>
       </c>
@@ -6575,7 +6589,7 @@
       <c r="B18" s="248" t="s">
         <v>250</v>
       </c>
-      <c r="C18" s="366"/>
+      <c r="C18" s="375"/>
       <c r="D18" s="307" t="s">
         <v>11</v>
       </c>
@@ -6587,7 +6601,7 @@
       <c r="B19" s="248" t="s">
         <v>740</v>
       </c>
-      <c r="C19" s="366"/>
+      <c r="C19" s="375"/>
       <c r="D19" s="306" t="s">
         <v>412</v>
       </c>
@@ -6599,7 +6613,7 @@
       <c r="B20" s="248" t="s">
         <v>741</v>
       </c>
-      <c r="C20" s="366"/>
+      <c r="C20" s="375"/>
       <c r="D20" s="306" t="s">
         <v>413</v>
       </c>
@@ -6611,7 +6625,7 @@
       <c r="B21" s="248" t="s">
         <v>742</v>
       </c>
-      <c r="C21" s="366"/>
+      <c r="C21" s="375"/>
       <c r="D21" s="306" t="s">
         <v>414</v>
       </c>
@@ -6623,7 +6637,7 @@
       <c r="B22" s="248" t="s">
         <v>743</v>
       </c>
-      <c r="C22" s="366"/>
+      <c r="C22" s="375"/>
       <c r="D22" s="307" t="s">
         <v>11</v>
       </c>
@@ -6635,7 +6649,7 @@
       <c r="B23" s="248" t="s">
         <v>744</v>
       </c>
-      <c r="C23" s="366"/>
+      <c r="C23" s="375"/>
       <c r="D23" s="307" t="s">
         <v>11</v>
       </c>
@@ -6647,7 +6661,7 @@
       <c r="B24" s="248" t="s">
         <v>745</v>
       </c>
-      <c r="C24" s="366"/>
+      <c r="C24" s="375"/>
       <c r="D24" s="306" t="s">
         <v>799</v>
       </c>
@@ -6659,7 +6673,7 @@
       <c r="B25" s="248" t="s">
         <v>746</v>
       </c>
-      <c r="C25" s="366"/>
+      <c r="C25" s="375"/>
       <c r="D25" s="306" t="s">
         <v>799</v>
       </c>
@@ -6671,7 +6685,7 @@
       <c r="B26" s="248" t="s">
         <v>251</v>
       </c>
-      <c r="C26" s="366"/>
+      <c r="C26" s="375"/>
       <c r="D26" s="306" t="s">
         <v>415</v>
       </c>
@@ -6683,7 +6697,7 @@
       <c r="B27" s="248" t="s">
         <v>252</v>
       </c>
-      <c r="C27" s="366"/>
+      <c r="C27" s="375"/>
       <c r="D27" s="306" t="s">
         <v>416</v>
       </c>
@@ -6695,7 +6709,7 @@
       <c r="B28" s="248" t="s">
         <v>747</v>
       </c>
-      <c r="C28" s="366"/>
+      <c r="C28" s="375"/>
       <c r="D28" s="306" t="s">
         <v>800</v>
       </c>
@@ -6707,7 +6721,7 @@
       <c r="B29" s="249" t="s">
         <v>748</v>
       </c>
-      <c r="C29" s="366"/>
+      <c r="C29" s="375"/>
       <c r="D29" s="306" t="s">
         <v>801</v>
       </c>
@@ -6719,7 +6733,7 @@
       <c r="B30" s="249" t="s">
         <v>749</v>
       </c>
-      <c r="C30" s="366"/>
+      <c r="C30" s="375"/>
       <c r="D30" s="306" t="s">
         <v>802</v>
       </c>
@@ -6731,7 +6745,7 @@
       <c r="B31" s="248" t="s">
         <v>351</v>
       </c>
-      <c r="C31" s="366"/>
+      <c r="C31" s="375"/>
       <c r="D31" s="306" t="s">
         <v>803</v>
       </c>
@@ -6743,7 +6757,7 @@
       <c r="B32" s="248" t="s">
         <v>750</v>
       </c>
-      <c r="C32" s="366"/>
+      <c r="C32" s="375"/>
       <c r="D32" s="306" t="s">
         <v>804</v>
       </c>
@@ -6755,7 +6769,7 @@
       <c r="B33" s="248" t="s">
         <v>751</v>
       </c>
-      <c r="C33" s="366"/>
+      <c r="C33" s="375"/>
       <c r="D33" s="306" t="s">
         <v>805</v>
       </c>
@@ -6767,7 +6781,7 @@
       <c r="B34" s="248" t="s">
         <v>806</v>
       </c>
-      <c r="C34" s="366"/>
+      <c r="C34" s="375"/>
       <c r="D34" s="306" t="s">
         <v>807</v>
       </c>
@@ -6779,7 +6793,7 @@
       <c r="B35" s="248" t="s">
         <v>808</v>
       </c>
-      <c r="C35" s="366"/>
+      <c r="C35" s="375"/>
       <c r="D35" s="306" t="s">
         <v>809</v>
       </c>
@@ -6791,7 +6805,7 @@
       <c r="B36" s="248" t="s">
         <v>834</v>
       </c>
-      <c r="C36" s="366"/>
+      <c r="C36" s="375"/>
       <c r="D36" s="306" t="s">
         <v>810</v>
       </c>
@@ -6803,7 +6817,7 @@
       <c r="B37" s="248" t="s">
         <v>835</v>
       </c>
-      <c r="C37" s="366"/>
+      <c r="C37" s="375"/>
       <c r="D37" s="307" t="s">
         <v>11</v>
       </c>
@@ -6815,7 +6829,7 @@
       <c r="B38" s="248" t="s">
         <v>836</v>
       </c>
-      <c r="C38" s="366"/>
+      <c r="C38" s="375"/>
       <c r="D38" s="307" t="s">
         <v>11</v>
       </c>
@@ -6827,7 +6841,7 @@
       <c r="B39" s="248" t="s">
         <v>837</v>
       </c>
-      <c r="C39" s="366"/>
+      <c r="C39" s="375"/>
       <c r="D39" s="307" t="s">
         <v>11</v>
       </c>
@@ -6839,7 +6853,7 @@
       <c r="B40" s="248" t="s">
         <v>838</v>
       </c>
-      <c r="C40" s="366"/>
+      <c r="C40" s="375"/>
       <c r="D40" s="307" t="s">
         <v>11</v>
       </c>
@@ -6851,7 +6865,7 @@
       <c r="B41" s="248" t="s">
         <v>839</v>
       </c>
-      <c r="C41" s="366"/>
+      <c r="C41" s="375"/>
       <c r="D41" s="307" t="s">
         <v>11</v>
       </c>
@@ -6863,7 +6877,7 @@
       <c r="B42" s="248" t="s">
         <v>840</v>
       </c>
-      <c r="C42" s="366"/>
+      <c r="C42" s="375"/>
       <c r="D42" s="307" t="s">
         <v>11</v>
       </c>
@@ -6875,7 +6889,7 @@
       <c r="B43" s="250" t="s">
         <v>841</v>
       </c>
-      <c r="C43" s="367"/>
+      <c r="C43" s="376"/>
       <c r="D43" s="308" t="s">
         <v>11</v>
       </c>
@@ -6887,7 +6901,7 @@
       <c r="B44" s="318" t="s">
         <v>253</v>
       </c>
-      <c r="C44" s="368" t="s">
+      <c r="C44" s="377" t="s">
         <v>398</v>
       </c>
       <c r="D44" s="306" t="s">
@@ -6901,7 +6915,7 @@
       <c r="B45" s="320" t="s">
         <v>754</v>
       </c>
-      <c r="C45" s="367"/>
+      <c r="C45" s="376"/>
       <c r="D45" s="310" t="s">
         <v>814</v>
       </c>
@@ -6913,7 +6927,7 @@
       <c r="B46" s="322" t="s">
         <v>254</v>
       </c>
-      <c r="C46" s="368" t="s">
+      <c r="C46" s="377" t="s">
         <v>811</v>
       </c>
       <c r="D46" s="306" t="s">
@@ -6927,7 +6941,7 @@
       <c r="B47" s="324" t="s">
         <v>255</v>
       </c>
-      <c r="C47" s="366"/>
+      <c r="C47" s="375"/>
       <c r="D47" s="306" t="s">
         <v>401</v>
       </c>
@@ -6939,7 +6953,7 @@
       <c r="B48" s="324" t="s">
         <v>256</v>
       </c>
-      <c r="C48" s="366"/>
+      <c r="C48" s="375"/>
       <c r="D48" s="306" t="s">
         <v>402</v>
       </c>
@@ -6951,7 +6965,7 @@
       <c r="B49" s="324" t="s">
         <v>257</v>
       </c>
-      <c r="C49" s="366"/>
+      <c r="C49" s="375"/>
       <c r="D49" s="306" t="s">
         <v>403</v>
       </c>
@@ -6963,7 +6977,7 @@
       <c r="B50" s="324" t="s">
         <v>258</v>
       </c>
-      <c r="C50" s="366"/>
+      <c r="C50" s="375"/>
       <c r="D50" s="306" t="s">
         <v>404</v>
       </c>
@@ -6975,7 +6989,7 @@
       <c r="B51" s="324" t="s">
         <v>259</v>
       </c>
-      <c r="C51" s="366"/>
+      <c r="C51" s="375"/>
       <c r="D51" s="306" t="s">
         <v>405</v>
       </c>
@@ -6987,7 +7001,7 @@
       <c r="B52" s="324" t="s">
         <v>755</v>
       </c>
-      <c r="C52" s="366"/>
+      <c r="C52" s="375"/>
       <c r="D52" s="306" t="s">
         <v>429</v>
       </c>
@@ -6999,7 +7013,7 @@
       <c r="B53" s="324" t="s">
         <v>756</v>
       </c>
-      <c r="C53" s="366"/>
+      <c r="C53" s="375"/>
       <c r="D53" s="306" t="s">
         <v>11</v>
       </c>
@@ -7011,7 +7025,7 @@
       <c r="B54" s="324" t="s">
         <v>757</v>
       </c>
-      <c r="C54" s="366"/>
+      <c r="C54" s="375"/>
       <c r="D54" s="306" t="s">
         <v>815</v>
       </c>
@@ -7023,7 +7037,7 @@
       <c r="B55" s="326" t="s">
         <v>758</v>
       </c>
-      <c r="C55" s="367"/>
+      <c r="C55" s="376"/>
       <c r="D55" s="52" t="s">
         <v>11</v>
       </c>
@@ -7035,7 +7049,7 @@
       <c r="B56" s="328" t="s">
         <v>260</v>
       </c>
-      <c r="C56" s="368" t="s">
+      <c r="C56" s="377" t="s">
         <v>108</v>
       </c>
       <c r="D56" s="311" t="s">
@@ -7049,7 +7063,7 @@
       <c r="B57" s="330" t="s">
         <v>261</v>
       </c>
-      <c r="C57" s="366"/>
+      <c r="C57" s="375"/>
       <c r="D57" s="311" t="s">
         <v>817</v>
       </c>
@@ -7061,7 +7075,7 @@
       <c r="B58" s="330" t="s">
         <v>262</v>
       </c>
-      <c r="C58" s="366"/>
+      <c r="C58" s="375"/>
       <c r="D58" s="311" t="s">
         <v>818</v>
       </c>
@@ -7073,7 +7087,7 @@
       <c r="B59" s="330" t="s">
         <v>263</v>
       </c>
-      <c r="C59" s="366"/>
+      <c r="C59" s="375"/>
       <c r="D59" s="311" t="s">
         <v>819</v>
       </c>
@@ -7085,7 +7099,7 @@
       <c r="B60" s="330" t="s">
         <v>794</v>
       </c>
-      <c r="C60" s="366"/>
+      <c r="C60" s="375"/>
       <c r="D60" s="311" t="s">
         <v>820</v>
       </c>
@@ -7097,7 +7111,7 @@
       <c r="B61" s="330" t="s">
         <v>759</v>
       </c>
-      <c r="C61" s="366"/>
+      <c r="C61" s="375"/>
       <c r="D61" s="311" t="s">
         <v>821</v>
       </c>
@@ -7109,7 +7123,7 @@
       <c r="B62" s="330" t="s">
         <v>264</v>
       </c>
-      <c r="C62" s="366"/>
+      <c r="C62" s="375"/>
       <c r="D62" s="311" t="s">
         <v>822</v>
       </c>
@@ -7121,7 +7135,7 @@
       <c r="B63" s="332" t="s">
         <v>265</v>
       </c>
-      <c r="C63" s="367"/>
+      <c r="C63" s="376"/>
       <c r="D63" s="52" t="s">
         <v>823</v>
       </c>
@@ -7133,7 +7147,7 @@
       <c r="B64" s="252" t="s">
         <v>266</v>
       </c>
-      <c r="C64" s="368" t="s">
+      <c r="C64" s="377" t="s">
         <v>824</v>
       </c>
       <c r="D64" s="309" t="s">
@@ -7147,7 +7161,7 @@
       <c r="B65" s="248" t="s">
         <v>267</v>
       </c>
-      <c r="C65" s="366"/>
+      <c r="C65" s="375"/>
       <c r="D65" s="306" t="s">
         <v>11</v>
       </c>
@@ -7159,7 +7173,7 @@
       <c r="B66" s="248" t="s">
         <v>268</v>
       </c>
-      <c r="C66" s="366"/>
+      <c r="C66" s="375"/>
       <c r="D66" s="306" t="s">
         <v>11</v>
       </c>
@@ -7171,7 +7185,7 @@
       <c r="B67" s="248" t="s">
         <v>269</v>
       </c>
-      <c r="C67" s="366"/>
+      <c r="C67" s="375"/>
       <c r="D67" s="306" t="s">
         <v>11</v>
       </c>
@@ -7183,7 +7197,7 @@
       <c r="B68" s="248" t="s">
         <v>270</v>
       </c>
-      <c r="C68" s="366"/>
+      <c r="C68" s="375"/>
       <c r="D68" s="306" t="s">
         <v>11</v>
       </c>
@@ -7195,7 +7209,7 @@
       <c r="B69" s="248" t="s">
         <v>760</v>
       </c>
-      <c r="C69" s="366"/>
+      <c r="C69" s="375"/>
       <c r="D69" s="306" t="s">
         <v>11</v>
       </c>
@@ -7207,7 +7221,7 @@
       <c r="B70" s="250" t="s">
         <v>761</v>
       </c>
-      <c r="C70" s="367"/>
+      <c r="C70" s="376"/>
       <c r="D70" s="52" t="s">
         <v>11</v>
       </c>
@@ -7219,7 +7233,7 @@
       <c r="B71" s="318" t="s">
         <v>762</v>
       </c>
-      <c r="C71" s="368" t="s">
+      <c r="C71" s="377" t="s">
         <v>812</v>
       </c>
       <c r="D71" s="304" t="s">
@@ -7233,7 +7247,7 @@
       <c r="B72" s="334" t="s">
         <v>763</v>
       </c>
-      <c r="C72" s="366"/>
+      <c r="C72" s="375"/>
       <c r="D72" s="304" t="s">
         <v>832</v>
       </c>
@@ -7245,7 +7259,7 @@
       <c r="B73" s="334" t="s">
         <v>352</v>
       </c>
-      <c r="C73" s="366"/>
+      <c r="C73" s="375"/>
       <c r="D73" s="165" t="s">
         <v>454</v>
       </c>
@@ -7257,7 +7271,7 @@
       <c r="B74" s="334" t="s">
         <v>764</v>
       </c>
-      <c r="C74" s="366"/>
+      <c r="C74" s="375"/>
       <c r="D74" s="165" t="s">
         <v>455</v>
       </c>
@@ -7269,7 +7283,7 @@
       <c r="B75" s="334" t="s">
         <v>353</v>
       </c>
-      <c r="C75" s="366"/>
+      <c r="C75" s="375"/>
       <c r="D75" s="165" t="s">
         <v>828</v>
       </c>
@@ -7281,7 +7295,7 @@
       <c r="B76" s="334" t="s">
         <v>765</v>
       </c>
-      <c r="C76" s="366"/>
+      <c r="C76" s="375"/>
       <c r="D76" s="165" t="s">
         <v>829</v>
       </c>
@@ -7293,7 +7307,7 @@
       <c r="B77" s="334" t="s">
         <v>766</v>
       </c>
-      <c r="C77" s="366"/>
+      <c r="C77" s="375"/>
       <c r="D77" s="165" t="s">
         <v>831</v>
       </c>
@@ -7305,7 +7319,7 @@
       <c r="B78" s="334" t="s">
         <v>767</v>
       </c>
-      <c r="C78" s="366"/>
+      <c r="C78" s="375"/>
       <c r="D78" s="165" t="s">
         <v>830</v>
       </c>
@@ -7317,7 +7331,7 @@
       <c r="B79" s="334" t="s">
         <v>768</v>
       </c>
-      <c r="C79" s="366"/>
+      <c r="C79" s="375"/>
       <c r="D79" s="311" t="s">
         <v>826</v>
       </c>
@@ -7329,7 +7343,7 @@
       <c r="B80" s="334" t="s">
         <v>769</v>
       </c>
-      <c r="C80" s="366"/>
+      <c r="C80" s="375"/>
       <c r="D80" s="306" t="s">
         <v>11</v>
       </c>
@@ -7341,7 +7355,7 @@
       <c r="B81" s="334" t="s">
         <v>770</v>
       </c>
-      <c r="C81" s="366"/>
+      <c r="C81" s="375"/>
       <c r="D81" s="306" t="s">
         <v>11</v>
       </c>
@@ -7353,7 +7367,7 @@
       <c r="B82" s="320" t="s">
         <v>771</v>
       </c>
-      <c r="C82" s="367"/>
+      <c r="C82" s="376"/>
       <c r="D82" s="52" t="s">
         <v>11</v>
       </c>
@@ -7365,7 +7379,7 @@
       <c r="B83" s="322" t="s">
         <v>772</v>
       </c>
-      <c r="C83" s="368" t="s">
+      <c r="C83" s="377" t="s">
         <v>451</v>
       </c>
       <c r="D83" s="309" t="s">
@@ -7379,7 +7393,7 @@
       <c r="B84" s="324" t="s">
         <v>773</v>
       </c>
-      <c r="C84" s="366"/>
+      <c r="C84" s="375"/>
       <c r="D84" s="306" t="s">
         <v>11</v>
       </c>
@@ -7391,7 +7405,7 @@
       <c r="B85" s="324" t="s">
         <v>774</v>
       </c>
-      <c r="C85" s="366"/>
+      <c r="C85" s="375"/>
       <c r="D85" s="306" t="s">
         <v>11</v>
       </c>
@@ -7403,7 +7417,7 @@
       <c r="B86" s="324" t="s">
         <v>775</v>
       </c>
-      <c r="C86" s="366"/>
+      <c r="C86" s="375"/>
       <c r="D86" s="306" t="s">
         <v>11</v>
       </c>
@@ -7415,7 +7429,7 @@
       <c r="B87" s="326" t="s">
         <v>776</v>
       </c>
-      <c r="C87" s="367"/>
+      <c r="C87" s="376"/>
       <c r="D87" s="52" t="s">
         <v>11</v>
       </c>
@@ -7437,7 +7451,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF02525E"/>
   </sheetPr>
@@ -7469,7 +7483,7 @@
       <c r="B2" s="210" t="s">
         <v>271</v>
       </c>
-      <c r="C2" s="363" t="s">
+      <c r="C2" s="372" t="s">
         <v>362</v>
       </c>
       <c r="D2" s="172" t="s">
@@ -7483,7 +7497,7 @@
       <c r="B3" s="343" t="s">
         <v>272</v>
       </c>
-      <c r="C3" s="364"/>
+      <c r="C3" s="373"/>
       <c r="D3" s="304" t="s">
         <v>11</v>
       </c>
@@ -7495,7 +7509,7 @@
       <c r="B4" s="343" t="s">
         <v>273</v>
       </c>
-      <c r="C4" s="364"/>
+      <c r="C4" s="373"/>
       <c r="D4" s="304" t="s">
         <v>11</v>
       </c>
@@ -7507,7 +7521,7 @@
       <c r="B5" s="343" t="s">
         <v>274</v>
       </c>
-      <c r="C5" s="364"/>
+      <c r="C5" s="373"/>
       <c r="D5" s="304" t="s">
         <v>11</v>
       </c>
@@ -7519,7 +7533,7 @@
       <c r="B6" s="343" t="s">
         <v>275</v>
       </c>
-      <c r="C6" s="364"/>
+      <c r="C6" s="373"/>
       <c r="D6" s="304" t="s">
         <v>11</v>
       </c>
@@ -7531,7 +7545,7 @@
       <c r="B7" s="212" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="365"/>
+      <c r="C7" s="374"/>
       <c r="D7" s="169" t="s">
         <v>11</v>
       </c>
@@ -7557,7 +7571,7 @@
       <c r="B9" s="162" t="s">
         <v>278</v>
       </c>
-      <c r="C9" s="369" t="s">
+      <c r="C9" s="378" t="s">
         <v>467</v>
       </c>
       <c r="D9" s="172" t="s">
@@ -7571,7 +7585,7 @@
       <c r="B10" s="164" t="s">
         <v>279</v>
       </c>
-      <c r="C10" s="370"/>
+      <c r="C10" s="379"/>
       <c r="D10" s="304" t="s">
         <v>469</v>
       </c>
@@ -7583,7 +7597,7 @@
       <c r="B11" s="164" t="s">
         <v>777</v>
       </c>
-      <c r="C11" s="370"/>
+      <c r="C11" s="379"/>
       <c r="D11" s="304" t="s">
         <v>825</v>
       </c>
@@ -7595,7 +7609,7 @@
       <c r="B12" s="164" t="s">
         <v>778</v>
       </c>
-      <c r="C12" s="370"/>
+      <c r="C12" s="379"/>
       <c r="D12" s="304" t="s">
         <v>11</v>
       </c>
@@ -7607,7 +7621,7 @@
       <c r="B13" s="164" t="s">
         <v>779</v>
       </c>
-      <c r="C13" s="370"/>
+      <c r="C13" s="379"/>
       <c r="D13" s="304" t="s">
         <v>11</v>
       </c>
@@ -7619,7 +7633,7 @@
       <c r="B14" s="164" t="s">
         <v>780</v>
       </c>
-      <c r="C14" s="370"/>
+      <c r="C14" s="379"/>
       <c r="D14" s="304" t="s">
         <v>11</v>
       </c>
@@ -7631,7 +7645,7 @@
       <c r="B15" s="164" t="s">
         <v>781</v>
       </c>
-      <c r="C15" s="370"/>
+      <c r="C15" s="379"/>
       <c r="D15" s="304" t="s">
         <v>11</v>
       </c>
@@ -7643,7 +7657,7 @@
       <c r="B16" s="164" t="s">
         <v>782</v>
       </c>
-      <c r="C16" s="370"/>
+      <c r="C16" s="379"/>
       <c r="D16" s="304" t="s">
         <v>11</v>
       </c>
@@ -7655,7 +7669,7 @@
       <c r="B17" s="204" t="s">
         <v>783</v>
       </c>
-      <c r="C17" s="371"/>
+      <c r="C17" s="380"/>
       <c r="D17" s="169" t="s">
         <v>11</v>
       </c>
@@ -7667,7 +7681,7 @@
       <c r="B18" s="202" t="s">
         <v>280</v>
       </c>
-      <c r="C18" s="363" t="s">
+      <c r="C18" s="372" t="s">
         <v>470</v>
       </c>
       <c r="D18" s="172" t="s">
@@ -7681,7 +7695,7 @@
       <c r="B19" s="338" t="s">
         <v>281</v>
       </c>
-      <c r="C19" s="364"/>
+      <c r="C19" s="373"/>
       <c r="D19" s="304" t="s">
         <v>472</v>
       </c>
@@ -7693,7 +7707,7 @@
       <c r="B20" s="203" t="s">
         <v>282</v>
       </c>
-      <c r="C20" s="365"/>
+      <c r="C20" s="374"/>
       <c r="D20" s="169" t="s">
         <v>473</v>
       </c>
@@ -7705,7 +7719,7 @@
       <c r="B21" s="180" t="s">
         <v>283</v>
       </c>
-      <c r="C21" s="369" t="s">
+      <c r="C21" s="378" t="s">
         <v>408</v>
       </c>
       <c r="D21" s="172" t="s">
@@ -7719,7 +7733,7 @@
       <c r="B22" s="181" t="s">
         <v>284</v>
       </c>
-      <c r="C22" s="370"/>
+      <c r="C22" s="379"/>
       <c r="D22" s="304" t="s">
         <v>11</v>
       </c>
@@ -7731,7 +7745,7 @@
       <c r="B23" s="181" t="s">
         <v>285</v>
       </c>
-      <c r="C23" s="370"/>
+      <c r="C23" s="379"/>
       <c r="D23" s="304" t="s">
         <v>11</v>
       </c>
@@ -7743,7 +7757,7 @@
       <c r="B24" s="181" t="s">
         <v>286</v>
       </c>
-      <c r="C24" s="370"/>
+      <c r="C24" s="379"/>
       <c r="D24" s="304" t="s">
         <v>11</v>
       </c>
@@ -7755,7 +7769,7 @@
       <c r="B25" s="181" t="s">
         <v>287</v>
       </c>
-      <c r="C25" s="370"/>
+      <c r="C25" s="379"/>
       <c r="D25" s="304" t="s">
         <v>11</v>
       </c>
@@ -7767,7 +7781,7 @@
       <c r="B26" s="181" t="s">
         <v>288</v>
       </c>
-      <c r="C26" s="370"/>
+      <c r="C26" s="379"/>
       <c r="D26" s="304" t="s">
         <v>11</v>
       </c>
@@ -7779,7 +7793,7 @@
       <c r="B27" s="181" t="s">
         <v>289</v>
       </c>
-      <c r="C27" s="370"/>
+      <c r="C27" s="379"/>
       <c r="D27" s="304" t="s">
         <v>11</v>
       </c>
@@ -7791,7 +7805,7 @@
       <c r="B28" s="181" t="s">
         <v>290</v>
       </c>
-      <c r="C28" s="370"/>
+      <c r="C28" s="379"/>
       <c r="D28" s="304" t="s">
         <v>11</v>
       </c>
@@ -7803,7 +7817,7 @@
       <c r="B29" s="181" t="s">
         <v>291</v>
       </c>
-      <c r="C29" s="370"/>
+      <c r="C29" s="379"/>
       <c r="D29" s="304" t="s">
         <v>11</v>
       </c>
@@ -7815,7 +7829,7 @@
       <c r="B30" s="181" t="s">
         <v>292</v>
       </c>
-      <c r="C30" s="370"/>
+      <c r="C30" s="379"/>
       <c r="D30" s="304" t="s">
         <v>11</v>
       </c>
@@ -7827,7 +7841,7 @@
       <c r="B31" s="181" t="s">
         <v>293</v>
       </c>
-      <c r="C31" s="370"/>
+      <c r="C31" s="379"/>
       <c r="D31" s="304" t="s">
         <v>11</v>
       </c>
@@ -7839,7 +7853,7 @@
       <c r="B32" s="181" t="s">
         <v>294</v>
       </c>
-      <c r="C32" s="370"/>
+      <c r="C32" s="379"/>
       <c r="D32" s="304" t="s">
         <v>11</v>
       </c>
@@ -7851,7 +7865,7 @@
       <c r="B33" s="181" t="s">
         <v>295</v>
       </c>
-      <c r="C33" s="370"/>
+      <c r="C33" s="379"/>
       <c r="D33" s="304" t="s">
         <v>411</v>
       </c>
@@ -7863,7 +7877,7 @@
       <c r="B34" s="181" t="s">
         <v>296</v>
       </c>
-      <c r="C34" s="370"/>
+      <c r="C34" s="379"/>
       <c r="D34" s="304" t="s">
         <v>412</v>
       </c>
@@ -7875,7 +7889,7 @@
       <c r="B35" s="181" t="s">
         <v>297</v>
       </c>
-      <c r="C35" s="370"/>
+      <c r="C35" s="379"/>
       <c r="D35" s="304" t="s">
         <v>413</v>
       </c>
@@ -7887,7 +7901,7 @@
       <c r="B36" s="181" t="s">
         <v>298</v>
       </c>
-      <c r="C36" s="370"/>
+      <c r="C36" s="379"/>
       <c r="D36" s="304" t="s">
         <v>414</v>
       </c>
@@ -7899,7 +7913,7 @@
       <c r="B37" s="181" t="s">
         <v>299</v>
       </c>
-      <c r="C37" s="370"/>
+      <c r="C37" s="379"/>
       <c r="D37" s="304" t="s">
         <v>475</v>
       </c>
@@ -7911,7 +7925,7 @@
       <c r="B38" s="181" t="s">
         <v>300</v>
       </c>
-      <c r="C38" s="370"/>
+      <c r="C38" s="379"/>
       <c r="D38" s="304" t="s">
         <v>475</v>
       </c>
@@ -7923,7 +7937,7 @@
       <c r="B39" s="181" t="s">
         <v>301</v>
       </c>
-      <c r="C39" s="370"/>
+      <c r="C39" s="379"/>
       <c r="D39" s="304" t="s">
         <v>441</v>
       </c>
@@ -7935,7 +7949,7 @@
       <c r="B40" s="181" t="s">
         <v>302</v>
       </c>
-      <c r="C40" s="370"/>
+      <c r="C40" s="379"/>
       <c r="D40" s="304" t="s">
         <v>441</v>
       </c>
@@ -7947,7 +7961,7 @@
       <c r="B41" s="181" t="s">
         <v>303</v>
       </c>
-      <c r="C41" s="370"/>
+      <c r="C41" s="379"/>
       <c r="D41" s="304" t="s">
         <v>415</v>
       </c>
@@ -7959,7 +7973,7 @@
       <c r="B42" s="181" t="s">
         <v>304</v>
       </c>
-      <c r="C42" s="370"/>
+      <c r="C42" s="379"/>
       <c r="D42" s="304" t="s">
         <v>416</v>
       </c>
@@ -7971,7 +7985,7 @@
       <c r="B43" s="181" t="s">
         <v>790</v>
       </c>
-      <c r="C43" s="370"/>
+      <c r="C43" s="379"/>
       <c r="D43" s="304" t="s">
         <v>809</v>
       </c>
@@ -7983,7 +7997,7 @@
       <c r="B44" s="181" t="s">
         <v>791</v>
       </c>
-      <c r="C44" s="370"/>
+      <c r="C44" s="379"/>
       <c r="D44" s="304" t="s">
         <v>810</v>
       </c>
@@ -7995,7 +8009,7 @@
       <c r="B45" s="181" t="s">
         <v>305</v>
       </c>
-      <c r="C45" s="370"/>
+      <c r="C45" s="379"/>
       <c r="D45" s="304" t="s">
         <v>476</v>
       </c>
@@ -8007,7 +8021,7 @@
       <c r="B46" s="181" t="s">
         <v>356</v>
       </c>
-      <c r="C46" s="370"/>
+      <c r="C46" s="379"/>
       <c r="D46" s="304" t="s">
         <v>477</v>
       </c>
@@ -8019,7 +8033,7 @@
       <c r="B47" s="181" t="s">
         <v>788</v>
       </c>
-      <c r="C47" s="370"/>
+      <c r="C47" s="379"/>
       <c r="D47" s="304" t="s">
         <v>801</v>
       </c>
@@ -8031,7 +8045,7 @@
       <c r="B48" s="201" t="s">
         <v>789</v>
       </c>
-      <c r="C48" s="371"/>
+      <c r="C48" s="380"/>
       <c r="D48" s="169" t="s">
         <v>802</v>
       </c>
@@ -8043,7 +8057,7 @@
       <c r="B49" s="202" t="s">
         <v>306</v>
       </c>
-      <c r="C49" s="363" t="s">
+      <c r="C49" s="372" t="s">
         <v>470</v>
       </c>
       <c r="D49" s="172" t="s">
@@ -8057,7 +8071,7 @@
       <c r="B50" s="338" t="s">
         <v>307</v>
       </c>
-      <c r="C50" s="364"/>
+      <c r="C50" s="373"/>
       <c r="D50" s="304" t="s">
         <v>401</v>
       </c>
@@ -8069,7 +8083,7 @@
       <c r="B51" s="338" t="s">
         <v>792</v>
       </c>
-      <c r="C51" s="364"/>
+      <c r="C51" s="373"/>
       <c r="D51" s="304" t="s">
         <v>402</v>
       </c>
@@ -8081,7 +8095,7 @@
       <c r="B52" s="338" t="s">
         <v>793</v>
       </c>
-      <c r="C52" s="364"/>
+      <c r="C52" s="373"/>
       <c r="D52" s="304" t="s">
         <v>403</v>
       </c>
@@ -8093,7 +8107,7 @@
       <c r="B53" s="338" t="s">
         <v>308</v>
       </c>
-      <c r="C53" s="364"/>
+      <c r="C53" s="373"/>
       <c r="D53" s="304" t="s">
         <v>404</v>
       </c>
@@ -8105,7 +8119,7 @@
       <c r="B54" s="338" t="s">
         <v>309</v>
       </c>
-      <c r="C54" s="364"/>
+      <c r="C54" s="373"/>
       <c r="D54" s="304" t="s">
         <v>405</v>
       </c>
@@ -8117,7 +8131,7 @@
       <c r="B55" s="338" t="s">
         <v>337</v>
       </c>
-      <c r="C55" s="364"/>
+      <c r="C55" s="373"/>
       <c r="D55" s="304" t="s">
         <v>833</v>
       </c>
@@ -8129,7 +8143,7 @@
       <c r="B56" s="203" t="s">
         <v>338</v>
       </c>
-      <c r="C56" s="365"/>
+      <c r="C56" s="374"/>
       <c r="D56" s="169" t="s">
         <v>11</v>
       </c>
@@ -8141,7 +8155,7 @@
       <c r="B57" s="206" t="s">
         <v>784</v>
       </c>
-      <c r="C57" s="363" t="s">
+      <c r="C57" s="372" t="s">
         <v>451</v>
       </c>
       <c r="D57" s="172" t="s">
@@ -8155,7 +8169,7 @@
       <c r="B58" s="339" t="s">
         <v>785</v>
       </c>
-      <c r="C58" s="364"/>
+      <c r="C58" s="373"/>
       <c r="D58" s="304" t="s">
         <v>832</v>
       </c>
@@ -8167,7 +8181,7 @@
       <c r="B59" s="339" t="s">
         <v>310</v>
       </c>
-      <c r="C59" s="364"/>
+      <c r="C59" s="373"/>
       <c r="D59" s="304" t="s">
         <v>478</v>
       </c>
@@ -8179,7 +8193,7 @@
       <c r="B60" s="339" t="s">
         <v>311</v>
       </c>
-      <c r="C60" s="364"/>
+      <c r="C60" s="373"/>
       <c r="D60" s="304" t="s">
         <v>11</v>
       </c>
@@ -8191,7 +8205,7 @@
       <c r="B61" s="339" t="s">
         <v>312</v>
       </c>
-      <c r="C61" s="364"/>
+      <c r="C61" s="373"/>
       <c r="D61" s="304" t="s">
         <v>11</v>
       </c>
@@ -8203,7 +8217,7 @@
       <c r="B62" s="339" t="s">
         <v>313</v>
       </c>
-      <c r="C62" s="364"/>
+      <c r="C62" s="373"/>
       <c r="D62" s="304" t="s">
         <v>11</v>
       </c>
@@ -8215,7 +8229,7 @@
       <c r="B63" s="339" t="s">
         <v>329</v>
       </c>
-      <c r="C63" s="364"/>
+      <c r="C63" s="373"/>
       <c r="D63" s="304" t="s">
         <v>454</v>
       </c>
@@ -8227,7 +8241,7 @@
       <c r="B64" s="339" t="s">
         <v>330</v>
       </c>
-      <c r="C64" s="364"/>
+      <c r="C64" s="373"/>
       <c r="D64" s="304" t="s">
         <v>455</v>
       </c>
@@ -8239,7 +8253,7 @@
       <c r="B65" s="339" t="s">
         <v>786</v>
       </c>
-      <c r="C65" s="364"/>
+      <c r="C65" s="373"/>
       <c r="D65" s="304" t="s">
         <v>828</v>
       </c>
@@ -8251,7 +8265,7 @@
       <c r="B66" s="339" t="s">
         <v>787</v>
       </c>
-      <c r="C66" s="364"/>
+      <c r="C66" s="373"/>
       <c r="D66" s="304" t="s">
         <v>829</v>
       </c>
@@ -8263,7 +8277,7 @@
       <c r="B67" s="339" t="s">
         <v>354</v>
       </c>
-      <c r="C67" s="364"/>
+      <c r="C67" s="373"/>
       <c r="D67" s="304" t="s">
         <v>463</v>
       </c>
@@ -8275,7 +8289,7 @@
       <c r="B68" s="339" t="s">
         <v>355</v>
       </c>
-      <c r="C68" s="364"/>
+      <c r="C68" s="373"/>
       <c r="D68" s="304" t="s">
         <v>464</v>
       </c>
@@ -8287,7 +8301,7 @@
       <c r="B69" s="339" t="s">
         <v>336</v>
       </c>
-      <c r="C69" s="364"/>
+      <c r="C69" s="373"/>
       <c r="D69" s="304" t="s">
         <v>456</v>
       </c>
@@ -8299,7 +8313,7 @@
       <c r="B70" s="339" t="s">
         <v>332</v>
       </c>
-      <c r="C70" s="364"/>
+      <c r="C70" s="373"/>
       <c r="D70" s="304" t="s">
         <v>11</v>
       </c>
@@ -8311,7 +8325,7 @@
       <c r="B71" s="339" t="s">
         <v>333</v>
       </c>
-      <c r="C71" s="364"/>
+      <c r="C71" s="373"/>
       <c r="D71" s="304" t="s">
         <v>11</v>
       </c>
@@ -8323,7 +8337,7 @@
       <c r="B72" s="339" t="s">
         <v>335</v>
       </c>
-      <c r="C72" s="364"/>
+      <c r="C72" s="373"/>
       <c r="D72" s="304" t="s">
         <v>11</v>
       </c>
@@ -8335,7 +8349,7 @@
       <c r="B73" s="339" t="s">
         <v>334</v>
       </c>
-      <c r="C73" s="364"/>
+      <c r="C73" s="373"/>
       <c r="D73" s="304" t="s">
         <v>11</v>
       </c>
@@ -8347,7 +8361,7 @@
       <c r="B74" s="339" t="s">
         <v>314</v>
       </c>
-      <c r="C74" s="364"/>
+      <c r="C74" s="373"/>
       <c r="D74" s="304" t="s">
         <v>457</v>
       </c>
@@ -8359,7 +8373,7 @@
       <c r="B75" s="339" t="s">
         <v>315</v>
       </c>
-      <c r="C75" s="364"/>
+      <c r="C75" s="373"/>
       <c r="D75" s="304" t="s">
         <v>458</v>
       </c>
@@ -8371,7 +8385,7 @@
       <c r="B76" s="339" t="s">
         <v>316</v>
       </c>
-      <c r="C76" s="364"/>
+      <c r="C76" s="373"/>
       <c r="D76" s="304" t="s">
         <v>459</v>
       </c>
@@ -8383,7 +8397,7 @@
       <c r="B77" s="208" t="s">
         <v>317</v>
       </c>
-      <c r="C77" s="365"/>
+      <c r="C77" s="374"/>
       <c r="D77" s="169" t="s">
         <v>460</v>
       </c>
@@ -8417,7 +8431,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54FFE98A-1C9B-40D8-B2B6-03FA45DA598B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF02525E"/>
   </sheetPr>
@@ -8443,36 +8457,36 @@
       </c>
     </row>
     <row r="156" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="380" t="s">
+      <c r="B156" s="371" t="s">
         <v>844</v>
       </c>
-      <c r="C156" s="380"/>
-      <c r="D156" s="380"/>
+      <c r="C156" s="371"/>
+      <c r="D156" s="371"/>
     </row>
     <row r="157" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="380"/>
-      <c r="C157" s="380"/>
-      <c r="D157" s="380"/>
+      <c r="B157" s="371"/>
+      <c r="C157" s="371"/>
+      <c r="D157" s="371"/>
     </row>
     <row r="158" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B158" s="380"/>
-      <c r="C158" s="380"/>
-      <c r="D158" s="380"/>
+      <c r="B158" s="371"/>
+      <c r="C158" s="371"/>
+      <c r="D158" s="371"/>
     </row>
     <row r="159" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="380"/>
-      <c r="C159" s="380"/>
-      <c r="D159" s="380"/>
+      <c r="B159" s="371"/>
+      <c r="C159" s="371"/>
+      <c r="D159" s="371"/>
     </row>
     <row r="160" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B160" s="380"/>
-      <c r="C160" s="380"/>
-      <c r="D160" s="380"/>
+      <c r="B160" s="371"/>
+      <c r="C160" s="371"/>
+      <c r="D160" s="371"/>
     </row>
     <row r="161" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="380"/>
-      <c r="C161" s="380"/>
-      <c r="D161" s="380"/>
+      <c r="B161" s="371"/>
+      <c r="C161" s="371"/>
+      <c r="D161" s="371"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -8485,7 +8499,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF02525E"/>
   </sheetPr>
@@ -8534,7 +8548,7 @@
         <f>'Custom cases'!D4</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.87pu</v>
       </c>
-      <c r="C3" s="363" t="s">
+      <c r="C3" s="372" t="s">
         <v>511</v>
       </c>
       <c r="D3" s="234" t="s">
@@ -8549,7 +8563,7 @@
         <f>'Custom cases'!D5</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.86pu</v>
       </c>
-      <c r="C4" s="364"/>
+      <c r="C4" s="373"/>
       <c r="D4" s="234" t="s">
         <v>11</v>
       </c>
@@ -8562,7 +8576,7 @@
         <f>'Custom cases'!D6</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.85pu</v>
       </c>
-      <c r="C5" s="364"/>
+      <c r="C5" s="373"/>
       <c r="D5" s="165" t="s">
         <v>513</v>
       </c>
@@ -8575,7 +8589,7 @@
         <f>'Custom cases'!D7</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.84pu</v>
       </c>
-      <c r="C6" s="364"/>
+      <c r="C6" s="373"/>
       <c r="D6" s="234" t="s">
         <v>11</v>
       </c>
@@ -8588,7 +8602,7 @@
         <f>'Custom cases'!D8</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.83pu</v>
       </c>
-      <c r="C7" s="364"/>
+      <c r="C7" s="373"/>
       <c r="D7" s="234" t="s">
         <v>11</v>
       </c>
@@ -8601,7 +8615,7 @@
         <f>'Custom cases'!D9</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.82pu</v>
       </c>
-      <c r="C8" s="364"/>
+      <c r="C8" s="373"/>
       <c r="D8" s="234" t="s">
         <v>11</v>
       </c>
@@ -8614,7 +8628,7 @@
         <f>'Custom cases'!D10</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.81pu</v>
       </c>
-      <c r="C9" s="364"/>
+      <c r="C9" s="373"/>
       <c r="D9" s="234" t="s">
         <v>11</v>
       </c>
@@ -8627,7 +8641,7 @@
         <f>'Custom cases'!D11</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.80pu</v>
       </c>
-      <c r="C10" s="364"/>
+      <c r="C10" s="373"/>
       <c r="D10" s="234" t="s">
         <v>11</v>
       </c>
@@ -8640,7 +8654,7 @@
         <f>'Custom cases'!D12</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.79pu</v>
       </c>
-      <c r="C11" s="364"/>
+      <c r="C11" s="373"/>
       <c r="D11" s="234" t="s">
         <v>11</v>
       </c>
@@ -8653,7 +8667,7 @@
         <f>'Custom cases'!D13</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.78pu</v>
       </c>
-      <c r="C12" s="365"/>
+      <c r="C12" s="374"/>
       <c r="D12" s="235" t="s">
         <v>11</v>
       </c>
@@ -8666,7 +8680,7 @@
         <f>'Custom cases'!D14</f>
         <v>Custom_RfG_LVRT_FRTexit_0.84pu</v>
       </c>
-      <c r="C13" s="363" t="s">
+      <c r="C13" s="372" t="s">
         <v>510</v>
       </c>
       <c r="D13" s="234" t="s">
@@ -8681,7 +8695,7 @@
         <f>'Custom cases'!D15</f>
         <v>Custom_RfG_LVRT_FRTexit_0.85pu</v>
       </c>
-      <c r="C14" s="364"/>
+      <c r="C14" s="373"/>
       <c r="D14" s="165" t="s">
         <v>512</v>
       </c>
@@ -8694,7 +8708,7 @@
         <f>'Custom cases'!D16</f>
         <v>Custom_RfG_LVRT_FRTexit_0.86pu</v>
       </c>
-      <c r="C15" s="364"/>
+      <c r="C15" s="373"/>
       <c r="D15" s="234" t="s">
         <v>11</v>
       </c>
@@ -8707,7 +8721,7 @@
         <f>'Custom cases'!D17</f>
         <v>Custom_RfG_LVRT_FRTexit_0.87pu</v>
       </c>
-      <c r="C16" s="364"/>
+      <c r="C16" s="373"/>
       <c r="D16" s="234" t="s">
         <v>11</v>
       </c>
@@ -8720,7 +8734,7 @@
         <f>'Custom cases'!D18</f>
         <v>Custom_RfG_LVRT_FRTexit_0.88pu</v>
       </c>
-      <c r="C17" s="364"/>
+      <c r="C17" s="373"/>
       <c r="D17" s="234" t="s">
         <v>11</v>
       </c>
@@ -8733,7 +8747,7 @@
         <f>'Custom cases'!D19</f>
         <v>Custom_RfG_LVRT_FRTexit_0.89pu</v>
       </c>
-      <c r="C18" s="365"/>
+      <c r="C18" s="374"/>
       <c r="D18" s="235" t="s">
         <v>11</v>
       </c>
@@ -8746,7 +8760,7 @@
         <f>'Custom cases'!D20</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.24pu</v>
       </c>
-      <c r="C19" s="363" t="s">
+      <c r="C19" s="372" t="s">
         <v>539</v>
       </c>
       <c r="D19" s="234" t="s">
@@ -8761,7 +8775,7 @@
         <f>'Custom cases'!D21</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.23pu</v>
       </c>
-      <c r="C20" s="364"/>
+      <c r="C20" s="373"/>
       <c r="D20" s="234" t="s">
         <v>11</v>
       </c>
@@ -8774,7 +8788,7 @@
         <f>'Custom cases'!D22</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.22pu</v>
       </c>
-      <c r="C21" s="364"/>
+      <c r="C21" s="373"/>
       <c r="D21" s="234" t="s">
         <v>11</v>
       </c>
@@ -8787,7 +8801,7 @@
         <f>'Custom cases'!D23</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.21pu</v>
       </c>
-      <c r="C22" s="364"/>
+      <c r="C22" s="373"/>
       <c r="D22" s="234" t="s">
         <v>11</v>
       </c>
@@ -8800,7 +8814,7 @@
         <f>'Custom cases'!D24</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.20pu</v>
       </c>
-      <c r="C23" s="364"/>
+      <c r="C23" s="373"/>
       <c r="D23" s="165" t="s">
         <v>540</v>
       </c>
@@ -8813,7 +8827,7 @@
         <f>'Custom cases'!D25</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.19pu</v>
       </c>
-      <c r="C24" s="364"/>
+      <c r="C24" s="373"/>
       <c r="D24" s="234" t="s">
         <v>11</v>
       </c>
@@ -8826,7 +8840,7 @@
         <f>'Custom cases'!D26</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.18pu</v>
       </c>
-      <c r="C25" s="364"/>
+      <c r="C25" s="373"/>
       <c r="D25" s="234" t="s">
         <v>11</v>
       </c>
@@ -8839,7 +8853,7 @@
         <f>'Custom cases'!D27</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.17pu</v>
       </c>
-      <c r="C26" s="364"/>
+      <c r="C26" s="373"/>
       <c r="D26" s="234" t="s">
         <v>11</v>
       </c>
@@ -8852,7 +8866,7 @@
         <f>'Custom cases'!D28</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.16pu</v>
       </c>
-      <c r="C27" s="364"/>
+      <c r="C27" s="373"/>
       <c r="D27" s="234" t="s">
         <v>11</v>
       </c>
@@ -8865,7 +8879,7 @@
         <f>'Custom cases'!D29</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.15pu</v>
       </c>
-      <c r="C28" s="365"/>
+      <c r="C28" s="374"/>
       <c r="D28" s="235" t="s">
         <v>11</v>
       </c>
@@ -8878,7 +8892,7 @@
         <f>'Custom cases'!D30</f>
         <v>Custom_RfG_Fault_3_0.2pu_Plim_0.5pu</v>
       </c>
-      <c r="C29" s="363" t="s">
+      <c r="C29" s="372" t="s">
         <v>514</v>
       </c>
       <c r="D29" s="165" t="s">
@@ -8893,7 +8907,7 @@
         <f>'Custom cases'!D31</f>
         <v>Custom_RfG_Fault_2_0.2pu_Plim_0.5pu</v>
       </c>
-      <c r="C30" s="364"/>
+      <c r="C30" s="373"/>
       <c r="D30" s="234" t="s">
         <v>11</v>
       </c>
@@ -8906,7 +8920,7 @@
         <f>'Custom cases'!D32</f>
         <v>Custom_RfG_Fault_1_0.2pu_Plim_0.5pu</v>
       </c>
-      <c r="C31" s="364"/>
+      <c r="C31" s="373"/>
       <c r="D31" s="234" t="s">
         <v>11</v>
       </c>
@@ -8919,7 +8933,7 @@
         <f>'Custom cases'!D33</f>
         <v>Custom_RfG_Fault_3_0.2pu_Plim_0.15pu</v>
       </c>
-      <c r="C32" s="364"/>
+      <c r="C32" s="373"/>
       <c r="D32" s="165" t="s">
         <v>515</v>
       </c>
@@ -8932,7 +8946,7 @@
         <f>'Custom cases'!D34</f>
         <v>Custom_RfG_Fault_2_0.2pu_Plim_0.15pu</v>
       </c>
-      <c r="C33" s="364"/>
+      <c r="C33" s="373"/>
       <c r="D33" s="234" t="s">
         <v>11</v>
       </c>
@@ -8945,7 +8959,7 @@
         <f>'Custom cases'!D35</f>
         <v>Custom_RfG_Fault_1_0.2pu_Plim_0.15pu</v>
       </c>
-      <c r="C34" s="365"/>
+      <c r="C34" s="374"/>
       <c r="D34" s="235" t="s">
         <v>11</v>
       </c>
@@ -8958,7 +8972,7 @@
         <f>'Custom cases'!D36</f>
         <v>Custom_RfG_Ucontrol_Plim_1.00pu</v>
       </c>
-      <c r="C35" s="363" t="s">
+      <c r="C35" s="372" t="s">
         <v>519</v>
       </c>
       <c r="D35" s="165" t="s">
@@ -8973,7 +8987,7 @@
         <f>'Custom cases'!D37</f>
         <v>Custom_RfG_Ucontrol_Plim_0.50pu</v>
       </c>
-      <c r="C36" s="364"/>
+      <c r="C36" s="373"/>
       <c r="D36" s="165" t="s">
         <v>516</v>
       </c>
@@ -8986,7 +9000,7 @@
         <f>'Custom cases'!D38</f>
         <v>Custom_RfG_Ucontrol_Plim_0.15pu</v>
       </c>
-      <c r="C37" s="365"/>
+      <c r="C37" s="374"/>
       <c r="D37" s="169" t="s">
         <v>518</v>
       </c>
@@ -8999,7 +9013,7 @@
         <f>'Custom cases'!D39</f>
         <v>Custom_Fault_3_0.20pu_U0_1.118pu</v>
       </c>
-      <c r="C38" s="363" t="s">
+      <c r="C38" s="372" t="s">
         <v>529</v>
       </c>
       <c r="D38" s="172" t="s">
@@ -9014,7 +9028,7 @@
         <f>'Custom cases'!D40</f>
         <v>Custom_Fault_2_0.20pu_U0_1.118pu</v>
       </c>
-      <c r="C39" s="364"/>
+      <c r="C39" s="373"/>
       <c r="D39" s="234" t="s">
         <v>11</v>
       </c>
@@ -9027,7 +9041,7 @@
         <f>'Custom cases'!D41</f>
         <v>Custom_Fault_1_0.20pu_U0_1.118pu</v>
       </c>
-      <c r="C40" s="364"/>
+      <c r="C40" s="373"/>
       <c r="D40" s="234" t="s">
         <v>11</v>
       </c>
@@ -9040,7 +9054,7 @@
         <f>'Custom cases'!D42</f>
         <v>Custom_Fault_3_0.20pu_U0_0.968pu</v>
       </c>
-      <c r="C41" s="364"/>
+      <c r="C41" s="373"/>
       <c r="D41" s="165" t="s">
         <v>521</v>
       </c>
@@ -9053,7 +9067,7 @@
         <f>'Custom cases'!D43</f>
         <v>Custom_Fault_2_0.20pu_U0_0.968pu</v>
       </c>
-      <c r="C42" s="364"/>
+      <c r="C42" s="373"/>
       <c r="D42" s="234" t="s">
         <v>11</v>
       </c>
@@ -9066,7 +9080,7 @@
         <f>'Custom cases'!D44</f>
         <v>Custom_Fault_1_0.20pu_U0_0.968pu</v>
       </c>
-      <c r="C43" s="365"/>
+      <c r="C43" s="374"/>
       <c r="D43" s="235" t="s">
         <v>11</v>
       </c>
@@ -9079,7 +9093,7 @@
         <f>'Custom cases'!D45</f>
         <v>Custom_Fault_3_U0_1.118_Uend_1.065</v>
       </c>
-      <c r="C44" s="363" t="s">
+      <c r="C44" s="372" t="s">
         <v>530</v>
       </c>
       <c r="D44" s="172" t="s">
@@ -9094,7 +9108,7 @@
         <f>'Custom cases'!D46</f>
         <v>Custom_Fault_2_U0_1.118_Uend_1.065</v>
       </c>
-      <c r="C45" s="364"/>
+      <c r="C45" s="373"/>
       <c r="D45" s="234" t="s">
         <v>11</v>
       </c>
@@ -9107,7 +9121,7 @@
         <f>'Custom cases'!D47</f>
         <v>Custom_Fault_1_U0_1.118_Uend_1.065</v>
       </c>
-      <c r="C46" s="364"/>
+      <c r="C46" s="373"/>
       <c r="D46" s="234" t="s">
         <v>11</v>
       </c>
@@ -9120,7 +9134,7 @@
         <f>'Custom cases'!D48</f>
         <v>Custom_Fault_3_U0_1.118_Uend_0.968</v>
       </c>
-      <c r="C47" s="364"/>
+      <c r="C47" s="373"/>
       <c r="D47" s="234" t="s">
         <v>11</v>
       </c>
@@ -9133,7 +9147,7 @@
         <f>'Custom cases'!D49</f>
         <v>Custom_Fault_3_U0_0.959_Uend_1.065</v>
       </c>
-      <c r="C48" s="364"/>
+      <c r="C48" s="373"/>
       <c r="D48" s="165" t="s">
         <v>522</v>
       </c>
@@ -9146,7 +9160,7 @@
         <f>'Custom cases'!D50</f>
         <v>Custom_Fault_2_U0_0.959_Uend_1.065</v>
       </c>
-      <c r="C49" s="364"/>
+      <c r="C49" s="373"/>
       <c r="D49" s="234" t="s">
         <v>11</v>
       </c>
@@ -9159,7 +9173,7 @@
         <f>'Custom cases'!D51</f>
         <v>Custom_Fault_1_U0_0.959_Uend_1.065</v>
       </c>
-      <c r="C50" s="364"/>
+      <c r="C50" s="373"/>
       <c r="D50" s="234" t="s">
         <v>11</v>
       </c>
@@ -9172,7 +9186,7 @@
         <f>'Custom cases'!D52</f>
         <v>Custom_Fault_3_U0_0.959_Uend_1.118</v>
       </c>
-      <c r="C51" s="364"/>
+      <c r="C51" s="373"/>
       <c r="D51" s="234" t="s">
         <v>11</v>
       </c>
@@ -9185,7 +9199,7 @@
         <f>'Custom cases'!D53</f>
         <v>Custom_Fault_3_U0_1.118_Uend_0.900</v>
       </c>
-      <c r="C52" s="364"/>
+      <c r="C52" s="373"/>
       <c r="D52" s="165" t="s">
         <v>524</v>
       </c>
@@ -9198,7 +9212,7 @@
         <f>'Custom cases'!D54</f>
         <v>Custom_Fault_3_U0_1.065_Uend_0.900</v>
       </c>
-      <c r="C53" s="364"/>
+      <c r="C53" s="373"/>
       <c r="D53" s="234" t="s">
         <v>11</v>
       </c>
@@ -9211,7 +9225,7 @@
         <f>'Custom cases'!D55</f>
         <v>Custom_Fault_3_U0_0.959_Uend_0.900</v>
       </c>
-      <c r="C54" s="365"/>
+      <c r="C54" s="374"/>
       <c r="D54" s="235" t="s">
         <v>11</v>
       </c>
@@ -9224,7 +9238,7 @@
         <f>'Custom cases'!D56</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.15</v>
       </c>
-      <c r="C55" s="363" t="s">
+      <c r="C55" s="372" t="s">
         <v>531</v>
       </c>
       <c r="D55" s="172" t="s">
@@ -9239,7 +9253,7 @@
         <f>'Custom cases'!D57</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.20</v>
       </c>
-      <c r="C56" s="364"/>
+      <c r="C56" s="373"/>
       <c r="D56" s="165" t="s">
         <v>526</v>
       </c>
@@ -9252,7 +9266,7 @@
         <f>'Custom cases'!D58</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.30</v>
       </c>
-      <c r="C57" s="364"/>
+      <c r="C57" s="373"/>
       <c r="D57" s="165" t="s">
         <v>525</v>
       </c>
@@ -9265,7 +9279,7 @@
         <f>'Custom cases'!D59</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.15</v>
       </c>
-      <c r="C58" s="364"/>
+      <c r="C58" s="373"/>
       <c r="D58" s="165" t="s">
         <v>527</v>
       </c>
@@ -9278,7 +9292,7 @@
         <f>'Custom cases'!D60</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.20</v>
       </c>
-      <c r="C59" s="364"/>
+      <c r="C59" s="373"/>
       <c r="D59" s="165" t="s">
         <v>527</v>
       </c>
@@ -9291,7 +9305,7 @@
         <f>'Custom cases'!D61</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.30</v>
       </c>
-      <c r="C60" s="365"/>
+      <c r="C60" s="374"/>
       <c r="D60" s="169" t="s">
         <v>528</v>
       </c>
@@ -9304,7 +9318,7 @@
         <f>'Custom cases'!D62</f>
         <v>Custom_Fault_3_0.20pu_SCR_2</v>
       </c>
-      <c r="C61" s="363" t="s">
+      <c r="C61" s="372" t="s">
         <v>532</v>
       </c>
       <c r="D61" s="172" t="s">
@@ -9319,7 +9333,7 @@
         <f>'Custom cases'!D63</f>
         <v>Custom_Fault_3_0.20pu_SCR_3</v>
       </c>
-      <c r="C62" s="364"/>
+      <c r="C62" s="373"/>
       <c r="D62" s="234" t="s">
         <v>11</v>
       </c>
@@ -9332,7 +9346,7 @@
         <f>'Custom cases'!D64</f>
         <v>Custom_Fault_3_0.20pu_SCR_4</v>
       </c>
-      <c r="C63" s="364"/>
+      <c r="C63" s="373"/>
       <c r="D63" s="234" t="s">
         <v>11</v>
       </c>
@@ -9345,7 +9359,7 @@
         <f>'Custom cases'!D65</f>
         <v>Custom_Fault_3_0.20pu_SCR_5</v>
       </c>
-      <c r="C64" s="364"/>
+      <c r="C64" s="373"/>
       <c r="D64" s="234" t="s">
         <v>11</v>
       </c>
@@ -9358,7 +9372,7 @@
         <f>'Custom cases'!D66</f>
         <v>Custom_Fault_3_0.20pu_SCR_6</v>
       </c>
-      <c r="C65" s="364"/>
+      <c r="C65" s="373"/>
       <c r="D65" s="234" t="s">
         <v>11</v>
       </c>
@@ -9371,7 +9385,7 @@
         <f>'Custom cases'!D67</f>
         <v>Custom_Fault_2_0.20pu_SCR_2</v>
       </c>
-      <c r="C66" s="364"/>
+      <c r="C66" s="373"/>
       <c r="D66" s="234" t="s">
         <v>11</v>
       </c>
@@ -9384,7 +9398,7 @@
         <f>'Custom cases'!D68</f>
         <v>Custom_Fault_2_0.20pu_SCR_3</v>
       </c>
-      <c r="C67" s="364"/>
+      <c r="C67" s="373"/>
       <c r="D67" s="234" t="s">
         <v>11</v>
       </c>
@@ -9397,7 +9411,7 @@
         <f>'Custom cases'!D69</f>
         <v>Custom_Fault_2_0.20pu_SCR_4</v>
       </c>
-      <c r="C68" s="364"/>
+      <c r="C68" s="373"/>
       <c r="D68" s="234" t="s">
         <v>11</v>
       </c>
@@ -9410,7 +9424,7 @@
         <f>'Custom cases'!D70</f>
         <v>Custom_Fault_2_0.20pu_SCR_5</v>
       </c>
-      <c r="C69" s="364"/>
+      <c r="C69" s="373"/>
       <c r="D69" s="234" t="s">
         <v>11</v>
       </c>
@@ -9423,7 +9437,7 @@
         <f>'Custom cases'!D71</f>
         <v>Custom_Fault_2_0.20pu_SCR_6</v>
       </c>
-      <c r="C70" s="364"/>
+      <c r="C70" s="373"/>
       <c r="D70" s="234" t="s">
         <v>11</v>
       </c>
@@ -9436,7 +9450,7 @@
         <f>'Custom cases'!D72</f>
         <v>Custom_Fault_3_0.70pu_SCR_2</v>
       </c>
-      <c r="C71" s="364"/>
+      <c r="C71" s="373"/>
       <c r="D71" s="234" t="s">
         <v>11</v>
       </c>
@@ -9449,7 +9463,7 @@
         <f>'Custom cases'!D73</f>
         <v>Custom_Fault_3_0.70pu_SCR_3</v>
       </c>
-      <c r="C72" s="364"/>
+      <c r="C72" s="373"/>
       <c r="D72" s="234" t="s">
         <v>11</v>
       </c>
@@ -9462,7 +9476,7 @@
         <f>'Custom cases'!D74</f>
         <v>Custom_Fault_3_0.70pu_SCR_4</v>
       </c>
-      <c r="C73" s="364"/>
+      <c r="C73" s="373"/>
       <c r="D73" s="234" t="s">
         <v>11</v>
       </c>
@@ -9475,7 +9489,7 @@
         <f>'Custom cases'!D75</f>
         <v>Custom_Fault_3_0.70pu_SCR_5</v>
       </c>
-      <c r="C74" s="364"/>
+      <c r="C74" s="373"/>
       <c r="D74" s="234" t="s">
         <v>11</v>
       </c>
@@ -9488,7 +9502,7 @@
         <f>'Custom cases'!D76</f>
         <v>Custom_Fault_3_0.70pu_SCR_6</v>
       </c>
-      <c r="C75" s="364"/>
+      <c r="C75" s="373"/>
       <c r="D75" s="234" t="s">
         <v>11</v>
       </c>
@@ -9501,7 +9515,7 @@
         <f>'Custom cases'!D77</f>
         <v>Custom_Fault_2_0.70pu_SCR_2</v>
       </c>
-      <c r="C76" s="364"/>
+      <c r="C76" s="373"/>
       <c r="D76" s="234" t="s">
         <v>11</v>
       </c>
@@ -9514,7 +9528,7 @@
         <f>'Custom cases'!D78</f>
         <v>Custom_Fault_2_0.70pu_SCR_3</v>
       </c>
-      <c r="C77" s="364"/>
+      <c r="C77" s="373"/>
       <c r="D77" s="234" t="s">
         <v>11</v>
       </c>
@@ -9527,7 +9541,7 @@
         <f>'Custom cases'!D79</f>
         <v>Custom_Fault_2_0.70pu_SCR_4</v>
       </c>
-      <c r="C78" s="364"/>
+      <c r="C78" s="373"/>
       <c r="D78" s="234" t="s">
         <v>11</v>
       </c>
@@ -9540,7 +9554,7 @@
         <f>'Custom cases'!D80</f>
         <v>Custom_Fault_2_0.70pu_SCR_5</v>
       </c>
-      <c r="C79" s="364"/>
+      <c r="C79" s="373"/>
       <c r="D79" s="234" t="s">
         <v>11</v>
       </c>
@@ -9553,7 +9567,7 @@
         <f>'Custom cases'!D81</f>
         <v>Custom_Fault_2_0.70pu_SCR_6</v>
       </c>
-      <c r="C80" s="365"/>
+      <c r="C80" s="374"/>
       <c r="D80" s="235" t="s">
         <v>11</v>
       </c>
@@ -9566,7 +9580,7 @@
         <f>'Custom cases'!D82</f>
         <v>Custom_Fault_3_0.20pu_Duration_80</v>
       </c>
-      <c r="C81" s="363" t="s">
+      <c r="C81" s="372" t="s">
         <v>534</v>
       </c>
       <c r="D81" s="165" t="s">
@@ -9581,7 +9595,7 @@
         <f>'Custom cases'!D83</f>
         <v>Custom_Fault_3_0.20pu_Duration_60</v>
       </c>
-      <c r="C82" s="364"/>
+      <c r="C82" s="373"/>
       <c r="D82" s="234" t="s">
         <v>11</v>
       </c>
@@ -9594,7 +9608,7 @@
         <f>'Custom cases'!D84</f>
         <v>Custom_Fault_3_0.20pu_Duration_40</v>
       </c>
-      <c r="C83" s="364"/>
+      <c r="C83" s="373"/>
       <c r="D83" s="234" t="s">
         <v>11</v>
       </c>
@@ -9607,7 +9621,7 @@
         <f>'Custom cases'!D85</f>
         <v>Custom_Shift_10_Fault_3_0.20pu</v>
       </c>
-      <c r="C84" s="364"/>
+      <c r="C84" s="373"/>
       <c r="D84" s="165" t="s">
         <v>536</v>
       </c>
@@ -9620,7 +9634,7 @@
         <f>'Custom cases'!D86</f>
         <v>Custom_Shift_20_Fault_3_0.20pu</v>
       </c>
-      <c r="C85" s="364"/>
+      <c r="C85" s="373"/>
       <c r="D85" s="234" t="s">
         <v>11</v>
       </c>
@@ -9633,7 +9647,7 @@
         <f>'Custom cases'!D87</f>
         <v>Custom_Shift_30_Fault_3_0.20pu</v>
       </c>
-      <c r="C86" s="364"/>
+      <c r="C86" s="373"/>
       <c r="D86" s="234" t="s">
         <v>11</v>
       </c>
@@ -9646,7 +9660,7 @@
         <f>'Custom cases'!D88</f>
         <v>Custom_Shift_40_Fault_3_0.20pu</v>
       </c>
-      <c r="C87" s="364"/>
+      <c r="C87" s="373"/>
       <c r="D87" s="234" t="s">
         <v>11</v>
       </c>
@@ -9659,7 +9673,7 @@
         <f>'Custom cases'!D89</f>
         <v>Custom_Shift_50_Fault_3_0.20pu</v>
       </c>
-      <c r="C88" s="365"/>
+      <c r="C88" s="374"/>
       <c r="D88" s="235" t="s">
         <v>11</v>
       </c>
@@ -9683,7 +9697,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9798,7 +9812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9814,22 +9828,22 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="41"/>
-      <c r="B1" s="348" t="s">
+      <c r="B1" s="354" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="349"/>
-      <c r="D1" s="350"/>
-      <c r="E1" s="348" t="s">
+      <c r="C1" s="355"/>
+      <c r="D1" s="356"/>
+      <c r="E1" s="354" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="349"/>
-      <c r="G1" s="349"/>
-      <c r="H1" s="373"/>
-      <c r="J1" s="372"/>
-      <c r="K1" s="374" t="s">
+      <c r="F1" s="355"/>
+      <c r="G1" s="355"/>
+      <c r="H1" s="347"/>
+      <c r="J1" s="346"/>
+      <c r="K1" s="357" t="s">
         <v>842</v>
       </c>
-      <c r="L1" s="375"/>
+      <c r="L1" s="358"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
@@ -9856,10 +9870,10 @@
       <c r="H2" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="377" t="s">
+      <c r="K2" s="349" t="s">
         <v>215</v>
       </c>
-      <c r="L2" s="376" t="b">
+      <c r="L2" s="348" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9874,10 +9888,10 @@
       <c r="F3" s="37"/>
       <c r="G3" s="37"/>
       <c r="H3" s="42"/>
-      <c r="K3" s="378" t="s">
+      <c r="K3" s="350" t="s">
         <v>216</v>
       </c>
-      <c r="L3" s="376" t="b">
+      <c r="L3" s="348" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9907,7 +9921,7 @@
         <f t="shared" ref="H4:H12" si="0">CHOOSE(IF(inp_Un&lt;110,0,1)+IF(inp_Un&gt;=300,1,0)+IF(inp_Area="DK1",0,3) + 1,B4,C4,D4,E4,F4,G4)</f>
         <v>50.2</v>
       </c>
-      <c r="K4" s="378" t="s">
+      <c r="K4" s="350" t="s">
         <v>217</v>
       </c>
       <c r="L4" s="311"/>
@@ -9941,7 +9955,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K5" s="378" t="s">
+      <c r="K5" s="350" t="s">
         <v>843</v>
       </c>
       <c r="L5" s="311"/>
@@ -9972,7 +9986,7 @@
         <f t="shared" si="0"/>
         <v>49.8</v>
       </c>
-      <c r="K6" s="379" t="s">
+      <c r="K6" s="351" t="s">
         <v>218</v>
       </c>
       <c r="L6" s="64"/>
@@ -10827,7 +10841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00847C"/>
   </sheetPr>
@@ -10903,103 +10917,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A1" s="352" t="s">
+      <c r="A1" s="360" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="352"/>
-      <c r="C1" s="352"/>
-      <c r="D1" s="352"/>
-      <c r="E1" s="353" t="s">
+      <c r="B1" s="360"/>
+      <c r="C1" s="360"/>
+      <c r="D1" s="360"/>
+      <c r="E1" s="361" t="s">
         <v>494</v>
       </c>
-      <c r="F1" s="354"/>
-      <c r="G1" s="354"/>
-      <c r="H1" s="354"/>
-      <c r="I1" s="354"/>
-      <c r="J1" s="354"/>
-      <c r="K1" s="354"/>
-      <c r="L1" s="354"/>
-      <c r="M1" s="354"/>
-      <c r="N1" s="354"/>
-      <c r="O1" s="355"/>
-      <c r="P1" s="351" t="s">
+      <c r="F1" s="362"/>
+      <c r="G1" s="362"/>
+      <c r="H1" s="362"/>
+      <c r="I1" s="362"/>
+      <c r="J1" s="362"/>
+      <c r="K1" s="362"/>
+      <c r="L1" s="362"/>
+      <c r="M1" s="362"/>
+      <c r="N1" s="362"/>
+      <c r="O1" s="363"/>
+      <c r="P1" s="359" t="s">
         <v>78</v>
       </c>
-      <c r="Q1" s="351"/>
-      <c r="R1" s="351"/>
-      <c r="S1" s="351"/>
-      <c r="T1" s="352" t="s">
+      <c r="Q1" s="359"/>
+      <c r="R1" s="359"/>
+      <c r="S1" s="359"/>
+      <c r="T1" s="360" t="s">
         <v>79</v>
       </c>
-      <c r="U1" s="352"/>
-      <c r="V1" s="352"/>
-      <c r="W1" s="352"/>
-      <c r="X1" s="351" t="s">
+      <c r="U1" s="360"/>
+      <c r="V1" s="360"/>
+      <c r="W1" s="360"/>
+      <c r="X1" s="359" t="s">
         <v>80</v>
       </c>
-      <c r="Y1" s="351"/>
-      <c r="Z1" s="351"/>
-      <c r="AA1" s="351"/>
-      <c r="AB1" s="352" t="s">
+      <c r="Y1" s="359"/>
+      <c r="Z1" s="359"/>
+      <c r="AA1" s="359"/>
+      <c r="AB1" s="360" t="s">
         <v>81</v>
       </c>
-      <c r="AC1" s="352"/>
-      <c r="AD1" s="352"/>
-      <c r="AE1" s="352"/>
-      <c r="AF1" s="351" t="s">
+      <c r="AC1" s="360"/>
+      <c r="AD1" s="360"/>
+      <c r="AE1" s="360"/>
+      <c r="AF1" s="359" t="s">
         <v>82</v>
       </c>
-      <c r="AG1" s="351"/>
-      <c r="AH1" s="351"/>
-      <c r="AI1" s="351"/>
-      <c r="AJ1" s="352" t="s">
+      <c r="AG1" s="359"/>
+      <c r="AH1" s="359"/>
+      <c r="AI1" s="359"/>
+      <c r="AJ1" s="360" t="s">
         <v>83</v>
       </c>
-      <c r="AK1" s="352"/>
-      <c r="AL1" s="352"/>
-      <c r="AM1" s="352"/>
-      <c r="AN1" s="351" t="s">
+      <c r="AK1" s="360"/>
+      <c r="AL1" s="360"/>
+      <c r="AM1" s="360"/>
+      <c r="AN1" s="359" t="s">
         <v>84</v>
       </c>
-      <c r="AO1" s="351"/>
-      <c r="AP1" s="351"/>
-      <c r="AQ1" s="351"/>
-      <c r="AR1" s="352" t="s">
+      <c r="AO1" s="359"/>
+      <c r="AP1" s="359"/>
+      <c r="AQ1" s="359"/>
+      <c r="AR1" s="360" t="s">
         <v>85</v>
       </c>
-      <c r="AS1" s="352"/>
-      <c r="AT1" s="352"/>
-      <c r="AU1" s="352"/>
-      <c r="AV1" s="351" t="s">
+      <c r="AS1" s="360"/>
+      <c r="AT1" s="360"/>
+      <c r="AU1" s="360"/>
+      <c r="AV1" s="359" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="351"/>
-      <c r="AX1" s="351"/>
-      <c r="AY1" s="351"/>
-      <c r="AZ1" s="352" t="s">
+      <c r="AW1" s="359"/>
+      <c r="AX1" s="359"/>
+      <c r="AY1" s="359"/>
+      <c r="AZ1" s="360" t="s">
         <v>87</v>
       </c>
-      <c r="BA1" s="352"/>
-      <c r="BB1" s="352"/>
-      <c r="BC1" s="352"/>
-      <c r="BD1" s="351" t="s">
+      <c r="BA1" s="360"/>
+      <c r="BB1" s="360"/>
+      <c r="BC1" s="360"/>
+      <c r="BD1" s="359" t="s">
         <v>88</v>
       </c>
-      <c r="BE1" s="351"/>
-      <c r="BF1" s="351"/>
-      <c r="BG1" s="351"/>
-      <c r="BH1" s="352" t="s">
+      <c r="BE1" s="359"/>
+      <c r="BF1" s="359"/>
+      <c r="BG1" s="359"/>
+      <c r="BH1" s="360" t="s">
         <v>89</v>
       </c>
-      <c r="BI1" s="352"/>
-      <c r="BJ1" s="352"/>
-      <c r="BK1" s="352"/>
-      <c r="BL1" s="351" t="s">
+      <c r="BI1" s="360"/>
+      <c r="BJ1" s="360"/>
+      <c r="BK1" s="360"/>
+      <c r="BL1" s="359" t="s">
         <v>498</v>
       </c>
-      <c r="BM1" s="351"/>
-      <c r="BN1" s="351"/>
-      <c r="BO1" s="351"/>
+      <c r="BM1" s="359"/>
+      <c r="BN1" s="359"/>
+      <c r="BO1" s="359"/>
     </row>
     <row r="2" spans="1:67" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -32757,7 +32771,7 @@
       <c r="O218" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BK178" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A2:BK178"/>
   <mergeCells count="15">
     <mergeCell ref="BL1:BO1"/>
     <mergeCell ref="A1:D1"/>
@@ -32784,43 +32798,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$E$1:$E$2</xm:f>
           </x14:formula1>
           <xm:sqref>B3:C186</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000001000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$C$1:$C$8</xm:f>
           </x14:formula1>
           <xm:sqref>H3:H1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000002000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$B$1:$B$8</xm:f>
           </x14:formula1>
           <xm:sqref>I3:I1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000003000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$941</xm:f>
           </x14:formula1>
           <xm:sqref>T38 T197:T216 T36 T97 AF97 AB97 X97 BD3:BD39 AF3:AF38 AJ3:AJ38 AN3:AN38 AB3:AB38 X30:X38 T30:T34 AV3:AV42 X3:X27 T3:T27 T136:T137 AF40:AF42 X40:X42 T40:T42 AB40:AB42 AR3:AR95 BH3:BH95 AZ3:AZ95 BD44:BD95 AV44:AV95 T71:T95 AJ40:AJ95 AN45:AN95 BL44:BL95 BL3:BL39 AB45:AB95 T45:T69 X45:X95 AF45:AF95 AR106:AR109 T106:T109 BH106:BH109 BL107:BL108 AJ106:AJ109 AV106:AV109 X106:X109 AB106:AB109 AF106:AF109 AZ106:AZ109</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000004000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$274</xm:f>
           </x14:formula1>
           <xm:sqref>T43:T44 X43:X44 AB43:AB44 T28:T29 X28:X29 BD43 T96 X96 AB96 AF96 AN43:AN44 AV43 AF43:AF44 BH110:BH151 AJ110:AJ151 AN110:AN151 AV110:AV151 AF110:AF151 AR110:AR151 T138:T151 AZ110:AZ151 X110 T110:T135 BD110:BD151 X112:X151 X98:X105 AB98:AB105 AR96:AR105 AF98:AF105 AV96:AV105 AN96:AN105 AJ96:AJ105 BH96:BH105 AZ96:AZ105 BD96:BD105 T98:T105 AB110:AB151 BL43 BL110:BL151 BL96:BL105</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000005000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$102</xm:f>
           </x14:formula1>
           <xm:sqref>T183:T196 AZ152:AZ196 AR152:AR195 BD152:BD197 AN152:AN194 AV152:AV195 AF152:AF197 AJ152:AJ195 BH152:BH197 AB152:AB197 X152:X197 T164:T177 T156:T161 BL152:BL197</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000006000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$94</xm:f>
           </x14:formula1>
@@ -32833,7 +32847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00847C"/>
   </sheetPr>
@@ -32904,96 +32918,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:94" x14ac:dyDescent="0.25">
-      <c r="A1" s="352" t="s">
+      <c r="A1" s="360" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="352"/>
-      <c r="C1" s="352"/>
-      <c r="D1" s="352"/>
-      <c r="E1" s="353" t="s">
+      <c r="B1" s="360"/>
+      <c r="C1" s="360"/>
+      <c r="D1" s="360"/>
+      <c r="E1" s="361" t="s">
         <v>494</v>
       </c>
-      <c r="F1" s="354"/>
-      <c r="G1" s="354"/>
-      <c r="H1" s="354"/>
-      <c r="I1" s="354"/>
-      <c r="J1" s="354"/>
-      <c r="K1" s="354"/>
-      <c r="L1" s="354"/>
-      <c r="M1" s="354"/>
-      <c r="N1" s="355"/>
-      <c r="O1" s="359" t="s">
+      <c r="F1" s="362"/>
+      <c r="G1" s="362"/>
+      <c r="H1" s="362"/>
+      <c r="I1" s="362"/>
+      <c r="J1" s="362"/>
+      <c r="K1" s="362"/>
+      <c r="L1" s="362"/>
+      <c r="M1" s="362"/>
+      <c r="N1" s="363"/>
+      <c r="O1" s="367" t="s">
         <v>78</v>
       </c>
-      <c r="P1" s="360"/>
-      <c r="Q1" s="360"/>
-      <c r="R1" s="361"/>
-      <c r="S1" s="353" t="s">
+      <c r="P1" s="368"/>
+      <c r="Q1" s="368"/>
+      <c r="R1" s="369"/>
+      <c r="S1" s="361" t="s">
         <v>79</v>
       </c>
-      <c r="T1" s="354"/>
-      <c r="U1" s="354"/>
-      <c r="V1" s="354"/>
-      <c r="W1" s="359" t="s">
+      <c r="T1" s="362"/>
+      <c r="U1" s="362"/>
+      <c r="V1" s="362"/>
+      <c r="W1" s="367" t="s">
         <v>80</v>
       </c>
-      <c r="X1" s="360"/>
-      <c r="Y1" s="360"/>
-      <c r="Z1" s="361"/>
-      <c r="AA1" s="356" t="s">
+      <c r="X1" s="368"/>
+      <c r="Y1" s="368"/>
+      <c r="Z1" s="369"/>
+      <c r="AA1" s="364" t="s">
         <v>81</v>
       </c>
-      <c r="AB1" s="357"/>
-      <c r="AC1" s="357"/>
-      <c r="AD1" s="358"/>
-      <c r="AE1" s="359" t="s">
+      <c r="AB1" s="365"/>
+      <c r="AC1" s="365"/>
+      <c r="AD1" s="366"/>
+      <c r="AE1" s="367" t="s">
         <v>82</v>
       </c>
-      <c r="AF1" s="360"/>
-      <c r="AG1" s="360"/>
-      <c r="AH1" s="361"/>
-      <c r="AI1" s="356" t="s">
+      <c r="AF1" s="368"/>
+      <c r="AG1" s="368"/>
+      <c r="AH1" s="369"/>
+      <c r="AI1" s="364" t="s">
         <v>83</v>
       </c>
-      <c r="AJ1" s="357"/>
-      <c r="AK1" s="357"/>
-      <c r="AL1" s="358"/>
-      <c r="AM1" s="359" t="s">
+      <c r="AJ1" s="365"/>
+      <c r="AK1" s="365"/>
+      <c r="AL1" s="366"/>
+      <c r="AM1" s="367" t="s">
         <v>84</v>
       </c>
-      <c r="AN1" s="360"/>
-      <c r="AO1" s="360"/>
-      <c r="AP1" s="361"/>
-      <c r="AQ1" s="356" t="s">
+      <c r="AN1" s="368"/>
+      <c r="AO1" s="368"/>
+      <c r="AP1" s="369"/>
+      <c r="AQ1" s="364" t="s">
         <v>85</v>
       </c>
-      <c r="AR1" s="357"/>
-      <c r="AS1" s="357"/>
-      <c r="AT1" s="358"/>
-      <c r="AU1" s="359" t="s">
+      <c r="AR1" s="365"/>
+      <c r="AS1" s="365"/>
+      <c r="AT1" s="366"/>
+      <c r="AU1" s="367" t="s">
         <v>86</v>
       </c>
-      <c r="AV1" s="360"/>
-      <c r="AW1" s="360"/>
-      <c r="AX1" s="361"/>
-      <c r="AY1" s="356" t="s">
+      <c r="AV1" s="368"/>
+      <c r="AW1" s="368"/>
+      <c r="AX1" s="369"/>
+      <c r="AY1" s="364" t="s">
         <v>87</v>
       </c>
-      <c r="AZ1" s="357"/>
-      <c r="BA1" s="357"/>
-      <c r="BB1" s="358"/>
-      <c r="BC1" s="359" t="s">
+      <c r="AZ1" s="365"/>
+      <c r="BA1" s="365"/>
+      <c r="BB1" s="366"/>
+      <c r="BC1" s="367" t="s">
         <v>88</v>
       </c>
-      <c r="BD1" s="360"/>
-      <c r="BE1" s="360"/>
-      <c r="BF1" s="361"/>
-      <c r="BG1" s="356" t="s">
+      <c r="BD1" s="368"/>
+      <c r="BE1" s="368"/>
+      <c r="BF1" s="369"/>
+      <c r="BG1" s="364" t="s">
         <v>89</v>
       </c>
-      <c r="BH1" s="357"/>
-      <c r="BI1" s="357"/>
-      <c r="BJ1" s="358"/>
+      <c r="BH1" s="365"/>
+      <c r="BI1" s="365"/>
+      <c r="BJ1" s="366"/>
     </row>
     <row r="2" spans="1:94" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -33194,7 +33208,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="144" t="s">
-        <v>357</v>
+        <v>845</v>
       </c>
       <c r="E3" s="145">
         <f t="shared" ref="E3:E7" si="0">inp_Uc/inp_Un</f>
@@ -33244,7 +33258,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="144" t="s">
-        <v>358</v>
+        <v>846</v>
       </c>
       <c r="E4" s="145">
         <f t="shared" si="0"/>
@@ -33341,7 +33355,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="144" t="s">
-        <v>359</v>
+        <v>847</v>
       </c>
       <c r="E5" s="145">
         <f t="shared" si="0"/>
@@ -33438,7 +33452,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="144" t="s">
-        <v>360</v>
+        <v>848</v>
       </c>
       <c r="E6" s="145">
         <f t="shared" si="0"/>
@@ -33535,7 +33549,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="144" t="s">
-        <v>361</v>
+        <v>849</v>
       </c>
       <c r="E7" s="145">
         <f t="shared" si="0"/>
@@ -36898,7 +36912,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="H37" s="20" t="s">
         <v>106</v>
@@ -36994,7 +37008,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="H38" s="20" t="s">
         <v>106</v>
@@ -37090,7 +37104,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="H39" s="20" t="s">
         <v>106</v>
@@ -37186,7 +37200,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="H40" s="20" t="s">
         <v>106</v>
@@ -37282,7 +37296,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="21" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="H41" s="20" t="s">
         <v>106</v>
@@ -37378,7 +37392,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="21" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="H42" s="20" t="s">
         <v>106</v>
@@ -37474,7 +37488,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="H43" s="20" t="s">
         <v>106</v>
@@ -37570,7 +37584,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="21" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="H44" s="20" t="s">
         <v>106</v>
@@ -43137,7 +43151,7 @@
       <c r="BJ180" s="76"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BJ2" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A2:BJ2"/>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
@@ -43159,31 +43173,31 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0300-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$C$1:$C$8</xm:f>
           </x14:formula1>
           <xm:sqref>G89:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0300-000001000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$B$1:$B$8</xm:f>
           </x14:formula1>
           <xm:sqref>H89:H1048576 H37:H44</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0300-000003000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$941</xm:f>
           </x14:formula1>
           <xm:sqref>O89:O1048576 AA45:AA46 S45:S46 W45:W46 AE45:AE46</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BC90EAFF-3C71-457D-9F57-CFBB11CF72E4}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$94</xm:f>
           </x14:formula1>
           <xm:sqref>O37:O46</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C0CD5072-92EB-45B4-AAD1-5E9818462A3C}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$E$1:$E$2</xm:f>
           </x14:formula1>
@@ -43196,7 +43210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00847C"/>
   </sheetPr>
@@ -43268,97 +43282,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A1" s="352" t="s">
+      <c r="A1" s="360" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="352"/>
-      <c r="C1" s="352"/>
-      <c r="D1" s="352"/>
-      <c r="E1" s="353" t="s">
+      <c r="B1" s="360"/>
+      <c r="C1" s="360"/>
+      <c r="D1" s="360"/>
+      <c r="E1" s="361" t="s">
         <v>494</v>
       </c>
-      <c r="F1" s="354"/>
-      <c r="G1" s="354"/>
-      <c r="H1" s="354"/>
-      <c r="I1" s="354"/>
-      <c r="J1" s="354"/>
-      <c r="K1" s="354"/>
-      <c r="L1" s="354"/>
-      <c r="M1" s="354"/>
-      <c r="N1" s="354"/>
-      <c r="O1" s="355"/>
-      <c r="P1" s="362" t="s">
+      <c r="F1" s="362"/>
+      <c r="G1" s="362"/>
+      <c r="H1" s="362"/>
+      <c r="I1" s="362"/>
+      <c r="J1" s="362"/>
+      <c r="K1" s="362"/>
+      <c r="L1" s="362"/>
+      <c r="M1" s="362"/>
+      <c r="N1" s="362"/>
+      <c r="O1" s="363"/>
+      <c r="P1" s="370" t="s">
         <v>78</v>
       </c>
-      <c r="Q1" s="362"/>
-      <c r="R1" s="362"/>
-      <c r="S1" s="362"/>
-      <c r="T1" s="352" t="s">
+      <c r="Q1" s="370"/>
+      <c r="R1" s="370"/>
+      <c r="S1" s="370"/>
+      <c r="T1" s="360" t="s">
         <v>79</v>
       </c>
-      <c r="U1" s="352"/>
-      <c r="V1" s="352"/>
-      <c r="W1" s="352"/>
-      <c r="X1" s="362" t="s">
+      <c r="U1" s="360"/>
+      <c r="V1" s="360"/>
+      <c r="W1" s="360"/>
+      <c r="X1" s="370" t="s">
         <v>80</v>
       </c>
-      <c r="Y1" s="362"/>
-      <c r="Z1" s="362"/>
-      <c r="AA1" s="362"/>
-      <c r="AB1" s="352" t="s">
+      <c r="Y1" s="370"/>
+      <c r="Z1" s="370"/>
+      <c r="AA1" s="370"/>
+      <c r="AB1" s="360" t="s">
         <v>81</v>
       </c>
-      <c r="AC1" s="352"/>
-      <c r="AD1" s="352"/>
-      <c r="AE1" s="352"/>
-      <c r="AF1" s="362" t="s">
+      <c r="AC1" s="360"/>
+      <c r="AD1" s="360"/>
+      <c r="AE1" s="360"/>
+      <c r="AF1" s="370" t="s">
         <v>82</v>
       </c>
-      <c r="AG1" s="362"/>
-      <c r="AH1" s="362"/>
-      <c r="AI1" s="362"/>
-      <c r="AJ1" s="352" t="s">
+      <c r="AG1" s="370"/>
+      <c r="AH1" s="370"/>
+      <c r="AI1" s="370"/>
+      <c r="AJ1" s="360" t="s">
         <v>83</v>
       </c>
-      <c r="AK1" s="352"/>
-      <c r="AL1" s="352"/>
-      <c r="AM1" s="352"/>
-      <c r="AN1" s="362" t="s">
+      <c r="AK1" s="360"/>
+      <c r="AL1" s="360"/>
+      <c r="AM1" s="360"/>
+      <c r="AN1" s="370" t="s">
         <v>84</v>
       </c>
-      <c r="AO1" s="362"/>
-      <c r="AP1" s="362"/>
-      <c r="AQ1" s="362"/>
-      <c r="AR1" s="352" t="s">
+      <c r="AO1" s="370"/>
+      <c r="AP1" s="370"/>
+      <c r="AQ1" s="370"/>
+      <c r="AR1" s="360" t="s">
         <v>85</v>
       </c>
-      <c r="AS1" s="352"/>
-      <c r="AT1" s="352"/>
-      <c r="AU1" s="352"/>
-      <c r="AV1" s="362" t="s">
+      <c r="AS1" s="360"/>
+      <c r="AT1" s="360"/>
+      <c r="AU1" s="360"/>
+      <c r="AV1" s="370" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="362"/>
-      <c r="AX1" s="362"/>
-      <c r="AY1" s="362"/>
-      <c r="AZ1" s="352" t="s">
+      <c r="AW1" s="370"/>
+      <c r="AX1" s="370"/>
+      <c r="AY1" s="370"/>
+      <c r="AZ1" s="360" t="s">
         <v>87</v>
       </c>
-      <c r="BA1" s="352"/>
-      <c r="BB1" s="352"/>
-      <c r="BC1" s="352"/>
-      <c r="BD1" s="362" t="s">
+      <c r="BA1" s="360"/>
+      <c r="BB1" s="360"/>
+      <c r="BC1" s="360"/>
+      <c r="BD1" s="370" t="s">
         <v>88</v>
       </c>
-      <c r="BE1" s="362"/>
-      <c r="BF1" s="362"/>
-      <c r="BG1" s="362"/>
-      <c r="BH1" s="352" t="s">
+      <c r="BE1" s="370"/>
+      <c r="BF1" s="370"/>
+      <c r="BG1" s="370"/>
+      <c r="BH1" s="360" t="s">
         <v>89</v>
       </c>
-      <c r="BI1" s="352"/>
-      <c r="BJ1" s="352"/>
-      <c r="BK1" s="352"/>
+      <c r="BI1" s="360"/>
+      <c r="BJ1" s="360"/>
+      <c r="BK1" s="360"/>
     </row>
     <row r="2" spans="1:63" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -52522,7 +52536,7 @@
       <c r="AA79" s="130"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BK2" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A2:BK2"/>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:O1"/>
@@ -52547,31 +52561,31 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$E$1:$E$2</xm:f>
           </x14:formula1>
           <xm:sqref>B70:C79 B54:C57 B60:C65 B46:C47 B19:C43 B50:C51 B3:C11</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000001000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$C$1:$C$8</xm:f>
           </x14:formula1>
           <xm:sqref>H70:H1048576 H3:H11 H60:H65 H46:H47 H19:H43 H50:H51 H54:H57</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000002000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$B$1:$B$8</xm:f>
           </x14:formula1>
           <xm:sqref>I70:I1048576 I3:I11 I60:I65 I46:I47 I19:I43 I50:I51 I54:I57</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000003000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$274</xm:f>
           </x14:formula1>
           <xm:sqref>AB50 AF70:AF78 AB70:AB78 X70:X79 T70:T79 BH70:BH78 AN70:AN78 AR70:AR78 AV70:AV78 AZ70:AZ78 BD70:BD78 P70:P79 AJ70:AJ78 AF50 T50 AZ60:AZ65 AV60:AV65 AR60:AR65 AN60:AN65 BH60:BH65 T60:T65 X60:X65 AJ50 AB60:AB65 AF60:AF65 AJ60:AJ65 BD60:BD65 P50 AN54:AN57 P3:P11 T3:T11 BH3:BH11 AN3:AN11 AR3:AR11 AV3:AV11 AZ3:AZ11 BD3:BD11 AF3:AF11 AB3:AB11 X3:X11 AJ3:AJ11 AJ54:AJ57 AF54:AF57 AB54:AB57 X54:X57 T54:T57 AR54:AR57 AV54:AV57 AZ54:AZ57 BD54:BD57 BD46:BD47 P54:P57 P60:P65 AZ46:AZ47 AV46:AV47 AR46:AR47 AN46:AN47 BH46:BH47 P46:P47 AJ46:AJ47 T46:T47 AF46:AF47 AB46:AB47 X46:X47 X50 X19:X43 AB19:AB43 AF19:AF43 T19:T43 AJ19:AJ43 P19:P43 BH19:BH43 AN19:AN43 AR19:AR43 AV19:AV43 AZ19:AZ43 BD19:BD43 BD50:BD51 AZ50:AZ51 AV50:AV51 AR50:AR51 AN50:AN51 BH50:BH51 BH54:BH57</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000004000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$941</xm:f>
           </x14:formula1>
@@ -52584,7 +52598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F554063-19B4-4961-A0AC-5A208C802E34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00847C"/>
   </sheetPr>
@@ -52660,103 +52674,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A1" s="352" t="s">
+      <c r="A1" s="360" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="352"/>
-      <c r="C1" s="352"/>
-      <c r="D1" s="352"/>
-      <c r="E1" s="353" t="s">
+      <c r="B1" s="360"/>
+      <c r="C1" s="360"/>
+      <c r="D1" s="360"/>
+      <c r="E1" s="361" t="s">
         <v>494</v>
       </c>
-      <c r="F1" s="354"/>
-      <c r="G1" s="354"/>
-      <c r="H1" s="354"/>
-      <c r="I1" s="354"/>
-      <c r="J1" s="354"/>
-      <c r="K1" s="354"/>
-      <c r="L1" s="354"/>
-      <c r="M1" s="354"/>
-      <c r="N1" s="354"/>
-      <c r="O1" s="355"/>
-      <c r="P1" s="351" t="s">
+      <c r="F1" s="362"/>
+      <c r="G1" s="362"/>
+      <c r="H1" s="362"/>
+      <c r="I1" s="362"/>
+      <c r="J1" s="362"/>
+      <c r="K1" s="362"/>
+      <c r="L1" s="362"/>
+      <c r="M1" s="362"/>
+      <c r="N1" s="362"/>
+      <c r="O1" s="363"/>
+      <c r="P1" s="359" t="s">
         <v>78</v>
       </c>
-      <c r="Q1" s="351"/>
-      <c r="R1" s="351"/>
-      <c r="S1" s="351"/>
-      <c r="T1" s="352" t="s">
+      <c r="Q1" s="359"/>
+      <c r="R1" s="359"/>
+      <c r="S1" s="359"/>
+      <c r="T1" s="360" t="s">
         <v>79</v>
       </c>
-      <c r="U1" s="352"/>
-      <c r="V1" s="352"/>
-      <c r="W1" s="352"/>
-      <c r="X1" s="351" t="s">
+      <c r="U1" s="360"/>
+      <c r="V1" s="360"/>
+      <c r="W1" s="360"/>
+      <c r="X1" s="359" t="s">
         <v>80</v>
       </c>
-      <c r="Y1" s="351"/>
-      <c r="Z1" s="351"/>
-      <c r="AA1" s="351"/>
-      <c r="AB1" s="352" t="s">
+      <c r="Y1" s="359"/>
+      <c r="Z1" s="359"/>
+      <c r="AA1" s="359"/>
+      <c r="AB1" s="360" t="s">
         <v>81</v>
       </c>
-      <c r="AC1" s="352"/>
-      <c r="AD1" s="352"/>
-      <c r="AE1" s="352"/>
-      <c r="AF1" s="351" t="s">
+      <c r="AC1" s="360"/>
+      <c r="AD1" s="360"/>
+      <c r="AE1" s="360"/>
+      <c r="AF1" s="359" t="s">
         <v>82</v>
       </c>
-      <c r="AG1" s="351"/>
-      <c r="AH1" s="351"/>
-      <c r="AI1" s="351"/>
-      <c r="AJ1" s="352" t="s">
+      <c r="AG1" s="359"/>
+      <c r="AH1" s="359"/>
+      <c r="AI1" s="359"/>
+      <c r="AJ1" s="360" t="s">
         <v>83</v>
       </c>
-      <c r="AK1" s="352"/>
-      <c r="AL1" s="352"/>
-      <c r="AM1" s="352"/>
-      <c r="AN1" s="351" t="s">
+      <c r="AK1" s="360"/>
+      <c r="AL1" s="360"/>
+      <c r="AM1" s="360"/>
+      <c r="AN1" s="359" t="s">
         <v>84</v>
       </c>
-      <c r="AO1" s="351"/>
-      <c r="AP1" s="351"/>
-      <c r="AQ1" s="351"/>
-      <c r="AR1" s="352" t="s">
+      <c r="AO1" s="359"/>
+      <c r="AP1" s="359"/>
+      <c r="AQ1" s="359"/>
+      <c r="AR1" s="360" t="s">
         <v>85</v>
       </c>
-      <c r="AS1" s="352"/>
-      <c r="AT1" s="352"/>
-      <c r="AU1" s="352"/>
-      <c r="AV1" s="351" t="s">
+      <c r="AS1" s="360"/>
+      <c r="AT1" s="360"/>
+      <c r="AU1" s="360"/>
+      <c r="AV1" s="359" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="351"/>
-      <c r="AX1" s="351"/>
-      <c r="AY1" s="351"/>
-      <c r="AZ1" s="352" t="s">
+      <c r="AW1" s="359"/>
+      <c r="AX1" s="359"/>
+      <c r="AY1" s="359"/>
+      <c r="AZ1" s="360" t="s">
         <v>87</v>
       </c>
-      <c r="BA1" s="352"/>
-      <c r="BB1" s="352"/>
-      <c r="BC1" s="352"/>
-      <c r="BD1" s="351" t="s">
+      <c r="BA1" s="360"/>
+      <c r="BB1" s="360"/>
+      <c r="BC1" s="360"/>
+      <c r="BD1" s="359" t="s">
         <v>88</v>
       </c>
-      <c r="BE1" s="351"/>
-      <c r="BF1" s="351"/>
-      <c r="BG1" s="351"/>
-      <c r="BH1" s="352" t="s">
+      <c r="BE1" s="359"/>
+      <c r="BF1" s="359"/>
+      <c r="BG1" s="359"/>
+      <c r="BH1" s="360" t="s">
         <v>89</v>
       </c>
-      <c r="BI1" s="352"/>
-      <c r="BJ1" s="352"/>
-      <c r="BK1" s="352"/>
-      <c r="BL1" s="351" t="s">
+      <c r="BI1" s="360"/>
+      <c r="BJ1" s="360"/>
+      <c r="BK1" s="360"/>
+      <c r="BL1" s="359" t="s">
         <v>498</v>
       </c>
-      <c r="BM1" s="351"/>
-      <c r="BN1" s="351"/>
-      <c r="BO1" s="351"/>
+      <c r="BM1" s="359"/>
+      <c r="BN1" s="359"/>
+      <c r="BO1" s="359"/>
     </row>
     <row r="2" spans="1:67" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -53030,21 +53044,21 @@
       <c r="BO3" s="96"/>
     </row>
     <row r="4" spans="1:67" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="380" t="s">
+      <c r="B4" s="371" t="s">
         <v>844</v>
       </c>
-      <c r="C4" s="380"/>
-      <c r="D4" s="380"/>
-      <c r="E4" s="380"/>
-      <c r="F4" s="380"/>
-      <c r="G4" s="380"/>
-      <c r="H4" s="380"/>
-      <c r="I4" s="380"/>
-      <c r="J4" s="380"/>
-      <c r="K4" s="380"/>
-      <c r="L4" s="380"/>
-      <c r="M4" s="380"/>
-      <c r="N4" s="380"/>
+      <c r="C4" s="371"/>
+      <c r="D4" s="371"/>
+      <c r="E4" s="371"/>
+      <c r="F4" s="371"/>
+      <c r="G4" s="371"/>
+      <c r="H4" s="371"/>
+      <c r="I4" s="371"/>
+      <c r="J4" s="371"/>
+      <c r="K4" s="371"/>
+      <c r="L4" s="371"/>
+      <c r="M4" s="371"/>
+      <c r="N4" s="371"/>
       <c r="O4" s="148"/>
       <c r="P4" s="149"/>
       <c r="Q4" s="96"/>
@@ -53100,19 +53114,19 @@
       <c r="BO4" s="96"/>
     </row>
     <row r="5" spans="1:67" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="380"/>
-      <c r="C5" s="380"/>
-      <c r="D5" s="380"/>
-      <c r="E5" s="380"/>
-      <c r="F5" s="380"/>
-      <c r="G5" s="380"/>
-      <c r="H5" s="380"/>
-      <c r="I5" s="380"/>
-      <c r="J5" s="380"/>
-      <c r="K5" s="380"/>
-      <c r="L5" s="380"/>
-      <c r="M5" s="380"/>
-      <c r="N5" s="380"/>
+      <c r="B5" s="371"/>
+      <c r="C5" s="371"/>
+      <c r="D5" s="371"/>
+      <c r="E5" s="371"/>
+      <c r="F5" s="371"/>
+      <c r="G5" s="371"/>
+      <c r="H5" s="371"/>
+      <c r="I5" s="371"/>
+      <c r="J5" s="371"/>
+      <c r="K5" s="371"/>
+      <c r="L5" s="371"/>
+      <c r="M5" s="371"/>
+      <c r="N5" s="371"/>
       <c r="O5" s="148"/>
       <c r="P5" s="149"/>
       <c r="Q5" s="96"/>
@@ -53168,19 +53182,19 @@
       <c r="BO5" s="96"/>
     </row>
     <row r="6" spans="1:67" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="380"/>
-      <c r="C6" s="380"/>
-      <c r="D6" s="380"/>
-      <c r="E6" s="380"/>
-      <c r="F6" s="380"/>
-      <c r="G6" s="380"/>
-      <c r="H6" s="380"/>
-      <c r="I6" s="380"/>
-      <c r="J6" s="380"/>
-      <c r="K6" s="380"/>
-      <c r="L6" s="380"/>
-      <c r="M6" s="380"/>
-      <c r="N6" s="380"/>
+      <c r="B6" s="371"/>
+      <c r="C6" s="371"/>
+      <c r="D6" s="371"/>
+      <c r="E6" s="371"/>
+      <c r="F6" s="371"/>
+      <c r="G6" s="371"/>
+      <c r="H6" s="371"/>
+      <c r="I6" s="371"/>
+      <c r="J6" s="371"/>
+      <c r="K6" s="371"/>
+      <c r="L6" s="371"/>
+      <c r="M6" s="371"/>
+      <c r="N6" s="371"/>
       <c r="O6" s="148"/>
       <c r="P6" s="149"/>
       <c r="Q6" s="96"/>
@@ -53236,19 +53250,19 @@
       <c r="BO6" s="96"/>
     </row>
     <row r="7" spans="1:67" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="380"/>
-      <c r="C7" s="380"/>
-      <c r="D7" s="380"/>
-      <c r="E7" s="380"/>
-      <c r="F7" s="380"/>
-      <c r="G7" s="380"/>
-      <c r="H7" s="380"/>
-      <c r="I7" s="380"/>
-      <c r="J7" s="380"/>
-      <c r="K7" s="380"/>
-      <c r="L7" s="380"/>
-      <c r="M7" s="380"/>
-      <c r="N7" s="380"/>
+      <c r="B7" s="371"/>
+      <c r="C7" s="371"/>
+      <c r="D7" s="371"/>
+      <c r="E7" s="371"/>
+      <c r="F7" s="371"/>
+      <c r="G7" s="371"/>
+      <c r="H7" s="371"/>
+      <c r="I7" s="371"/>
+      <c r="J7" s="371"/>
+      <c r="K7" s="371"/>
+      <c r="L7" s="371"/>
+      <c r="M7" s="371"/>
+      <c r="N7" s="371"/>
       <c r="O7" s="148"/>
       <c r="P7" s="149"/>
       <c r="Q7" s="96"/>
@@ -53304,19 +53318,19 @@
       <c r="BO7" s="96"/>
     </row>
     <row r="8" spans="1:67" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="380"/>
-      <c r="C8" s="380"/>
-      <c r="D8" s="380"/>
-      <c r="E8" s="380"/>
-      <c r="F8" s="380"/>
-      <c r="G8" s="380"/>
-      <c r="H8" s="380"/>
-      <c r="I8" s="380"/>
-      <c r="J8" s="380"/>
-      <c r="K8" s="380"/>
-      <c r="L8" s="380"/>
-      <c r="M8" s="380"/>
-      <c r="N8" s="380"/>
+      <c r="B8" s="371"/>
+      <c r="C8" s="371"/>
+      <c r="D8" s="371"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
+      <c r="G8" s="371"/>
+      <c r="H8" s="371"/>
+      <c r="I8" s="371"/>
+      <c r="J8" s="371"/>
+      <c r="K8" s="371"/>
+      <c r="L8" s="371"/>
+      <c r="M8" s="371"/>
+      <c r="N8" s="371"/>
       <c r="O8" s="148"/>
       <c r="P8" s="149"/>
       <c r="Q8" s="96"/>
@@ -53372,19 +53386,19 @@
       <c r="BO8" s="96"/>
     </row>
     <row r="9" spans="1:67" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="380"/>
-      <c r="C9" s="380"/>
-      <c r="D9" s="380"/>
-      <c r="E9" s="380"/>
-      <c r="F9" s="380"/>
-      <c r="G9" s="380"/>
-      <c r="H9" s="380"/>
-      <c r="I9" s="380"/>
-      <c r="J9" s="380"/>
-      <c r="K9" s="380"/>
-      <c r="L9" s="380"/>
-      <c r="M9" s="380"/>
-      <c r="N9" s="380"/>
+      <c r="B9" s="371"/>
+      <c r="C9" s="371"/>
+      <c r="D9" s="371"/>
+      <c r="E9" s="371"/>
+      <c r="F9" s="371"/>
+      <c r="G9" s="371"/>
+      <c r="H9" s="371"/>
+      <c r="I9" s="371"/>
+      <c r="J9" s="371"/>
+      <c r="K9" s="371"/>
+      <c r="L9" s="371"/>
+      <c r="M9" s="371"/>
+      <c r="N9" s="371"/>
       <c r="O9" s="148"/>
       <c r="P9" s="149"/>
       <c r="Q9" s="96"/>
@@ -64599,7 +64613,7 @@
       <c r="O218" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BK178" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A2:BK178"/>
   <mergeCells count="16">
     <mergeCell ref="BD1:BG1"/>
     <mergeCell ref="BH1:BK1"/>
@@ -64623,43 +64637,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A5E736FC-E069-4F29-A515-23C9D2FECFA8}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$94</xm:f>
           </x14:formula1>
           <xm:sqref>T178:T186 T70 X111 T152:T163 P3:P1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{821210E9-CBF1-4810-832E-38228FEF41AF}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$102</xm:f>
           </x14:formula1>
           <xm:sqref>T183:T196 AZ152:AZ196 AR152:AR195 BD152:BD197 AN152:AN194 AV152:AV195 AF152:AF197 AJ152:AJ195 BH152:BH197 AB152:AB197 X152:X197 T164:T177 T156:T161 BL152:BL197</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F5DC88E8-78D7-454D-85AF-92B22181E099}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$274</xm:f>
           </x14:formula1>
           <xm:sqref>T43:T44 X43:X44 AB43:AB44 T28:T29 X28:X29 BD43 T96 X96 AB96 AF96 AN43:AN44 AV43 AF43:AF44 BH110:BH151 AJ110:AJ151 AN110:AN151 AV110:AV151 AF110:AF151 AR110:AR151 T138:T151 AZ110:AZ151 X110 T110:T135 BD110:BD151 X112:X151 X98:X105 AB98:AB105 AR96:AR105 AF98:AF105 AV96:AV105 AN96:AN105 AJ96:AJ105 BH96:BH105 AZ96:AZ105 BD96:BD105 T98:T105 AB110:AB151 BL43 BL110:BL151 BL96:BL105</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D4DBCBC4-5E8A-42C8-87D6-C2F18C2D811E}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$941</xm:f>
           </x14:formula1>
           <xm:sqref>T38 T197:T216 T36 T97 AF97 AB97 X97 BD3:BD39 AF3:AF38 AJ3:AJ38 AN3:AN38 AB3:AB38 X30:X38 T30:T34 AV3:AV42 X3:X27 T3:T27 T136:T137 AF40:AF42 X40:X42 T40:T42 AB40:AB42 AR3:AR95 BH3:BH95 AZ3:AZ95 BD44:BD95 AV44:AV95 T71:T95 AJ40:AJ95 AN45:AN95 BL44:BL95 BL3:BL39 AB45:AB95 T45:T69 X45:X95 AF45:AF95 AR106:AR109 T106:T109 BH106:BH109 BL107:BL108 AJ106:AJ109 AV106:AV109 X106:X109 AB106:AB109 AF106:AF109 AZ106:AZ109</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0AD0397C-C936-42E2-860B-CC1BF93B58C1}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$B$1:$B$8</xm:f>
           </x14:formula1>
           <xm:sqref>I3 I10:I1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{91E6A4EB-6405-44C6-B786-8DEA3004C946}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$C$1:$C$8</xm:f>
           </x14:formula1>
           <xm:sqref>H3 H10:H1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{48ECFAF8-CC0A-4FE3-815F-F5B0F5CE1AA4}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$E$1:$E$2</xm:f>
           </x14:formula1>
@@ -64672,7 +64686,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00847C"/>
   </sheetPr>
@@ -64745,97 +64759,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A1" s="352" t="s">
+      <c r="A1" s="360" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="352"/>
-      <c r="C1" s="352"/>
-      <c r="D1" s="352"/>
-      <c r="E1" s="353" t="s">
+      <c r="B1" s="360"/>
+      <c r="C1" s="360"/>
+      <c r="D1" s="360"/>
+      <c r="E1" s="361" t="s">
         <v>494</v>
       </c>
-      <c r="F1" s="354"/>
-      <c r="G1" s="354"/>
-      <c r="H1" s="354"/>
-      <c r="I1" s="354"/>
-      <c r="J1" s="354"/>
-      <c r="K1" s="354"/>
-      <c r="L1" s="354"/>
-      <c r="M1" s="354"/>
-      <c r="N1" s="354"/>
-      <c r="O1" s="355"/>
-      <c r="P1" s="362" t="s">
+      <c r="F1" s="362"/>
+      <c r="G1" s="362"/>
+      <c r="H1" s="362"/>
+      <c r="I1" s="362"/>
+      <c r="J1" s="362"/>
+      <c r="K1" s="362"/>
+      <c r="L1" s="362"/>
+      <c r="M1" s="362"/>
+      <c r="N1" s="362"/>
+      <c r="O1" s="363"/>
+      <c r="P1" s="370" t="s">
         <v>78</v>
       </c>
-      <c r="Q1" s="362"/>
-      <c r="R1" s="362"/>
-      <c r="S1" s="362"/>
-      <c r="T1" s="353" t="s">
+      <c r="Q1" s="370"/>
+      <c r="R1" s="370"/>
+      <c r="S1" s="370"/>
+      <c r="T1" s="361" t="s">
         <v>79</v>
       </c>
-      <c r="U1" s="354"/>
-      <c r="V1" s="354"/>
-      <c r="W1" s="354"/>
-      <c r="X1" s="362" t="s">
+      <c r="U1" s="362"/>
+      <c r="V1" s="362"/>
+      <c r="W1" s="362"/>
+      <c r="X1" s="370" t="s">
         <v>80</v>
       </c>
-      <c r="Y1" s="362"/>
-      <c r="Z1" s="362"/>
-      <c r="AA1" s="362"/>
-      <c r="AB1" s="353" t="s">
+      <c r="Y1" s="370"/>
+      <c r="Z1" s="370"/>
+      <c r="AA1" s="370"/>
+      <c r="AB1" s="361" t="s">
         <v>81</v>
       </c>
-      <c r="AC1" s="354"/>
-      <c r="AD1" s="354"/>
-      <c r="AE1" s="354"/>
-      <c r="AF1" s="362" t="s">
+      <c r="AC1" s="362"/>
+      <c r="AD1" s="362"/>
+      <c r="AE1" s="362"/>
+      <c r="AF1" s="370" t="s">
         <v>82</v>
       </c>
-      <c r="AG1" s="362"/>
-      <c r="AH1" s="362"/>
-      <c r="AI1" s="362"/>
-      <c r="AJ1" s="353" t="s">
+      <c r="AG1" s="370"/>
+      <c r="AH1" s="370"/>
+      <c r="AI1" s="370"/>
+      <c r="AJ1" s="361" t="s">
         <v>83</v>
       </c>
-      <c r="AK1" s="354"/>
-      <c r="AL1" s="354"/>
-      <c r="AM1" s="354"/>
-      <c r="AN1" s="362" t="s">
+      <c r="AK1" s="362"/>
+      <c r="AL1" s="362"/>
+      <c r="AM1" s="362"/>
+      <c r="AN1" s="370" t="s">
         <v>84</v>
       </c>
-      <c r="AO1" s="362"/>
-      <c r="AP1" s="362"/>
-      <c r="AQ1" s="362"/>
-      <c r="AR1" s="353" t="s">
+      <c r="AO1" s="370"/>
+      <c r="AP1" s="370"/>
+      <c r="AQ1" s="370"/>
+      <c r="AR1" s="361" t="s">
         <v>85</v>
       </c>
-      <c r="AS1" s="354"/>
-      <c r="AT1" s="354"/>
-      <c r="AU1" s="354"/>
-      <c r="AV1" s="362" t="s">
+      <c r="AS1" s="362"/>
+      <c r="AT1" s="362"/>
+      <c r="AU1" s="362"/>
+      <c r="AV1" s="370" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="362"/>
-      <c r="AX1" s="362"/>
-      <c r="AY1" s="362"/>
-      <c r="AZ1" s="353" t="s">
+      <c r="AW1" s="370"/>
+      <c r="AX1" s="370"/>
+      <c r="AY1" s="370"/>
+      <c r="AZ1" s="361" t="s">
         <v>87</v>
       </c>
-      <c r="BA1" s="354"/>
-      <c r="BB1" s="354"/>
-      <c r="BC1" s="354"/>
-      <c r="BD1" s="362" t="s">
+      <c r="BA1" s="362"/>
+      <c r="BB1" s="362"/>
+      <c r="BC1" s="362"/>
+      <c r="BD1" s="370" t="s">
         <v>88</v>
       </c>
-      <c r="BE1" s="362"/>
-      <c r="BF1" s="362"/>
-      <c r="BG1" s="362"/>
-      <c r="BH1" s="353" t="s">
+      <c r="BE1" s="370"/>
+      <c r="BF1" s="370"/>
+      <c r="BG1" s="370"/>
+      <c r="BH1" s="361" t="s">
         <v>89</v>
       </c>
-      <c r="BI1" s="354"/>
-      <c r="BJ1" s="354"/>
-      <c r="BK1" s="354"/>
+      <c r="BI1" s="362"/>
+      <c r="BJ1" s="362"/>
+      <c r="BK1" s="362"/>
     </row>
     <row r="2" spans="1:63" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -71599,7 +71613,7 @@
       <c r="N186" s="91"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BK2" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A2:BK2"/>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:O1"/>
@@ -71621,37 +71635,37 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$E$1:$E$2</xm:f>
           </x14:formula1>
           <xm:sqref>B3:C89</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000001000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$C$1:$C$8</xm:f>
           </x14:formula1>
           <xm:sqref>H3:H1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000002000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>datavalidation!$B$1:$B$8</xm:f>
           </x14:formula1>
           <xm:sqref>I3:I1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000003000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$941</xm:f>
           </x14:formula1>
           <xm:sqref>P4:P13 AJ15:AJ19 AF14:AF19 X14:X19 T14:T19 AB14:AB19 X56:X61 X36:X38 AF36:AF38 AB56:AB61 P82:P1048576 P20:P38</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000004000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$48</xm:f>
           </x14:formula1>
           <xm:sqref>T3:T13 AB36:AB38 T20:T1048576 P39:P81</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000005000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Event types'!$A$2:$A$94</xm:f>
           </x14:formula1>
@@ -71664,7 +71678,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -72623,7 +72637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF02525E"/>
   </sheetPr>
@@ -72655,7 +72669,7 @@
       <c r="B2" s="150" t="s">
         <v>554</v>
       </c>
-      <c r="C2" s="363" t="s">
+      <c r="C2" s="372" t="s">
         <v>362</v>
       </c>
       <c r="D2" s="172" t="s">
@@ -72669,7 +72683,7 @@
       <c r="B3" s="151" t="s">
         <v>555</v>
       </c>
-      <c r="C3" s="364"/>
+      <c r="C3" s="373"/>
       <c r="D3" s="165" t="s">
         <v>364</v>
       </c>
@@ -72681,7 +72695,7 @@
       <c r="B4" s="151" t="s">
         <v>556</v>
       </c>
-      <c r="C4" s="364"/>
+      <c r="C4" s="373"/>
       <c r="D4" s="165" t="s">
         <v>11</v>
       </c>
@@ -72693,7 +72707,7 @@
       <c r="B5" s="151" t="s">
         <v>557</v>
       </c>
-      <c r="C5" s="364"/>
+      <c r="C5" s="373"/>
       <c r="D5" s="165" t="s">
         <v>11</v>
       </c>
@@ -72705,7 +72719,7 @@
       <c r="B6" s="151" t="s">
         <v>558</v>
       </c>
-      <c r="C6" s="364"/>
+      <c r="C6" s="373"/>
       <c r="D6" s="165" t="s">
         <v>11</v>
       </c>
@@ -72717,7 +72731,7 @@
       <c r="B7" s="151" t="s">
         <v>559</v>
       </c>
-      <c r="C7" s="364"/>
+      <c r="C7" s="373"/>
       <c r="D7" s="165" t="s">
         <v>11</v>
       </c>
@@ -72729,7 +72743,7 @@
       <c r="B8" s="151" t="s">
         <v>560</v>
       </c>
-      <c r="C8" s="364"/>
+      <c r="C8" s="373"/>
       <c r="D8" s="165" t="s">
         <v>11</v>
       </c>
@@ -72741,7 +72755,7 @@
       <c r="B9" s="151" t="s">
         <v>561</v>
       </c>
-      <c r="C9" s="364"/>
+      <c r="C9" s="373"/>
       <c r="D9" s="165" t="s">
         <v>11</v>
       </c>
@@ -72753,7 +72767,7 @@
       <c r="B10" s="151" t="s">
         <v>563</v>
       </c>
-      <c r="C10" s="364"/>
+      <c r="C10" s="373"/>
       <c r="D10" s="165" t="s">
         <v>11</v>
       </c>
@@ -72765,7 +72779,7 @@
       <c r="B11" s="154" t="s">
         <v>562</v>
       </c>
-      <c r="C11" s="365"/>
+      <c r="C11" s="374"/>
       <c r="D11" s="169" t="s">
         <v>11</v>
       </c>
@@ -72777,7 +72791,7 @@
       <c r="B12" s="155" t="s">
         <v>564</v>
       </c>
-      <c r="C12" s="363" t="s">
+      <c r="C12" s="372" t="s">
         <v>365</v>
       </c>
       <c r="D12" s="172" t="s">
@@ -72791,7 +72805,7 @@
       <c r="B13" s="156" t="s">
         <v>565</v>
       </c>
-      <c r="C13" s="364"/>
+      <c r="C13" s="373"/>
       <c r="D13" s="165" t="s">
         <v>367</v>
       </c>
@@ -72803,7 +72817,7 @@
       <c r="B14" s="156" t="s">
         <v>566</v>
       </c>
-      <c r="C14" s="364"/>
+      <c r="C14" s="373"/>
       <c r="D14" s="165" t="s">
         <v>11</v>
       </c>
@@ -72815,7 +72829,7 @@
       <c r="B15" s="156" t="s">
         <v>567</v>
       </c>
-      <c r="C15" s="364"/>
+      <c r="C15" s="373"/>
       <c r="D15" s="165" t="s">
         <v>11</v>
       </c>
@@ -72827,7 +72841,7 @@
       <c r="B16" s="156" t="s">
         <v>568</v>
       </c>
-      <c r="C16" s="364"/>
+      <c r="C16" s="373"/>
       <c r="D16" s="165" t="s">
         <v>11</v>
       </c>
@@ -72839,7 +72853,7 @@
       <c r="B17" s="157" t="s">
         <v>569</v>
       </c>
-      <c r="C17" s="365"/>
+      <c r="C17" s="374"/>
       <c r="D17" s="169" t="s">
         <v>11</v>
       </c>
@@ -72851,7 +72865,7 @@
       <c r="B18" s="158" t="s">
         <v>570</v>
       </c>
-      <c r="C18" s="363" t="s">
+      <c r="C18" s="372" t="s">
         <v>108</v>
       </c>
       <c r="D18" s="172" t="s">
@@ -72865,7 +72879,7 @@
       <c r="B19" s="160" t="s">
         <v>571</v>
       </c>
-      <c r="C19" s="364"/>
+      <c r="C19" s="373"/>
       <c r="D19" s="165" t="s">
         <v>369</v>
       </c>
@@ -72877,7 +72891,7 @@
       <c r="B20" s="159" t="s">
         <v>572</v>
       </c>
-      <c r="C20" s="364"/>
+      <c r="C20" s="373"/>
       <c r="D20" s="165" t="s">
         <v>370</v>
       </c>
@@ -72889,7 +72903,7 @@
       <c r="B21" s="159" t="s">
         <v>573</v>
       </c>
-      <c r="C21" s="364"/>
+      <c r="C21" s="373"/>
       <c r="D21" s="165" t="s">
         <v>371</v>
       </c>
@@ -72901,7 +72915,7 @@
       <c r="B22" s="159" t="s">
         <v>574</v>
       </c>
-      <c r="C22" s="364"/>
+      <c r="C22" s="373"/>
       <c r="D22" s="165" t="s">
         <v>372</v>
       </c>
@@ -72913,7 +72927,7 @@
       <c r="B23" s="159" t="s">
         <v>575</v>
       </c>
-      <c r="C23" s="364"/>
+      <c r="C23" s="373"/>
       <c r="D23" s="165" t="s">
         <v>373</v>
       </c>
@@ -72925,7 +72939,7 @@
       <c r="B24" s="159" t="s">
         <v>576</v>
       </c>
-      <c r="C24" s="364"/>
+      <c r="C24" s="373"/>
       <c r="D24" s="165" t="s">
         <v>11</v>
       </c>
@@ -72937,7 +72951,7 @@
       <c r="B25" s="159" t="s">
         <v>577</v>
       </c>
-      <c r="C25" s="364"/>
+      <c r="C25" s="373"/>
       <c r="D25" s="165" t="s">
         <v>374</v>
       </c>
@@ -72949,7 +72963,7 @@
       <c r="B26" s="159" t="s">
         <v>578</v>
       </c>
-      <c r="C26" s="364"/>
+      <c r="C26" s="373"/>
       <c r="D26" s="165" t="s">
         <v>11</v>
       </c>
@@ -72961,7 +72975,7 @@
       <c r="B27" s="160" t="s">
         <v>638</v>
       </c>
-      <c r="C27" s="364"/>
+      <c r="C27" s="373"/>
       <c r="D27" s="165" t="s">
         <v>375</v>
       </c>
@@ -72973,7 +72987,7 @@
       <c r="B28" s="160" t="s">
         <v>639</v>
       </c>
-      <c r="C28" s="365"/>
+      <c r="C28" s="374"/>
       <c r="D28" s="165" t="s">
         <v>376</v>
       </c>
@@ -72985,7 +72999,7 @@
       <c r="B29" s="162" t="s">
         <v>579</v>
       </c>
-      <c r="C29" s="363" t="s">
+      <c r="C29" s="372" t="s">
         <v>377</v>
       </c>
       <c r="D29" s="172" t="s">
@@ -72999,7 +73013,7 @@
       <c r="B30" s="163" t="s">
         <v>580</v>
       </c>
-      <c r="C30" s="364"/>
+      <c r="C30" s="373"/>
       <c r="D30" s="165" t="s">
         <v>490</v>
       </c>
@@ -73011,7 +73025,7 @@
       <c r="B31" s="164" t="s">
         <v>581</v>
       </c>
-      <c r="C31" s="364"/>
+      <c r="C31" s="373"/>
       <c r="D31" s="165" t="s">
         <v>379</v>
       </c>
@@ -73023,7 +73037,7 @@
       <c r="B32" s="164" t="s">
         <v>582</v>
       </c>
-      <c r="C32" s="364"/>
+      <c r="C32" s="373"/>
       <c r="D32" s="165" t="s">
         <v>380</v>
       </c>
@@ -73035,7 +73049,7 @@
       <c r="B33" s="164" t="s">
         <v>583</v>
       </c>
-      <c r="C33" s="364"/>
+      <c r="C33" s="373"/>
       <c r="D33" s="165" t="s">
         <v>381</v>
       </c>
@@ -73047,7 +73061,7 @@
       <c r="B34" s="163" t="s">
         <v>584</v>
       </c>
-      <c r="C34" s="364"/>
+      <c r="C34" s="373"/>
       <c r="D34" s="165" t="s">
         <v>382</v>
       </c>
@@ -73059,7 +73073,7 @@
       <c r="B35" s="164" t="s">
         <v>585</v>
       </c>
-      <c r="C35" s="364"/>
+      <c r="C35" s="373"/>
       <c r="D35" s="165" t="s">
         <v>383</v>
       </c>
@@ -73071,7 +73085,7 @@
       <c r="B36" s="163" t="s">
         <v>586</v>
       </c>
-      <c r="C36" s="364"/>
+      <c r="C36" s="373"/>
       <c r="D36" s="165" t="s">
         <v>383</v>
       </c>
@@ -73083,7 +73097,7 @@
       <c r="B37" s="164" t="s">
         <v>587</v>
       </c>
-      <c r="C37" s="364"/>
+      <c r="C37" s="373"/>
       <c r="D37" s="165" t="s">
         <v>384</v>
       </c>
@@ -73095,7 +73109,7 @@
       <c r="B38" s="163" t="s">
         <v>588</v>
       </c>
-      <c r="C38" s="364"/>
+      <c r="C38" s="373"/>
       <c r="D38" s="165" t="s">
         <v>384</v>
       </c>
@@ -73107,7 +73121,7 @@
       <c r="B39" s="164" t="s">
         <v>589</v>
       </c>
-      <c r="C39" s="364"/>
+      <c r="C39" s="373"/>
       <c r="D39" s="165" t="s">
         <v>486</v>
       </c>
@@ -73119,7 +73133,7 @@
       <c r="B40" s="163" t="s">
         <v>590</v>
       </c>
-      <c r="C40" s="364"/>
+      <c r="C40" s="373"/>
       <c r="D40" s="165" t="s">
         <v>385</v>
       </c>
@@ -73131,7 +73145,7 @@
       <c r="B41" s="164" t="s">
         <v>591</v>
       </c>
-      <c r="C41" s="364"/>
+      <c r="C41" s="373"/>
       <c r="D41" s="165" t="s">
         <v>386</v>
       </c>
@@ -73143,7 +73157,7 @@
       <c r="B42" s="163" t="s">
         <v>592</v>
       </c>
-      <c r="C42" s="364"/>
+      <c r="C42" s="373"/>
       <c r="D42" s="165" t="s">
         <v>387</v>
       </c>
@@ -73155,7 +73169,7 @@
       <c r="B43" s="167" t="s">
         <v>593</v>
       </c>
-      <c r="C43" s="365"/>
+      <c r="C43" s="374"/>
       <c r="D43" s="169" t="s">
         <v>388</v>
       </c>
@@ -73168,7 +73182,7 @@
       <c r="B44" s="171" t="s">
         <v>594</v>
       </c>
-      <c r="C44" s="363" t="s">
+      <c r="C44" s="372" t="s">
         <v>389</v>
       </c>
       <c r="D44" s="172" t="s">
@@ -73182,7 +73196,7 @@
       <c r="B45" s="173" t="s">
         <v>595</v>
       </c>
-      <c r="C45" s="364"/>
+      <c r="C45" s="373"/>
       <c r="D45" s="165" t="s">
         <v>11</v>
       </c>
@@ -73194,7 +73208,7 @@
       <c r="B46" s="173" t="s">
         <v>596</v>
       </c>
-      <c r="C46" s="364"/>
+      <c r="C46" s="373"/>
       <c r="D46" s="165" t="s">
         <v>390</v>
       </c>
@@ -73206,7 +73220,7 @@
       <c r="B47" s="173" t="s">
         <v>597</v>
       </c>
-      <c r="C47" s="364"/>
+      <c r="C47" s="373"/>
       <c r="D47" s="165" t="s">
         <v>391</v>
       </c>
@@ -73218,7 +73232,7 @@
       <c r="B48" s="173" t="s">
         <v>598</v>
       </c>
-      <c r="C48" s="364"/>
+      <c r="C48" s="373"/>
       <c r="D48" s="165" t="s">
         <v>11</v>
       </c>
@@ -73230,7 +73244,7 @@
       <c r="B49" s="173" t="s">
         <v>599</v>
       </c>
-      <c r="C49" s="364"/>
+      <c r="C49" s="373"/>
       <c r="D49" s="165" t="s">
         <v>392</v>
       </c>
@@ -73242,7 +73256,7 @@
       <c r="B50" s="173" t="s">
         <v>600</v>
       </c>
-      <c r="C50" s="364"/>
+      <c r="C50" s="373"/>
       <c r="D50" s="165" t="s">
         <v>11</v>
       </c>
@@ -73254,7 +73268,7 @@
       <c r="B51" s="173" t="s">
         <v>601</v>
       </c>
-      <c r="C51" s="364"/>
+      <c r="C51" s="373"/>
       <c r="D51" s="165" t="s">
         <v>491</v>
       </c>
@@ -73266,7 +73280,7 @@
       <c r="B52" s="173" t="s">
         <v>602</v>
       </c>
-      <c r="C52" s="364"/>
+      <c r="C52" s="373"/>
       <c r="D52" s="165" t="s">
         <v>391</v>
       </c>
@@ -73278,7 +73292,7 @@
       <c r="B53" s="174" t="s">
         <v>603</v>
       </c>
-      <c r="C53" s="365"/>
+      <c r="C53" s="374"/>
       <c r="D53" s="169" t="s">
         <v>11</v>
       </c>
@@ -73290,7 +73304,7 @@
       <c r="B54" s="175" t="s">
         <v>604</v>
       </c>
-      <c r="C54" s="363" t="s">
+      <c r="C54" s="372" t="s">
         <v>393</v>
       </c>
       <c r="D54" s="165" t="s">
@@ -73304,7 +73318,7 @@
       <c r="B55" s="175" t="s">
         <v>605</v>
       </c>
-      <c r="C55" s="364"/>
+      <c r="C55" s="373"/>
       <c r="D55" s="165" t="s">
         <v>395</v>
       </c>
@@ -73316,7 +73330,7 @@
       <c r="B56" s="175" t="s">
         <v>739</v>
       </c>
-      <c r="C56" s="364"/>
+      <c r="C56" s="373"/>
       <c r="D56" s="165" t="s">
         <v>396</v>
       </c>
@@ -73328,7 +73342,7 @@
       <c r="B57" s="175" t="s">
         <v>728</v>
       </c>
-      <c r="C57" s="365"/>
+      <c r="C57" s="374"/>
       <c r="D57" s="165" t="s">
         <v>397</v>
       </c>
@@ -73340,7 +73354,7 @@
       <c r="B58" s="221" t="s">
         <v>734</v>
       </c>
-      <c r="C58" s="363" t="s">
+      <c r="C58" s="372" t="s">
         <v>398</v>
       </c>
       <c r="D58" s="172" t="s">
@@ -73354,7 +73368,7 @@
       <c r="B59" s="267" t="s">
         <v>735</v>
       </c>
-      <c r="C59" s="364"/>
+      <c r="C59" s="373"/>
       <c r="D59" s="269" t="s">
         <v>543</v>
       </c>
@@ -73366,7 +73380,7 @@
       <c r="B60" s="176" t="s">
         <v>736</v>
       </c>
-      <c r="C60" s="365"/>
+      <c r="C60" s="374"/>
       <c r="D60" s="169" t="s">
         <v>489</v>
       </c>
@@ -73378,7 +73392,7 @@
       <c r="B61" s="177" t="s">
         <v>606</v>
       </c>
-      <c r="C61" s="363" t="s">
+      <c r="C61" s="372" t="s">
         <v>399</v>
       </c>
       <c r="D61" s="165" t="s">
@@ -73392,7 +73406,7 @@
       <c r="B62" s="177" t="s">
         <v>607</v>
       </c>
-      <c r="C62" s="364"/>
+      <c r="C62" s="373"/>
       <c r="D62" s="165" t="s">
         <v>401</v>
       </c>
@@ -73404,7 +73418,7 @@
       <c r="B63" s="177" t="s">
         <v>608</v>
       </c>
-      <c r="C63" s="364"/>
+      <c r="C63" s="373"/>
       <c r="D63" s="165" t="s">
         <v>402</v>
       </c>
@@ -73416,7 +73430,7 @@
       <c r="B64" s="177" t="s">
         <v>609</v>
       </c>
-      <c r="C64" s="364"/>
+      <c r="C64" s="373"/>
       <c r="D64" s="165" t="s">
         <v>403</v>
       </c>
@@ -73428,7 +73442,7 @@
       <c r="B65" s="177" t="s">
         <v>610</v>
       </c>
-      <c r="C65" s="364"/>
+      <c r="C65" s="373"/>
       <c r="D65" s="165" t="s">
         <v>404</v>
       </c>
@@ -73440,7 +73454,7 @@
       <c r="B66" s="177" t="s">
         <v>611</v>
       </c>
-      <c r="C66" s="364"/>
+      <c r="C66" s="373"/>
       <c r="D66" s="165" t="s">
         <v>405</v>
       </c>
@@ -73452,7 +73466,7 @@
       <c r="B67" s="177" t="s">
         <v>612</v>
       </c>
-      <c r="C67" s="364"/>
+      <c r="C67" s="373"/>
       <c r="D67" s="165" t="s">
         <v>406</v>
       </c>
@@ -73464,7 +73478,7 @@
       <c r="B68" s="177" t="s">
         <v>726</v>
       </c>
-      <c r="C68" s="364"/>
+      <c r="C68" s="373"/>
       <c r="D68" s="165" t="s">
         <v>499</v>
       </c>
@@ -73476,7 +73490,7 @@
       <c r="B69" s="229" t="s">
         <v>727</v>
       </c>
-      <c r="C69" s="364"/>
+      <c r="C69" s="373"/>
       <c r="D69" s="165" t="s">
         <v>500</v>
       </c>
@@ -73488,7 +73502,7 @@
       <c r="B70" s="178" t="s">
         <v>613</v>
       </c>
-      <c r="C70" s="365"/>
+      <c r="C70" s="374"/>
       <c r="D70" s="169" t="s">
         <v>407</v>
       </c>
@@ -73500,7 +73514,7 @@
       <c r="B71" s="180" t="s">
         <v>614</v>
       </c>
-      <c r="C71" s="363" t="s">
+      <c r="C71" s="372" t="s">
         <v>408</v>
       </c>
       <c r="D71" s="172" t="s">
@@ -73514,7 +73528,7 @@
       <c r="B72" s="181" t="s">
         <v>615</v>
       </c>
-      <c r="C72" s="364"/>
+      <c r="C72" s="373"/>
       <c r="D72" s="165" t="s">
         <v>11</v>
       </c>
@@ -73526,7 +73540,7 @@
       <c r="B73" s="181" t="s">
         <v>616</v>
       </c>
-      <c r="C73" s="364"/>
+      <c r="C73" s="373"/>
       <c r="D73" s="165" t="s">
         <v>11</v>
       </c>
@@ -73538,7 +73552,7 @@
       <c r="B74" s="181" t="s">
         <v>617</v>
       </c>
-      <c r="C74" s="364"/>
+      <c r="C74" s="373"/>
       <c r="D74" s="165" t="s">
         <v>11</v>
       </c>
@@ -73550,7 +73564,7 @@
       <c r="B75" s="181" t="s">
         <v>618</v>
       </c>
-      <c r="C75" s="364"/>
+      <c r="C75" s="373"/>
       <c r="D75" s="165" t="s">
         <v>11</v>
       </c>
@@ -73562,7 +73576,7 @@
       <c r="B76" s="181" t="s">
         <v>619</v>
       </c>
-      <c r="C76" s="364"/>
+      <c r="C76" s="373"/>
       <c r="D76" s="165" t="s">
         <v>410</v>
       </c>
@@ -73574,7 +73588,7 @@
       <c r="B77" s="181" t="s">
         <v>620</v>
       </c>
-      <c r="C77" s="364"/>
+      <c r="C77" s="373"/>
       <c r="D77" s="165" t="s">
         <v>11</v>
       </c>
@@ -73586,7 +73600,7 @@
       <c r="B78" s="181" t="s">
         <v>621</v>
       </c>
-      <c r="C78" s="364"/>
+      <c r="C78" s="373"/>
       <c r="D78" s="165" t="s">
         <v>11</v>
       </c>
@@ -73598,7 +73612,7 @@
       <c r="B79" s="181" t="s">
         <v>622</v>
       </c>
-      <c r="C79" s="364"/>
+      <c r="C79" s="373"/>
       <c r="D79" s="165" t="s">
         <v>11</v>
       </c>
@@ -73610,7 +73624,7 @@
       <c r="B80" s="181" t="s">
         <v>623</v>
       </c>
-      <c r="C80" s="364"/>
+      <c r="C80" s="373"/>
       <c r="D80" s="165" t="s">
         <v>11</v>
       </c>
@@ -73622,7 +73636,7 @@
       <c r="B81" s="181" t="s">
         <v>624</v>
       </c>
-      <c r="C81" s="364"/>
+      <c r="C81" s="373"/>
       <c r="D81" s="165" t="s">
         <v>11</v>
       </c>
@@ -73634,7 +73648,7 @@
       <c r="B82" s="181" t="s">
         <v>625</v>
       </c>
-      <c r="C82" s="364"/>
+      <c r="C82" s="373"/>
       <c r="D82" s="165" t="s">
         <v>410</v>
       </c>
@@ -73646,7 +73660,7 @@
       <c r="B83" s="181" t="s">
         <v>626</v>
       </c>
-      <c r="C83" s="364"/>
+      <c r="C83" s="373"/>
       <c r="D83" s="165" t="s">
         <v>11</v>
       </c>
@@ -73658,7 +73672,7 @@
       <c r="B84" s="181" t="s">
         <v>627</v>
       </c>
-      <c r="C84" s="364"/>
+      <c r="C84" s="373"/>
       <c r="D84" s="165" t="s">
         <v>11</v>
       </c>
@@ -73670,7 +73684,7 @@
       <c r="B85" s="182" t="s">
         <v>628</v>
       </c>
-      <c r="C85" s="364"/>
+      <c r="C85" s="373"/>
       <c r="D85" s="165" t="s">
         <v>11</v>
       </c>
@@ -73682,7 +73696,7 @@
       <c r="B86" s="182" t="s">
         <v>629</v>
       </c>
-      <c r="C86" s="364"/>
+      <c r="C86" s="373"/>
       <c r="D86" s="165" t="s">
         <v>11</v>
       </c>
@@ -73694,7 +73708,7 @@
       <c r="B87" s="182" t="s">
         <v>630</v>
       </c>
-      <c r="C87" s="364"/>
+      <c r="C87" s="373"/>
       <c r="D87" s="165" t="s">
         <v>11</v>
       </c>
@@ -73706,7 +73720,7 @@
       <c r="B88" s="182" t="s">
         <v>631</v>
       </c>
-      <c r="C88" s="364"/>
+      <c r="C88" s="373"/>
       <c r="D88" s="165" t="s">
         <v>410</v>
       </c>
@@ -73718,7 +73732,7 @@
       <c r="B89" s="182" t="s">
         <v>632</v>
       </c>
-      <c r="C89" s="364"/>
+      <c r="C89" s="373"/>
       <c r="D89" s="165" t="s">
         <v>411</v>
       </c>
@@ -73730,7 +73744,7 @@
       <c r="B90" s="183" t="s">
         <v>633</v>
       </c>
-      <c r="C90" s="364"/>
+      <c r="C90" s="373"/>
       <c r="D90" s="165" t="s">
         <v>412</v>
       </c>
@@ -73742,7 +73756,7 @@
       <c r="B91" s="183" t="s">
         <v>634</v>
       </c>
-      <c r="C91" s="364"/>
+      <c r="C91" s="373"/>
       <c r="D91" s="165" t="s">
         <v>413</v>
       </c>
@@ -73754,7 +73768,7 @@
       <c r="B92" s="183" t="s">
         <v>635</v>
       </c>
-      <c r="C92" s="364"/>
+      <c r="C92" s="373"/>
       <c r="D92" s="165" t="s">
         <v>414</v>
       </c>
@@ -73766,7 +73780,7 @@
       <c r="B93" s="183" t="s">
         <v>636</v>
       </c>
-      <c r="C93" s="364"/>
+      <c r="C93" s="373"/>
       <c r="D93" s="165" t="s">
         <v>415</v>
       </c>
@@ -73778,7 +73792,7 @@
       <c r="B94" s="185" t="s">
         <v>637</v>
       </c>
-      <c r="C94" s="365"/>
+      <c r="C94" s="374"/>
       <c r="D94" s="169" t="s">
         <v>416</v>
       </c>
@@ -73790,7 +73804,7 @@
       <c r="B95" s="186" t="s">
         <v>640</v>
       </c>
-      <c r="C95" s="363" t="s">
+      <c r="C95" s="372" t="s">
         <v>417</v>
       </c>
       <c r="D95" s="165" t="s">
@@ -73804,7 +73818,7 @@
       <c r="B96" s="186" t="s">
         <v>641</v>
       </c>
-      <c r="C96" s="364"/>
+      <c r="C96" s="373"/>
       <c r="D96" s="268" t="s">
         <v>419</v>
       </c>
@@ -73816,7 +73830,7 @@
       <c r="B97" s="186" t="s">
         <v>642</v>
       </c>
-      <c r="C97" s="364"/>
+      <c r="C97" s="373"/>
       <c r="D97" s="187" t="s">
         <v>420</v>
       </c>
@@ -73828,7 +73842,7 @@
       <c r="B98" s="188" t="s">
         <v>643</v>
       </c>
-      <c r="C98" s="365"/>
+      <c r="C98" s="374"/>
       <c r="D98" s="169" t="s">
         <v>421</v>
       </c>
@@ -73840,7 +73854,7 @@
       <c r="B99" s="171" t="s">
         <v>644</v>
       </c>
-      <c r="C99" s="363" t="s">
+      <c r="C99" s="372" t="s">
         <v>422</v>
       </c>
       <c r="D99" s="172" t="s">
@@ -73854,7 +73868,7 @@
       <c r="B100" s="173" t="s">
         <v>645</v>
       </c>
-      <c r="C100" s="364"/>
+      <c r="C100" s="373"/>
       <c r="D100" s="165" t="s">
         <v>424</v>
       </c>
@@ -73866,7 +73880,7 @@
       <c r="B101" s="173" t="s">
         <v>646</v>
       </c>
-      <c r="C101" s="364"/>
+      <c r="C101" s="373"/>
       <c r="D101" s="165" t="s">
         <v>425</v>
       </c>
@@ -73878,7 +73892,7 @@
       <c r="B102" s="173" t="s">
         <v>647</v>
       </c>
-      <c r="C102" s="364"/>
+      <c r="C102" s="373"/>
       <c r="D102" s="165" t="s">
         <v>426</v>
       </c>
@@ -73890,7 +73904,7 @@
       <c r="B103" s="173" t="s">
         <v>648</v>
       </c>
-      <c r="C103" s="364"/>
+      <c r="C103" s="373"/>
       <c r="D103" s="165" t="s">
         <v>427</v>
       </c>
@@ -73902,7 +73916,7 @@
       <c r="B104" s="173" t="s">
         <v>649</v>
       </c>
-      <c r="C104" s="364"/>
+      <c r="C104" s="373"/>
       <c r="D104" s="165" t="s">
         <v>483</v>
       </c>
@@ -73914,7 +73928,7 @@
       <c r="B105" s="173" t="s">
         <v>650</v>
       </c>
-      <c r="C105" s="364"/>
+      <c r="C105" s="373"/>
       <c r="D105" s="165" t="s">
         <v>501</v>
       </c>
@@ -73926,7 +73940,7 @@
       <c r="B106" s="173" t="s">
         <v>651</v>
       </c>
-      <c r="C106" s="364"/>
+      <c r="C106" s="373"/>
       <c r="D106" s="165" t="s">
         <v>502</v>
       </c>
@@ -73938,7 +73952,7 @@
       <c r="B107" s="173" t="s">
         <v>652</v>
       </c>
-      <c r="C107" s="364"/>
+      <c r="C107" s="373"/>
       <c r="D107" s="165" t="s">
         <v>503</v>
       </c>
@@ -73950,7 +73964,7 @@
       <c r="B108" s="173" t="s">
         <v>653</v>
       </c>
-      <c r="C108" s="365"/>
+      <c r="C108" s="374"/>
       <c r="D108" s="165" t="s">
         <v>504</v>
       </c>
@@ -73962,7 +73976,7 @@
       <c r="B109" s="190" t="s">
         <v>654</v>
       </c>
-      <c r="C109" s="363" t="s">
+      <c r="C109" s="372" t="s">
         <v>428</v>
       </c>
       <c r="D109" s="172" t="s">
@@ -73976,7 +73990,7 @@
       <c r="B110" s="191" t="s">
         <v>725</v>
       </c>
-      <c r="C110" s="364"/>
+      <c r="C110" s="373"/>
       <c r="D110" s="165" t="s">
         <v>542</v>
       </c>
@@ -73988,7 +74002,7 @@
       <c r="B111" s="191" t="s">
         <v>655</v>
       </c>
-      <c r="C111" s="364"/>
+      <c r="C111" s="373"/>
       <c r="D111" s="165" t="s">
         <v>429</v>
       </c>
@@ -74000,7 +74014,7 @@
       <c r="B112" s="191" t="s">
         <v>656</v>
       </c>
-      <c r="C112" s="364"/>
+      <c r="C112" s="373"/>
       <c r="D112" s="165" t="s">
         <v>430</v>
       </c>
@@ -74012,7 +74026,7 @@
       <c r="B113" s="191" t="s">
         <v>657</v>
       </c>
-      <c r="C113" s="364"/>
+      <c r="C113" s="373"/>
       <c r="D113" s="165" t="s">
         <v>430</v>
       </c>
@@ -74024,7 +74038,7 @@
       <c r="B114" s="191" t="s">
         <v>658</v>
       </c>
-      <c r="C114" s="364"/>
+      <c r="C114" s="373"/>
       <c r="D114" s="165" t="s">
         <v>431</v>
       </c>
@@ -74036,7 +74050,7 @@
       <c r="B115" s="193" t="s">
         <v>659</v>
       </c>
-      <c r="C115" s="365"/>
+      <c r="C115" s="374"/>
       <c r="D115" s="169" t="s">
         <v>431</v>
       </c>
@@ -74048,7 +74062,7 @@
       <c r="B116" s="194" t="s">
         <v>660</v>
       </c>
-      <c r="C116" s="363" t="s">
+      <c r="C116" s="372" t="s">
         <v>432</v>
       </c>
       <c r="D116" s="172" t="s">
@@ -74062,7 +74076,7 @@
       <c r="B117" s="195" t="s">
         <v>661</v>
       </c>
-      <c r="C117" s="364"/>
+      <c r="C117" s="373"/>
       <c r="D117" s="165" t="s">
         <v>11</v>
       </c>
@@ -74074,7 +74088,7 @@
       <c r="B118" s="195" t="s">
         <v>662</v>
       </c>
-      <c r="C118" s="364"/>
+      <c r="C118" s="373"/>
       <c r="D118" s="165" t="s">
         <v>11</v>
       </c>
@@ -74086,7 +74100,7 @@
       <c r="B119" s="195" t="s">
         <v>663</v>
       </c>
-      <c r="C119" s="364"/>
+      <c r="C119" s="373"/>
       <c r="D119" s="165" t="s">
         <v>11</v>
       </c>
@@ -74098,7 +74112,7 @@
       <c r="B120" s="195" t="s">
         <v>664</v>
       </c>
-      <c r="C120" s="364"/>
+      <c r="C120" s="373"/>
       <c r="D120" s="165" t="s">
         <v>11</v>
       </c>
@@ -74110,7 +74124,7 @@
       <c r="B121" s="195" t="s">
         <v>665</v>
       </c>
-      <c r="C121" s="364"/>
+      <c r="C121" s="373"/>
       <c r="D121" s="165" t="s">
         <v>410</v>
       </c>
@@ -74122,7 +74136,7 @@
       <c r="B122" s="195" t="s">
         <v>666</v>
       </c>
-      <c r="C122" s="364"/>
+      <c r="C122" s="373"/>
       <c r="D122" s="165" t="s">
         <v>11</v>
       </c>
@@ -74134,7 +74148,7 @@
       <c r="B123" s="195" t="s">
         <v>667</v>
       </c>
-      <c r="C123" s="364"/>
+      <c r="C123" s="373"/>
       <c r="D123" s="165" t="s">
         <v>11</v>
       </c>
@@ -74146,7 +74160,7 @@
       <c r="B124" s="195" t="s">
         <v>668</v>
       </c>
-      <c r="C124" s="364"/>
+      <c r="C124" s="373"/>
       <c r="D124" s="165" t="s">
         <v>11</v>
       </c>
@@ -74158,7 +74172,7 @@
       <c r="B125" s="195" t="s">
         <v>669</v>
       </c>
-      <c r="C125" s="364"/>
+      <c r="C125" s="373"/>
       <c r="D125" s="165" t="s">
         <v>11</v>
       </c>
@@ -74170,7 +74184,7 @@
       <c r="B126" s="195" t="s">
         <v>670</v>
       </c>
-      <c r="C126" s="364"/>
+      <c r="C126" s="373"/>
       <c r="D126" s="165" t="s">
         <v>11</v>
       </c>
@@ -74182,7 +74196,7 @@
       <c r="B127" s="195" t="s">
         <v>671</v>
       </c>
-      <c r="C127" s="364"/>
+      <c r="C127" s="373"/>
       <c r="D127" s="165" t="s">
         <v>11</v>
       </c>
@@ -74194,7 +74208,7 @@
       <c r="B128" s="195" t="s">
         <v>672</v>
       </c>
-      <c r="C128" s="364"/>
+      <c r="C128" s="373"/>
       <c r="D128" s="165" t="s">
         <v>11</v>
       </c>
@@ -74206,7 +74220,7 @@
       <c r="B129" s="195" t="s">
         <v>673</v>
       </c>
-      <c r="C129" s="364"/>
+      <c r="C129" s="373"/>
       <c r="D129" s="165" t="s">
         <v>11</v>
       </c>
@@ -74218,7 +74232,7 @@
       <c r="B130" s="195" t="s">
         <v>674</v>
       </c>
-      <c r="C130" s="364"/>
+      <c r="C130" s="373"/>
       <c r="D130" s="165" t="s">
         <v>434</v>
       </c>
@@ -74230,7 +74244,7 @@
       <c r="B131" s="195" t="s">
         <v>675</v>
       </c>
-      <c r="C131" s="364"/>
+      <c r="C131" s="373"/>
       <c r="D131" s="165" t="s">
         <v>435</v>
       </c>
@@ -74242,7 +74256,7 @@
       <c r="B132" s="195" t="s">
         <v>676</v>
       </c>
-      <c r="C132" s="364"/>
+      <c r="C132" s="373"/>
       <c r="D132" s="165" t="s">
         <v>436</v>
       </c>
@@ -74254,7 +74268,7 @@
       <c r="B133" s="195" t="s">
         <v>677</v>
       </c>
-      <c r="C133" s="364"/>
+      <c r="C133" s="373"/>
       <c r="D133" s="165" t="s">
         <v>437</v>
       </c>
@@ -74266,7 +74280,7 @@
       <c r="B134" s="195" t="s">
         <v>678</v>
       </c>
-      <c r="C134" s="364"/>
+      <c r="C134" s="373"/>
       <c r="D134" s="165" t="s">
         <v>438</v>
       </c>
@@ -74278,7 +74292,7 @@
       <c r="B135" s="195" t="s">
         <v>679</v>
       </c>
-      <c r="C135" s="364"/>
+      <c r="C135" s="373"/>
       <c r="D135" s="165" t="s">
         <v>439</v>
       </c>
@@ -74290,7 +74304,7 @@
       <c r="B136" s="195" t="s">
         <v>680</v>
       </c>
-      <c r="C136" s="364"/>
+      <c r="C136" s="373"/>
       <c r="D136" s="165" t="s">
         <v>440</v>
       </c>
@@ -74302,7 +74316,7 @@
       <c r="B137" s="195" t="s">
         <v>681</v>
       </c>
-      <c r="C137" s="364"/>
+      <c r="C137" s="373"/>
       <c r="D137" s="165" t="s">
         <v>441</v>
       </c>
@@ -74314,7 +74328,7 @@
       <c r="B138" s="195" t="s">
         <v>682</v>
       </c>
-      <c r="C138" s="364"/>
+      <c r="C138" s="373"/>
       <c r="D138" s="165" t="s">
         <v>441</v>
       </c>
@@ -74326,7 +74340,7 @@
       <c r="B139" s="195" t="s">
         <v>737</v>
       </c>
-      <c r="C139" s="364"/>
+      <c r="C139" s="373"/>
       <c r="D139" s="165" t="s">
         <v>487</v>
       </c>
@@ -74338,7 +74352,7 @@
       <c r="B140" s="195" t="s">
         <v>738</v>
       </c>
-      <c r="C140" s="364"/>
+      <c r="C140" s="373"/>
       <c r="D140" s="165" t="s">
         <v>442</v>
       </c>
@@ -74350,7 +74364,7 @@
       <c r="B141" s="195" t="s">
         <v>683</v>
       </c>
-      <c r="C141" s="364"/>
+      <c r="C141" s="373"/>
       <c r="D141" s="165" t="s">
         <v>488</v>
       </c>
@@ -74362,7 +74376,7 @@
       <c r="B142" s="195" t="s">
         <v>684</v>
       </c>
-      <c r="C142" s="364"/>
+      <c r="C142" s="373"/>
       <c r="D142" s="165" t="s">
         <v>485</v>
       </c>
@@ -74374,7 +74388,7 @@
       <c r="B143" s="195" t="s">
         <v>723</v>
       </c>
-      <c r="C143" s="364"/>
+      <c r="C143" s="373"/>
       <c r="D143" s="165" t="s">
         <v>443</v>
       </c>
@@ -74386,7 +74400,7 @@
       <c r="B144" s="195" t="s">
         <v>724</v>
       </c>
-      <c r="C144" s="364"/>
+      <c r="C144" s="373"/>
       <c r="D144" s="165" t="s">
         <v>444</v>
       </c>
@@ -74398,7 +74412,7 @@
       <c r="B145" s="195" t="s">
         <v>685</v>
       </c>
-      <c r="C145" s="364"/>
+      <c r="C145" s="373"/>
       <c r="D145" s="165" t="s">
         <v>445</v>
       </c>
@@ -74410,7 +74424,7 @@
       <c r="B146" s="195" t="s">
         <v>686</v>
       </c>
-      <c r="C146" s="364"/>
+      <c r="C146" s="373"/>
       <c r="D146" s="165" t="s">
         <v>446</v>
       </c>
@@ -74422,7 +74436,7 @@
       <c r="B147" s="195" t="s">
         <v>687</v>
       </c>
-      <c r="C147" s="364"/>
+      <c r="C147" s="373"/>
       <c r="D147" s="165" t="s">
         <v>447</v>
       </c>
@@ -74434,7 +74448,7 @@
       <c r="B148" s="195" t="s">
         <v>688</v>
       </c>
-      <c r="C148" s="364"/>
+      <c r="C148" s="373"/>
       <c r="D148" s="165" t="s">
         <v>448</v>
       </c>
@@ -74446,7 +74460,7 @@
       <c r="B149" s="195" t="s">
         <v>689</v>
       </c>
-      <c r="C149" s="364"/>
+      <c r="C149" s="373"/>
       <c r="D149" s="165" t="s">
         <v>449</v>
       </c>
@@ -74458,7 +74472,7 @@
       <c r="B150" s="195" t="s">
         <v>690</v>
       </c>
-      <c r="C150" s="364"/>
+      <c r="C150" s="373"/>
       <c r="D150" s="165" t="s">
         <v>450</v>
       </c>
@@ -74470,7 +74484,7 @@
       <c r="B151" s="195" t="s">
         <v>691</v>
       </c>
-      <c r="C151" s="364"/>
+      <c r="C151" s="373"/>
       <c r="D151" s="165" t="s">
         <v>505</v>
       </c>
@@ -74482,7 +74496,7 @@
       <c r="B152" s="195" t="s">
         <v>692</v>
       </c>
-      <c r="C152" s="364"/>
+      <c r="C152" s="373"/>
       <c r="D152" s="165" t="s">
         <v>11</v>
       </c>
@@ -74494,7 +74508,7 @@
       <c r="B153" s="195" t="s">
         <v>693</v>
       </c>
-      <c r="C153" s="364"/>
+      <c r="C153" s="373"/>
       <c r="D153" s="165" t="s">
         <v>11</v>
       </c>
@@ -74506,7 +74520,7 @@
       <c r="B154" s="195" t="s">
         <v>694</v>
       </c>
-      <c r="C154" s="364"/>
+      <c r="C154" s="373"/>
       <c r="D154" s="165" t="s">
         <v>11</v>
       </c>
@@ -74518,7 +74532,7 @@
       <c r="B155" s="195" t="s">
         <v>695</v>
       </c>
-      <c r="C155" s="364"/>
+      <c r="C155" s="373"/>
       <c r="D155" s="165" t="s">
         <v>11</v>
       </c>
@@ -74530,7 +74544,7 @@
       <c r="B156" s="195" t="s">
         <v>696</v>
       </c>
-      <c r="C156" s="364"/>
+      <c r="C156" s="373"/>
       <c r="D156" s="165" t="s">
         <v>11</v>
       </c>
@@ -74542,7 +74556,7 @@
       <c r="B157" s="195" t="s">
         <v>697</v>
       </c>
-      <c r="C157" s="364"/>
+      <c r="C157" s="373"/>
       <c r="D157" s="165" t="s">
         <v>11</v>
       </c>
@@ -74554,7 +74568,7 @@
       <c r="B158" s="195" t="s">
         <v>698</v>
       </c>
-      <c r="C158" s="364"/>
+      <c r="C158" s="373"/>
       <c r="D158" s="165" t="s">
         <v>11</v>
       </c>
@@ -74566,7 +74580,7 @@
       <c r="B159" s="195" t="s">
         <v>699</v>
       </c>
-      <c r="C159" s="364"/>
+      <c r="C159" s="373"/>
       <c r="D159" s="165" t="s">
         <v>506</v>
       </c>
@@ -74578,7 +74592,7 @@
       <c r="B160" s="195" t="s">
         <v>700</v>
       </c>
-      <c r="C160" s="364"/>
+      <c r="C160" s="373"/>
       <c r="D160" s="165" t="s">
         <v>507</v>
       </c>
@@ -74590,7 +74604,7 @@
       <c r="B161" s="195" t="s">
         <v>701</v>
       </c>
-      <c r="C161" s="364"/>
+      <c r="C161" s="373"/>
       <c r="D161" s="165" t="s">
         <v>508</v>
       </c>
@@ -74602,7 +74616,7 @@
       <c r="B162" s="196" t="s">
         <v>702</v>
       </c>
-      <c r="C162" s="365"/>
+      <c r="C162" s="374"/>
       <c r="D162" s="235" t="s">
         <v>11</v>
       </c>
@@ -74614,7 +74628,7 @@
       <c r="B163" s="197" t="s">
         <v>703</v>
       </c>
-      <c r="C163" s="363" t="s">
+      <c r="C163" s="372" t="s">
         <v>451</v>
       </c>
       <c r="D163" s="165" t="s">
@@ -74628,7 +74642,7 @@
       <c r="B164" s="197" t="s">
         <v>704</v>
       </c>
-      <c r="C164" s="364"/>
+      <c r="C164" s="373"/>
       <c r="D164" s="165" t="s">
         <v>453</v>
       </c>
@@ -74640,7 +74654,7 @@
       <c r="B165" s="197" t="s">
         <v>705</v>
       </c>
-      <c r="C165" s="364"/>
+      <c r="C165" s="373"/>
       <c r="D165" s="165" t="s">
         <v>11</v>
       </c>
@@ -74652,7 +74666,7 @@
       <c r="B166" s="197" t="s">
         <v>706</v>
       </c>
-      <c r="C166" s="364"/>
+      <c r="C166" s="373"/>
       <c r="D166" s="165" t="s">
         <v>11</v>
       </c>
@@ -74664,7 +74678,7 @@
       <c r="B167" s="197" t="s">
         <v>707</v>
       </c>
-      <c r="C167" s="364"/>
+      <c r="C167" s="373"/>
       <c r="D167" s="165" t="s">
         <v>454</v>
       </c>
@@ -74676,7 +74690,7 @@
       <c r="B168" s="197" t="s">
         <v>708</v>
       </c>
-      <c r="C168" s="364"/>
+      <c r="C168" s="373"/>
       <c r="D168" s="165" t="s">
         <v>455</v>
       </c>
@@ -74688,7 +74702,7 @@
       <c r="B169" s="197" t="s">
         <v>709</v>
       </c>
-      <c r="C169" s="364"/>
+      <c r="C169" s="373"/>
       <c r="D169" s="165" t="s">
         <v>456</v>
       </c>
@@ -74700,7 +74714,7 @@
       <c r="B170" s="197" t="s">
         <v>710</v>
       </c>
-      <c r="C170" s="364"/>
+      <c r="C170" s="373"/>
       <c r="D170" s="165" t="s">
         <v>11</v>
       </c>
@@ -74712,7 +74726,7 @@
       <c r="B171" s="197" t="s">
         <v>711</v>
       </c>
-      <c r="C171" s="364"/>
+      <c r="C171" s="373"/>
       <c r="D171" s="165" t="s">
         <v>11</v>
       </c>
@@ -74724,7 +74738,7 @@
       <c r="B172" s="197" t="s">
         <v>712</v>
       </c>
-      <c r="C172" s="364"/>
+      <c r="C172" s="373"/>
       <c r="D172" s="165" t="s">
         <v>11</v>
       </c>
@@ -74736,7 +74750,7 @@
       <c r="B173" s="197" t="s">
         <v>713</v>
       </c>
-      <c r="C173" s="364"/>
+      <c r="C173" s="373"/>
       <c r="D173" s="165" t="s">
         <v>457</v>
       </c>
@@ -74748,7 +74762,7 @@
       <c r="B174" s="197" t="s">
         <v>714</v>
       </c>
-      <c r="C174" s="364"/>
+      <c r="C174" s="373"/>
       <c r="D174" s="165" t="s">
         <v>458</v>
       </c>
@@ -74760,7 +74774,7 @@
       <c r="B175" s="197" t="s">
         <v>715</v>
       </c>
-      <c r="C175" s="364"/>
+      <c r="C175" s="373"/>
       <c r="D175" s="165" t="s">
         <v>459</v>
       </c>
@@ -74772,7 +74786,7 @@
       <c r="B176" s="198" t="s">
         <v>729</v>
       </c>
-      <c r="C176" s="365"/>
+      <c r="C176" s="374"/>
       <c r="D176" s="169" t="s">
         <v>460</v>
       </c>
@@ -74794,6 +74808,13 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="14">
+    <mergeCell ref="C163:C176"/>
+    <mergeCell ref="C61:C70"/>
+    <mergeCell ref="C71:C94"/>
+    <mergeCell ref="C95:C98"/>
+    <mergeCell ref="C99:C108"/>
+    <mergeCell ref="C109:C115"/>
+    <mergeCell ref="C116:C162"/>
     <mergeCell ref="C58:C60"/>
     <mergeCell ref="C54:C57"/>
     <mergeCell ref="C2:C11"/>
@@ -74801,13 +74822,6 @@
     <mergeCell ref="C18:C28"/>
     <mergeCell ref="C44:C53"/>
     <mergeCell ref="C29:C43"/>
-    <mergeCell ref="C163:C176"/>
-    <mergeCell ref="C61:C70"/>
-    <mergeCell ref="C71:C94"/>
-    <mergeCell ref="C95:C98"/>
-    <mergeCell ref="C99:C108"/>
-    <mergeCell ref="C109:C115"/>
-    <mergeCell ref="C116:C162"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -74815,26 +74829,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="107e75b3-53cc-4838-92d2-ebc011bd4832">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="888ccf44-0d39-41a2-ab17-f7efb2bf6977" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101004FD8CECCB51EC843BF514AFE68379818" ma:contentTypeVersion="18" ma:contentTypeDescription="Opret et nyt dokument." ma:contentTypeScope="" ma:versionID="eda339f53f012ceb64677667a741b441">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="107e75b3-53cc-4838-92d2-ebc011bd4832" xmlns:ns3="888ccf44-0d39-41a2-ab17-f7efb2bf6977" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="04a86f3db711706e561c315688f1c464" ns2:_="" ns3:_="">
     <xsd:import namespace="107e75b3-53cc-4838-92d2-ebc011bd4832"/>
@@ -75083,10 +75077,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="107e75b3-53cc-4838-92d2-ebc011bd4832">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="888ccf44-0d39-41a2-ab17-f7efb2bf6977" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B21D61-7BBD-4BD3-A9A5-1E8F98F2F686}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F91B7B9-75FF-4624-B506-952B5B54766C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="107e75b3-53cc-4838-92d2-ebc011bd4832"/>
+    <ds:schemaRef ds:uri="888ccf44-0d39-41a2-ab17-f7efb2bf6977"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -75109,20 +75134,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F91B7B9-75FF-4624-B506-952B5B54766C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B21D61-7BBD-4BD3-A9A5-1E8F98F2F686}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="107e75b3-53cc-4838-92d2-ebc011bd4832"/>
-    <ds:schemaRef ds:uri="888ccf44-0d39-41a2-ab17-f7efb2bf6977"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/testcases.xlsx
+++ b/testcases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\energinet.local\endk_funktion\Dynsim\13_Medarbejdermapper\CVL\MTB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F823045A-D44E-42E5-8429-939B5689F20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0766EC9-A7A5-4765-A13C-18FF12E68EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2440" yWindow="14290" windowWidth="29020" windowHeight="17500" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="29" r:id="rId1"/>
@@ -3738,7 +3738,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3881,12 +3881,6 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="72"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -5668,9 +5662,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5752,17 +5743,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6319,16 +6313,16 @@
         <v>322</v>
       </c>
       <c r="G3" s="124"/>
-      <c r="H3" s="384" t="s">
+      <c r="H3" s="383" t="s">
         <v>339</v>
       </c>
-      <c r="I3" s="384"/>
-      <c r="J3" s="384"/>
-      <c r="K3" s="384" t="s">
+      <c r="I3" s="383"/>
+      <c r="J3" s="383"/>
+      <c r="K3" s="383" t="s">
         <v>340</v>
       </c>
-      <c r="L3" s="384"/>
-      <c r="M3" s="385"/>
+      <c r="L3" s="383"/>
+      <c r="M3" s="384"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="249" t="s">
@@ -7196,7 +7190,7 @@
       <c r="B2" s="279" t="s">
         <v>356</v>
       </c>
-      <c r="C2" s="404" t="s">
+      <c r="C2" s="403" t="s">
         <v>794</v>
       </c>
       <c r="D2" s="272" t="s">
@@ -7210,7 +7204,7 @@
       <c r="B3" s="279" t="s">
         <v>357</v>
       </c>
-      <c r="C3" s="404"/>
+      <c r="C3" s="403"/>
       <c r="D3" s="273" t="s">
         <v>795</v>
       </c>
@@ -7222,7 +7216,7 @@
       <c r="B4" s="279" t="s">
         <v>358</v>
       </c>
-      <c r="C4" s="404"/>
+      <c r="C4" s="403"/>
       <c r="D4" s="274" t="s">
         <v>10</v>
       </c>
@@ -7234,7 +7228,7 @@
       <c r="B5" s="279" t="s">
         <v>359</v>
       </c>
-      <c r="C5" s="404"/>
+      <c r="C5" s="403"/>
       <c r="D5" s="274" t="s">
         <v>10</v>
       </c>
@@ -7246,7 +7240,7 @@
       <c r="B6" s="280" t="s">
         <v>360</v>
       </c>
-      <c r="C6" s="405"/>
+      <c r="C6" s="404"/>
       <c r="D6" s="275" t="s">
         <v>10</v>
       </c>
@@ -7258,7 +7252,7 @@
       <c r="B7" s="221" t="s">
         <v>238</v>
       </c>
-      <c r="C7" s="403" t="s">
+      <c r="C7" s="402" t="s">
         <v>796</v>
       </c>
       <c r="D7" s="276" t="s">
@@ -7272,7 +7266,7 @@
       <c r="B8" s="217" t="s">
         <v>239</v>
       </c>
-      <c r="C8" s="404"/>
+      <c r="C8" s="403"/>
       <c r="D8" s="274" t="s">
         <v>10</v>
       </c>
@@ -7284,7 +7278,7 @@
       <c r="B9" s="217" t="s">
         <v>240</v>
       </c>
-      <c r="C9" s="404"/>
+      <c r="C9" s="403"/>
       <c r="D9" s="274" t="s">
         <v>10</v>
       </c>
@@ -7296,7 +7290,7 @@
       <c r="B10" s="217" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="404"/>
+      <c r="C10" s="403"/>
       <c r="D10" s="274" t="s">
         <v>10</v>
       </c>
@@ -7308,7 +7302,7 @@
       <c r="B11" s="217" t="s">
         <v>242</v>
       </c>
-      <c r="C11" s="404"/>
+      <c r="C11" s="403"/>
       <c r="D11" s="274" t="s">
         <v>10</v>
       </c>
@@ -7320,7 +7314,7 @@
       <c r="B12" s="217" t="s">
         <v>243</v>
       </c>
-      <c r="C12" s="404"/>
+      <c r="C12" s="403"/>
       <c r="D12" s="274" t="s">
         <v>10</v>
       </c>
@@ -7332,7 +7326,7 @@
       <c r="B13" s="217" t="s">
         <v>244</v>
       </c>
-      <c r="C13" s="404"/>
+      <c r="C13" s="403"/>
       <c r="D13" s="274" t="s">
         <v>10</v>
       </c>
@@ -7344,7 +7338,7 @@
       <c r="B14" s="217" t="s">
         <v>245</v>
       </c>
-      <c r="C14" s="404"/>
+      <c r="C14" s="403"/>
       <c r="D14" s="274" t="s">
         <v>10</v>
       </c>
@@ -7356,7 +7350,7 @@
       <c r="B15" s="217" t="s">
         <v>246</v>
       </c>
-      <c r="C15" s="404"/>
+      <c r="C15" s="403"/>
       <c r="D15" s="274" t="s">
         <v>10</v>
       </c>
@@ -7368,7 +7362,7 @@
       <c r="B16" s="217" t="s">
         <v>247</v>
       </c>
-      <c r="C16" s="404"/>
+      <c r="C16" s="403"/>
       <c r="D16" s="274" t="s">
         <v>10</v>
       </c>
@@ -7380,7 +7374,7 @@
       <c r="B17" s="217" t="s">
         <v>248</v>
       </c>
-      <c r="C17" s="404"/>
+      <c r="C17" s="403"/>
       <c r="D17" s="274" t="s">
         <v>10</v>
       </c>
@@ -7392,7 +7386,7 @@
       <c r="B18" s="217" t="s">
         <v>249</v>
       </c>
-      <c r="C18" s="404"/>
+      <c r="C18" s="403"/>
       <c r="D18" s="274" t="s">
         <v>10</v>
       </c>
@@ -7404,7 +7398,7 @@
       <c r="B19" s="217" t="s">
         <v>739</v>
       </c>
-      <c r="C19" s="404"/>
+      <c r="C19" s="403"/>
       <c r="D19" s="273" t="s">
         <v>411</v>
       </c>
@@ -7416,7 +7410,7 @@
       <c r="B20" s="217" t="s">
         <v>740</v>
       </c>
-      <c r="C20" s="404"/>
+      <c r="C20" s="403"/>
       <c r="D20" s="273" t="s">
         <v>412</v>
       </c>
@@ -7428,7 +7422,7 @@
       <c r="B21" s="217" t="s">
         <v>741</v>
       </c>
-      <c r="C21" s="404"/>
+      <c r="C21" s="403"/>
       <c r="D21" s="273" t="s">
         <v>413</v>
       </c>
@@ -7440,7 +7434,7 @@
       <c r="B22" s="217" t="s">
         <v>742</v>
       </c>
-      <c r="C22" s="404"/>
+      <c r="C22" s="403"/>
       <c r="D22" s="274" t="s">
         <v>10</v>
       </c>
@@ -7452,7 +7446,7 @@
       <c r="B23" s="217" t="s">
         <v>743</v>
       </c>
-      <c r="C23" s="404"/>
+      <c r="C23" s="403"/>
       <c r="D23" s="274" t="s">
         <v>10</v>
       </c>
@@ -7464,7 +7458,7 @@
       <c r="B24" s="217" t="s">
         <v>744</v>
       </c>
-      <c r="C24" s="404"/>
+      <c r="C24" s="403"/>
       <c r="D24" s="273" t="s">
         <v>798</v>
       </c>
@@ -7476,7 +7470,7 @@
       <c r="B25" s="217" t="s">
         <v>745</v>
       </c>
-      <c r="C25" s="404"/>
+      <c r="C25" s="403"/>
       <c r="D25" s="273" t="s">
         <v>798</v>
       </c>
@@ -7488,7 +7482,7 @@
       <c r="B26" s="217" t="s">
         <v>250</v>
       </c>
-      <c r="C26" s="404"/>
+      <c r="C26" s="403"/>
       <c r="D26" s="273" t="s">
         <v>414</v>
       </c>
@@ -7500,7 +7494,7 @@
       <c r="B27" s="217" t="s">
         <v>251</v>
       </c>
-      <c r="C27" s="404"/>
+      <c r="C27" s="403"/>
       <c r="D27" s="273" t="s">
         <v>415</v>
       </c>
@@ -7512,7 +7506,7 @@
       <c r="B28" s="217" t="s">
         <v>746</v>
       </c>
-      <c r="C28" s="404"/>
+      <c r="C28" s="403"/>
       <c r="D28" s="273" t="s">
         <v>799</v>
       </c>
@@ -7524,7 +7518,7 @@
       <c r="B29" s="218" t="s">
         <v>747</v>
       </c>
-      <c r="C29" s="404"/>
+      <c r="C29" s="403"/>
       <c r="D29" s="273" t="s">
         <v>800</v>
       </c>
@@ -7536,7 +7530,7 @@
       <c r="B30" s="218" t="s">
         <v>748</v>
       </c>
-      <c r="C30" s="404"/>
+      <c r="C30" s="403"/>
       <c r="D30" s="273" t="s">
         <v>801</v>
       </c>
@@ -7548,7 +7542,7 @@
       <c r="B31" s="217" t="s">
         <v>350</v>
       </c>
-      <c r="C31" s="404"/>
+      <c r="C31" s="403"/>
       <c r="D31" s="273" t="s">
         <v>802</v>
       </c>
@@ -7560,7 +7554,7 @@
       <c r="B32" s="217" t="s">
         <v>749</v>
       </c>
-      <c r="C32" s="404"/>
+      <c r="C32" s="403"/>
       <c r="D32" s="273" t="s">
         <v>803</v>
       </c>
@@ -7572,7 +7566,7 @@
       <c r="B33" s="217" t="s">
         <v>750</v>
       </c>
-      <c r="C33" s="404"/>
+      <c r="C33" s="403"/>
       <c r="D33" s="273" t="s">
         <v>804</v>
       </c>
@@ -7584,7 +7578,7 @@
       <c r="B34" s="217" t="s">
         <v>805</v>
       </c>
-      <c r="C34" s="404"/>
+      <c r="C34" s="403"/>
       <c r="D34" s="273" t="s">
         <v>806</v>
       </c>
@@ -7596,7 +7590,7 @@
       <c r="B35" s="217" t="s">
         <v>807</v>
       </c>
-      <c r="C35" s="404"/>
+      <c r="C35" s="403"/>
       <c r="D35" s="273" t="s">
         <v>808</v>
       </c>
@@ -7608,7 +7602,7 @@
       <c r="B36" s="217" t="s">
         <v>833</v>
       </c>
-      <c r="C36" s="404"/>
+      <c r="C36" s="403"/>
       <c r="D36" s="273" t="s">
         <v>809</v>
       </c>
@@ -7620,7 +7614,7 @@
       <c r="B37" s="217" t="s">
         <v>834</v>
       </c>
-      <c r="C37" s="404"/>
+      <c r="C37" s="403"/>
       <c r="D37" s="274" t="s">
         <v>10</v>
       </c>
@@ -7632,7 +7626,7 @@
       <c r="B38" s="217" t="s">
         <v>835</v>
       </c>
-      <c r="C38" s="404"/>
+      <c r="C38" s="403"/>
       <c r="D38" s="274" t="s">
         <v>10</v>
       </c>
@@ -7644,7 +7638,7 @@
       <c r="B39" s="217" t="s">
         <v>836</v>
       </c>
-      <c r="C39" s="404"/>
+      <c r="C39" s="403"/>
       <c r="D39" s="274" t="s">
         <v>10</v>
       </c>
@@ -7656,7 +7650,7 @@
       <c r="B40" s="217" t="s">
         <v>837</v>
       </c>
-      <c r="C40" s="404"/>
+      <c r="C40" s="403"/>
       <c r="D40" s="274" t="s">
         <v>10</v>
       </c>
@@ -7668,7 +7662,7 @@
       <c r="B41" s="217" t="s">
         <v>838</v>
       </c>
-      <c r="C41" s="404"/>
+      <c r="C41" s="403"/>
       <c r="D41" s="274" t="s">
         <v>10</v>
       </c>
@@ -7680,7 +7674,7 @@
       <c r="B42" s="217" t="s">
         <v>839</v>
       </c>
-      <c r="C42" s="404"/>
+      <c r="C42" s="403"/>
       <c r="D42" s="274" t="s">
         <v>10</v>
       </c>
@@ -7692,7 +7686,7 @@
       <c r="B43" s="219" t="s">
         <v>840</v>
       </c>
-      <c r="C43" s="405"/>
+      <c r="C43" s="404"/>
       <c r="D43" s="275" t="s">
         <v>10</v>
       </c>
@@ -7704,7 +7698,7 @@
       <c r="B44" s="282" t="s">
         <v>252</v>
       </c>
-      <c r="C44" s="403" t="s">
+      <c r="C44" s="402" t="s">
         <v>397</v>
       </c>
       <c r="D44" s="273" t="s">
@@ -7718,7 +7712,7 @@
       <c r="B45" s="284" t="s">
         <v>753</v>
       </c>
-      <c r="C45" s="405"/>
+      <c r="C45" s="404"/>
       <c r="D45" s="277" t="s">
         <v>813</v>
       </c>
@@ -7730,7 +7724,7 @@
       <c r="B46" s="286" t="s">
         <v>253</v>
       </c>
-      <c r="C46" s="403" t="s">
+      <c r="C46" s="402" t="s">
         <v>810</v>
       </c>
       <c r="D46" s="273" t="s">
@@ -7744,7 +7738,7 @@
       <c r="B47" s="288" t="s">
         <v>254</v>
       </c>
-      <c r="C47" s="404"/>
+      <c r="C47" s="403"/>
       <c r="D47" s="273" t="s">
         <v>400</v>
       </c>
@@ -7756,7 +7750,7 @@
       <c r="B48" s="288" t="s">
         <v>255</v>
       </c>
-      <c r="C48" s="404"/>
+      <c r="C48" s="403"/>
       <c r="D48" s="273" t="s">
         <v>401</v>
       </c>
@@ -7768,7 +7762,7 @@
       <c r="B49" s="288" t="s">
         <v>256</v>
       </c>
-      <c r="C49" s="404"/>
+      <c r="C49" s="403"/>
       <c r="D49" s="273" t="s">
         <v>402</v>
       </c>
@@ -7780,7 +7774,7 @@
       <c r="B50" s="288" t="s">
         <v>257</v>
       </c>
-      <c r="C50" s="404"/>
+      <c r="C50" s="403"/>
       <c r="D50" s="273" t="s">
         <v>403</v>
       </c>
@@ -7792,7 +7786,7 @@
       <c r="B51" s="288" t="s">
         <v>258</v>
       </c>
-      <c r="C51" s="404"/>
+      <c r="C51" s="403"/>
       <c r="D51" s="273" t="s">
         <v>404</v>
       </c>
@@ -7804,7 +7798,7 @@
       <c r="B52" s="288" t="s">
         <v>754</v>
       </c>
-      <c r="C52" s="404"/>
+      <c r="C52" s="403"/>
       <c r="D52" s="273" t="s">
         <v>428</v>
       </c>
@@ -7816,7 +7810,7 @@
       <c r="B53" s="288" t="s">
         <v>755</v>
       </c>
-      <c r="C53" s="404"/>
+      <c r="C53" s="403"/>
       <c r="D53" s="273" t="s">
         <v>10</v>
       </c>
@@ -7828,7 +7822,7 @@
       <c r="B54" s="288" t="s">
         <v>756</v>
       </c>
-      <c r="C54" s="404"/>
+      <c r="C54" s="403"/>
       <c r="D54" s="273" t="s">
         <v>814</v>
       </c>
@@ -7840,7 +7834,7 @@
       <c r="B55" s="290" t="s">
         <v>757</v>
       </c>
-      <c r="C55" s="405"/>
+      <c r="C55" s="404"/>
       <c r="D55" s="44" t="s">
         <v>10</v>
       </c>
@@ -7852,7 +7846,7 @@
       <c r="B56" s="292" t="s">
         <v>259</v>
       </c>
-      <c r="C56" s="403" t="s">
+      <c r="C56" s="402" t="s">
         <v>107</v>
       </c>
       <c r="D56" s="278" t="s">
@@ -7866,7 +7860,7 @@
       <c r="B57" s="294" t="s">
         <v>260</v>
       </c>
-      <c r="C57" s="404"/>
+      <c r="C57" s="403"/>
       <c r="D57" s="278" t="s">
         <v>816</v>
       </c>
@@ -7878,7 +7872,7 @@
       <c r="B58" s="294" t="s">
         <v>261</v>
       </c>
-      <c r="C58" s="404"/>
+      <c r="C58" s="403"/>
       <c r="D58" s="278" t="s">
         <v>817</v>
       </c>
@@ -7890,7 +7884,7 @@
       <c r="B59" s="294" t="s">
         <v>262</v>
       </c>
-      <c r="C59" s="404"/>
+      <c r="C59" s="403"/>
       <c r="D59" s="278" t="s">
         <v>818</v>
       </c>
@@ -7902,7 +7896,7 @@
       <c r="B60" s="294" t="s">
         <v>793</v>
       </c>
-      <c r="C60" s="404"/>
+      <c r="C60" s="403"/>
       <c r="D60" s="278" t="s">
         <v>819</v>
       </c>
@@ -7914,7 +7908,7 @@
       <c r="B61" s="294" t="s">
         <v>758</v>
       </c>
-      <c r="C61" s="404"/>
+      <c r="C61" s="403"/>
       <c r="D61" s="278" t="s">
         <v>820</v>
       </c>
@@ -7926,7 +7920,7 @@
       <c r="B62" s="294" t="s">
         <v>263</v>
       </c>
-      <c r="C62" s="404"/>
+      <c r="C62" s="403"/>
       <c r="D62" s="278" t="s">
         <v>821</v>
       </c>
@@ -7938,7 +7932,7 @@
       <c r="B63" s="296" t="s">
         <v>264</v>
       </c>
-      <c r="C63" s="405"/>
+      <c r="C63" s="404"/>
       <c r="D63" s="44" t="s">
         <v>822</v>
       </c>
@@ -7950,7 +7944,7 @@
       <c r="B64" s="221" t="s">
         <v>265</v>
       </c>
-      <c r="C64" s="403" t="s">
+      <c r="C64" s="402" t="s">
         <v>823</v>
       </c>
       <c r="D64" s="276" t="s">
@@ -7964,7 +7958,7 @@
       <c r="B65" s="217" t="s">
         <v>266</v>
       </c>
-      <c r="C65" s="404"/>
+      <c r="C65" s="403"/>
       <c r="D65" s="273" t="s">
         <v>10</v>
       </c>
@@ -7976,7 +7970,7 @@
       <c r="B66" s="217" t="s">
         <v>267</v>
       </c>
-      <c r="C66" s="404"/>
+      <c r="C66" s="403"/>
       <c r="D66" s="273" t="s">
         <v>10</v>
       </c>
@@ -7988,7 +7982,7 @@
       <c r="B67" s="217" t="s">
         <v>268</v>
       </c>
-      <c r="C67" s="404"/>
+      <c r="C67" s="403"/>
       <c r="D67" s="273" t="s">
         <v>10</v>
       </c>
@@ -8000,7 +7994,7 @@
       <c r="B68" s="217" t="s">
         <v>269</v>
       </c>
-      <c r="C68" s="404"/>
+      <c r="C68" s="403"/>
       <c r="D68" s="273" t="s">
         <v>10</v>
       </c>
@@ -8012,7 +8006,7 @@
       <c r="B69" s="217" t="s">
         <v>759</v>
       </c>
-      <c r="C69" s="404"/>
+      <c r="C69" s="403"/>
       <c r="D69" s="273" t="s">
         <v>10</v>
       </c>
@@ -8024,7 +8018,7 @@
       <c r="B70" s="219" t="s">
         <v>760</v>
       </c>
-      <c r="C70" s="405"/>
+      <c r="C70" s="404"/>
       <c r="D70" s="44" t="s">
         <v>10</v>
       </c>
@@ -8036,7 +8030,7 @@
       <c r="B71" s="282" t="s">
         <v>761</v>
       </c>
-      <c r="C71" s="403" t="s">
+      <c r="C71" s="402" t="s">
         <v>811</v>
       </c>
       <c r="D71" s="271" t="s">
@@ -8050,7 +8044,7 @@
       <c r="B72" s="298" t="s">
         <v>762</v>
       </c>
-      <c r="C72" s="404"/>
+      <c r="C72" s="403"/>
       <c r="D72" s="271" t="s">
         <v>831</v>
       </c>
@@ -8062,7 +8056,7 @@
       <c r="B73" s="298" t="s">
         <v>351</v>
       </c>
-      <c r="C73" s="404"/>
+      <c r="C73" s="403"/>
       <c r="D73" s="139" t="s">
         <v>453</v>
       </c>
@@ -8074,7 +8068,7 @@
       <c r="B74" s="298" t="s">
         <v>763</v>
       </c>
-      <c r="C74" s="404"/>
+      <c r="C74" s="403"/>
       <c r="D74" s="139" t="s">
         <v>454</v>
       </c>
@@ -8086,7 +8080,7 @@
       <c r="B75" s="298" t="s">
         <v>352</v>
       </c>
-      <c r="C75" s="404"/>
+      <c r="C75" s="403"/>
       <c r="D75" s="139" t="s">
         <v>827</v>
       </c>
@@ -8098,7 +8092,7 @@
       <c r="B76" s="298" t="s">
         <v>764</v>
       </c>
-      <c r="C76" s="404"/>
+      <c r="C76" s="403"/>
       <c r="D76" s="139" t="s">
         <v>828</v>
       </c>
@@ -8110,7 +8104,7 @@
       <c r="B77" s="298" t="s">
         <v>765</v>
       </c>
-      <c r="C77" s="404"/>
+      <c r="C77" s="403"/>
       <c r="D77" s="139" t="s">
         <v>830</v>
       </c>
@@ -8122,7 +8116,7 @@
       <c r="B78" s="298" t="s">
         <v>766</v>
       </c>
-      <c r="C78" s="404"/>
+      <c r="C78" s="403"/>
       <c r="D78" s="139" t="s">
         <v>829</v>
       </c>
@@ -8134,7 +8128,7 @@
       <c r="B79" s="298" t="s">
         <v>767</v>
       </c>
-      <c r="C79" s="404"/>
+      <c r="C79" s="403"/>
       <c r="D79" s="278" t="s">
         <v>825</v>
       </c>
@@ -8146,7 +8140,7 @@
       <c r="B80" s="298" t="s">
         <v>768</v>
       </c>
-      <c r="C80" s="404"/>
+      <c r="C80" s="403"/>
       <c r="D80" s="273" t="s">
         <v>10</v>
       </c>
@@ -8158,7 +8152,7 @@
       <c r="B81" s="298" t="s">
         <v>769</v>
       </c>
-      <c r="C81" s="404"/>
+      <c r="C81" s="403"/>
       <c r="D81" s="273" t="s">
         <v>10</v>
       </c>
@@ -8170,7 +8164,7 @@
       <c r="B82" s="284" t="s">
         <v>770</v>
       </c>
-      <c r="C82" s="405"/>
+      <c r="C82" s="404"/>
       <c r="D82" s="44" t="s">
         <v>10</v>
       </c>
@@ -8182,7 +8176,7 @@
       <c r="B83" s="286" t="s">
         <v>771</v>
       </c>
-      <c r="C83" s="403" t="s">
+      <c r="C83" s="402" t="s">
         <v>450</v>
       </c>
       <c r="D83" s="276" t="s">
@@ -8196,7 +8190,7 @@
       <c r="B84" s="288" t="s">
         <v>772</v>
       </c>
-      <c r="C84" s="404"/>
+      <c r="C84" s="403"/>
       <c r="D84" s="273" t="s">
         <v>10</v>
       </c>
@@ -8208,7 +8202,7 @@
       <c r="B85" s="288" t="s">
         <v>773</v>
       </c>
-      <c r="C85" s="404"/>
+      <c r="C85" s="403"/>
       <c r="D85" s="273" t="s">
         <v>10</v>
       </c>
@@ -8220,7 +8214,7 @@
       <c r="B86" s="288" t="s">
         <v>774</v>
       </c>
-      <c r="C86" s="404"/>
+      <c r="C86" s="403"/>
       <c r="D86" s="273" t="s">
         <v>10</v>
       </c>
@@ -8232,7 +8226,7 @@
       <c r="B87" s="290" t="s">
         <v>775</v>
       </c>
-      <c r="C87" s="405"/>
+      <c r="C87" s="404"/>
       <c r="D87" s="44" t="s">
         <v>10</v>
       </c>
@@ -8286,7 +8280,7 @@
       <c r="B2" s="184" t="s">
         <v>270</v>
       </c>
-      <c r="C2" s="403" t="s">
+      <c r="C2" s="402" t="s">
         <v>361</v>
       </c>
       <c r="D2" s="146" t="s">
@@ -8300,7 +8294,7 @@
       <c r="B3" s="307" t="s">
         <v>271</v>
       </c>
-      <c r="C3" s="404"/>
+      <c r="C3" s="403"/>
       <c r="D3" s="271" t="s">
         <v>10</v>
       </c>
@@ -8312,7 +8306,7 @@
       <c r="B4" s="307" t="s">
         <v>272</v>
       </c>
-      <c r="C4" s="404"/>
+      <c r="C4" s="403"/>
       <c r="D4" s="271" t="s">
         <v>10</v>
       </c>
@@ -8324,7 +8318,7 @@
       <c r="B5" s="307" t="s">
         <v>273</v>
       </c>
-      <c r="C5" s="404"/>
+      <c r="C5" s="403"/>
       <c r="D5" s="271" t="s">
         <v>10</v>
       </c>
@@ -8336,7 +8330,7 @@
       <c r="B6" s="307" t="s">
         <v>274</v>
       </c>
-      <c r="C6" s="404"/>
+      <c r="C6" s="403"/>
       <c r="D6" s="271" t="s">
         <v>10</v>
       </c>
@@ -8348,7 +8342,7 @@
       <c r="B7" s="186" t="s">
         <v>275</v>
       </c>
-      <c r="C7" s="405"/>
+      <c r="C7" s="404"/>
       <c r="D7" s="143" t="s">
         <v>10</v>
       </c>
@@ -8374,7 +8368,7 @@
       <c r="B9" s="136" t="s">
         <v>277</v>
       </c>
-      <c r="C9" s="406" t="s">
+      <c r="C9" s="405" t="s">
         <v>466</v>
       </c>
       <c r="D9" s="146" t="s">
@@ -8388,7 +8382,7 @@
       <c r="B10" s="138" t="s">
         <v>278</v>
       </c>
-      <c r="C10" s="407"/>
+      <c r="C10" s="406"/>
       <c r="D10" s="271" t="s">
         <v>468</v>
       </c>
@@ -8400,7 +8394,7 @@
       <c r="B11" s="138" t="s">
         <v>776</v>
       </c>
-      <c r="C11" s="407"/>
+      <c r="C11" s="406"/>
       <c r="D11" s="271" t="s">
         <v>824</v>
       </c>
@@ -8412,7 +8406,7 @@
       <c r="B12" s="138" t="s">
         <v>777</v>
       </c>
-      <c r="C12" s="407"/>
+      <c r="C12" s="406"/>
       <c r="D12" s="271" t="s">
         <v>10</v>
       </c>
@@ -8424,7 +8418,7 @@
       <c r="B13" s="138" t="s">
         <v>778</v>
       </c>
-      <c r="C13" s="407"/>
+      <c r="C13" s="406"/>
       <c r="D13" s="271" t="s">
         <v>10</v>
       </c>
@@ -8436,7 +8430,7 @@
       <c r="B14" s="138" t="s">
         <v>779</v>
       </c>
-      <c r="C14" s="407"/>
+      <c r="C14" s="406"/>
       <c r="D14" s="271" t="s">
         <v>10</v>
       </c>
@@ -8448,7 +8442,7 @@
       <c r="B15" s="138" t="s">
         <v>780</v>
       </c>
-      <c r="C15" s="407"/>
+      <c r="C15" s="406"/>
       <c r="D15" s="271" t="s">
         <v>10</v>
       </c>
@@ -8460,7 +8454,7 @@
       <c r="B16" s="138" t="s">
         <v>781</v>
       </c>
-      <c r="C16" s="407"/>
+      <c r="C16" s="406"/>
       <c r="D16" s="271" t="s">
         <v>10</v>
       </c>
@@ -8472,7 +8466,7 @@
       <c r="B17" s="178" t="s">
         <v>782</v>
       </c>
-      <c r="C17" s="408"/>
+      <c r="C17" s="407"/>
       <c r="D17" s="143" t="s">
         <v>10</v>
       </c>
@@ -8484,7 +8478,7 @@
       <c r="B18" s="176" t="s">
         <v>279</v>
       </c>
-      <c r="C18" s="403" t="s">
+      <c r="C18" s="402" t="s">
         <v>469</v>
       </c>
       <c r="D18" s="146" t="s">
@@ -8498,7 +8492,7 @@
       <c r="B19" s="302" t="s">
         <v>280</v>
       </c>
-      <c r="C19" s="404"/>
+      <c r="C19" s="403"/>
       <c r="D19" s="271" t="s">
         <v>471</v>
       </c>
@@ -8510,7 +8504,7 @@
       <c r="B20" s="177" t="s">
         <v>281</v>
       </c>
-      <c r="C20" s="405"/>
+      <c r="C20" s="404"/>
       <c r="D20" s="143" t="s">
         <v>472</v>
       </c>
@@ -8522,7 +8516,7 @@
       <c r="B21" s="154" t="s">
         <v>282</v>
       </c>
-      <c r="C21" s="406" t="s">
+      <c r="C21" s="405" t="s">
         <v>407</v>
       </c>
       <c r="D21" s="146" t="s">
@@ -8536,7 +8530,7 @@
       <c r="B22" s="155" t="s">
         <v>283</v>
       </c>
-      <c r="C22" s="407"/>
+      <c r="C22" s="406"/>
       <c r="D22" s="271" t="s">
         <v>10</v>
       </c>
@@ -8548,7 +8542,7 @@
       <c r="B23" s="155" t="s">
         <v>284</v>
       </c>
-      <c r="C23" s="407"/>
+      <c r="C23" s="406"/>
       <c r="D23" s="271" t="s">
         <v>10</v>
       </c>
@@ -8560,7 +8554,7 @@
       <c r="B24" s="155" t="s">
         <v>285</v>
       </c>
-      <c r="C24" s="407"/>
+      <c r="C24" s="406"/>
       <c r="D24" s="271" t="s">
         <v>10</v>
       </c>
@@ -8572,7 +8566,7 @@
       <c r="B25" s="155" t="s">
         <v>286</v>
       </c>
-      <c r="C25" s="407"/>
+      <c r="C25" s="406"/>
       <c r="D25" s="271" t="s">
         <v>10</v>
       </c>
@@ -8584,7 +8578,7 @@
       <c r="B26" s="155" t="s">
         <v>287</v>
       </c>
-      <c r="C26" s="407"/>
+      <c r="C26" s="406"/>
       <c r="D26" s="271" t="s">
         <v>10</v>
       </c>
@@ -8596,7 +8590,7 @@
       <c r="B27" s="155" t="s">
         <v>288</v>
       </c>
-      <c r="C27" s="407"/>
+      <c r="C27" s="406"/>
       <c r="D27" s="271" t="s">
         <v>10</v>
       </c>
@@ -8608,7 +8602,7 @@
       <c r="B28" s="155" t="s">
         <v>289</v>
       </c>
-      <c r="C28" s="407"/>
+      <c r="C28" s="406"/>
       <c r="D28" s="271" t="s">
         <v>10</v>
       </c>
@@ -8620,7 +8614,7 @@
       <c r="B29" s="155" t="s">
         <v>290</v>
       </c>
-      <c r="C29" s="407"/>
+      <c r="C29" s="406"/>
       <c r="D29" s="271" t="s">
         <v>10</v>
       </c>
@@ -8632,7 +8626,7 @@
       <c r="B30" s="155" t="s">
         <v>291</v>
       </c>
-      <c r="C30" s="407"/>
+      <c r="C30" s="406"/>
       <c r="D30" s="271" t="s">
         <v>10</v>
       </c>
@@ -8644,7 +8638,7 @@
       <c r="B31" s="155" t="s">
         <v>292</v>
       </c>
-      <c r="C31" s="407"/>
+      <c r="C31" s="406"/>
       <c r="D31" s="271" t="s">
         <v>10</v>
       </c>
@@ -8656,7 +8650,7 @@
       <c r="B32" s="155" t="s">
         <v>293</v>
       </c>
-      <c r="C32" s="407"/>
+      <c r="C32" s="406"/>
       <c r="D32" s="271" t="s">
         <v>10</v>
       </c>
@@ -8668,7 +8662,7 @@
       <c r="B33" s="155" t="s">
         <v>294</v>
       </c>
-      <c r="C33" s="407"/>
+      <c r="C33" s="406"/>
       <c r="D33" s="271" t="s">
         <v>410</v>
       </c>
@@ -8680,7 +8674,7 @@
       <c r="B34" s="155" t="s">
         <v>295</v>
       </c>
-      <c r="C34" s="407"/>
+      <c r="C34" s="406"/>
       <c r="D34" s="271" t="s">
         <v>411</v>
       </c>
@@ -8692,7 +8686,7 @@
       <c r="B35" s="155" t="s">
         <v>296</v>
       </c>
-      <c r="C35" s="407"/>
+      <c r="C35" s="406"/>
       <c r="D35" s="271" t="s">
         <v>412</v>
       </c>
@@ -8704,7 +8698,7 @@
       <c r="B36" s="155" t="s">
         <v>297</v>
       </c>
-      <c r="C36" s="407"/>
+      <c r="C36" s="406"/>
       <c r="D36" s="271" t="s">
         <v>413</v>
       </c>
@@ -8716,7 +8710,7 @@
       <c r="B37" s="155" t="s">
         <v>298</v>
       </c>
-      <c r="C37" s="407"/>
+      <c r="C37" s="406"/>
       <c r="D37" s="271" t="s">
         <v>474</v>
       </c>
@@ -8728,7 +8722,7 @@
       <c r="B38" s="155" t="s">
         <v>299</v>
       </c>
-      <c r="C38" s="407"/>
+      <c r="C38" s="406"/>
       <c r="D38" s="271" t="s">
         <v>474</v>
       </c>
@@ -8740,7 +8734,7 @@
       <c r="B39" s="155" t="s">
         <v>300</v>
       </c>
-      <c r="C39" s="407"/>
+      <c r="C39" s="406"/>
       <c r="D39" s="271" t="s">
         <v>440</v>
       </c>
@@ -8752,7 +8746,7 @@
       <c r="B40" s="155" t="s">
         <v>301</v>
       </c>
-      <c r="C40" s="407"/>
+      <c r="C40" s="406"/>
       <c r="D40" s="271" t="s">
         <v>440</v>
       </c>
@@ -8764,7 +8758,7 @@
       <c r="B41" s="155" t="s">
         <v>302</v>
       </c>
-      <c r="C41" s="407"/>
+      <c r="C41" s="406"/>
       <c r="D41" s="271" t="s">
         <v>414</v>
       </c>
@@ -8776,7 +8770,7 @@
       <c r="B42" s="155" t="s">
         <v>303</v>
       </c>
-      <c r="C42" s="407"/>
+      <c r="C42" s="406"/>
       <c r="D42" s="271" t="s">
         <v>415</v>
       </c>
@@ -8788,7 +8782,7 @@
       <c r="B43" s="155" t="s">
         <v>789</v>
       </c>
-      <c r="C43" s="407"/>
+      <c r="C43" s="406"/>
       <c r="D43" s="271" t="s">
         <v>808</v>
       </c>
@@ -8800,7 +8794,7 @@
       <c r="B44" s="155" t="s">
         <v>790</v>
       </c>
-      <c r="C44" s="407"/>
+      <c r="C44" s="406"/>
       <c r="D44" s="271" t="s">
         <v>809</v>
       </c>
@@ -8812,7 +8806,7 @@
       <c r="B45" s="155" t="s">
         <v>304</v>
       </c>
-      <c r="C45" s="407"/>
+      <c r="C45" s="406"/>
       <c r="D45" s="271" t="s">
         <v>475</v>
       </c>
@@ -8824,7 +8818,7 @@
       <c r="B46" s="155" t="s">
         <v>355</v>
       </c>
-      <c r="C46" s="407"/>
+      <c r="C46" s="406"/>
       <c r="D46" s="271" t="s">
         <v>476</v>
       </c>
@@ -8836,7 +8830,7 @@
       <c r="B47" s="155" t="s">
         <v>787</v>
       </c>
-      <c r="C47" s="407"/>
+      <c r="C47" s="406"/>
       <c r="D47" s="271" t="s">
         <v>800</v>
       </c>
@@ -8848,7 +8842,7 @@
       <c r="B48" s="175" t="s">
         <v>788</v>
       </c>
-      <c r="C48" s="408"/>
+      <c r="C48" s="407"/>
       <c r="D48" s="143" t="s">
         <v>801</v>
       </c>
@@ -8860,7 +8854,7 @@
       <c r="B49" s="176" t="s">
         <v>305</v>
       </c>
-      <c r="C49" s="403" t="s">
+      <c r="C49" s="402" t="s">
         <v>469</v>
       </c>
       <c r="D49" s="146" t="s">
@@ -8874,7 +8868,7 @@
       <c r="B50" s="302" t="s">
         <v>306</v>
       </c>
-      <c r="C50" s="404"/>
+      <c r="C50" s="403"/>
       <c r="D50" s="271" t="s">
         <v>400</v>
       </c>
@@ -8886,7 +8880,7 @@
       <c r="B51" s="302" t="s">
         <v>791</v>
       </c>
-      <c r="C51" s="404"/>
+      <c r="C51" s="403"/>
       <c r="D51" s="271" t="s">
         <v>401</v>
       </c>
@@ -8898,7 +8892,7 @@
       <c r="B52" s="302" t="s">
         <v>792</v>
       </c>
-      <c r="C52" s="404"/>
+      <c r="C52" s="403"/>
       <c r="D52" s="271" t="s">
         <v>402</v>
       </c>
@@ -8910,7 +8904,7 @@
       <c r="B53" s="302" t="s">
         <v>307</v>
       </c>
-      <c r="C53" s="404"/>
+      <c r="C53" s="403"/>
       <c r="D53" s="271" t="s">
         <v>403</v>
       </c>
@@ -8922,7 +8916,7 @@
       <c r="B54" s="302" t="s">
         <v>308</v>
       </c>
-      <c r="C54" s="404"/>
+      <c r="C54" s="403"/>
       <c r="D54" s="271" t="s">
         <v>404</v>
       </c>
@@ -8934,7 +8928,7 @@
       <c r="B55" s="302" t="s">
         <v>336</v>
       </c>
-      <c r="C55" s="404"/>
+      <c r="C55" s="403"/>
       <c r="D55" s="271" t="s">
         <v>832</v>
       </c>
@@ -8946,7 +8940,7 @@
       <c r="B56" s="177" t="s">
         <v>337</v>
       </c>
-      <c r="C56" s="405"/>
+      <c r="C56" s="404"/>
       <c r="D56" s="143" t="s">
         <v>10</v>
       </c>
@@ -8958,7 +8952,7 @@
       <c r="B57" s="180" t="s">
         <v>783</v>
       </c>
-      <c r="C57" s="403" t="s">
+      <c r="C57" s="402" t="s">
         <v>450</v>
       </c>
       <c r="D57" s="146" t="s">
@@ -8972,7 +8966,7 @@
       <c r="B58" s="303" t="s">
         <v>784</v>
       </c>
-      <c r="C58" s="404"/>
+      <c r="C58" s="403"/>
       <c r="D58" s="271" t="s">
         <v>831</v>
       </c>
@@ -8984,7 +8978,7 @@
       <c r="B59" s="303" t="s">
         <v>309</v>
       </c>
-      <c r="C59" s="404"/>
+      <c r="C59" s="403"/>
       <c r="D59" s="271" t="s">
         <v>477</v>
       </c>
@@ -8996,7 +8990,7 @@
       <c r="B60" s="303" t="s">
         <v>310</v>
       </c>
-      <c r="C60" s="404"/>
+      <c r="C60" s="403"/>
       <c r="D60" s="271" t="s">
         <v>10</v>
       </c>
@@ -9008,7 +9002,7 @@
       <c r="B61" s="303" t="s">
         <v>311</v>
       </c>
-      <c r="C61" s="404"/>
+      <c r="C61" s="403"/>
       <c r="D61" s="271" t="s">
         <v>10</v>
       </c>
@@ -9020,7 +9014,7 @@
       <c r="B62" s="303" t="s">
         <v>312</v>
       </c>
-      <c r="C62" s="404"/>
+      <c r="C62" s="403"/>
       <c r="D62" s="271" t="s">
         <v>10</v>
       </c>
@@ -9032,7 +9026,7 @@
       <c r="B63" s="303" t="s">
         <v>328</v>
       </c>
-      <c r="C63" s="404"/>
+      <c r="C63" s="403"/>
       <c r="D63" s="271" t="s">
         <v>453</v>
       </c>
@@ -9044,7 +9038,7 @@
       <c r="B64" s="303" t="s">
         <v>329</v>
       </c>
-      <c r="C64" s="404"/>
+      <c r="C64" s="403"/>
       <c r="D64" s="271" t="s">
         <v>454</v>
       </c>
@@ -9056,7 +9050,7 @@
       <c r="B65" s="303" t="s">
         <v>785</v>
       </c>
-      <c r="C65" s="404"/>
+      <c r="C65" s="403"/>
       <c r="D65" s="271" t="s">
         <v>827</v>
       </c>
@@ -9068,7 +9062,7 @@
       <c r="B66" s="303" t="s">
         <v>786</v>
       </c>
-      <c r="C66" s="404"/>
+      <c r="C66" s="403"/>
       <c r="D66" s="271" t="s">
         <v>828</v>
       </c>
@@ -9080,7 +9074,7 @@
       <c r="B67" s="303" t="s">
         <v>353</v>
       </c>
-      <c r="C67" s="404"/>
+      <c r="C67" s="403"/>
       <c r="D67" s="271" t="s">
         <v>462</v>
       </c>
@@ -9092,7 +9086,7 @@
       <c r="B68" s="303" t="s">
         <v>354</v>
       </c>
-      <c r="C68" s="404"/>
+      <c r="C68" s="403"/>
       <c r="D68" s="271" t="s">
         <v>463</v>
       </c>
@@ -9104,7 +9098,7 @@
       <c r="B69" s="303" t="s">
         <v>335</v>
       </c>
-      <c r="C69" s="404"/>
+      <c r="C69" s="403"/>
       <c r="D69" s="271" t="s">
         <v>455</v>
       </c>
@@ -9116,7 +9110,7 @@
       <c r="B70" s="303" t="s">
         <v>331</v>
       </c>
-      <c r="C70" s="404"/>
+      <c r="C70" s="403"/>
       <c r="D70" s="271" t="s">
         <v>10</v>
       </c>
@@ -9128,7 +9122,7 @@
       <c r="B71" s="303" t="s">
         <v>332</v>
       </c>
-      <c r="C71" s="404"/>
+      <c r="C71" s="403"/>
       <c r="D71" s="271" t="s">
         <v>10</v>
       </c>
@@ -9140,7 +9134,7 @@
       <c r="B72" s="303" t="s">
         <v>334</v>
       </c>
-      <c r="C72" s="404"/>
+      <c r="C72" s="403"/>
       <c r="D72" s="271" t="s">
         <v>10</v>
       </c>
@@ -9152,7 +9146,7 @@
       <c r="B73" s="303" t="s">
         <v>333</v>
       </c>
-      <c r="C73" s="404"/>
+      <c r="C73" s="403"/>
       <c r="D73" s="271" t="s">
         <v>10</v>
       </c>
@@ -9164,7 +9158,7 @@
       <c r="B74" s="303" t="s">
         <v>313</v>
       </c>
-      <c r="C74" s="404"/>
+      <c r="C74" s="403"/>
       <c r="D74" s="271" t="s">
         <v>456</v>
       </c>
@@ -9176,7 +9170,7 @@
       <c r="B75" s="303" t="s">
         <v>314</v>
       </c>
-      <c r="C75" s="404"/>
+      <c r="C75" s="403"/>
       <c r="D75" s="271" t="s">
         <v>457</v>
       </c>
@@ -9188,7 +9182,7 @@
       <c r="B76" s="303" t="s">
         <v>315</v>
       </c>
-      <c r="C76" s="404"/>
+      <c r="C76" s="403"/>
       <c r="D76" s="271" t="s">
         <v>458</v>
       </c>
@@ -9200,7 +9194,7 @@
       <c r="B77" s="182" t="s">
         <v>316</v>
       </c>
-      <c r="C77" s="405"/>
+      <c r="C77" s="404"/>
       <c r="D77" s="143" t="s">
         <v>459</v>
       </c>
@@ -9262,1002 +9256,1002 @@
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="334"/>
       <c r="B2" s="334"/>
-      <c r="C2" s="409" t="s">
+      <c r="C2" s="410" t="s">
         <v>848</v>
       </c>
-      <c r="D2" s="411" t="s">
+      <c r="D2" s="408" t="s">
         <v>912</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="334"/>
       <c r="B3" s="334"/>
-      <c r="C3" s="409"/>
-      <c r="D3" s="411"/>
+      <c r="C3" s="410"/>
+      <c r="D3" s="408"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="334"/>
       <c r="B4" s="334"/>
-      <c r="C4" s="409"/>
-      <c r="D4" s="411"/>
+      <c r="C4" s="410"/>
+      <c r="D4" s="408"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="334"/>
       <c r="B5" s="334"/>
-      <c r="C5" s="409"/>
-      <c r="D5" s="411"/>
+      <c r="C5" s="410"/>
+      <c r="D5" s="408"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="334"/>
       <c r="B6" s="334"/>
-      <c r="C6" s="409"/>
-      <c r="D6" s="411"/>
+      <c r="C6" s="410"/>
+      <c r="D6" s="408"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="334"/>
       <c r="B7" s="334"/>
-      <c r="C7" s="409"/>
-      <c r="D7" s="411"/>
+      <c r="C7" s="410"/>
+      <c r="D7" s="408"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="334"/>
       <c r="B8" s="334"/>
-      <c r="C8" s="409"/>
-      <c r="D8" s="411"/>
+      <c r="C8" s="410"/>
+      <c r="D8" s="408"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="334"/>
       <c r="B9" s="334"/>
-      <c r="C9" s="409"/>
-      <c r="D9" s="411"/>
+      <c r="C9" s="410"/>
+      <c r="D9" s="408"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="334"/>
       <c r="B10" s="334"/>
-      <c r="C10" s="409"/>
-      <c r="D10" s="411"/>
+      <c r="C10" s="410"/>
+      <c r="D10" s="408"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="334"/>
       <c r="B11" s="334"/>
-      <c r="C11" s="409"/>
-      <c r="D11" s="411"/>
+      <c r="C11" s="410"/>
+      <c r="D11" s="408"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="334"/>
       <c r="B12" s="334"/>
-      <c r="C12" s="409"/>
-      <c r="D12" s="411"/>
+      <c r="C12" s="410"/>
+      <c r="D12" s="408"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="334"/>
       <c r="B13" s="334"/>
-      <c r="C13" s="409"/>
-      <c r="D13" s="411"/>
+      <c r="C13" s="410"/>
+      <c r="D13" s="408"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="334"/>
       <c r="B14" s="334"/>
-      <c r="C14" s="409"/>
-      <c r="D14" s="411"/>
+      <c r="C14" s="410"/>
+      <c r="D14" s="408"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="334"/>
       <c r="B15" s="334"/>
-      <c r="C15" s="409"/>
-      <c r="D15" s="411"/>
+      <c r="C15" s="410"/>
+      <c r="D15" s="408"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="334"/>
       <c r="B16" s="334"/>
-      <c r="C16" s="409"/>
-      <c r="D16" s="411"/>
+      <c r="C16" s="410"/>
+      <c r="D16" s="408"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="316"/>
       <c r="B17" s="316"/>
-      <c r="C17" s="410"/>
-      <c r="D17" s="412"/>
+      <c r="C17" s="411"/>
+      <c r="D17" s="409"/>
     </row>
     <row r="18" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="336"/>
       <c r="B18" s="336"/>
-      <c r="C18" s="404" t="s">
+      <c r="C18" s="403" t="s">
         <v>361</v>
       </c>
-      <c r="D18" s="411" t="s">
+      <c r="D18" s="408" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="336"/>
       <c r="B19" s="336"/>
-      <c r="C19" s="404"/>
-      <c r="D19" s="411"/>
+      <c r="C19" s="403"/>
+      <c r="D19" s="408"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="336"/>
       <c r="B20" s="336"/>
-      <c r="C20" s="404"/>
-      <c r="D20" s="411"/>
+      <c r="C20" s="403"/>
+      <c r="D20" s="408"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="336"/>
       <c r="B21" s="336"/>
-      <c r="C21" s="404"/>
-      <c r="D21" s="411"/>
+      <c r="C21" s="403"/>
+      <c r="D21" s="408"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="336"/>
       <c r="B22" s="336"/>
-      <c r="C22" s="404"/>
-      <c r="D22" s="411"/>
+      <c r="C22" s="403"/>
+      <c r="D22" s="408"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="336"/>
       <c r="B23" s="336"/>
-      <c r="C23" s="404"/>
-      <c r="D23" s="411"/>
+      <c r="C23" s="403"/>
+      <c r="D23" s="408"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="336"/>
       <c r="B24" s="336"/>
-      <c r="C24" s="404"/>
-      <c r="D24" s="411"/>
+      <c r="C24" s="403"/>
+      <c r="D24" s="408"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="336"/>
       <c r="B25" s="336"/>
-      <c r="C25" s="404"/>
-      <c r="D25" s="411"/>
+      <c r="C25" s="403"/>
+      <c r="D25" s="408"/>
     </row>
     <row r="26" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="336"/>
       <c r="B26" s="336"/>
-      <c r="C26" s="404"/>
-      <c r="D26" s="411"/>
+      <c r="C26" s="403"/>
+      <c r="D26" s="408"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="336"/>
       <c r="B27" s="336"/>
-      <c r="C27" s="404"/>
-      <c r="D27" s="411"/>
+      <c r="C27" s="403"/>
+      <c r="D27" s="408"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="336"/>
       <c r="B28" s="336"/>
-      <c r="C28" s="404"/>
-      <c r="D28" s="411"/>
+      <c r="C28" s="403"/>
+      <c r="D28" s="408"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="336"/>
       <c r="B29" s="336"/>
-      <c r="C29" s="404"/>
-      <c r="D29" s="411"/>
+      <c r="C29" s="403"/>
+      <c r="D29" s="408"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="336"/>
       <c r="B30" s="336"/>
-      <c r="C30" s="404"/>
-      <c r="D30" s="411"/>
+      <c r="C30" s="403"/>
+      <c r="D30" s="408"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="336"/>
       <c r="B31" s="336"/>
-      <c r="C31" s="404"/>
-      <c r="D31" s="411"/>
+      <c r="C31" s="403"/>
+      <c r="D31" s="408"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="336"/>
       <c r="B32" s="336"/>
-      <c r="C32" s="404"/>
-      <c r="D32" s="411"/>
+      <c r="C32" s="403"/>
+      <c r="D32" s="408"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="336"/>
       <c r="B33" s="336"/>
-      <c r="C33" s="404"/>
-      <c r="D33" s="411"/>
+      <c r="C33" s="403"/>
+      <c r="D33" s="408"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="336"/>
       <c r="B34" s="336"/>
-      <c r="C34" s="404"/>
-      <c r="D34" s="411"/>
+      <c r="C34" s="403"/>
+      <c r="D34" s="408"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="336"/>
       <c r="B35" s="336"/>
-      <c r="C35" s="404"/>
-      <c r="D35" s="411"/>
+      <c r="C35" s="403"/>
+      <c r="D35" s="408"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="336"/>
       <c r="B36" s="336"/>
-      <c r="C36" s="404"/>
-      <c r="D36" s="411"/>
+      <c r="C36" s="403"/>
+      <c r="D36" s="408"/>
     </row>
     <row r="37" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="317"/>
       <c r="B37" s="317"/>
-      <c r="C37" s="405"/>
-      <c r="D37" s="412"/>
+      <c r="C37" s="404"/>
+      <c r="D37" s="409"/>
     </row>
     <row r="38" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="335"/>
       <c r="B38" s="335"/>
-      <c r="C38" s="404" t="s">
+      <c r="C38" s="403" t="s">
         <v>850</v>
       </c>
-      <c r="D38" s="411" t="s">
+      <c r="D38" s="408" t="s">
         <v>851</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="335"/>
       <c r="B39" s="335"/>
-      <c r="C39" s="404"/>
-      <c r="D39" s="411"/>
+      <c r="C39" s="403"/>
+      <c r="D39" s="408"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="335"/>
       <c r="B40" s="335"/>
-      <c r="C40" s="404"/>
-      <c r="D40" s="411"/>
+      <c r="C40" s="403"/>
+      <c r="D40" s="408"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="335"/>
       <c r="B41" s="335"/>
-      <c r="C41" s="404"/>
-      <c r="D41" s="411"/>
+      <c r="C41" s="403"/>
+      <c r="D41" s="408"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="335"/>
       <c r="B42" s="335"/>
-      <c r="C42" s="404"/>
-      <c r="D42" s="411"/>
+      <c r="C42" s="403"/>
+      <c r="D42" s="408"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="335"/>
       <c r="B43" s="335"/>
-      <c r="C43" s="404"/>
-      <c r="D43" s="411"/>
+      <c r="C43" s="403"/>
+      <c r="D43" s="408"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="335"/>
       <c r="B44" s="335"/>
-      <c r="C44" s="404"/>
-      <c r="D44" s="411"/>
+      <c r="C44" s="403"/>
+      <c r="D44" s="408"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="335"/>
       <c r="B45" s="335"/>
-      <c r="C45" s="404"/>
-      <c r="D45" s="411"/>
+      <c r="C45" s="403"/>
+      <c r="D45" s="408"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="335"/>
       <c r="B46" s="335"/>
-      <c r="C46" s="404"/>
-      <c r="D46" s="411"/>
+      <c r="C46" s="403"/>
+      <c r="D46" s="408"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="335"/>
       <c r="B47" s="335"/>
-      <c r="C47" s="404"/>
-      <c r="D47" s="411"/>
+      <c r="C47" s="403"/>
+      <c r="D47" s="408"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="335"/>
       <c r="B48" s="335"/>
-      <c r="C48" s="404"/>
-      <c r="D48" s="411"/>
+      <c r="C48" s="403"/>
+      <c r="D48" s="408"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="335"/>
       <c r="B49" s="335"/>
-      <c r="C49" s="404"/>
-      <c r="D49" s="411"/>
+      <c r="C49" s="403"/>
+      <c r="D49" s="408"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="335"/>
       <c r="B50" s="335"/>
-      <c r="C50" s="404"/>
-      <c r="D50" s="411"/>
+      <c r="C50" s="403"/>
+      <c r="D50" s="408"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="335"/>
       <c r="B51" s="335"/>
-      <c r="C51" s="404"/>
-      <c r="D51" s="411"/>
+      <c r="C51" s="403"/>
+      <c r="D51" s="408"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="335"/>
       <c r="B52" s="335"/>
-      <c r="C52" s="404"/>
-      <c r="D52" s="411"/>
+      <c r="C52" s="403"/>
+      <c r="D52" s="408"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="335"/>
       <c r="B53" s="335"/>
-      <c r="C53" s="404"/>
-      <c r="D53" s="411"/>
+      <c r="C53" s="403"/>
+      <c r="D53" s="408"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="335"/>
       <c r="B54" s="335"/>
-      <c r="C54" s="404"/>
-      <c r="D54" s="411"/>
+      <c r="C54" s="403"/>
+      <c r="D54" s="408"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="335"/>
       <c r="B55" s="335"/>
-      <c r="C55" s="404"/>
-      <c r="D55" s="411"/>
+      <c r="C55" s="403"/>
+      <c r="D55" s="408"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="335"/>
       <c r="B56" s="335"/>
-      <c r="C56" s="404"/>
-      <c r="D56" s="411"/>
+      <c r="C56" s="403"/>
+      <c r="D56" s="408"/>
     </row>
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="318"/>
       <c r="B57" s="318"/>
-      <c r="C57" s="405"/>
-      <c r="D57" s="412"/>
+      <c r="C57" s="404"/>
+      <c r="D57" s="409"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="337"/>
       <c r="B58" s="337"/>
-      <c r="C58" s="404" t="s">
+      <c r="C58" s="403" t="s">
         <v>852</v>
       </c>
-      <c r="D58" s="411" t="s">
+      <c r="D58" s="408" t="s">
         <v>853</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="337"/>
       <c r="B59" s="337"/>
-      <c r="C59" s="404"/>
-      <c r="D59" s="411"/>
+      <c r="C59" s="403"/>
+      <c r="D59" s="408"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="337"/>
       <c r="B60" s="337"/>
-      <c r="C60" s="404"/>
-      <c r="D60" s="411"/>
+      <c r="C60" s="403"/>
+      <c r="D60" s="408"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="337"/>
       <c r="B61" s="337"/>
-      <c r="C61" s="404"/>
-      <c r="D61" s="411"/>
+      <c r="C61" s="403"/>
+      <c r="D61" s="408"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="337"/>
       <c r="B62" s="337"/>
-      <c r="C62" s="404"/>
-      <c r="D62" s="411"/>
+      <c r="C62" s="403"/>
+      <c r="D62" s="408"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="337"/>
       <c r="B63" s="337"/>
-      <c r="C63" s="404"/>
-      <c r="D63" s="411"/>
+      <c r="C63" s="403"/>
+      <c r="D63" s="408"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="337"/>
       <c r="B64" s="337"/>
-      <c r="C64" s="404"/>
-      <c r="D64" s="411"/>
+      <c r="C64" s="403"/>
+      <c r="D64" s="408"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="337"/>
       <c r="B65" s="337"/>
-      <c r="C65" s="404"/>
-      <c r="D65" s="411"/>
+      <c r="C65" s="403"/>
+      <c r="D65" s="408"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="337"/>
       <c r="B66" s="337"/>
-      <c r="C66" s="404"/>
-      <c r="D66" s="411"/>
+      <c r="C66" s="403"/>
+      <c r="D66" s="408"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="337"/>
       <c r="B67" s="337"/>
-      <c r="C67" s="404"/>
-      <c r="D67" s="411"/>
+      <c r="C67" s="403"/>
+      <c r="D67" s="408"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="337"/>
       <c r="B68" s="337"/>
-      <c r="C68" s="404"/>
-      <c r="D68" s="411"/>
+      <c r="C68" s="403"/>
+      <c r="D68" s="408"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="337"/>
       <c r="B69" s="337"/>
-      <c r="C69" s="404"/>
-      <c r="D69" s="411"/>
+      <c r="C69" s="403"/>
+      <c r="D69" s="408"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="337"/>
       <c r="B70" s="337"/>
-      <c r="C70" s="404"/>
-      <c r="D70" s="411"/>
+      <c r="C70" s="403"/>
+      <c r="D70" s="408"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="337"/>
       <c r="B71" s="337"/>
-      <c r="C71" s="404"/>
-      <c r="D71" s="411"/>
+      <c r="C71" s="403"/>
+      <c r="D71" s="408"/>
     </row>
     <row r="72" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="319"/>
       <c r="B72" s="319"/>
-      <c r="C72" s="405"/>
-      <c r="D72" s="412"/>
+      <c r="C72" s="404"/>
+      <c r="D72" s="409"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="339"/>
       <c r="B73" s="339"/>
-      <c r="C73" s="404" t="s">
+      <c r="C73" s="403" t="s">
         <v>854</v>
       </c>
-      <c r="D73" s="411" t="s">
+      <c r="D73" s="408" t="s">
         <v>855</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="339"/>
       <c r="B74" s="339"/>
-      <c r="C74" s="404"/>
-      <c r="D74" s="411"/>
+      <c r="C74" s="403"/>
+      <c r="D74" s="408"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="339"/>
       <c r="B75" s="339"/>
-      <c r="C75" s="404"/>
-      <c r="D75" s="411"/>
+      <c r="C75" s="403"/>
+      <c r="D75" s="408"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="339"/>
       <c r="B76" s="339"/>
-      <c r="C76" s="404"/>
-      <c r="D76" s="411"/>
+      <c r="C76" s="403"/>
+      <c r="D76" s="408"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="339"/>
       <c r="B77" s="339"/>
-      <c r="C77" s="404"/>
-      <c r="D77" s="411"/>
+      <c r="C77" s="403"/>
+      <c r="D77" s="408"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="339"/>
       <c r="B78" s="339"/>
-      <c r="C78" s="404"/>
-      <c r="D78" s="411"/>
+      <c r="C78" s="403"/>
+      <c r="D78" s="408"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="339"/>
       <c r="B79" s="339"/>
-      <c r="C79" s="404"/>
-      <c r="D79" s="411"/>
+      <c r="C79" s="403"/>
+      <c r="D79" s="408"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="339"/>
       <c r="B80" s="339"/>
-      <c r="C80" s="404"/>
-      <c r="D80" s="411"/>
+      <c r="C80" s="403"/>
+      <c r="D80" s="408"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="339"/>
       <c r="B81" s="339"/>
-      <c r="C81" s="404"/>
-      <c r="D81" s="411"/>
+      <c r="C81" s="403"/>
+      <c r="D81" s="408"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="339"/>
       <c r="B82" s="339"/>
-      <c r="C82" s="404"/>
-      <c r="D82" s="411"/>
+      <c r="C82" s="403"/>
+      <c r="D82" s="408"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="339"/>
       <c r="B83" s="339"/>
-      <c r="C83" s="404"/>
-      <c r="D83" s="411"/>
+      <c r="C83" s="403"/>
+      <c r="D83" s="408"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="339"/>
       <c r="B84" s="339"/>
-      <c r="C84" s="404"/>
-      <c r="D84" s="411"/>
+      <c r="C84" s="403"/>
+      <c r="D84" s="408"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="339"/>
       <c r="B85" s="339"/>
-      <c r="C85" s="404"/>
-      <c r="D85" s="411"/>
+      <c r="C85" s="403"/>
+      <c r="D85" s="408"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="339"/>
       <c r="B86" s="339"/>
-      <c r="C86" s="404"/>
-      <c r="D86" s="411"/>
+      <c r="C86" s="403"/>
+      <c r="D86" s="408"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="339"/>
       <c r="B87" s="339"/>
-      <c r="C87" s="404"/>
-      <c r="D87" s="411"/>
+      <c r="C87" s="403"/>
+      <c r="D87" s="408"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="339"/>
       <c r="B88" s="339"/>
-      <c r="C88" s="404"/>
-      <c r="D88" s="411"/>
+      <c r="C88" s="403"/>
+      <c r="D88" s="408"/>
     </row>
     <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="320"/>
       <c r="B89" s="320"/>
-      <c r="C89" s="405"/>
-      <c r="D89" s="412"/>
+      <c r="C89" s="404"/>
+      <c r="D89" s="409"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="338"/>
       <c r="B90" s="338"/>
-      <c r="C90" s="404" t="s">
+      <c r="C90" s="403" t="s">
         <v>856</v>
       </c>
-      <c r="D90" s="411" t="s">
+      <c r="D90" s="408" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="338"/>
       <c r="B91" s="338"/>
-      <c r="C91" s="404"/>
-      <c r="D91" s="411"/>
+      <c r="C91" s="403"/>
+      <c r="D91" s="408"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="338"/>
       <c r="B92" s="338"/>
-      <c r="C92" s="404"/>
-      <c r="D92" s="411"/>
+      <c r="C92" s="403"/>
+      <c r="D92" s="408"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="338"/>
       <c r="B93" s="338"/>
-      <c r="C93" s="404"/>
-      <c r="D93" s="411"/>
+      <c r="C93" s="403"/>
+      <c r="D93" s="408"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="338"/>
       <c r="B94" s="338"/>
-      <c r="C94" s="404"/>
-      <c r="D94" s="411"/>
+      <c r="C94" s="403"/>
+      <c r="D94" s="408"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="338"/>
       <c r="B95" s="338"/>
-      <c r="C95" s="404"/>
-      <c r="D95" s="411"/>
+      <c r="C95" s="403"/>
+      <c r="D95" s="408"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="338"/>
       <c r="B96" s="338"/>
-      <c r="C96" s="404"/>
-      <c r="D96" s="411"/>
+      <c r="C96" s="403"/>
+      <c r="D96" s="408"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="338"/>
       <c r="B97" s="338"/>
-      <c r="C97" s="404"/>
-      <c r="D97" s="411"/>
+      <c r="C97" s="403"/>
+      <c r="D97" s="408"/>
     </row>
     <row r="98" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="321"/>
       <c r="B98" s="321"/>
-      <c r="C98" s="405"/>
-      <c r="D98" s="412"/>
+      <c r="C98" s="404"/>
+      <c r="D98" s="409"/>
     </row>
     <row r="99" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="340"/>
       <c r="B99" s="340"/>
-      <c r="C99" s="407" t="s">
+      <c r="C99" s="406" t="s">
         <v>858</v>
       </c>
-      <c r="D99" s="411" t="s">
+      <c r="D99" s="408" t="s">
         <v>859</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="340"/>
       <c r="B100" s="340"/>
-      <c r="C100" s="407"/>
-      <c r="D100" s="411"/>
+      <c r="C100" s="406"/>
+      <c r="D100" s="408"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="340"/>
       <c r="B101" s="340"/>
-      <c r="C101" s="407"/>
-      <c r="D101" s="411"/>
+      <c r="C101" s="406"/>
+      <c r="D101" s="408"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="340"/>
       <c r="B102" s="340"/>
-      <c r="C102" s="407"/>
-      <c r="D102" s="411"/>
+      <c r="C102" s="406"/>
+      <c r="D102" s="408"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="340"/>
       <c r="B103" s="340"/>
-      <c r="C103" s="407"/>
-      <c r="D103" s="411"/>
+      <c r="C103" s="406"/>
+      <c r="D103" s="408"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="340"/>
       <c r="B104" s="340"/>
-      <c r="C104" s="407"/>
-      <c r="D104" s="411"/>
+      <c r="C104" s="406"/>
+      <c r="D104" s="408"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="340"/>
       <c r="B105" s="340"/>
-      <c r="C105" s="407"/>
-      <c r="D105" s="411"/>
+      <c r="C105" s="406"/>
+      <c r="D105" s="408"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="340"/>
       <c r="B106" s="340"/>
-      <c r="C106" s="407"/>
-      <c r="D106" s="411"/>
+      <c r="C106" s="406"/>
+      <c r="D106" s="408"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="340"/>
       <c r="B107" s="340"/>
-      <c r="C107" s="407"/>
-      <c r="D107" s="411"/>
+      <c r="C107" s="406"/>
+      <c r="D107" s="408"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="340"/>
       <c r="B108" s="340"/>
-      <c r="C108" s="407"/>
-      <c r="D108" s="411"/>
+      <c r="C108" s="406"/>
+      <c r="D108" s="408"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="340"/>
       <c r="B109" s="340"/>
-      <c r="C109" s="407"/>
-      <c r="D109" s="411"/>
+      <c r="C109" s="406"/>
+      <c r="D109" s="408"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="340"/>
       <c r="B110" s="340"/>
-      <c r="C110" s="407"/>
-      <c r="D110" s="411"/>
+      <c r="C110" s="406"/>
+      <c r="D110" s="408"/>
     </row>
     <row r="111" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="322"/>
       <c r="B111" s="322"/>
-      <c r="C111" s="408"/>
-      <c r="D111" s="412"/>
+      <c r="C111" s="407"/>
+      <c r="D111" s="409"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="336"/>
       <c r="B112" s="336"/>
-      <c r="C112" s="404" t="s">
+      <c r="C112" s="403" t="s">
         <v>860</v>
       </c>
-      <c r="D112" s="411" t="s">
+      <c r="D112" s="408" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="336"/>
       <c r="B113" s="336"/>
-      <c r="C113" s="404"/>
-      <c r="D113" s="411"/>
+      <c r="C113" s="403"/>
+      <c r="D113" s="408"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="336"/>
       <c r="B114" s="336"/>
-      <c r="C114" s="404"/>
-      <c r="D114" s="411"/>
+      <c r="C114" s="403"/>
+      <c r="D114" s="408"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="336"/>
       <c r="B115" s="336"/>
-      <c r="C115" s="404"/>
-      <c r="D115" s="411"/>
+      <c r="C115" s="403"/>
+      <c r="D115" s="408"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="336"/>
       <c r="B116" s="336"/>
-      <c r="C116" s="404"/>
-      <c r="D116" s="411"/>
+      <c r="C116" s="403"/>
+      <c r="D116" s="408"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="336"/>
       <c r="B117" s="336"/>
-      <c r="C117" s="404"/>
-      <c r="D117" s="411"/>
+      <c r="C117" s="403"/>
+      <c r="D117" s="408"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="336"/>
       <c r="B118" s="336"/>
-      <c r="C118" s="404"/>
-      <c r="D118" s="411"/>
+      <c r="C118" s="403"/>
+      <c r="D118" s="408"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="336"/>
       <c r="B119" s="336"/>
-      <c r="C119" s="404"/>
-      <c r="D119" s="411"/>
+      <c r="C119" s="403"/>
+      <c r="D119" s="408"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="336"/>
       <c r="B120" s="336"/>
-      <c r="C120" s="404"/>
-      <c r="D120" s="411"/>
+      <c r="C120" s="403"/>
+      <c r="D120" s="408"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="336"/>
       <c r="B121" s="336"/>
-      <c r="C121" s="404"/>
-      <c r="D121" s="411"/>
+      <c r="C121" s="403"/>
+      <c r="D121" s="408"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="336"/>
       <c r="B122" s="336"/>
-      <c r="C122" s="404"/>
-      <c r="D122" s="411"/>
+      <c r="C122" s="403"/>
+      <c r="D122" s="408"/>
     </row>
     <row r="123" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="317"/>
       <c r="B123" s="317"/>
-      <c r="C123" s="405"/>
-      <c r="D123" s="412"/>
+      <c r="C123" s="404"/>
+      <c r="D123" s="409"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="335"/>
       <c r="B124" s="335"/>
-      <c r="C124" s="404" t="s">
+      <c r="C124" s="403" t="s">
         <v>862</v>
       </c>
-      <c r="D124" s="411" t="s">
+      <c r="D124" s="408" t="s">
         <v>863</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="335"/>
       <c r="B125" s="335"/>
-      <c r="C125" s="404"/>
-      <c r="D125" s="411"/>
+      <c r="C125" s="403"/>
+      <c r="D125" s="408"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="335"/>
       <c r="B126" s="335"/>
-      <c r="C126" s="404"/>
-      <c r="D126" s="411"/>
+      <c r="C126" s="403"/>
+      <c r="D126" s="408"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="335"/>
       <c r="B127" s="335"/>
-      <c r="C127" s="404"/>
-      <c r="D127" s="411"/>
+      <c r="C127" s="403"/>
+      <c r="D127" s="408"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="335"/>
       <c r="B128" s="335"/>
-      <c r="C128" s="404"/>
-      <c r="D128" s="411"/>
+      <c r="C128" s="403"/>
+      <c r="D128" s="408"/>
     </row>
     <row r="129" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="318"/>
       <c r="B129" s="318"/>
-      <c r="C129" s="405"/>
-      <c r="D129" s="412"/>
+      <c r="C129" s="404"/>
+      <c r="D129" s="409"/>
     </row>
     <row r="130" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="33"/>
       <c r="B130" s="33"/>
-      <c r="C130" s="404" t="s">
+      <c r="C130" s="403" t="s">
         <v>864</v>
       </c>
-      <c r="D130" s="411" t="s">
+      <c r="D130" s="408" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="33"/>
       <c r="B131" s="33"/>
-      <c r="C131" s="404"/>
-      <c r="D131" s="411"/>
+      <c r="C131" s="403"/>
+      <c r="D131" s="408"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="33"/>
       <c r="B132" s="33"/>
-      <c r="C132" s="404"/>
-      <c r="D132" s="411"/>
+      <c r="C132" s="403"/>
+      <c r="D132" s="408"/>
     </row>
     <row r="133" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="323"/>
       <c r="B133" s="323"/>
-      <c r="C133" s="405"/>
-      <c r="D133" s="412"/>
+      <c r="C133" s="404"/>
+      <c r="D133" s="409"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="339"/>
       <c r="B134" s="339"/>
-      <c r="C134" s="404" t="s">
+      <c r="C134" s="403" t="s">
         <v>866</v>
       </c>
-      <c r="D134" s="411" t="s">
+      <c r="D134" s="408" t="s">
         <v>867</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="339"/>
       <c r="B135" s="339"/>
-      <c r="C135" s="404"/>
-      <c r="D135" s="411"/>
+      <c r="C135" s="403"/>
+      <c r="D135" s="408"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="339"/>
       <c r="B136" s="339"/>
-      <c r="C136" s="404"/>
-      <c r="D136" s="411"/>
+      <c r="C136" s="403"/>
+      <c r="D136" s="408"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="339"/>
       <c r="B137" s="339"/>
-      <c r="C137" s="404"/>
-      <c r="D137" s="411"/>
+      <c r="C137" s="403"/>
+      <c r="D137" s="408"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="339"/>
       <c r="B138" s="339"/>
-      <c r="C138" s="404"/>
-      <c r="D138" s="411"/>
+      <c r="C138" s="403"/>
+      <c r="D138" s="408"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="339"/>
       <c r="B139" s="339"/>
-      <c r="C139" s="404"/>
-      <c r="D139" s="411"/>
+      <c r="C139" s="403"/>
+      <c r="D139" s="408"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="339"/>
       <c r="B140" s="339"/>
-      <c r="C140" s="404"/>
-      <c r="D140" s="411"/>
+      <c r="C140" s="403"/>
+      <c r="D140" s="408"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="339"/>
       <c r="B141" s="339"/>
-      <c r="C141" s="404"/>
-      <c r="D141" s="411"/>
+      <c r="C141" s="403"/>
+      <c r="D141" s="408"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="339"/>
       <c r="B142" s="339"/>
-      <c r="C142" s="404"/>
-      <c r="D142" s="411"/>
+      <c r="C142" s="403"/>
+      <c r="D142" s="408"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="339"/>
       <c r="B143" s="339"/>
-      <c r="C143" s="404"/>
-      <c r="D143" s="411"/>
+      <c r="C143" s="403"/>
+      <c r="D143" s="408"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="339"/>
       <c r="B144" s="339"/>
-      <c r="C144" s="404"/>
-      <c r="D144" s="411"/>
+      <c r="C144" s="403"/>
+      <c r="D144" s="408"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="339"/>
       <c r="B145" s="339"/>
-      <c r="C145" s="404"/>
-      <c r="D145" s="411"/>
+      <c r="C145" s="403"/>
+      <c r="D145" s="408"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="339"/>
       <c r="B146" s="339"/>
-      <c r="C146" s="404"/>
-      <c r="D146" s="411"/>
+      <c r="C146" s="403"/>
+      <c r="D146" s="408"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="339"/>
       <c r="B147" s="339"/>
-      <c r="C147" s="404"/>
-      <c r="D147" s="411"/>
+      <c r="C147" s="403"/>
+      <c r="D147" s="408"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="339"/>
       <c r="B148" s="339"/>
-      <c r="C148" s="404"/>
-      <c r="D148" s="411"/>
+      <c r="C148" s="403"/>
+      <c r="D148" s="408"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="339"/>
       <c r="B149" s="339"/>
-      <c r="C149" s="404"/>
-      <c r="D149" s="411"/>
+      <c r="C149" s="403"/>
+      <c r="D149" s="408"/>
     </row>
     <row r="150" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="339"/>
       <c r="B150" s="339"/>
-      <c r="C150" s="404"/>
-      <c r="D150" s="411"/>
+      <c r="C150" s="403"/>
+      <c r="D150" s="408"/>
     </row>
     <row r="151" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="320"/>
       <c r="B151" s="320"/>
-      <c r="C151" s="405"/>
-      <c r="D151" s="412"/>
+      <c r="C151" s="404"/>
+      <c r="D151" s="409"/>
     </row>
     <row r="152" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="341"/>
       <c r="B152" s="341"/>
-      <c r="C152" s="404" t="s">
+      <c r="C152" s="403" t="s">
         <v>868</v>
       </c>
-      <c r="D152" s="411" t="s">
+      <c r="D152" s="408" t="s">
         <v>869</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="341"/>
       <c r="B153" s="341"/>
-      <c r="C153" s="404"/>
-      <c r="D153" s="411"/>
+      <c r="C153" s="403"/>
+      <c r="D153" s="408"/>
     </row>
     <row r="154" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="341"/>
       <c r="B154" s="341"/>
-      <c r="C154" s="404"/>
-      <c r="D154" s="411"/>
+      <c r="C154" s="403"/>
+      <c r="D154" s="408"/>
     </row>
     <row r="155" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="324"/>
       <c r="B155" s="324"/>
-      <c r="C155" s="405"/>
-      <c r="D155" s="412"/>
+      <c r="C155" s="404"/>
+      <c r="D155" s="409"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="24">
+    <mergeCell ref="C2:C17"/>
+    <mergeCell ref="D2:D17"/>
+    <mergeCell ref="C18:C37"/>
+    <mergeCell ref="D18:D37"/>
+    <mergeCell ref="C38:C57"/>
+    <mergeCell ref="D38:D57"/>
+    <mergeCell ref="C58:C72"/>
+    <mergeCell ref="D58:D72"/>
+    <mergeCell ref="C73:C89"/>
+    <mergeCell ref="D73:D89"/>
+    <mergeCell ref="C90:C98"/>
+    <mergeCell ref="D90:D98"/>
+    <mergeCell ref="C99:C111"/>
+    <mergeCell ref="D99:D111"/>
+    <mergeCell ref="C112:C123"/>
+    <mergeCell ref="D112:D123"/>
+    <mergeCell ref="C124:C129"/>
+    <mergeCell ref="D124:D129"/>
     <mergeCell ref="C130:C133"/>
     <mergeCell ref="D130:D133"/>
     <mergeCell ref="C134:C151"/>
     <mergeCell ref="D134:D151"/>
     <mergeCell ref="C152:C155"/>
     <mergeCell ref="D152:D155"/>
-    <mergeCell ref="C99:C111"/>
-    <mergeCell ref="D99:D111"/>
-    <mergeCell ref="C112:C123"/>
-    <mergeCell ref="D112:D123"/>
-    <mergeCell ref="C124:C129"/>
-    <mergeCell ref="D124:D129"/>
-    <mergeCell ref="C58:C72"/>
-    <mergeCell ref="D58:D72"/>
-    <mergeCell ref="C73:C89"/>
-    <mergeCell ref="D73:D89"/>
-    <mergeCell ref="C90:C98"/>
-    <mergeCell ref="D90:D98"/>
-    <mergeCell ref="C2:C17"/>
-    <mergeCell ref="D2:D17"/>
-    <mergeCell ref="C18:C37"/>
-    <mergeCell ref="D18:D37"/>
-    <mergeCell ref="C38:C57"/>
-    <mergeCell ref="D38:D57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -10314,7 +10308,7 @@
         <f>'Custom cases'!D4</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.87pu</v>
       </c>
-      <c r="C3" s="403" t="s">
+      <c r="C3" s="402" t="s">
         <v>510</v>
       </c>
       <c r="D3" s="203" t="s">
@@ -10329,7 +10323,7 @@
         <f>'Custom cases'!D5</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.86pu</v>
       </c>
-      <c r="C4" s="404"/>
+      <c r="C4" s="403"/>
       <c r="D4" s="203" t="s">
         <v>10</v>
       </c>
@@ -10342,7 +10336,7 @@
         <f>'Custom cases'!D6</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.85pu</v>
       </c>
-      <c r="C5" s="404"/>
+      <c r="C5" s="403"/>
       <c r="D5" s="139" t="s">
         <v>512</v>
       </c>
@@ -10355,7 +10349,7 @@
         <f>'Custom cases'!D7</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.84pu</v>
       </c>
-      <c r="C6" s="404"/>
+      <c r="C6" s="403"/>
       <c r="D6" s="203" t="s">
         <v>10</v>
       </c>
@@ -10368,7 +10362,7 @@
         <f>'Custom cases'!D8</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.83pu</v>
       </c>
-      <c r="C7" s="404"/>
+      <c r="C7" s="403"/>
       <c r="D7" s="203" t="s">
         <v>10</v>
       </c>
@@ -10381,7 +10375,7 @@
         <f>'Custom cases'!D9</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.82pu</v>
       </c>
-      <c r="C8" s="404"/>
+      <c r="C8" s="403"/>
       <c r="D8" s="203" t="s">
         <v>10</v>
       </c>
@@ -10394,7 +10388,7 @@
         <f>'Custom cases'!D10</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.81pu</v>
       </c>
-      <c r="C9" s="404"/>
+      <c r="C9" s="403"/>
       <c r="D9" s="203" t="s">
         <v>10</v>
       </c>
@@ -10407,7 +10401,7 @@
         <f>'Custom cases'!D11</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.80pu</v>
       </c>
-      <c r="C10" s="404"/>
+      <c r="C10" s="403"/>
       <c r="D10" s="203" t="s">
         <v>10</v>
       </c>
@@ -10420,7 +10414,7 @@
         <f>'Custom cases'!D12</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.79pu</v>
       </c>
-      <c r="C11" s="404"/>
+      <c r="C11" s="403"/>
       <c r="D11" s="203" t="s">
         <v>10</v>
       </c>
@@ -10433,7 +10427,7 @@
         <f>'Custom cases'!D13</f>
         <v>Custom_RfG_Fault_3_FRTtrig_0.78pu</v>
       </c>
-      <c r="C12" s="405"/>
+      <c r="C12" s="404"/>
       <c r="D12" s="204" t="s">
         <v>10</v>
       </c>
@@ -10446,7 +10440,7 @@
         <f>'Custom cases'!D14</f>
         <v>Custom_RfG_LVRT_FRTexit_0.84pu</v>
       </c>
-      <c r="C13" s="403" t="s">
+      <c r="C13" s="402" t="s">
         <v>509</v>
       </c>
       <c r="D13" s="203" t="s">
@@ -10461,7 +10455,7 @@
         <f>'Custom cases'!D15</f>
         <v>Custom_RfG_LVRT_FRTexit_0.85pu</v>
       </c>
-      <c r="C14" s="404"/>
+      <c r="C14" s="403"/>
       <c r="D14" s="139" t="s">
         <v>511</v>
       </c>
@@ -10474,7 +10468,7 @@
         <f>'Custom cases'!D16</f>
         <v>Custom_RfG_LVRT_FRTexit_0.86pu</v>
       </c>
-      <c r="C15" s="404"/>
+      <c r="C15" s="403"/>
       <c r="D15" s="203" t="s">
         <v>10</v>
       </c>
@@ -10487,7 +10481,7 @@
         <f>'Custom cases'!D17</f>
         <v>Custom_RfG_LVRT_FRTexit_0.87pu</v>
       </c>
-      <c r="C16" s="404"/>
+      <c r="C16" s="403"/>
       <c r="D16" s="203" t="s">
         <v>10</v>
       </c>
@@ -10500,7 +10494,7 @@
         <f>'Custom cases'!D18</f>
         <v>Custom_RfG_LVRT_FRTexit_0.88pu</v>
       </c>
-      <c r="C17" s="404"/>
+      <c r="C17" s="403"/>
       <c r="D17" s="203" t="s">
         <v>10</v>
       </c>
@@ -10513,7 +10507,7 @@
         <f>'Custom cases'!D19</f>
         <v>Custom_RfG_LVRT_FRTexit_0.89pu</v>
       </c>
-      <c r="C18" s="405"/>
+      <c r="C18" s="404"/>
       <c r="D18" s="204" t="s">
         <v>10</v>
       </c>
@@ -10526,7 +10520,7 @@
         <f>'Custom cases'!D20</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.24pu</v>
       </c>
-      <c r="C19" s="403" t="s">
+      <c r="C19" s="402" t="s">
         <v>538</v>
       </c>
       <c r="D19" s="203" t="s">
@@ -10541,7 +10535,7 @@
         <f>'Custom cases'!D21</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.23pu</v>
       </c>
-      <c r="C20" s="404"/>
+      <c r="C20" s="403"/>
       <c r="D20" s="203" t="s">
         <v>10</v>
       </c>
@@ -10554,7 +10548,7 @@
         <f>'Custom cases'!D22</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.22pu</v>
       </c>
-      <c r="C21" s="404"/>
+      <c r="C21" s="403"/>
       <c r="D21" s="203" t="s">
         <v>10</v>
       </c>
@@ -10567,7 +10561,7 @@
         <f>'Custom cases'!D23</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.21pu</v>
       </c>
-      <c r="C22" s="404"/>
+      <c r="C22" s="403"/>
       <c r="D22" s="203" t="s">
         <v>10</v>
       </c>
@@ -10580,7 +10574,7 @@
         <f>'Custom cases'!D24</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.20pu</v>
       </c>
-      <c r="C23" s="404"/>
+      <c r="C23" s="403"/>
       <c r="D23" s="139" t="s">
         <v>539</v>
       </c>
@@ -10593,7 +10587,7 @@
         <f>'Custom cases'!D25</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.19pu</v>
       </c>
-      <c r="C24" s="404"/>
+      <c r="C24" s="403"/>
       <c r="D24" s="203" t="s">
         <v>10</v>
       </c>
@@ -10606,7 +10600,7 @@
         <f>'Custom cases'!D26</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.18pu</v>
       </c>
-      <c r="C25" s="404"/>
+      <c r="C25" s="403"/>
       <c r="D25" s="203" t="s">
         <v>10</v>
       </c>
@@ -10619,7 +10613,7 @@
         <f>'Custom cases'!D27</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.17pu</v>
       </c>
-      <c r="C26" s="404"/>
+      <c r="C26" s="403"/>
       <c r="D26" s="203" t="s">
         <v>10</v>
       </c>
@@ -10632,7 +10626,7 @@
         <f>'Custom cases'!D28</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.16pu</v>
       </c>
-      <c r="C27" s="404"/>
+      <c r="C27" s="403"/>
       <c r="D27" s="203" t="s">
         <v>10</v>
       </c>
@@ -10645,7 +10639,7 @@
         <f>'Custom cases'!D29</f>
         <v>Custom_RfG_Fault_3_MaxIQ_0.15pu</v>
       </c>
-      <c r="C28" s="405"/>
+      <c r="C28" s="404"/>
       <c r="D28" s="204" t="s">
         <v>10</v>
       </c>
@@ -10658,7 +10652,7 @@
         <f>'Custom cases'!D30</f>
         <v>Custom_RfG_Fault_3_0.2pu_Plim_0.5pu</v>
       </c>
-      <c r="C29" s="403" t="s">
+      <c r="C29" s="402" t="s">
         <v>513</v>
       </c>
       <c r="D29" s="139" t="s">
@@ -10673,7 +10667,7 @@
         <f>'Custom cases'!D31</f>
         <v>Custom_RfG_Fault_2_0.2pu_Plim_0.5pu</v>
       </c>
-      <c r="C30" s="404"/>
+      <c r="C30" s="403"/>
       <c r="D30" s="203" t="s">
         <v>10</v>
       </c>
@@ -10686,7 +10680,7 @@
         <f>'Custom cases'!D32</f>
         <v>Custom_RfG_Fault_1_0.2pu_Plim_0.5pu</v>
       </c>
-      <c r="C31" s="404"/>
+      <c r="C31" s="403"/>
       <c r="D31" s="203" t="s">
         <v>10</v>
       </c>
@@ -10699,7 +10693,7 @@
         <f>'Custom cases'!D33</f>
         <v>Custom_RfG_Fault_3_0.2pu_Plim_0.15pu</v>
       </c>
-      <c r="C32" s="404"/>
+      <c r="C32" s="403"/>
       <c r="D32" s="139" t="s">
         <v>514</v>
       </c>
@@ -10712,7 +10706,7 @@
         <f>'Custom cases'!D34</f>
         <v>Custom_RfG_Fault_2_0.2pu_Plim_0.15pu</v>
       </c>
-      <c r="C33" s="404"/>
+      <c r="C33" s="403"/>
       <c r="D33" s="203" t="s">
         <v>10</v>
       </c>
@@ -10725,7 +10719,7 @@
         <f>'Custom cases'!D35</f>
         <v>Custom_RfG_Fault_1_0.2pu_Plim_0.15pu</v>
       </c>
-      <c r="C34" s="405"/>
+      <c r="C34" s="404"/>
       <c r="D34" s="204" t="s">
         <v>10</v>
       </c>
@@ -10738,7 +10732,7 @@
         <f>'Custom cases'!D36</f>
         <v>Custom_RfG_Ucontrol_Plim_1.00pu</v>
       </c>
-      <c r="C35" s="403" t="s">
+      <c r="C35" s="402" t="s">
         <v>518</v>
       </c>
       <c r="D35" s="139" t="s">
@@ -10753,7 +10747,7 @@
         <f>'Custom cases'!D37</f>
         <v>Custom_RfG_Ucontrol_Plim_0.50pu</v>
       </c>
-      <c r="C36" s="404"/>
+      <c r="C36" s="403"/>
       <c r="D36" s="139" t="s">
         <v>515</v>
       </c>
@@ -10766,7 +10760,7 @@
         <f>'Custom cases'!D38</f>
         <v>Custom_RfG_Ucontrol_Plim_0.15pu</v>
       </c>
-      <c r="C37" s="405"/>
+      <c r="C37" s="404"/>
       <c r="D37" s="143" t="s">
         <v>517</v>
       </c>
@@ -10779,7 +10773,7 @@
         <f>'Custom cases'!D39</f>
         <v>Custom_Fault_3_0.20pu_U0_1.118pu</v>
       </c>
-      <c r="C38" s="403" t="s">
+      <c r="C38" s="402" t="s">
         <v>528</v>
       </c>
       <c r="D38" s="146" t="s">
@@ -10794,7 +10788,7 @@
         <f>'Custom cases'!D40</f>
         <v>Custom_Fault_2_0.20pu_U0_1.118pu</v>
       </c>
-      <c r="C39" s="404"/>
+      <c r="C39" s="403"/>
       <c r="D39" s="203" t="s">
         <v>10</v>
       </c>
@@ -10807,7 +10801,7 @@
         <f>'Custom cases'!D41</f>
         <v>Custom_Fault_1_0.20pu_U0_1.118pu</v>
       </c>
-      <c r="C40" s="404"/>
+      <c r="C40" s="403"/>
       <c r="D40" s="203" t="s">
         <v>10</v>
       </c>
@@ -10820,7 +10814,7 @@
         <f>'Custom cases'!D42</f>
         <v>Custom_Fault_3_0.20pu_U0_0.968pu</v>
       </c>
-      <c r="C41" s="404"/>
+      <c r="C41" s="403"/>
       <c r="D41" s="139" t="s">
         <v>520</v>
       </c>
@@ -10833,7 +10827,7 @@
         <f>'Custom cases'!D43</f>
         <v>Custom_Fault_2_0.20pu_U0_0.968pu</v>
       </c>
-      <c r="C42" s="404"/>
+      <c r="C42" s="403"/>
       <c r="D42" s="203" t="s">
         <v>10</v>
       </c>
@@ -10846,7 +10840,7 @@
         <f>'Custom cases'!D44</f>
         <v>Custom_Fault_1_0.20pu_U0_0.968pu</v>
       </c>
-      <c r="C43" s="405"/>
+      <c r="C43" s="404"/>
       <c r="D43" s="204" t="s">
         <v>10</v>
       </c>
@@ -10859,7 +10853,7 @@
         <f>'Custom cases'!D45</f>
         <v>Custom_Fault_3_U0_1.118_Uend_1.065</v>
       </c>
-      <c r="C44" s="403" t="s">
+      <c r="C44" s="402" t="s">
         <v>529</v>
       </c>
       <c r="D44" s="146" t="s">
@@ -10874,7 +10868,7 @@
         <f>'Custom cases'!D46</f>
         <v>Custom_Fault_2_U0_1.118_Uend_1.065</v>
       </c>
-      <c r="C45" s="404"/>
+      <c r="C45" s="403"/>
       <c r="D45" s="203" t="s">
         <v>10</v>
       </c>
@@ -10887,7 +10881,7 @@
         <f>'Custom cases'!D47</f>
         <v>Custom_Fault_1_U0_1.118_Uend_1.065</v>
       </c>
-      <c r="C46" s="404"/>
+      <c r="C46" s="403"/>
       <c r="D46" s="203" t="s">
         <v>10</v>
       </c>
@@ -10900,7 +10894,7 @@
         <f>'Custom cases'!D48</f>
         <v>Custom_Fault_3_U0_1.118_Uend_0.968</v>
       </c>
-      <c r="C47" s="404"/>
+      <c r="C47" s="403"/>
       <c r="D47" s="203" t="s">
         <v>10</v>
       </c>
@@ -10913,7 +10907,7 @@
         <f>'Custom cases'!D49</f>
         <v>Custom_Fault_3_U0_0.959_Uend_1.065</v>
       </c>
-      <c r="C48" s="404"/>
+      <c r="C48" s="403"/>
       <c r="D48" s="139" t="s">
         <v>521</v>
       </c>
@@ -10926,7 +10920,7 @@
         <f>'Custom cases'!D50</f>
         <v>Custom_Fault_2_U0_0.959_Uend_1.065</v>
       </c>
-      <c r="C49" s="404"/>
+      <c r="C49" s="403"/>
       <c r="D49" s="203" t="s">
         <v>10</v>
       </c>
@@ -10939,7 +10933,7 @@
         <f>'Custom cases'!D51</f>
         <v>Custom_Fault_1_U0_0.959_Uend_1.065</v>
       </c>
-      <c r="C50" s="404"/>
+      <c r="C50" s="403"/>
       <c r="D50" s="203" t="s">
         <v>10</v>
       </c>
@@ -10952,7 +10946,7 @@
         <f>'Custom cases'!D52</f>
         <v>Custom_Fault_3_U0_0.959_Uend_1.118</v>
       </c>
-      <c r="C51" s="404"/>
+      <c r="C51" s="403"/>
       <c r="D51" s="203" t="s">
         <v>10</v>
       </c>
@@ -10965,7 +10959,7 @@
         <f>'Custom cases'!D53</f>
         <v>Custom_Fault_3_U0_1.118_Uend_0.900</v>
       </c>
-      <c r="C52" s="404"/>
+      <c r="C52" s="403"/>
       <c r="D52" s="139" t="s">
         <v>523</v>
       </c>
@@ -10978,7 +10972,7 @@
         <f>'Custom cases'!D54</f>
         <v>Custom_Fault_3_U0_1.065_Uend_0.900</v>
       </c>
-      <c r="C53" s="404"/>
+      <c r="C53" s="403"/>
       <c r="D53" s="203" t="s">
         <v>10</v>
       </c>
@@ -10991,7 +10985,7 @@
         <f>'Custom cases'!D55</f>
         <v>Custom_Fault_3_U0_0.959_Uend_0.900</v>
       </c>
-      <c r="C54" s="405"/>
+      <c r="C54" s="404"/>
       <c r="D54" s="204" t="s">
         <v>10</v>
       </c>
@@ -11004,7 +10998,7 @@
         <f>'Custom cases'!D56</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.15</v>
       </c>
-      <c r="C55" s="403" t="s">
+      <c r="C55" s="402" t="s">
         <v>530</v>
       </c>
       <c r="D55" s="146" t="s">
@@ -11019,7 +11013,7 @@
         <f>'Custom cases'!D57</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.20</v>
       </c>
-      <c r="C56" s="404"/>
+      <c r="C56" s="403"/>
       <c r="D56" s="139" t="s">
         <v>525</v>
       </c>
@@ -11032,7 +11026,7 @@
         <f>'Custom cases'!D58</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.30</v>
       </c>
-      <c r="C57" s="404"/>
+      <c r="C57" s="403"/>
       <c r="D57" s="139" t="s">
         <v>524</v>
       </c>
@@ -11045,7 +11039,7 @@
         <f>'Custom cases'!D59</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.15</v>
       </c>
-      <c r="C58" s="404"/>
+      <c r="C58" s="403"/>
       <c r="D58" s="139" t="s">
         <v>526</v>
       </c>
@@ -11058,7 +11052,7 @@
         <f>'Custom cases'!D60</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.20</v>
       </c>
-      <c r="C59" s="404"/>
+      <c r="C59" s="403"/>
       <c r="D59" s="139" t="s">
         <v>526</v>
       </c>
@@ -11071,7 +11065,7 @@
         <f>'Custom cases'!D61</f>
         <v>Custom_Fault_3_U0_1.065pu_OVRT_1.30</v>
       </c>
-      <c r="C60" s="405"/>
+      <c r="C60" s="404"/>
       <c r="D60" s="143" t="s">
         <v>527</v>
       </c>
@@ -11084,7 +11078,7 @@
         <f>'Custom cases'!D62</f>
         <v>Custom_Fault_3_0.20pu_SCR_2</v>
       </c>
-      <c r="C61" s="403" t="s">
+      <c r="C61" s="402" t="s">
         <v>531</v>
       </c>
       <c r="D61" s="146" t="s">
@@ -11099,7 +11093,7 @@
         <f>'Custom cases'!D63</f>
         <v>Custom_Fault_3_0.20pu_SCR_3</v>
       </c>
-      <c r="C62" s="404"/>
+      <c r="C62" s="403"/>
       <c r="D62" s="203" t="s">
         <v>10</v>
       </c>
@@ -11112,7 +11106,7 @@
         <f>'Custom cases'!D64</f>
         <v>Custom_Fault_3_0.20pu_SCR_4</v>
       </c>
-      <c r="C63" s="404"/>
+      <c r="C63" s="403"/>
       <c r="D63" s="203" t="s">
         <v>10</v>
       </c>
@@ -11125,7 +11119,7 @@
         <f>'Custom cases'!D65</f>
         <v>Custom_Fault_3_0.20pu_SCR_5</v>
       </c>
-      <c r="C64" s="404"/>
+      <c r="C64" s="403"/>
       <c r="D64" s="203" t="s">
         <v>10</v>
       </c>
@@ -11138,7 +11132,7 @@
         <f>'Custom cases'!D66</f>
         <v>Custom_Fault_3_0.20pu_SCR_6</v>
       </c>
-      <c r="C65" s="404"/>
+      <c r="C65" s="403"/>
       <c r="D65" s="203" t="s">
         <v>10</v>
       </c>
@@ -11151,7 +11145,7 @@
         <f>'Custom cases'!D67</f>
         <v>Custom_Fault_2_0.20pu_SCR_2</v>
       </c>
-      <c r="C66" s="404"/>
+      <c r="C66" s="403"/>
       <c r="D66" s="203" t="s">
         <v>10</v>
       </c>
@@ -11164,7 +11158,7 @@
         <f>'Custom cases'!D68</f>
         <v>Custom_Fault_2_0.20pu_SCR_3</v>
       </c>
-      <c r="C67" s="404"/>
+      <c r="C67" s="403"/>
       <c r="D67" s="203" t="s">
         <v>10</v>
       </c>
@@ -11177,7 +11171,7 @@
         <f>'Custom cases'!D69</f>
         <v>Custom_Fault_2_0.20pu_SCR_4</v>
       </c>
-      <c r="C68" s="404"/>
+      <c r="C68" s="403"/>
       <c r="D68" s="203" t="s">
         <v>10</v>
       </c>
@@ -11190,7 +11184,7 @@
         <f>'Custom cases'!D70</f>
         <v>Custom_Fault_2_0.20pu_SCR_5</v>
       </c>
-      <c r="C69" s="404"/>
+      <c r="C69" s="403"/>
       <c r="D69" s="203" t="s">
         <v>10</v>
       </c>
@@ -11203,7 +11197,7 @@
         <f>'Custom cases'!D71</f>
         <v>Custom_Fault_2_0.20pu_SCR_6</v>
       </c>
-      <c r="C70" s="404"/>
+      <c r="C70" s="403"/>
       <c r="D70" s="203" t="s">
         <v>10</v>
       </c>
@@ -11216,7 +11210,7 @@
         <f>'Custom cases'!D72</f>
         <v>Custom_Fault_3_0.70pu_SCR_2</v>
       </c>
-      <c r="C71" s="404"/>
+      <c r="C71" s="403"/>
       <c r="D71" s="203" t="s">
         <v>10</v>
       </c>
@@ -11229,7 +11223,7 @@
         <f>'Custom cases'!D73</f>
         <v>Custom_Fault_3_0.70pu_SCR_3</v>
       </c>
-      <c r="C72" s="404"/>
+      <c r="C72" s="403"/>
       <c r="D72" s="203" t="s">
         <v>10</v>
       </c>
@@ -11242,7 +11236,7 @@
         <f>'Custom cases'!D74</f>
         <v>Custom_Fault_3_0.70pu_SCR_4</v>
       </c>
-      <c r="C73" s="404"/>
+      <c r="C73" s="403"/>
       <c r="D73" s="203" t="s">
         <v>10</v>
       </c>
@@ -11255,7 +11249,7 @@
         <f>'Custom cases'!D75</f>
         <v>Custom_Fault_3_0.70pu_SCR_5</v>
       </c>
-      <c r="C74" s="404"/>
+      <c r="C74" s="403"/>
       <c r="D74" s="203" t="s">
         <v>10</v>
       </c>
@@ -11268,7 +11262,7 @@
         <f>'Custom cases'!D76</f>
         <v>Custom_Fault_3_0.70pu_SCR_6</v>
       </c>
-      <c r="C75" s="404"/>
+      <c r="C75" s="403"/>
       <c r="D75" s="203" t="s">
         <v>10</v>
       </c>
@@ -11281,7 +11275,7 @@
         <f>'Custom cases'!D77</f>
         <v>Custom_Fault_2_0.70pu_SCR_2</v>
       </c>
-      <c r="C76" s="404"/>
+      <c r="C76" s="403"/>
       <c r="D76" s="203" t="s">
         <v>10</v>
       </c>
@@ -11294,7 +11288,7 @@
         <f>'Custom cases'!D78</f>
         <v>Custom_Fault_2_0.70pu_SCR_3</v>
       </c>
-      <c r="C77" s="404"/>
+      <c r="C77" s="403"/>
       <c r="D77" s="203" t="s">
         <v>10</v>
       </c>
@@ -11307,7 +11301,7 @@
         <f>'Custom cases'!D79</f>
         <v>Custom_Fault_2_0.70pu_SCR_4</v>
       </c>
-      <c r="C78" s="404"/>
+      <c r="C78" s="403"/>
       <c r="D78" s="203" t="s">
         <v>10</v>
       </c>
@@ -11320,7 +11314,7 @@
         <f>'Custom cases'!D80</f>
         <v>Custom_Fault_2_0.70pu_SCR_5</v>
       </c>
-      <c r="C79" s="404"/>
+      <c r="C79" s="403"/>
       <c r="D79" s="203" t="s">
         <v>10</v>
       </c>
@@ -11333,7 +11327,7 @@
         <f>'Custom cases'!D81</f>
         <v>Custom_Fault_2_0.70pu_SCR_6</v>
       </c>
-      <c r="C80" s="405"/>
+      <c r="C80" s="404"/>
       <c r="D80" s="204" t="s">
         <v>10</v>
       </c>
@@ -11346,7 +11340,7 @@
         <f>'Custom cases'!D82</f>
         <v>Custom_Fault_3_0.20pu_Duration_80</v>
       </c>
-      <c r="C81" s="403" t="s">
+      <c r="C81" s="402" t="s">
         <v>533</v>
       </c>
       <c r="D81" s="139" t="s">
@@ -11361,7 +11355,7 @@
         <f>'Custom cases'!D83</f>
         <v>Custom_Fault_3_0.20pu_Duration_60</v>
       </c>
-      <c r="C82" s="404"/>
+      <c r="C82" s="403"/>
       <c r="D82" s="203" t="s">
         <v>10</v>
       </c>
@@ -11374,7 +11368,7 @@
         <f>'Custom cases'!D84</f>
         <v>Custom_Fault_3_0.20pu_Duration_40</v>
       </c>
-      <c r="C83" s="404"/>
+      <c r="C83" s="403"/>
       <c r="D83" s="203" t="s">
         <v>10</v>
       </c>
@@ -11387,7 +11381,7 @@
         <f>'Custom cases'!D85</f>
         <v>Custom_Shift_10_Fault_3_0.20pu</v>
       </c>
-      <c r="C84" s="404"/>
+      <c r="C84" s="403"/>
       <c r="D84" s="139" t="s">
         <v>535</v>
       </c>
@@ -11400,7 +11394,7 @@
         <f>'Custom cases'!D86</f>
         <v>Custom_Shift_20_Fault_3_0.20pu</v>
       </c>
-      <c r="C85" s="404"/>
+      <c r="C85" s="403"/>
       <c r="D85" s="203" t="s">
         <v>10</v>
       </c>
@@ -11413,7 +11407,7 @@
         <f>'Custom cases'!D87</f>
         <v>Custom_Shift_30_Fault_3_0.20pu</v>
       </c>
-      <c r="C86" s="404"/>
+      <c r="C86" s="403"/>
       <c r="D86" s="203" t="s">
         <v>10</v>
       </c>
@@ -11426,7 +11420,7 @@
         <f>'Custom cases'!D88</f>
         <v>Custom_Shift_40_Fault_3_0.20pu</v>
       </c>
-      <c r="C87" s="404"/>
+      <c r="C87" s="403"/>
       <c r="D87" s="203" t="s">
         <v>10</v>
       </c>
@@ -11439,7 +11433,7 @@
         <f>'Custom cases'!D89</f>
         <v>Custom_Shift_50_Fault_3_0.20pu</v>
       </c>
-      <c r="C88" s="405"/>
+      <c r="C88" s="404"/>
       <c r="D88" s="204" t="s">
         <v>10</v>
       </c>
@@ -11595,21 +11589,21 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33"/>
-      <c r="B1" s="386" t="s">
+      <c r="B1" s="385" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="387"/>
-      <c r="D1" s="388"/>
-      <c r="E1" s="386" t="s">
+      <c r="C1" s="386"/>
+      <c r="D1" s="387"/>
+      <c r="E1" s="385" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="387"/>
-      <c r="G1" s="387"/>
+      <c r="F1" s="386"/>
+      <c r="G1" s="386"/>
       <c r="H1" s="310"/>
-      <c r="K1" s="389" t="s">
+      <c r="K1" s="388" t="s">
         <v>841</v>
       </c>
-      <c r="L1" s="390"/>
+      <c r="L1" s="389"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="61" t="s">
@@ -12683,103 +12677,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A1" s="392" t="s">
+      <c r="A1" s="391" t="s">
         <v>492</v>
       </c>
-      <c r="B1" s="392"/>
-      <c r="C1" s="392"/>
-      <c r="D1" s="392"/>
-      <c r="E1" s="393" t="s">
+      <c r="B1" s="391"/>
+      <c r="C1" s="391"/>
+      <c r="D1" s="391"/>
+      <c r="E1" s="392" t="s">
         <v>493</v>
       </c>
-      <c r="F1" s="394"/>
-      <c r="G1" s="394"/>
-      <c r="H1" s="394"/>
-      <c r="I1" s="394"/>
-      <c r="J1" s="394"/>
-      <c r="K1" s="394"/>
-      <c r="L1" s="394"/>
-      <c r="M1" s="394"/>
-      <c r="N1" s="394"/>
-      <c r="O1" s="395"/>
-      <c r="P1" s="391" t="s">
+      <c r="F1" s="393"/>
+      <c r="G1" s="393"/>
+      <c r="H1" s="393"/>
+      <c r="I1" s="393"/>
+      <c r="J1" s="393"/>
+      <c r="K1" s="393"/>
+      <c r="L1" s="393"/>
+      <c r="M1" s="393"/>
+      <c r="N1" s="393"/>
+      <c r="O1" s="394"/>
+      <c r="P1" s="390" t="s">
         <v>77</v>
       </c>
-      <c r="Q1" s="391"/>
-      <c r="R1" s="391"/>
-      <c r="S1" s="391"/>
-      <c r="T1" s="392" t="s">
+      <c r="Q1" s="390"/>
+      <c r="R1" s="390"/>
+      <c r="S1" s="390"/>
+      <c r="T1" s="391" t="s">
         <v>78</v>
       </c>
-      <c r="U1" s="392"/>
-      <c r="V1" s="392"/>
-      <c r="W1" s="392"/>
-      <c r="X1" s="391" t="s">
+      <c r="U1" s="391"/>
+      <c r="V1" s="391"/>
+      <c r="W1" s="391"/>
+      <c r="X1" s="390" t="s">
         <v>79</v>
       </c>
-      <c r="Y1" s="391"/>
-      <c r="Z1" s="391"/>
-      <c r="AA1" s="391"/>
-      <c r="AB1" s="392" t="s">
+      <c r="Y1" s="390"/>
+      <c r="Z1" s="390"/>
+      <c r="AA1" s="390"/>
+      <c r="AB1" s="391" t="s">
         <v>80</v>
       </c>
-      <c r="AC1" s="392"/>
-      <c r="AD1" s="392"/>
-      <c r="AE1" s="392"/>
-      <c r="AF1" s="391" t="s">
+      <c r="AC1" s="391"/>
+      <c r="AD1" s="391"/>
+      <c r="AE1" s="391"/>
+      <c r="AF1" s="390" t="s">
         <v>81</v>
       </c>
-      <c r="AG1" s="391"/>
-      <c r="AH1" s="391"/>
-      <c r="AI1" s="391"/>
-      <c r="AJ1" s="392" t="s">
+      <c r="AG1" s="390"/>
+      <c r="AH1" s="390"/>
+      <c r="AI1" s="390"/>
+      <c r="AJ1" s="391" t="s">
         <v>82</v>
       </c>
-      <c r="AK1" s="392"/>
-      <c r="AL1" s="392"/>
-      <c r="AM1" s="392"/>
-      <c r="AN1" s="391" t="s">
+      <c r="AK1" s="391"/>
+      <c r="AL1" s="391"/>
+      <c r="AM1" s="391"/>
+      <c r="AN1" s="390" t="s">
         <v>83</v>
       </c>
-      <c r="AO1" s="391"/>
-      <c r="AP1" s="391"/>
-      <c r="AQ1" s="391"/>
-      <c r="AR1" s="392" t="s">
+      <c r="AO1" s="390"/>
+      <c r="AP1" s="390"/>
+      <c r="AQ1" s="390"/>
+      <c r="AR1" s="391" t="s">
         <v>84</v>
       </c>
-      <c r="AS1" s="392"/>
-      <c r="AT1" s="392"/>
-      <c r="AU1" s="392"/>
-      <c r="AV1" s="391" t="s">
+      <c r="AS1" s="391"/>
+      <c r="AT1" s="391"/>
+      <c r="AU1" s="391"/>
+      <c r="AV1" s="390" t="s">
         <v>85</v>
       </c>
-      <c r="AW1" s="391"/>
-      <c r="AX1" s="391"/>
-      <c r="AY1" s="391"/>
-      <c r="AZ1" s="392" t="s">
+      <c r="AW1" s="390"/>
+      <c r="AX1" s="390"/>
+      <c r="AY1" s="390"/>
+      <c r="AZ1" s="391" t="s">
         <v>86</v>
       </c>
-      <c r="BA1" s="392"/>
-      <c r="BB1" s="392"/>
-      <c r="BC1" s="392"/>
-      <c r="BD1" s="391" t="s">
+      <c r="BA1" s="391"/>
+      <c r="BB1" s="391"/>
+      <c r="BC1" s="391"/>
+      <c r="BD1" s="390" t="s">
         <v>87</v>
       </c>
-      <c r="BE1" s="391"/>
-      <c r="BF1" s="391"/>
-      <c r="BG1" s="391"/>
-      <c r="BH1" s="392" t="s">
+      <c r="BE1" s="390"/>
+      <c r="BF1" s="390"/>
+      <c r="BG1" s="390"/>
+      <c r="BH1" s="391" t="s">
         <v>88</v>
       </c>
-      <c r="BI1" s="392"/>
-      <c r="BJ1" s="392"/>
-      <c r="BK1" s="392"/>
-      <c r="BL1" s="391" t="s">
+      <c r="BI1" s="391"/>
+      <c r="BJ1" s="391"/>
+      <c r="BK1" s="391"/>
+      <c r="BL1" s="390" t="s">
         <v>497</v>
       </c>
-      <c r="BM1" s="391"/>
-      <c r="BN1" s="391"/>
-      <c r="BO1" s="391"/>
+      <c r="BM1" s="390"/>
+      <c r="BN1" s="390"/>
+      <c r="BO1" s="390"/>
     </row>
     <row r="2" spans="1:67" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -34684,96 +34678,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:94" x14ac:dyDescent="0.25">
-      <c r="A1" s="392" t="s">
+      <c r="A1" s="391" t="s">
         <v>492</v>
       </c>
-      <c r="B1" s="392"/>
-      <c r="C1" s="392"/>
-      <c r="D1" s="392"/>
-      <c r="E1" s="393" t="s">
+      <c r="B1" s="391"/>
+      <c r="C1" s="391"/>
+      <c r="D1" s="391"/>
+      <c r="E1" s="392" t="s">
         <v>493</v>
       </c>
-      <c r="F1" s="394"/>
-      <c r="G1" s="394"/>
-      <c r="H1" s="394"/>
-      <c r="I1" s="394"/>
-      <c r="J1" s="394"/>
-      <c r="K1" s="394"/>
-      <c r="L1" s="394"/>
-      <c r="M1" s="394"/>
-      <c r="N1" s="395"/>
-      <c r="O1" s="399" t="s">
+      <c r="F1" s="393"/>
+      <c r="G1" s="393"/>
+      <c r="H1" s="393"/>
+      <c r="I1" s="393"/>
+      <c r="J1" s="393"/>
+      <c r="K1" s="393"/>
+      <c r="L1" s="393"/>
+      <c r="M1" s="393"/>
+      <c r="N1" s="394"/>
+      <c r="O1" s="398" t="s">
         <v>77</v>
       </c>
-      <c r="P1" s="400"/>
-      <c r="Q1" s="400"/>
-      <c r="R1" s="401"/>
-      <c r="S1" s="393" t="s">
+      <c r="P1" s="399"/>
+      <c r="Q1" s="399"/>
+      <c r="R1" s="400"/>
+      <c r="S1" s="392" t="s">
         <v>78</v>
       </c>
-      <c r="T1" s="394"/>
-      <c r="U1" s="394"/>
-      <c r="V1" s="394"/>
-      <c r="W1" s="399" t="s">
+      <c r="T1" s="393"/>
+      <c r="U1" s="393"/>
+      <c r="V1" s="393"/>
+      <c r="W1" s="398" t="s">
         <v>79</v>
       </c>
-      <c r="X1" s="400"/>
-      <c r="Y1" s="400"/>
-      <c r="Z1" s="401"/>
-      <c r="AA1" s="396" t="s">
+      <c r="X1" s="399"/>
+      <c r="Y1" s="399"/>
+      <c r="Z1" s="400"/>
+      <c r="AA1" s="395" t="s">
         <v>80</v>
       </c>
-      <c r="AB1" s="397"/>
-      <c r="AC1" s="397"/>
-      <c r="AD1" s="398"/>
-      <c r="AE1" s="399" t="s">
+      <c r="AB1" s="396"/>
+      <c r="AC1" s="396"/>
+      <c r="AD1" s="397"/>
+      <c r="AE1" s="398" t="s">
         <v>81</v>
       </c>
-      <c r="AF1" s="400"/>
-      <c r="AG1" s="400"/>
-      <c r="AH1" s="401"/>
-      <c r="AI1" s="396" t="s">
+      <c r="AF1" s="399"/>
+      <c r="AG1" s="399"/>
+      <c r="AH1" s="400"/>
+      <c r="AI1" s="395" t="s">
         <v>82</v>
       </c>
-      <c r="AJ1" s="397"/>
-      <c r="AK1" s="397"/>
-      <c r="AL1" s="398"/>
-      <c r="AM1" s="399" t="s">
+      <c r="AJ1" s="396"/>
+      <c r="AK1" s="396"/>
+      <c r="AL1" s="397"/>
+      <c r="AM1" s="398" t="s">
         <v>83</v>
       </c>
-      <c r="AN1" s="400"/>
-      <c r="AO1" s="400"/>
-      <c r="AP1" s="401"/>
-      <c r="AQ1" s="396" t="s">
+      <c r="AN1" s="399"/>
+      <c r="AO1" s="399"/>
+      <c r="AP1" s="400"/>
+      <c r="AQ1" s="395" t="s">
         <v>84</v>
       </c>
-      <c r="AR1" s="397"/>
-      <c r="AS1" s="397"/>
-      <c r="AT1" s="398"/>
-      <c r="AU1" s="399" t="s">
+      <c r="AR1" s="396"/>
+      <c r="AS1" s="396"/>
+      <c r="AT1" s="397"/>
+      <c r="AU1" s="398" t="s">
         <v>85</v>
       </c>
-      <c r="AV1" s="400"/>
-      <c r="AW1" s="400"/>
-      <c r="AX1" s="401"/>
-      <c r="AY1" s="396" t="s">
+      <c r="AV1" s="399"/>
+      <c r="AW1" s="399"/>
+      <c r="AX1" s="400"/>
+      <c r="AY1" s="395" t="s">
         <v>86</v>
       </c>
-      <c r="AZ1" s="397"/>
-      <c r="BA1" s="397"/>
-      <c r="BB1" s="398"/>
-      <c r="BC1" s="399" t="s">
+      <c r="AZ1" s="396"/>
+      <c r="BA1" s="396"/>
+      <c r="BB1" s="397"/>
+      <c r="BC1" s="398" t="s">
         <v>87</v>
       </c>
-      <c r="BD1" s="400"/>
-      <c r="BE1" s="400"/>
-      <c r="BF1" s="401"/>
-      <c r="BG1" s="396" t="s">
+      <c r="BD1" s="399"/>
+      <c r="BE1" s="399"/>
+      <c r="BF1" s="400"/>
+      <c r="BG1" s="395" t="s">
         <v>88</v>
       </c>
-      <c r="BH1" s="397"/>
-      <c r="BI1" s="397"/>
-      <c r="BJ1" s="398"/>
+      <c r="BH1" s="396"/>
+      <c r="BI1" s="396"/>
+      <c r="BJ1" s="397"/>
     </row>
     <row r="2" spans="1:94" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -45050,97 +45044,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A1" s="392" t="s">
+      <c r="A1" s="391" t="s">
         <v>492</v>
       </c>
-      <c r="B1" s="392"/>
-      <c r="C1" s="392"/>
-      <c r="D1" s="392"/>
-      <c r="E1" s="393" t="s">
+      <c r="B1" s="391"/>
+      <c r="C1" s="391"/>
+      <c r="D1" s="391"/>
+      <c r="E1" s="392" t="s">
         <v>493</v>
       </c>
-      <c r="F1" s="394"/>
-      <c r="G1" s="394"/>
-      <c r="H1" s="394"/>
-      <c r="I1" s="394"/>
-      <c r="J1" s="394"/>
-      <c r="K1" s="394"/>
-      <c r="L1" s="394"/>
-      <c r="M1" s="394"/>
-      <c r="N1" s="394"/>
-      <c r="O1" s="395"/>
-      <c r="P1" s="402" t="s">
+      <c r="F1" s="393"/>
+      <c r="G1" s="393"/>
+      <c r="H1" s="393"/>
+      <c r="I1" s="393"/>
+      <c r="J1" s="393"/>
+      <c r="K1" s="393"/>
+      <c r="L1" s="393"/>
+      <c r="M1" s="393"/>
+      <c r="N1" s="393"/>
+      <c r="O1" s="394"/>
+      <c r="P1" s="401" t="s">
         <v>77</v>
       </c>
-      <c r="Q1" s="402"/>
-      <c r="R1" s="402"/>
-      <c r="S1" s="402"/>
-      <c r="T1" s="392" t="s">
+      <c r="Q1" s="401"/>
+      <c r="R1" s="401"/>
+      <c r="S1" s="401"/>
+      <c r="T1" s="391" t="s">
         <v>78</v>
       </c>
-      <c r="U1" s="392"/>
-      <c r="V1" s="392"/>
-      <c r="W1" s="392"/>
-      <c r="X1" s="402" t="s">
+      <c r="U1" s="391"/>
+      <c r="V1" s="391"/>
+      <c r="W1" s="391"/>
+      <c r="X1" s="401" t="s">
         <v>79</v>
       </c>
-      <c r="Y1" s="402"/>
-      <c r="Z1" s="402"/>
-      <c r="AA1" s="402"/>
-      <c r="AB1" s="392" t="s">
+      <c r="Y1" s="401"/>
+      <c r="Z1" s="401"/>
+      <c r="AA1" s="401"/>
+      <c r="AB1" s="391" t="s">
         <v>80</v>
       </c>
-      <c r="AC1" s="392"/>
-      <c r="AD1" s="392"/>
-      <c r="AE1" s="392"/>
-      <c r="AF1" s="402" t="s">
+      <c r="AC1" s="391"/>
+      <c r="AD1" s="391"/>
+      <c r="AE1" s="391"/>
+      <c r="AF1" s="401" t="s">
         <v>81</v>
       </c>
-      <c r="AG1" s="402"/>
-      <c r="AH1" s="402"/>
-      <c r="AI1" s="402"/>
-      <c r="AJ1" s="392" t="s">
+      <c r="AG1" s="401"/>
+      <c r="AH1" s="401"/>
+      <c r="AI1" s="401"/>
+      <c r="AJ1" s="391" t="s">
         <v>82</v>
       </c>
-      <c r="AK1" s="392"/>
-      <c r="AL1" s="392"/>
-      <c r="AM1" s="392"/>
-      <c r="AN1" s="402" t="s">
+      <c r="AK1" s="391"/>
+      <c r="AL1" s="391"/>
+      <c r="AM1" s="391"/>
+      <c r="AN1" s="401" t="s">
         <v>83</v>
       </c>
-      <c r="AO1" s="402"/>
-      <c r="AP1" s="402"/>
-      <c r="AQ1" s="402"/>
-      <c r="AR1" s="392" t="s">
+      <c r="AO1" s="401"/>
+      <c r="AP1" s="401"/>
+      <c r="AQ1" s="401"/>
+      <c r="AR1" s="391" t="s">
         <v>84</v>
       </c>
-      <c r="AS1" s="392"/>
-      <c r="AT1" s="392"/>
-      <c r="AU1" s="392"/>
-      <c r="AV1" s="402" t="s">
+      <c r="AS1" s="391"/>
+      <c r="AT1" s="391"/>
+      <c r="AU1" s="391"/>
+      <c r="AV1" s="401" t="s">
         <v>85</v>
       </c>
-      <c r="AW1" s="402"/>
-      <c r="AX1" s="402"/>
-      <c r="AY1" s="402"/>
-      <c r="AZ1" s="392" t="s">
+      <c r="AW1" s="401"/>
+      <c r="AX1" s="401"/>
+      <c r="AY1" s="401"/>
+      <c r="AZ1" s="391" t="s">
         <v>86</v>
       </c>
-      <c r="BA1" s="392"/>
-      <c r="BB1" s="392"/>
-      <c r="BC1" s="392"/>
-      <c r="BD1" s="402" t="s">
+      <c r="BA1" s="391"/>
+      <c r="BB1" s="391"/>
+      <c r="BC1" s="391"/>
+      <c r="BD1" s="401" t="s">
         <v>87</v>
       </c>
-      <c r="BE1" s="402"/>
-      <c r="BF1" s="402"/>
-      <c r="BG1" s="402"/>
-      <c r="BH1" s="392" t="s">
+      <c r="BE1" s="401"/>
+      <c r="BF1" s="401"/>
+      <c r="BG1" s="401"/>
+      <c r="BH1" s="391" t="s">
         <v>88</v>
       </c>
-      <c r="BI1" s="392"/>
-      <c r="BJ1" s="392"/>
-      <c r="BK1" s="392"/>
+      <c r="BI1" s="391"/>
+      <c r="BJ1" s="391"/>
+      <c r="BK1" s="391"/>
     </row>
     <row r="2" spans="1:63" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -54448,109 +54442,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A1" s="392" t="s">
+      <c r="A1" s="391" t="s">
         <v>492</v>
       </c>
-      <c r="B1" s="392"/>
-      <c r="C1" s="392"/>
-      <c r="D1" s="392"/>
-      <c r="E1" s="393" t="s">
+      <c r="B1" s="391"/>
+      <c r="C1" s="391"/>
+      <c r="D1" s="391"/>
+      <c r="E1" s="392" t="s">
         <v>493</v>
       </c>
-      <c r="F1" s="394"/>
-      <c r="G1" s="394"/>
-      <c r="H1" s="394"/>
-      <c r="I1" s="394"/>
-      <c r="J1" s="394"/>
-      <c r="K1" s="394"/>
-      <c r="L1" s="394"/>
-      <c r="M1" s="394"/>
-      <c r="N1" s="394"/>
-      <c r="O1" s="394"/>
-      <c r="P1" s="394"/>
-      <c r="Q1" s="394"/>
-      <c r="R1" s="394"/>
-      <c r="S1" s="394"/>
-      <c r="T1" s="394"/>
-      <c r="U1" s="395"/>
-      <c r="V1" s="391" t="s">
+      <c r="F1" s="393"/>
+      <c r="G1" s="393"/>
+      <c r="H1" s="393"/>
+      <c r="I1" s="393"/>
+      <c r="J1" s="393"/>
+      <c r="K1" s="393"/>
+      <c r="L1" s="393"/>
+      <c r="M1" s="393"/>
+      <c r="N1" s="393"/>
+      <c r="O1" s="393"/>
+      <c r="P1" s="393"/>
+      <c r="Q1" s="393"/>
+      <c r="R1" s="393"/>
+      <c r="S1" s="393"/>
+      <c r="T1" s="393"/>
+      <c r="U1" s="394"/>
+      <c r="V1" s="390" t="s">
         <v>77</v>
       </c>
-      <c r="W1" s="391"/>
-      <c r="X1" s="391"/>
-      <c r="Y1" s="391"/>
-      <c r="Z1" s="392" t="s">
+      <c r="W1" s="390"/>
+      <c r="X1" s="390"/>
+      <c r="Y1" s="390"/>
+      <c r="Z1" s="391" t="s">
         <v>78</v>
       </c>
-      <c r="AA1" s="392"/>
-      <c r="AB1" s="392"/>
-      <c r="AC1" s="392"/>
-      <c r="AD1" s="391" t="s">
+      <c r="AA1" s="391"/>
+      <c r="AB1" s="391"/>
+      <c r="AC1" s="391"/>
+      <c r="AD1" s="390" t="s">
         <v>79</v>
       </c>
-      <c r="AE1" s="391"/>
-      <c r="AF1" s="391"/>
-      <c r="AG1" s="391"/>
-      <c r="AH1" s="392" t="s">
+      <c r="AE1" s="390"/>
+      <c r="AF1" s="390"/>
+      <c r="AG1" s="390"/>
+      <c r="AH1" s="391" t="s">
         <v>80</v>
       </c>
-      <c r="AI1" s="392"/>
-      <c r="AJ1" s="392"/>
-      <c r="AK1" s="392"/>
-      <c r="AL1" s="391" t="s">
+      <c r="AI1" s="391"/>
+      <c r="AJ1" s="391"/>
+      <c r="AK1" s="391"/>
+      <c r="AL1" s="390" t="s">
         <v>81</v>
       </c>
-      <c r="AM1" s="391"/>
-      <c r="AN1" s="391"/>
-      <c r="AO1" s="391"/>
-      <c r="AP1" s="392" t="s">
+      <c r="AM1" s="390"/>
+      <c r="AN1" s="390"/>
+      <c r="AO1" s="390"/>
+      <c r="AP1" s="391" t="s">
         <v>82</v>
       </c>
-      <c r="AQ1" s="392"/>
-      <c r="AR1" s="392"/>
-      <c r="AS1" s="392"/>
-      <c r="AT1" s="391" t="s">
+      <c r="AQ1" s="391"/>
+      <c r="AR1" s="391"/>
+      <c r="AS1" s="391"/>
+      <c r="AT1" s="390" t="s">
         <v>83</v>
       </c>
-      <c r="AU1" s="391"/>
-      <c r="AV1" s="391"/>
-      <c r="AW1" s="391"/>
-      <c r="AX1" s="392" t="s">
+      <c r="AU1" s="390"/>
+      <c r="AV1" s="390"/>
+      <c r="AW1" s="390"/>
+      <c r="AX1" s="391" t="s">
         <v>84</v>
       </c>
-      <c r="AY1" s="392"/>
-      <c r="AZ1" s="392"/>
-      <c r="BA1" s="392"/>
-      <c r="BB1" s="391" t="s">
+      <c r="AY1" s="391"/>
+      <c r="AZ1" s="391"/>
+      <c r="BA1" s="391"/>
+      <c r="BB1" s="390" t="s">
         <v>85</v>
       </c>
-      <c r="BC1" s="391"/>
-      <c r="BD1" s="391"/>
-      <c r="BE1" s="391"/>
-      <c r="BF1" s="392" t="s">
+      <c r="BC1" s="390"/>
+      <c r="BD1" s="390"/>
+      <c r="BE1" s="390"/>
+      <c r="BF1" s="391" t="s">
         <v>86</v>
       </c>
-      <c r="BG1" s="392"/>
-      <c r="BH1" s="392"/>
-      <c r="BI1" s="392"/>
-      <c r="BJ1" s="391" t="s">
+      <c r="BG1" s="391"/>
+      <c r="BH1" s="391"/>
+      <c r="BI1" s="391"/>
+      <c r="BJ1" s="390" t="s">
         <v>87</v>
       </c>
-      <c r="BK1" s="391"/>
-      <c r="BL1" s="391"/>
-      <c r="BM1" s="391"/>
-      <c r="BN1" s="392" t="s">
+      <c r="BK1" s="390"/>
+      <c r="BL1" s="390"/>
+      <c r="BM1" s="390"/>
+      <c r="BN1" s="391" t="s">
         <v>88</v>
       </c>
-      <c r="BO1" s="392"/>
-      <c r="BP1" s="392"/>
-      <c r="BQ1" s="392"/>
-      <c r="BR1" s="391" t="s">
+      <c r="BO1" s="391"/>
+      <c r="BP1" s="391"/>
+      <c r="BQ1" s="391"/>
+      <c r="BR1" s="390" t="s">
         <v>497</v>
       </c>
-      <c r="BS1" s="391"/>
-      <c r="BT1" s="391"/>
-      <c r="BU1" s="391"/>
+      <c r="BS1" s="390"/>
+      <c r="BT1" s="390"/>
+      <c r="BU1" s="390"/>
     </row>
     <row r="2" spans="1:73" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -54850,25 +54844,25 @@
     </row>
     <row r="4" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="118"/>
-      <c r="B4" s="381"/>
-      <c r="C4" s="381"/>
-      <c r="D4" s="381"/>
-      <c r="E4" s="381"/>
-      <c r="F4" s="381"/>
-      <c r="G4" s="381"/>
-      <c r="H4" s="381"/>
-      <c r="I4" s="381"/>
-      <c r="J4" s="381"/>
-      <c r="K4" s="381"/>
-      <c r="L4" s="381"/>
-      <c r="M4" s="381"/>
-      <c r="N4" s="381"/>
-      <c r="O4" s="381"/>
-      <c r="P4" s="381"/>
-      <c r="Q4" s="381"/>
-      <c r="R4" s="381"/>
-      <c r="S4" s="381"/>
-      <c r="T4" s="381"/>
+      <c r="B4" s="412"/>
+      <c r="C4" s="412"/>
+      <c r="D4" s="412"/>
+      <c r="E4" s="412"/>
+      <c r="F4" s="412"/>
+      <c r="G4" s="412"/>
+      <c r="H4" s="412"/>
+      <c r="I4" s="412"/>
+      <c r="J4" s="412"/>
+      <c r="K4" s="412"/>
+      <c r="L4" s="412"/>
+      <c r="M4" s="412"/>
+      <c r="N4" s="412"/>
+      <c r="O4" s="412"/>
+      <c r="P4" s="412"/>
+      <c r="Q4" s="412"/>
+      <c r="R4" s="412"/>
+      <c r="S4" s="412"/>
+      <c r="T4" s="412"/>
       <c r="U4" s="121"/>
       <c r="V4" s="122"/>
       <c r="W4" s="122"/>
@@ -54925,25 +54919,25 @@
     </row>
     <row r="5" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="118"/>
-      <c r="B5" s="381"/>
-      <c r="C5" s="381"/>
-      <c r="D5" s="381"/>
-      <c r="E5" s="381"/>
-      <c r="F5" s="381"/>
-      <c r="G5" s="381"/>
-      <c r="H5" s="381"/>
-      <c r="I5" s="381"/>
-      <c r="J5" s="381"/>
-      <c r="K5" s="381"/>
-      <c r="L5" s="381"/>
-      <c r="M5" s="381"/>
-      <c r="N5" s="381"/>
-      <c r="O5" s="381"/>
-      <c r="P5" s="381"/>
-      <c r="Q5" s="381"/>
-      <c r="R5" s="381"/>
-      <c r="S5" s="381"/>
-      <c r="T5" s="381"/>
+      <c r="B5" s="412"/>
+      <c r="C5" s="412"/>
+      <c r="D5" s="412"/>
+      <c r="E5" s="412"/>
+      <c r="F5" s="412"/>
+      <c r="G5" s="412"/>
+      <c r="H5" s="412"/>
+      <c r="I5" s="412"/>
+      <c r="J5" s="412"/>
+      <c r="K5" s="412"/>
+      <c r="L5" s="412"/>
+      <c r="M5" s="412"/>
+      <c r="N5" s="412"/>
+      <c r="O5" s="412"/>
+      <c r="P5" s="412"/>
+      <c r="Q5" s="412"/>
+      <c r="R5" s="412"/>
+      <c r="S5" s="412"/>
+      <c r="T5" s="412"/>
       <c r="U5" s="121"/>
       <c r="V5" s="122"/>
       <c r="W5" s="122"/>
@@ -55000,25 +54994,25 @@
     </row>
     <row r="6" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="118"/>
-      <c r="B6" s="381"/>
-      <c r="C6" s="381"/>
-      <c r="D6" s="381"/>
-      <c r="E6" s="381"/>
-      <c r="F6" s="381"/>
-      <c r="G6" s="381"/>
-      <c r="H6" s="381"/>
-      <c r="I6" s="381"/>
-      <c r="J6" s="381"/>
-      <c r="K6" s="381"/>
-      <c r="L6" s="381"/>
-      <c r="M6" s="381"/>
-      <c r="N6" s="381"/>
-      <c r="O6" s="381"/>
-      <c r="P6" s="381"/>
-      <c r="Q6" s="381"/>
-      <c r="R6" s="381"/>
-      <c r="S6" s="381"/>
-      <c r="T6" s="381"/>
+      <c r="B6" s="412"/>
+      <c r="C6" s="412"/>
+      <c r="D6" s="412"/>
+      <c r="E6" s="412"/>
+      <c r="F6" s="412"/>
+      <c r="G6" s="412"/>
+      <c r="H6" s="412"/>
+      <c r="I6" s="412"/>
+      <c r="J6" s="412"/>
+      <c r="K6" s="412"/>
+      <c r="L6" s="412"/>
+      <c r="M6" s="412"/>
+      <c r="N6" s="412"/>
+      <c r="O6" s="412"/>
+      <c r="P6" s="412"/>
+      <c r="Q6" s="412"/>
+      <c r="R6" s="412"/>
+      <c r="S6" s="412"/>
+      <c r="T6" s="412"/>
       <c r="U6" s="121"/>
       <c r="V6" s="122"/>
       <c r="W6" s="122"/>
@@ -55075,25 +55069,25 @@
     </row>
     <row r="7" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="118"/>
-      <c r="B7" s="381"/>
-      <c r="C7" s="381"/>
-      <c r="D7" s="381"/>
-      <c r="E7" s="381"/>
-      <c r="F7" s="381"/>
-      <c r="G7" s="381"/>
-      <c r="H7" s="381"/>
-      <c r="I7" s="381"/>
-      <c r="J7" s="381"/>
-      <c r="K7" s="381"/>
-      <c r="L7" s="381"/>
-      <c r="M7" s="381"/>
-      <c r="N7" s="381"/>
-      <c r="O7" s="381"/>
-      <c r="P7" s="381"/>
-      <c r="Q7" s="381"/>
-      <c r="R7" s="381"/>
-      <c r="S7" s="381"/>
-      <c r="T7" s="381"/>
+      <c r="B7" s="412"/>
+      <c r="C7" s="412"/>
+      <c r="D7" s="412"/>
+      <c r="E7" s="412"/>
+      <c r="F7" s="412"/>
+      <c r="G7" s="412"/>
+      <c r="H7" s="412"/>
+      <c r="I7" s="412"/>
+      <c r="J7" s="412"/>
+      <c r="K7" s="412"/>
+      <c r="L7" s="412"/>
+      <c r="M7" s="412"/>
+      <c r="N7" s="412"/>
+      <c r="O7" s="412"/>
+      <c r="P7" s="412"/>
+      <c r="Q7" s="412"/>
+      <c r="R7" s="412"/>
+      <c r="S7" s="412"/>
+      <c r="T7" s="412"/>
       <c r="U7" s="121"/>
       <c r="V7" s="122"/>
       <c r="W7" s="122"/>
@@ -55150,25 +55144,25 @@
     </row>
     <row r="8" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="118"/>
-      <c r="B8" s="381"/>
-      <c r="C8" s="381"/>
-      <c r="D8" s="381"/>
-      <c r="E8" s="381"/>
-      <c r="F8" s="381"/>
-      <c r="G8" s="381"/>
-      <c r="H8" s="381"/>
-      <c r="I8" s="381"/>
-      <c r="J8" s="381"/>
-      <c r="K8" s="381"/>
-      <c r="L8" s="381"/>
-      <c r="M8" s="381"/>
-      <c r="N8" s="381"/>
-      <c r="O8" s="381"/>
-      <c r="P8" s="381"/>
-      <c r="Q8" s="381"/>
-      <c r="R8" s="381"/>
-      <c r="S8" s="381"/>
-      <c r="T8" s="381"/>
+      <c r="B8" s="412"/>
+      <c r="C8" s="412"/>
+      <c r="D8" s="412"/>
+      <c r="E8" s="412"/>
+      <c r="F8" s="412"/>
+      <c r="G8" s="412"/>
+      <c r="H8" s="412"/>
+      <c r="I8" s="412"/>
+      <c r="J8" s="412"/>
+      <c r="K8" s="412"/>
+      <c r="L8" s="412"/>
+      <c r="M8" s="412"/>
+      <c r="N8" s="412"/>
+      <c r="O8" s="412"/>
+      <c r="P8" s="412"/>
+      <c r="Q8" s="412"/>
+      <c r="R8" s="412"/>
+      <c r="S8" s="412"/>
+      <c r="T8" s="412"/>
       <c r="U8" s="121"/>
       <c r="V8" s="122"/>
       <c r="W8" s="122"/>
@@ -55225,25 +55219,25 @@
     </row>
     <row r="9" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="118"/>
-      <c r="B9" s="381"/>
-      <c r="C9" s="381"/>
-      <c r="D9" s="381"/>
-      <c r="E9" s="381"/>
-      <c r="F9" s="381"/>
-      <c r="G9" s="381"/>
-      <c r="H9" s="381"/>
-      <c r="I9" s="381"/>
-      <c r="J9" s="381"/>
-      <c r="K9" s="381"/>
-      <c r="L9" s="381"/>
-      <c r="M9" s="381"/>
-      <c r="N9" s="381"/>
-      <c r="O9" s="381"/>
-      <c r="P9" s="381"/>
-      <c r="Q9" s="381"/>
-      <c r="R9" s="381"/>
-      <c r="S9" s="381"/>
-      <c r="T9" s="381"/>
+      <c r="B9" s="412"/>
+      <c r="C9" s="412"/>
+      <c r="D9" s="412"/>
+      <c r="E9" s="412"/>
+      <c r="F9" s="412"/>
+      <c r="G9" s="412"/>
+      <c r="H9" s="412"/>
+      <c r="I9" s="412"/>
+      <c r="J9" s="412"/>
+      <c r="K9" s="412"/>
+      <c r="L9" s="412"/>
+      <c r="M9" s="412"/>
+      <c r="N9" s="412"/>
+      <c r="O9" s="412"/>
+      <c r="P9" s="412"/>
+      <c r="Q9" s="412"/>
+      <c r="R9" s="412"/>
+      <c r="S9" s="412"/>
+      <c r="T9" s="412"/>
       <c r="U9" s="121"/>
       <c r="V9" s="122"/>
       <c r="W9" s="122"/>
@@ -55901,7 +55895,7 @@
     <row r="18" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A18" s="118"/>
       <c r="B18" s="117"/>
-      <c r="C18" s="382"/>
+      <c r="C18" s="381"/>
       <c r="D18" s="118"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
@@ -57125,7 +57119,7 @@
       <c r="X34" s="122"/>
       <c r="Y34" s="122"/>
       <c r="Z34" s="24"/>
-      <c r="AA34" s="383"/>
+      <c r="AA34" s="382"/>
       <c r="AB34" s="77"/>
       <c r="AC34" s="77"/>
       <c r="AD34" s="88"/>
@@ -57303,7 +57297,7 @@
       <c r="X36" s="122"/>
       <c r="Y36" s="122"/>
       <c r="Z36" s="24"/>
-      <c r="AA36" s="383"/>
+      <c r="AA36" s="382"/>
       <c r="AB36" s="77"/>
       <c r="AC36" s="77"/>
       <c r="AD36" s="88"/>
@@ -57453,7 +57447,7 @@
       <c r="X38" s="122"/>
       <c r="Y38" s="122"/>
       <c r="Z38" s="24"/>
-      <c r="AA38" s="383"/>
+      <c r="AA38" s="382"/>
       <c r="AB38" s="77"/>
       <c r="AC38" s="77"/>
       <c r="AD38" s="88"/>
@@ -57577,7 +57571,7 @@
     <row r="40" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A40" s="118"/>
       <c r="B40" s="117"/>
-      <c r="C40" s="382"/>
+      <c r="C40" s="381"/>
       <c r="D40" s="118"/>
       <c r="E40" s="24"/>
       <c r="F40" s="24"/>
@@ -57724,7 +57718,7 @@
     <row r="42" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A42" s="118"/>
       <c r="B42" s="117"/>
-      <c r="C42" s="382"/>
+      <c r="C42" s="381"/>
       <c r="D42" s="118"/>
       <c r="E42" s="24"/>
       <c r="F42" s="24"/>
@@ -58570,7 +58564,7 @@
       <c r="X53" s="122"/>
       <c r="Y53" s="122"/>
       <c r="Z53" s="24"/>
-      <c r="AA53" s="383"/>
+      <c r="AA53" s="382"/>
       <c r="AB53" s="100"/>
       <c r="AC53" s="103"/>
       <c r="AD53" s="89"/>
@@ -58645,7 +58639,7 @@
       <c r="X54" s="122"/>
       <c r="Y54" s="122"/>
       <c r="Z54" s="24"/>
-      <c r="AA54" s="383"/>
+      <c r="AA54" s="382"/>
       <c r="AB54" s="100"/>
       <c r="AC54" s="103"/>
       <c r="AD54" s="89"/>
@@ -67592,6 +67586,12 @@
   </sheetData>
   <autoFilter ref="A2:BQ178" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="15">
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:U1"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="BN1:BQ1"/>
     <mergeCell ref="BR1:BU1"/>
@@ -67601,12 +67601,6 @@
     <mergeCell ref="AX1:BA1"/>
     <mergeCell ref="BB1:BE1"/>
     <mergeCell ref="BF1:BI1"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:U1"/>
-    <mergeCell ref="V1:Y1"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="AD1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -67736,97 +67730,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A1" s="392" t="s">
+      <c r="A1" s="391" t="s">
         <v>492</v>
       </c>
-      <c r="B1" s="392"/>
-      <c r="C1" s="392"/>
-      <c r="D1" s="392"/>
-      <c r="E1" s="393" t="s">
+      <c r="B1" s="391"/>
+      <c r="C1" s="391"/>
+      <c r="D1" s="391"/>
+      <c r="E1" s="392" t="s">
         <v>493</v>
       </c>
-      <c r="F1" s="394"/>
-      <c r="G1" s="394"/>
-      <c r="H1" s="394"/>
-      <c r="I1" s="394"/>
-      <c r="J1" s="394"/>
-      <c r="K1" s="394"/>
-      <c r="L1" s="394"/>
-      <c r="M1" s="394"/>
-      <c r="N1" s="394"/>
-      <c r="O1" s="395"/>
-      <c r="P1" s="402" t="s">
+      <c r="F1" s="393"/>
+      <c r="G1" s="393"/>
+      <c r="H1" s="393"/>
+      <c r="I1" s="393"/>
+      <c r="J1" s="393"/>
+      <c r="K1" s="393"/>
+      <c r="L1" s="393"/>
+      <c r="M1" s="393"/>
+      <c r="N1" s="393"/>
+      <c r="O1" s="394"/>
+      <c r="P1" s="401" t="s">
         <v>77</v>
       </c>
-      <c r="Q1" s="402"/>
-      <c r="R1" s="402"/>
-      <c r="S1" s="402"/>
-      <c r="T1" s="393" t="s">
+      <c r="Q1" s="401"/>
+      <c r="R1" s="401"/>
+      <c r="S1" s="401"/>
+      <c r="T1" s="392" t="s">
         <v>78</v>
       </c>
-      <c r="U1" s="394"/>
-      <c r="V1" s="394"/>
-      <c r="W1" s="394"/>
-      <c r="X1" s="402" t="s">
+      <c r="U1" s="393"/>
+      <c r="V1" s="393"/>
+      <c r="W1" s="393"/>
+      <c r="X1" s="401" t="s">
         <v>79</v>
       </c>
-      <c r="Y1" s="402"/>
-      <c r="Z1" s="402"/>
-      <c r="AA1" s="402"/>
-      <c r="AB1" s="393" t="s">
+      <c r="Y1" s="401"/>
+      <c r="Z1" s="401"/>
+      <c r="AA1" s="401"/>
+      <c r="AB1" s="392" t="s">
         <v>80</v>
       </c>
-      <c r="AC1" s="394"/>
-      <c r="AD1" s="394"/>
-      <c r="AE1" s="394"/>
-      <c r="AF1" s="402" t="s">
+      <c r="AC1" s="393"/>
+      <c r="AD1" s="393"/>
+      <c r="AE1" s="393"/>
+      <c r="AF1" s="401" t="s">
         <v>81</v>
       </c>
-      <c r="AG1" s="402"/>
-      <c r="AH1" s="402"/>
-      <c r="AI1" s="402"/>
-      <c r="AJ1" s="393" t="s">
+      <c r="AG1" s="401"/>
+      <c r="AH1" s="401"/>
+      <c r="AI1" s="401"/>
+      <c r="AJ1" s="392" t="s">
         <v>82</v>
       </c>
-      <c r="AK1" s="394"/>
-      <c r="AL1" s="394"/>
-      <c r="AM1" s="394"/>
-      <c r="AN1" s="402" t="s">
+      <c r="AK1" s="393"/>
+      <c r="AL1" s="393"/>
+      <c r="AM1" s="393"/>
+      <c r="AN1" s="401" t="s">
         <v>83</v>
       </c>
-      <c r="AO1" s="402"/>
-      <c r="AP1" s="402"/>
-      <c r="AQ1" s="402"/>
-      <c r="AR1" s="393" t="s">
+      <c r="AO1" s="401"/>
+      <c r="AP1" s="401"/>
+      <c r="AQ1" s="401"/>
+      <c r="AR1" s="392" t="s">
         <v>84</v>
       </c>
-      <c r="AS1" s="394"/>
-      <c r="AT1" s="394"/>
-      <c r="AU1" s="394"/>
-      <c r="AV1" s="402" t="s">
+      <c r="AS1" s="393"/>
+      <c r="AT1" s="393"/>
+      <c r="AU1" s="393"/>
+      <c r="AV1" s="401" t="s">
         <v>85</v>
       </c>
-      <c r="AW1" s="402"/>
-      <c r="AX1" s="402"/>
-      <c r="AY1" s="402"/>
-      <c r="AZ1" s="393" t="s">
+      <c r="AW1" s="401"/>
+      <c r="AX1" s="401"/>
+      <c r="AY1" s="401"/>
+      <c r="AZ1" s="392" t="s">
         <v>86</v>
       </c>
-      <c r="BA1" s="394"/>
-      <c r="BB1" s="394"/>
-      <c r="BC1" s="394"/>
-      <c r="BD1" s="402" t="s">
+      <c r="BA1" s="393"/>
+      <c r="BB1" s="393"/>
+      <c r="BC1" s="393"/>
+      <c r="BD1" s="401" t="s">
         <v>87</v>
       </c>
-      <c r="BE1" s="402"/>
-      <c r="BF1" s="402"/>
-      <c r="BG1" s="402"/>
-      <c r="BH1" s="393" t="s">
+      <c r="BE1" s="401"/>
+      <c r="BF1" s="401"/>
+      <c r="BG1" s="401"/>
+      <c r="BH1" s="392" t="s">
         <v>88</v>
       </c>
-      <c r="BI1" s="394"/>
-      <c r="BJ1" s="394"/>
-      <c r="BK1" s="394"/>
+      <c r="BI1" s="393"/>
+      <c r="BJ1" s="393"/>
+      <c r="BK1" s="393"/>
     </row>
     <row r="2" spans="1:63" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -75806,7 +75800,7 @@
       <c r="B2" s="326" t="s">
         <v>553</v>
       </c>
-      <c r="C2" s="403" t="s">
+      <c r="C2" s="402" t="s">
         <v>361</v>
       </c>
       <c r="D2" s="146" t="s">
@@ -75820,7 +75814,7 @@
       <c r="B3" s="327" t="s">
         <v>554</v>
       </c>
-      <c r="C3" s="404"/>
+      <c r="C3" s="403"/>
       <c r="D3" s="139" t="s">
         <v>363</v>
       </c>
@@ -75832,7 +75826,7 @@
       <c r="B4" s="327" t="s">
         <v>555</v>
       </c>
-      <c r="C4" s="404"/>
+      <c r="C4" s="403"/>
       <c r="D4" s="139" t="s">
         <v>10</v>
       </c>
@@ -75844,7 +75838,7 @@
       <c r="B5" s="327" t="s">
         <v>556</v>
       </c>
-      <c r="C5" s="404"/>
+      <c r="C5" s="403"/>
       <c r="D5" s="139" t="s">
         <v>10</v>
       </c>
@@ -75856,7 +75850,7 @@
       <c r="B6" s="327" t="s">
         <v>557</v>
       </c>
-      <c r="C6" s="404"/>
+      <c r="C6" s="403"/>
       <c r="D6" s="139" t="s">
         <v>10</v>
       </c>
@@ -75868,7 +75862,7 @@
       <c r="B7" s="327" t="s">
         <v>558</v>
       </c>
-      <c r="C7" s="404"/>
+      <c r="C7" s="403"/>
       <c r="D7" s="139" t="s">
         <v>10</v>
       </c>
@@ -75880,7 +75874,7 @@
       <c r="B8" s="327" t="s">
         <v>559</v>
       </c>
-      <c r="C8" s="404"/>
+      <c r="C8" s="403"/>
       <c r="D8" s="139" t="s">
         <v>10</v>
       </c>
@@ -75892,7 +75886,7 @@
       <c r="B9" s="327" t="s">
         <v>560</v>
       </c>
-      <c r="C9" s="404"/>
+      <c r="C9" s="403"/>
       <c r="D9" s="139" t="s">
         <v>10</v>
       </c>
@@ -75904,7 +75898,7 @@
       <c r="B10" s="327" t="s">
         <v>562</v>
       </c>
-      <c r="C10" s="404"/>
+      <c r="C10" s="403"/>
       <c r="D10" s="139" t="s">
         <v>10</v>
       </c>
@@ -75916,7 +75910,7 @@
       <c r="B11" s="205" t="s">
         <v>561</v>
       </c>
-      <c r="C11" s="405"/>
+      <c r="C11" s="404"/>
       <c r="D11" s="143" t="s">
         <v>10</v>
       </c>
@@ -75928,7 +75922,7 @@
       <c r="B12" s="129" t="s">
         <v>563</v>
       </c>
-      <c r="C12" s="403" t="s">
+      <c r="C12" s="402" t="s">
         <v>364</v>
       </c>
       <c r="D12" s="146" t="s">
@@ -75942,7 +75936,7 @@
       <c r="B13" s="130" t="s">
         <v>564</v>
       </c>
-      <c r="C13" s="404"/>
+      <c r="C13" s="403"/>
       <c r="D13" s="139" t="s">
         <v>366</v>
       </c>
@@ -75954,7 +75948,7 @@
       <c r="B14" s="130" t="s">
         <v>565</v>
       </c>
-      <c r="C14" s="404"/>
+      <c r="C14" s="403"/>
       <c r="D14" s="139" t="s">
         <v>10</v>
       </c>
@@ -75966,7 +75960,7 @@
       <c r="B15" s="130" t="s">
         <v>566</v>
       </c>
-      <c r="C15" s="404"/>
+      <c r="C15" s="403"/>
       <c r="D15" s="139" t="s">
         <v>10</v>
       </c>
@@ -75978,7 +75972,7 @@
       <c r="B16" s="130" t="s">
         <v>567</v>
       </c>
-      <c r="C16" s="404"/>
+      <c r="C16" s="403"/>
       <c r="D16" s="139" t="s">
         <v>10</v>
       </c>
@@ -75990,7 +75984,7 @@
       <c r="B17" s="131" t="s">
         <v>568</v>
       </c>
-      <c r="C17" s="405"/>
+      <c r="C17" s="404"/>
       <c r="D17" s="143" t="s">
         <v>10</v>
       </c>
@@ -76002,7 +75996,7 @@
       <c r="B18" s="132" t="s">
         <v>569</v>
       </c>
-      <c r="C18" s="403" t="s">
+      <c r="C18" s="402" t="s">
         <v>107</v>
       </c>
       <c r="D18" s="146" t="s">
@@ -76016,7 +76010,7 @@
       <c r="B19" s="134" t="s">
         <v>570</v>
       </c>
-      <c r="C19" s="404"/>
+      <c r="C19" s="403"/>
       <c r="D19" s="139" t="s">
         <v>368</v>
       </c>
@@ -76028,7 +76022,7 @@
       <c r="B20" s="133" t="s">
         <v>571</v>
       </c>
-      <c r="C20" s="404"/>
+      <c r="C20" s="403"/>
       <c r="D20" s="139" t="s">
         <v>369</v>
       </c>
@@ -76040,7 +76034,7 @@
       <c r="B21" s="133" t="s">
         <v>572</v>
       </c>
-      <c r="C21" s="404"/>
+      <c r="C21" s="403"/>
       <c r="D21" s="139" t="s">
         <v>370</v>
       </c>
@@ -76052,7 +76046,7 @@
       <c r="B22" s="133" t="s">
         <v>573</v>
       </c>
-      <c r="C22" s="404"/>
+      <c r="C22" s="403"/>
       <c r="D22" s="139" t="s">
         <v>371</v>
       </c>
@@ -76064,7 +76058,7 @@
       <c r="B23" s="133" t="s">
         <v>574</v>
       </c>
-      <c r="C23" s="404"/>
+      <c r="C23" s="403"/>
       <c r="D23" s="139" t="s">
         <v>372</v>
       </c>
@@ -76076,7 +76070,7 @@
       <c r="B24" s="133" t="s">
         <v>575</v>
       </c>
-      <c r="C24" s="404"/>
+      <c r="C24" s="403"/>
       <c r="D24" s="139" t="s">
         <v>10</v>
       </c>
@@ -76088,7 +76082,7 @@
       <c r="B25" s="133" t="s">
         <v>576</v>
       </c>
-      <c r="C25" s="404"/>
+      <c r="C25" s="403"/>
       <c r="D25" s="139" t="s">
         <v>373</v>
       </c>
@@ -76100,7 +76094,7 @@
       <c r="B26" s="133" t="s">
         <v>577</v>
       </c>
-      <c r="C26" s="404"/>
+      <c r="C26" s="403"/>
       <c r="D26" s="139" t="s">
         <v>10</v>
       </c>
@@ -76112,7 +76106,7 @@
       <c r="B27" s="134" t="s">
         <v>637</v>
       </c>
-      <c r="C27" s="404"/>
+      <c r="C27" s="403"/>
       <c r="D27" s="139" t="s">
         <v>374</v>
       </c>
@@ -76124,7 +76118,7 @@
       <c r="B28" s="134" t="s">
         <v>638</v>
       </c>
-      <c r="C28" s="405"/>
+      <c r="C28" s="404"/>
       <c r="D28" s="139" t="s">
         <v>375</v>
       </c>
@@ -76136,7 +76130,7 @@
       <c r="B29" s="136" t="s">
         <v>578</v>
       </c>
-      <c r="C29" s="403" t="s">
+      <c r="C29" s="402" t="s">
         <v>376</v>
       </c>
       <c r="D29" s="146" t="s">
@@ -76150,7 +76144,7 @@
       <c r="B30" s="137" t="s">
         <v>579</v>
       </c>
-      <c r="C30" s="404"/>
+      <c r="C30" s="403"/>
       <c r="D30" s="139" t="s">
         <v>489</v>
       </c>
@@ -76162,7 +76156,7 @@
       <c r="B31" s="138" t="s">
         <v>580</v>
       </c>
-      <c r="C31" s="404"/>
+      <c r="C31" s="403"/>
       <c r="D31" s="139" t="s">
         <v>378</v>
       </c>
@@ -76174,7 +76168,7 @@
       <c r="B32" s="138" t="s">
         <v>581</v>
       </c>
-      <c r="C32" s="404"/>
+      <c r="C32" s="403"/>
       <c r="D32" s="139" t="s">
         <v>379</v>
       </c>
@@ -76186,7 +76180,7 @@
       <c r="B33" s="138" t="s">
         <v>582</v>
       </c>
-      <c r="C33" s="404"/>
+      <c r="C33" s="403"/>
       <c r="D33" s="139" t="s">
         <v>380</v>
       </c>
@@ -76198,7 +76192,7 @@
       <c r="B34" s="137" t="s">
         <v>583</v>
       </c>
-      <c r="C34" s="404"/>
+      <c r="C34" s="403"/>
       <c r="D34" s="139" t="s">
         <v>381</v>
       </c>
@@ -76210,7 +76204,7 @@
       <c r="B35" s="138" t="s">
         <v>584</v>
       </c>
-      <c r="C35" s="404"/>
+      <c r="C35" s="403"/>
       <c r="D35" s="139" t="s">
         <v>382</v>
       </c>
@@ -76222,7 +76216,7 @@
       <c r="B36" s="137" t="s">
         <v>585</v>
       </c>
-      <c r="C36" s="404"/>
+      <c r="C36" s="403"/>
       <c r="D36" s="139" t="s">
         <v>382</v>
       </c>
@@ -76234,7 +76228,7 @@
       <c r="B37" s="138" t="s">
         <v>586</v>
       </c>
-      <c r="C37" s="404"/>
+      <c r="C37" s="403"/>
       <c r="D37" s="139" t="s">
         <v>383</v>
       </c>
@@ -76246,7 +76240,7 @@
       <c r="B38" s="137" t="s">
         <v>587</v>
       </c>
-      <c r="C38" s="404"/>
+      <c r="C38" s="403"/>
       <c r="D38" s="139" t="s">
         <v>383</v>
       </c>
@@ -76258,7 +76252,7 @@
       <c r="B39" s="138" t="s">
         <v>588</v>
       </c>
-      <c r="C39" s="404"/>
+      <c r="C39" s="403"/>
       <c r="D39" s="139" t="s">
         <v>485</v>
       </c>
@@ -76270,7 +76264,7 @@
       <c r="B40" s="137" t="s">
         <v>589</v>
       </c>
-      <c r="C40" s="404"/>
+      <c r="C40" s="403"/>
       <c r="D40" s="139" t="s">
         <v>384</v>
       </c>
@@ -76282,7 +76276,7 @@
       <c r="B41" s="138" t="s">
         <v>590</v>
       </c>
-      <c r="C41" s="404"/>
+      <c r="C41" s="403"/>
       <c r="D41" s="139" t="s">
         <v>385</v>
       </c>
@@ -76294,7 +76288,7 @@
       <c r="B42" s="137" t="s">
         <v>591</v>
       </c>
-      <c r="C42" s="404"/>
+      <c r="C42" s="403"/>
       <c r="D42" s="139" t="s">
         <v>386</v>
       </c>
@@ -76306,7 +76300,7 @@
       <c r="B43" s="141" t="s">
         <v>592</v>
       </c>
-      <c r="C43" s="405"/>
+      <c r="C43" s="404"/>
       <c r="D43" s="143" t="s">
         <v>387</v>
       </c>
@@ -76319,7 +76313,7 @@
       <c r="B44" s="145" t="s">
         <v>593</v>
       </c>
-      <c r="C44" s="403" t="s">
+      <c r="C44" s="402" t="s">
         <v>388</v>
       </c>
       <c r="D44" s="146" t="s">
@@ -76333,7 +76327,7 @@
       <c r="B45" s="147" t="s">
         <v>594</v>
       </c>
-      <c r="C45" s="404"/>
+      <c r="C45" s="403"/>
       <c r="D45" s="139" t="s">
         <v>10</v>
       </c>
@@ -76345,7 +76339,7 @@
       <c r="B46" s="147" t="s">
         <v>595</v>
       </c>
-      <c r="C46" s="404"/>
+      <c r="C46" s="403"/>
       <c r="D46" s="139" t="s">
         <v>389</v>
       </c>
@@ -76357,7 +76351,7 @@
       <c r="B47" s="147" t="s">
         <v>596</v>
       </c>
-      <c r="C47" s="404"/>
+      <c r="C47" s="403"/>
       <c r="D47" s="139" t="s">
         <v>390</v>
       </c>
@@ -76369,7 +76363,7 @@
       <c r="B48" s="147" t="s">
         <v>597</v>
       </c>
-      <c r="C48" s="404"/>
+      <c r="C48" s="403"/>
       <c r="D48" s="139" t="s">
         <v>10</v>
       </c>
@@ -76381,7 +76375,7 @@
       <c r="B49" s="147" t="s">
         <v>598</v>
       </c>
-      <c r="C49" s="404"/>
+      <c r="C49" s="403"/>
       <c r="D49" s="139" t="s">
         <v>391</v>
       </c>
@@ -76393,7 +76387,7 @@
       <c r="B50" s="147" t="s">
         <v>599</v>
       </c>
-      <c r="C50" s="404"/>
+      <c r="C50" s="403"/>
       <c r="D50" s="139" t="s">
         <v>10</v>
       </c>
@@ -76405,7 +76399,7 @@
       <c r="B51" s="147" t="s">
         <v>600</v>
       </c>
-      <c r="C51" s="404"/>
+      <c r="C51" s="403"/>
       <c r="D51" s="139" t="s">
         <v>490</v>
       </c>
@@ -76417,7 +76411,7 @@
       <c r="B52" s="147" t="s">
         <v>601</v>
       </c>
-      <c r="C52" s="404"/>
+      <c r="C52" s="403"/>
       <c r="D52" s="139" t="s">
         <v>390</v>
       </c>
@@ -76429,7 +76423,7 @@
       <c r="B53" s="148" t="s">
         <v>602</v>
       </c>
-      <c r="C53" s="405"/>
+      <c r="C53" s="404"/>
       <c r="D53" s="143" t="s">
         <v>10</v>
       </c>
@@ -76441,7 +76435,7 @@
       <c r="B54" s="149" t="s">
         <v>603</v>
       </c>
-      <c r="C54" s="403" t="s">
+      <c r="C54" s="402" t="s">
         <v>392</v>
       </c>
       <c r="D54" s="139" t="s">
@@ -76455,7 +76449,7 @@
       <c r="B55" s="149" t="s">
         <v>604</v>
       </c>
-      <c r="C55" s="404"/>
+      <c r="C55" s="403"/>
       <c r="D55" s="139" t="s">
         <v>394</v>
       </c>
@@ -76467,7 +76461,7 @@
       <c r="B56" s="149" t="s">
         <v>738</v>
       </c>
-      <c r="C56" s="404"/>
+      <c r="C56" s="403"/>
       <c r="D56" s="139" t="s">
         <v>395</v>
       </c>
@@ -76479,7 +76473,7 @@
       <c r="B57" s="149" t="s">
         <v>727</v>
       </c>
-      <c r="C57" s="405"/>
+      <c r="C57" s="404"/>
       <c r="D57" s="139" t="s">
         <v>396</v>
       </c>
@@ -76491,7 +76485,7 @@
       <c r="B58" s="194" t="s">
         <v>733</v>
       </c>
-      <c r="C58" s="403" t="s">
+      <c r="C58" s="402" t="s">
         <v>397</v>
       </c>
       <c r="D58" s="146" t="s">
@@ -76505,7 +76499,7 @@
       <c r="B59" s="236" t="s">
         <v>734</v>
       </c>
-      <c r="C59" s="404"/>
+      <c r="C59" s="403"/>
       <c r="D59" s="238" t="s">
         <v>542</v>
       </c>
@@ -76517,7 +76511,7 @@
       <c r="B60" s="150" t="s">
         <v>735</v>
       </c>
-      <c r="C60" s="405"/>
+      <c r="C60" s="404"/>
       <c r="D60" s="143" t="s">
         <v>488</v>
       </c>
@@ -76529,7 +76523,7 @@
       <c r="B61" s="151" t="s">
         <v>605</v>
       </c>
-      <c r="C61" s="403" t="s">
+      <c r="C61" s="402" t="s">
         <v>398</v>
       </c>
       <c r="D61" s="139" t="s">
@@ -76543,7 +76537,7 @@
       <c r="B62" s="151" t="s">
         <v>606</v>
       </c>
-      <c r="C62" s="404"/>
+      <c r="C62" s="403"/>
       <c r="D62" s="139" t="s">
         <v>400</v>
       </c>
@@ -76555,7 +76549,7 @@
       <c r="B63" s="151" t="s">
         <v>607</v>
       </c>
-      <c r="C63" s="404"/>
+      <c r="C63" s="403"/>
       <c r="D63" s="139" t="s">
         <v>401</v>
       </c>
@@ -76567,7 +76561,7 @@
       <c r="B64" s="151" t="s">
         <v>608</v>
       </c>
-      <c r="C64" s="404"/>
+      <c r="C64" s="403"/>
       <c r="D64" s="139" t="s">
         <v>402</v>
       </c>
@@ -76579,7 +76573,7 @@
       <c r="B65" s="151" t="s">
         <v>609</v>
       </c>
-      <c r="C65" s="404"/>
+      <c r="C65" s="403"/>
       <c r="D65" s="139" t="s">
         <v>403</v>
       </c>
@@ -76591,7 +76585,7 @@
       <c r="B66" s="151" t="s">
         <v>610</v>
       </c>
-      <c r="C66" s="404"/>
+      <c r="C66" s="403"/>
       <c r="D66" s="139" t="s">
         <v>404</v>
       </c>
@@ -76603,7 +76597,7 @@
       <c r="B67" s="151" t="s">
         <v>611</v>
       </c>
-      <c r="C67" s="404"/>
+      <c r="C67" s="403"/>
       <c r="D67" s="139" t="s">
         <v>405</v>
       </c>
@@ -76615,7 +76609,7 @@
       <c r="B68" s="151" t="s">
         <v>725</v>
       </c>
-      <c r="C68" s="404"/>
+      <c r="C68" s="403"/>
       <c r="D68" s="139" t="s">
         <v>498</v>
       </c>
@@ -76627,7 +76621,7 @@
       <c r="B69" s="201" t="s">
         <v>726</v>
       </c>
-      <c r="C69" s="404"/>
+      <c r="C69" s="403"/>
       <c r="D69" s="139" t="s">
         <v>499</v>
       </c>
@@ -76639,7 +76633,7 @@
       <c r="B70" s="152" t="s">
         <v>612</v>
       </c>
-      <c r="C70" s="405"/>
+      <c r="C70" s="404"/>
       <c r="D70" s="143" t="s">
         <v>406</v>
       </c>
@@ -76651,7 +76645,7 @@
       <c r="B71" s="154" t="s">
         <v>613</v>
       </c>
-      <c r="C71" s="403" t="s">
+      <c r="C71" s="402" t="s">
         <v>407</v>
       </c>
       <c r="D71" s="146" t="s">
@@ -76665,7 +76659,7 @@
       <c r="B72" s="155" t="s">
         <v>614</v>
       </c>
-      <c r="C72" s="404"/>
+      <c r="C72" s="403"/>
       <c r="D72" s="139" t="s">
         <v>10</v>
       </c>
@@ -76677,7 +76671,7 @@
       <c r="B73" s="155" t="s">
         <v>615</v>
       </c>
-      <c r="C73" s="404"/>
+      <c r="C73" s="403"/>
       <c r="D73" s="139" t="s">
         <v>10</v>
       </c>
@@ -76689,7 +76683,7 @@
       <c r="B74" s="155" t="s">
         <v>616</v>
       </c>
-      <c r="C74" s="404"/>
+      <c r="C74" s="403"/>
       <c r="D74" s="139" t="s">
         <v>10</v>
       </c>
@@ -76701,7 +76695,7 @@
       <c r="B75" s="155" t="s">
         <v>617</v>
       </c>
-      <c r="C75" s="404"/>
+      <c r="C75" s="403"/>
       <c r="D75" s="139" t="s">
         <v>10</v>
       </c>
@@ -76713,7 +76707,7 @@
       <c r="B76" s="155" t="s">
         <v>618</v>
       </c>
-      <c r="C76" s="404"/>
+      <c r="C76" s="403"/>
       <c r="D76" s="139" t="s">
         <v>409</v>
       </c>
@@ -76725,7 +76719,7 @@
       <c r="B77" s="155" t="s">
         <v>619</v>
       </c>
-      <c r="C77" s="404"/>
+      <c r="C77" s="403"/>
       <c r="D77" s="139" t="s">
         <v>10</v>
       </c>
@@ -76737,7 +76731,7 @@
       <c r="B78" s="155" t="s">
         <v>620</v>
       </c>
-      <c r="C78" s="404"/>
+      <c r="C78" s="403"/>
       <c r="D78" s="139" t="s">
         <v>10</v>
       </c>
@@ -76749,7 +76743,7 @@
       <c r="B79" s="155" t="s">
         <v>621</v>
       </c>
-      <c r="C79" s="404"/>
+      <c r="C79" s="403"/>
       <c r="D79" s="139" t="s">
         <v>10</v>
       </c>
@@ -76761,7 +76755,7 @@
       <c r="B80" s="155" t="s">
         <v>622</v>
       </c>
-      <c r="C80" s="404"/>
+      <c r="C80" s="403"/>
       <c r="D80" s="139" t="s">
         <v>10</v>
       </c>
@@ -76773,7 +76767,7 @@
       <c r="B81" s="155" t="s">
         <v>623</v>
       </c>
-      <c r="C81" s="404"/>
+      <c r="C81" s="403"/>
       <c r="D81" s="139" t="s">
         <v>10</v>
       </c>
@@ -76785,7 +76779,7 @@
       <c r="B82" s="155" t="s">
         <v>624</v>
       </c>
-      <c r="C82" s="404"/>
+      <c r="C82" s="403"/>
       <c r="D82" s="139" t="s">
         <v>409</v>
       </c>
@@ -76797,7 +76791,7 @@
       <c r="B83" s="155" t="s">
         <v>625</v>
       </c>
-      <c r="C83" s="404"/>
+      <c r="C83" s="403"/>
       <c r="D83" s="139" t="s">
         <v>10</v>
       </c>
@@ -76809,7 +76803,7 @@
       <c r="B84" s="155" t="s">
         <v>626</v>
       </c>
-      <c r="C84" s="404"/>
+      <c r="C84" s="403"/>
       <c r="D84" s="139" t="s">
         <v>10</v>
       </c>
@@ -76821,7 +76815,7 @@
       <c r="B85" s="156" t="s">
         <v>627</v>
       </c>
-      <c r="C85" s="404"/>
+      <c r="C85" s="403"/>
       <c r="D85" s="139" t="s">
         <v>10</v>
       </c>
@@ -76833,7 +76827,7 @@
       <c r="B86" s="156" t="s">
         <v>628</v>
       </c>
-      <c r="C86" s="404"/>
+      <c r="C86" s="403"/>
       <c r="D86" s="139" t="s">
         <v>10</v>
       </c>
@@ -76845,7 +76839,7 @@
       <c r="B87" s="156" t="s">
         <v>629</v>
       </c>
-      <c r="C87" s="404"/>
+      <c r="C87" s="403"/>
       <c r="D87" s="139" t="s">
         <v>10</v>
       </c>
@@ -76857,7 +76851,7 @@
       <c r="B88" s="156" t="s">
         <v>630</v>
       </c>
-      <c r="C88" s="404"/>
+      <c r="C88" s="403"/>
       <c r="D88" s="139" t="s">
         <v>409</v>
       </c>
@@ -76869,7 +76863,7 @@
       <c r="B89" s="156" t="s">
         <v>631</v>
       </c>
-      <c r="C89" s="404"/>
+      <c r="C89" s="403"/>
       <c r="D89" s="139" t="s">
         <v>410</v>
       </c>
@@ -76881,7 +76875,7 @@
       <c r="B90" s="157" t="s">
         <v>632</v>
       </c>
-      <c r="C90" s="404"/>
+      <c r="C90" s="403"/>
       <c r="D90" s="139" t="s">
         <v>411</v>
       </c>
@@ -76893,7 +76887,7 @@
       <c r="B91" s="157" t="s">
         <v>633</v>
       </c>
-      <c r="C91" s="404"/>
+      <c r="C91" s="403"/>
       <c r="D91" s="139" t="s">
         <v>412</v>
       </c>
@@ -76905,7 +76899,7 @@
       <c r="B92" s="157" t="s">
         <v>634</v>
       </c>
-      <c r="C92" s="404"/>
+      <c r="C92" s="403"/>
       <c r="D92" s="139" t="s">
         <v>413</v>
       </c>
@@ -76917,7 +76911,7 @@
       <c r="B93" s="157" t="s">
         <v>635</v>
       </c>
-      <c r="C93" s="404"/>
+      <c r="C93" s="403"/>
       <c r="D93" s="139" t="s">
         <v>414</v>
       </c>
@@ -76929,7 +76923,7 @@
       <c r="B94" s="159" t="s">
         <v>636</v>
       </c>
-      <c r="C94" s="405"/>
+      <c r="C94" s="404"/>
       <c r="D94" s="143" t="s">
         <v>415</v>
       </c>
@@ -76941,7 +76935,7 @@
       <c r="B95" s="160" t="s">
         <v>639</v>
       </c>
-      <c r="C95" s="403" t="s">
+      <c r="C95" s="402" t="s">
         <v>416</v>
       </c>
       <c r="D95" s="139" t="s">
@@ -76955,7 +76949,7 @@
       <c r="B96" s="160" t="s">
         <v>640</v>
       </c>
-      <c r="C96" s="404"/>
+      <c r="C96" s="403"/>
       <c r="D96" s="237" t="s">
         <v>418</v>
       </c>
@@ -76967,7 +76961,7 @@
       <c r="B97" s="160" t="s">
         <v>641</v>
       </c>
-      <c r="C97" s="404"/>
+      <c r="C97" s="403"/>
       <c r="D97" s="161" t="s">
         <v>419</v>
       </c>
@@ -76979,7 +76973,7 @@
       <c r="B98" s="162" t="s">
         <v>642</v>
       </c>
-      <c r="C98" s="405"/>
+      <c r="C98" s="404"/>
       <c r="D98" s="143" t="s">
         <v>420</v>
       </c>
@@ -76991,7 +76985,7 @@
       <c r="B99" s="145" t="s">
         <v>643</v>
       </c>
-      <c r="C99" s="403" t="s">
+      <c r="C99" s="402" t="s">
         <v>421</v>
       </c>
       <c r="D99" s="146" t="s">
@@ -77005,7 +76999,7 @@
       <c r="B100" s="147" t="s">
         <v>644</v>
       </c>
-      <c r="C100" s="404"/>
+      <c r="C100" s="403"/>
       <c r="D100" s="139" t="s">
         <v>423</v>
       </c>
@@ -77017,7 +77011,7 @@
       <c r="B101" s="147" t="s">
         <v>645</v>
       </c>
-      <c r="C101" s="404"/>
+      <c r="C101" s="403"/>
       <c r="D101" s="139" t="s">
         <v>424</v>
       </c>
@@ -77029,7 +77023,7 @@
       <c r="B102" s="147" t="s">
         <v>646</v>
       </c>
-      <c r="C102" s="404"/>
+      <c r="C102" s="403"/>
       <c r="D102" s="139" t="s">
         <v>425</v>
       </c>
@@ -77041,7 +77035,7 @@
       <c r="B103" s="147" t="s">
         <v>647</v>
       </c>
-      <c r="C103" s="404"/>
+      <c r="C103" s="403"/>
       <c r="D103" s="139" t="s">
         <v>426</v>
       </c>
@@ -77053,7 +77047,7 @@
       <c r="B104" s="147" t="s">
         <v>648</v>
       </c>
-      <c r="C104" s="404"/>
+      <c r="C104" s="403"/>
       <c r="D104" s="139" t="s">
         <v>482</v>
       </c>
@@ -77065,7 +77059,7 @@
       <c r="B105" s="147" t="s">
         <v>649</v>
       </c>
-      <c r="C105" s="404"/>
+      <c r="C105" s="403"/>
       <c r="D105" s="139" t="s">
         <v>500</v>
       </c>
@@ -77077,7 +77071,7 @@
       <c r="B106" s="147" t="s">
         <v>650</v>
       </c>
-      <c r="C106" s="404"/>
+      <c r="C106" s="403"/>
       <c r="D106" s="139" t="s">
         <v>501</v>
       </c>
@@ -77089,7 +77083,7 @@
       <c r="B107" s="147" t="s">
         <v>651</v>
       </c>
-      <c r="C107" s="404"/>
+      <c r="C107" s="403"/>
       <c r="D107" s="139" t="s">
         <v>502</v>
       </c>
@@ -77101,7 +77095,7 @@
       <c r="B108" s="147" t="s">
         <v>652</v>
       </c>
-      <c r="C108" s="405"/>
+      <c r="C108" s="404"/>
       <c r="D108" s="139" t="s">
         <v>503</v>
       </c>
@@ -77113,7 +77107,7 @@
       <c r="B109" s="164" t="s">
         <v>653</v>
       </c>
-      <c r="C109" s="403" t="s">
+      <c r="C109" s="402" t="s">
         <v>427</v>
       </c>
       <c r="D109" s="146" t="s">
@@ -77127,7 +77121,7 @@
       <c r="B110" s="165" t="s">
         <v>724</v>
       </c>
-      <c r="C110" s="404"/>
+      <c r="C110" s="403"/>
       <c r="D110" s="139" t="s">
         <v>541</v>
       </c>
@@ -77139,7 +77133,7 @@
       <c r="B111" s="165" t="s">
         <v>654</v>
       </c>
-      <c r="C111" s="404"/>
+      <c r="C111" s="403"/>
       <c r="D111" s="139" t="s">
         <v>428</v>
       </c>
@@ -77151,7 +77145,7 @@
       <c r="B112" s="165" t="s">
         <v>655</v>
       </c>
-      <c r="C112" s="404"/>
+      <c r="C112" s="403"/>
       <c r="D112" s="139" t="s">
         <v>429</v>
       </c>
@@ -77163,7 +77157,7 @@
       <c r="B113" s="165" t="s">
         <v>656</v>
       </c>
-      <c r="C113" s="404"/>
+      <c r="C113" s="403"/>
       <c r="D113" s="139" t="s">
         <v>429</v>
       </c>
@@ -77175,7 +77169,7 @@
       <c r="B114" s="165" t="s">
         <v>657</v>
       </c>
-      <c r="C114" s="404"/>
+      <c r="C114" s="403"/>
       <c r="D114" s="139" t="s">
         <v>430</v>
       </c>
@@ -77187,7 +77181,7 @@
       <c r="B115" s="167" t="s">
         <v>658</v>
       </c>
-      <c r="C115" s="405"/>
+      <c r="C115" s="404"/>
       <c r="D115" s="143" t="s">
         <v>430</v>
       </c>
@@ -77199,7 +77193,7 @@
       <c r="B116" s="168" t="s">
         <v>659</v>
       </c>
-      <c r="C116" s="403" t="s">
+      <c r="C116" s="402" t="s">
         <v>431</v>
       </c>
       <c r="D116" s="146" t="s">
@@ -77213,7 +77207,7 @@
       <c r="B117" s="169" t="s">
         <v>660</v>
       </c>
-      <c r="C117" s="404"/>
+      <c r="C117" s="403"/>
       <c r="D117" s="139" t="s">
         <v>10</v>
       </c>
@@ -77225,7 +77219,7 @@
       <c r="B118" s="169" t="s">
         <v>661</v>
       </c>
-      <c r="C118" s="404"/>
+      <c r="C118" s="403"/>
       <c r="D118" s="139" t="s">
         <v>10</v>
       </c>
@@ -77237,7 +77231,7 @@
       <c r="B119" s="169" t="s">
         <v>662</v>
       </c>
-      <c r="C119" s="404"/>
+      <c r="C119" s="403"/>
       <c r="D119" s="139" t="s">
         <v>10</v>
       </c>
@@ -77249,7 +77243,7 @@
       <c r="B120" s="169" t="s">
         <v>663</v>
       </c>
-      <c r="C120" s="404"/>
+      <c r="C120" s="403"/>
       <c r="D120" s="139" t="s">
         <v>10</v>
       </c>
@@ -77261,7 +77255,7 @@
       <c r="B121" s="169" t="s">
         <v>664</v>
       </c>
-      <c r="C121" s="404"/>
+      <c r="C121" s="403"/>
       <c r="D121" s="139" t="s">
         <v>409</v>
       </c>
@@ -77273,7 +77267,7 @@
       <c r="B122" s="169" t="s">
         <v>665</v>
       </c>
-      <c r="C122" s="404"/>
+      <c r="C122" s="403"/>
       <c r="D122" s="139" t="s">
         <v>10</v>
       </c>
@@ -77285,7 +77279,7 @@
       <c r="B123" s="169" t="s">
         <v>666</v>
       </c>
-      <c r="C123" s="404"/>
+      <c r="C123" s="403"/>
       <c r="D123" s="139" t="s">
         <v>10</v>
       </c>
@@ -77297,7 +77291,7 @@
       <c r="B124" s="169" t="s">
         <v>667</v>
       </c>
-      <c r="C124" s="404"/>
+      <c r="C124" s="403"/>
       <c r="D124" s="139" t="s">
         <v>10</v>
       </c>
@@ -77309,7 +77303,7 @@
       <c r="B125" s="169" t="s">
         <v>668</v>
       </c>
-      <c r="C125" s="404"/>
+      <c r="C125" s="403"/>
       <c r="D125" s="139" t="s">
         <v>10</v>
       </c>
@@ -77321,7 +77315,7 @@
       <c r="B126" s="169" t="s">
         <v>669</v>
       </c>
-      <c r="C126" s="404"/>
+      <c r="C126" s="403"/>
       <c r="D126" s="139" t="s">
         <v>10</v>
       </c>
@@ -77333,7 +77327,7 @@
       <c r="B127" s="169" t="s">
         <v>670</v>
       </c>
-      <c r="C127" s="404"/>
+      <c r="C127" s="403"/>
       <c r="D127" s="139" t="s">
         <v>10</v>
       </c>
@@ -77345,7 +77339,7 @@
       <c r="B128" s="169" t="s">
         <v>671</v>
       </c>
-      <c r="C128" s="404"/>
+      <c r="C128" s="403"/>
       <c r="D128" s="139" t="s">
         <v>10</v>
       </c>
@@ -77357,7 +77351,7 @@
       <c r="B129" s="169" t="s">
         <v>672</v>
       </c>
-      <c r="C129" s="404"/>
+      <c r="C129" s="403"/>
       <c r="D129" s="139" t="s">
         <v>10</v>
       </c>
@@ -77369,7 +77363,7 @@
       <c r="B130" s="169" t="s">
         <v>673</v>
       </c>
-      <c r="C130" s="404"/>
+      <c r="C130" s="403"/>
       <c r="D130" s="139" t="s">
         <v>433</v>
       </c>
@@ -77381,7 +77375,7 @@
       <c r="B131" s="169" t="s">
         <v>674</v>
       </c>
-      <c r="C131" s="404"/>
+      <c r="C131" s="403"/>
       <c r="D131" s="139" t="s">
         <v>434</v>
       </c>
@@ -77393,7 +77387,7 @@
       <c r="B132" s="169" t="s">
         <v>675</v>
       </c>
-      <c r="C132" s="404"/>
+      <c r="C132" s="403"/>
       <c r="D132" s="139" t="s">
         <v>435</v>
       </c>
@@ -77405,7 +77399,7 @@
       <c r="B133" s="169" t="s">
         <v>676</v>
       </c>
-      <c r="C133" s="404"/>
+      <c r="C133" s="403"/>
       <c r="D133" s="139" t="s">
         <v>436</v>
       </c>
@@ -77417,7 +77411,7 @@
       <c r="B134" s="169" t="s">
         <v>677</v>
       </c>
-      <c r="C134" s="404"/>
+      <c r="C134" s="403"/>
       <c r="D134" s="139" t="s">
         <v>437</v>
       </c>
@@ -77429,7 +77423,7 @@
       <c r="B135" s="169" t="s">
         <v>678</v>
       </c>
-      <c r="C135" s="404"/>
+      <c r="C135" s="403"/>
       <c r="D135" s="139" t="s">
         <v>438</v>
       </c>
@@ -77441,7 +77435,7 @@
       <c r="B136" s="169" t="s">
         <v>679</v>
       </c>
-      <c r="C136" s="404"/>
+      <c r="C136" s="403"/>
       <c r="D136" s="139" t="s">
         <v>439</v>
       </c>
@@ -77453,7 +77447,7 @@
       <c r="B137" s="169" t="s">
         <v>680</v>
       </c>
-      <c r="C137" s="404"/>
+      <c r="C137" s="403"/>
       <c r="D137" s="139" t="s">
         <v>440</v>
       </c>
@@ -77465,7 +77459,7 @@
       <c r="B138" s="169" t="s">
         <v>681</v>
       </c>
-      <c r="C138" s="404"/>
+      <c r="C138" s="403"/>
       <c r="D138" s="139" t="s">
         <v>440</v>
       </c>
@@ -77477,7 +77471,7 @@
       <c r="B139" s="169" t="s">
         <v>736</v>
       </c>
-      <c r="C139" s="404"/>
+      <c r="C139" s="403"/>
       <c r="D139" s="139" t="s">
         <v>486</v>
       </c>
@@ -77489,7 +77483,7 @@
       <c r="B140" s="169" t="s">
         <v>737</v>
       </c>
-      <c r="C140" s="404"/>
+      <c r="C140" s="403"/>
       <c r="D140" s="139" t="s">
         <v>441</v>
       </c>
@@ -77501,7 +77495,7 @@
       <c r="B141" s="169" t="s">
         <v>682</v>
       </c>
-      <c r="C141" s="404"/>
+      <c r="C141" s="403"/>
       <c r="D141" s="139" t="s">
         <v>487</v>
       </c>
@@ -77513,7 +77507,7 @@
       <c r="B142" s="169" t="s">
         <v>683</v>
       </c>
-      <c r="C142" s="404"/>
+      <c r="C142" s="403"/>
       <c r="D142" s="139" t="s">
         <v>484</v>
       </c>
@@ -77525,7 +77519,7 @@
       <c r="B143" s="169" t="s">
         <v>722</v>
       </c>
-      <c r="C143" s="404"/>
+      <c r="C143" s="403"/>
       <c r="D143" s="139" t="s">
         <v>442</v>
       </c>
@@ -77537,7 +77531,7 @@
       <c r="B144" s="169" t="s">
         <v>723</v>
       </c>
-      <c r="C144" s="404"/>
+      <c r="C144" s="403"/>
       <c r="D144" s="139" t="s">
         <v>443</v>
       </c>
@@ -77549,7 +77543,7 @@
       <c r="B145" s="169" t="s">
         <v>684</v>
       </c>
-      <c r="C145" s="404"/>
+      <c r="C145" s="403"/>
       <c r="D145" s="139" t="s">
         <v>444</v>
       </c>
@@ -77561,7 +77555,7 @@
       <c r="B146" s="169" t="s">
         <v>685</v>
       </c>
-      <c r="C146" s="404"/>
+      <c r="C146" s="403"/>
       <c r="D146" s="139" t="s">
         <v>445</v>
       </c>
@@ -77573,7 +77567,7 @@
       <c r="B147" s="169" t="s">
         <v>686</v>
       </c>
-      <c r="C147" s="404"/>
+      <c r="C147" s="403"/>
       <c r="D147" s="139" t="s">
         <v>446</v>
       </c>
@@ -77585,7 +77579,7 @@
       <c r="B148" s="169" t="s">
         <v>687</v>
       </c>
-      <c r="C148" s="404"/>
+      <c r="C148" s="403"/>
       <c r="D148" s="139" t="s">
         <v>447</v>
       </c>
@@ -77597,7 +77591,7 @@
       <c r="B149" s="169" t="s">
         <v>688</v>
       </c>
-      <c r="C149" s="404"/>
+      <c r="C149" s="403"/>
       <c r="D149" s="139" t="s">
         <v>448</v>
       </c>
@@ -77609,7 +77603,7 @@
       <c r="B150" s="169" t="s">
         <v>689</v>
       </c>
-      <c r="C150" s="404"/>
+      <c r="C150" s="403"/>
       <c r="D150" s="139" t="s">
         <v>449</v>
       </c>
@@ -77621,7 +77615,7 @@
       <c r="B151" s="169" t="s">
         <v>690</v>
       </c>
-      <c r="C151" s="404"/>
+      <c r="C151" s="403"/>
       <c r="D151" s="139" t="s">
         <v>504</v>
       </c>
@@ -77633,7 +77627,7 @@
       <c r="B152" s="169" t="s">
         <v>691</v>
       </c>
-      <c r="C152" s="404"/>
+      <c r="C152" s="403"/>
       <c r="D152" s="139" t="s">
         <v>10</v>
       </c>
@@ -77645,7 +77639,7 @@
       <c r="B153" s="169" t="s">
         <v>692</v>
       </c>
-      <c r="C153" s="404"/>
+      <c r="C153" s="403"/>
       <c r="D153" s="139" t="s">
         <v>10</v>
       </c>
@@ -77657,7 +77651,7 @@
       <c r="B154" s="169" t="s">
         <v>693</v>
       </c>
-      <c r="C154" s="404"/>
+      <c r="C154" s="403"/>
       <c r="D154" s="139" t="s">
         <v>10</v>
       </c>
@@ -77669,7 +77663,7 @@
       <c r="B155" s="169" t="s">
         <v>694</v>
       </c>
-      <c r="C155" s="404"/>
+      <c r="C155" s="403"/>
       <c r="D155" s="139" t="s">
         <v>10</v>
       </c>
@@ -77681,7 +77675,7 @@
       <c r="B156" s="169" t="s">
         <v>695</v>
       </c>
-      <c r="C156" s="404"/>
+      <c r="C156" s="403"/>
       <c r="D156" s="139" t="s">
         <v>10</v>
       </c>
@@ -77693,7 +77687,7 @@
       <c r="B157" s="169" t="s">
         <v>696</v>
       </c>
-      <c r="C157" s="404"/>
+      <c r="C157" s="403"/>
       <c r="D157" s="139" t="s">
         <v>10</v>
       </c>
@@ -77705,7 +77699,7 @@
       <c r="B158" s="169" t="s">
         <v>697</v>
       </c>
-      <c r="C158" s="404"/>
+      <c r="C158" s="403"/>
       <c r="D158" s="139" t="s">
         <v>10</v>
       </c>
@@ -77717,7 +77711,7 @@
       <c r="B159" s="169" t="s">
         <v>698</v>
       </c>
-      <c r="C159" s="404"/>
+      <c r="C159" s="403"/>
       <c r="D159" s="139" t="s">
         <v>505</v>
       </c>
@@ -77729,7 +77723,7 @@
       <c r="B160" s="169" t="s">
         <v>699</v>
       </c>
-      <c r="C160" s="404"/>
+      <c r="C160" s="403"/>
       <c r="D160" s="139" t="s">
         <v>506</v>
       </c>
@@ -77741,7 +77735,7 @@
       <c r="B161" s="169" t="s">
         <v>700</v>
       </c>
-      <c r="C161" s="404"/>
+      <c r="C161" s="403"/>
       <c r="D161" s="139" t="s">
         <v>507</v>
       </c>
@@ -77753,7 +77747,7 @@
       <c r="B162" s="170" t="s">
         <v>701</v>
       </c>
-      <c r="C162" s="405"/>
+      <c r="C162" s="404"/>
       <c r="D162" s="204" t="s">
         <v>10</v>
       </c>
@@ -77765,7 +77759,7 @@
       <c r="B163" s="171" t="s">
         <v>702</v>
       </c>
-      <c r="C163" s="403" t="s">
+      <c r="C163" s="402" t="s">
         <v>450</v>
       </c>
       <c r="D163" s="139" t="s">
@@ -77779,7 +77773,7 @@
       <c r="B164" s="171" t="s">
         <v>703</v>
       </c>
-      <c r="C164" s="404"/>
+      <c r="C164" s="403"/>
       <c r="D164" s="139" t="s">
         <v>452</v>
       </c>
@@ -77791,7 +77785,7 @@
       <c r="B165" s="171" t="s">
         <v>704</v>
       </c>
-      <c r="C165" s="404"/>
+      <c r="C165" s="403"/>
       <c r="D165" s="139" t="s">
         <v>10</v>
       </c>
@@ -77803,7 +77797,7 @@
       <c r="B166" s="171" t="s">
         <v>705</v>
       </c>
-      <c r="C166" s="404"/>
+      <c r="C166" s="403"/>
       <c r="D166" s="139" t="s">
         <v>10</v>
       </c>
@@ -77815,7 +77809,7 @@
       <c r="B167" s="171" t="s">
         <v>706</v>
       </c>
-      <c r="C167" s="404"/>
+      <c r="C167" s="403"/>
       <c r="D167" s="139" t="s">
         <v>453</v>
       </c>
@@ -77827,7 +77821,7 @@
       <c r="B168" s="171" t="s">
         <v>707</v>
       </c>
-      <c r="C168" s="404"/>
+      <c r="C168" s="403"/>
       <c r="D168" s="139" t="s">
         <v>454</v>
       </c>
@@ -77839,7 +77833,7 @@
       <c r="B169" s="171" t="s">
         <v>708</v>
       </c>
-      <c r="C169" s="404"/>
+      <c r="C169" s="403"/>
       <c r="D169" s="139" t="s">
         <v>455</v>
       </c>
@@ -77851,7 +77845,7 @@
       <c r="B170" s="171" t="s">
         <v>709</v>
       </c>
-      <c r="C170" s="404"/>
+      <c r="C170" s="403"/>
       <c r="D170" s="139" t="s">
         <v>10</v>
       </c>
@@ -77863,7 +77857,7 @@
       <c r="B171" s="171" t="s">
         <v>710</v>
       </c>
-      <c r="C171" s="404"/>
+      <c r="C171" s="403"/>
       <c r="D171" s="139" t="s">
         <v>10</v>
       </c>
@@ -77875,7 +77869,7 @@
       <c r="B172" s="171" t="s">
         <v>711</v>
       </c>
-      <c r="C172" s="404"/>
+      <c r="C172" s="403"/>
       <c r="D172" s="139" t="s">
         <v>10</v>
       </c>
@@ -77887,7 +77881,7 @@
       <c r="B173" s="171" t="s">
         <v>712</v>
       </c>
-      <c r="C173" s="404"/>
+      <c r="C173" s="403"/>
       <c r="D173" s="139" t="s">
         <v>456</v>
       </c>
@@ -77899,7 +77893,7 @@
       <c r="B174" s="171" t="s">
         <v>713</v>
       </c>
-      <c r="C174" s="404"/>
+      <c r="C174" s="403"/>
       <c r="D174" s="139" t="s">
         <v>457</v>
       </c>
@@ -77911,7 +77905,7 @@
       <c r="B175" s="171" t="s">
         <v>714</v>
       </c>
-      <c r="C175" s="404"/>
+      <c r="C175" s="403"/>
       <c r="D175" s="139" t="s">
         <v>458</v>
       </c>
@@ -77923,7 +77917,7 @@
       <c r="B176" s="172" t="s">
         <v>728</v>
       </c>
-      <c r="C176" s="405"/>
+      <c r="C176" s="404"/>
       <c r="D176" s="143" t="s">
         <v>459</v>
       </c>
@@ -77945,6 +77939,13 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="14">
+    <mergeCell ref="C163:C176"/>
+    <mergeCell ref="C61:C70"/>
+    <mergeCell ref="C71:C94"/>
+    <mergeCell ref="C95:C98"/>
+    <mergeCell ref="C99:C108"/>
+    <mergeCell ref="C109:C115"/>
+    <mergeCell ref="C116:C162"/>
     <mergeCell ref="C58:C60"/>
     <mergeCell ref="C54:C57"/>
     <mergeCell ref="C2:C11"/>
@@ -77952,13 +77953,6 @@
     <mergeCell ref="C18:C28"/>
     <mergeCell ref="C44:C53"/>
     <mergeCell ref="C29:C43"/>
-    <mergeCell ref="C163:C176"/>
-    <mergeCell ref="C61:C70"/>
-    <mergeCell ref="C71:C94"/>
-    <mergeCell ref="C95:C98"/>
-    <mergeCell ref="C99:C108"/>
-    <mergeCell ref="C109:C115"/>
-    <mergeCell ref="C116:C162"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -77966,15 +77960,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="107e75b3-53cc-4838-92d2-ebc011bd4832">
@@ -77983,6 +77968,15 @@
     <TaxCatchAll xmlns="888ccf44-0d39-41a2-ab17-f7efb2bf6977" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -78235,14 +78229,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B21D61-7BBD-4BD3-A9A5-1E8F98F2F686}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2288FB7-E85A-4FE8-9E7A-FE572FF16064}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -78255,6 +78241,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="888ccf44-0d39-41a2-ab17-f7efb2bf6977"/>
     <ds:schemaRef ds:uri="107e75b3-53cc-4838-92d2-ebc011bd4832"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B21D61-7BBD-4BD3-A9A5-1E8F98F2F686}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/testcases.xlsx
+++ b/testcases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\energinet.local\endk_funktion\Dynsim\13_Medarbejdermapper\CVL\MTB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0766EC9-A7A5-4765-A13C-18FF12E68EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200E89C6-411A-4F33-AC6B-03B1B8EF80A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2440" yWindow="14290" windowWidth="29020" windowHeight="17500" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4667,7 +4667,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="413">
+  <cellXfs count="412">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -5743,20 +5743,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -9256,102 +9253,102 @@
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="334"/>
       <c r="B2" s="334"/>
-      <c r="C2" s="410" t="s">
+      <c r="C2" s="408" t="s">
         <v>848</v>
       </c>
-      <c r="D2" s="408" t="s">
+      <c r="D2" s="410" t="s">
         <v>912</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="334"/>
       <c r="B3" s="334"/>
-      <c r="C3" s="410"/>
-      <c r="D3" s="408"/>
+      <c r="C3" s="408"/>
+      <c r="D3" s="410"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="334"/>
       <c r="B4" s="334"/>
-      <c r="C4" s="410"/>
-      <c r="D4" s="408"/>
+      <c r="C4" s="408"/>
+      <c r="D4" s="410"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="334"/>
       <c r="B5" s="334"/>
-      <c r="C5" s="410"/>
-      <c r="D5" s="408"/>
+      <c r="C5" s="408"/>
+      <c r="D5" s="410"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="334"/>
       <c r="B6" s="334"/>
-      <c r="C6" s="410"/>
-      <c r="D6" s="408"/>
+      <c r="C6" s="408"/>
+      <c r="D6" s="410"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="334"/>
       <c r="B7" s="334"/>
-      <c r="C7" s="410"/>
-      <c r="D7" s="408"/>
+      <c r="C7" s="408"/>
+      <c r="D7" s="410"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="334"/>
       <c r="B8" s="334"/>
-      <c r="C8" s="410"/>
-      <c r="D8" s="408"/>
+      <c r="C8" s="408"/>
+      <c r="D8" s="410"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="334"/>
       <c r="B9" s="334"/>
-      <c r="C9" s="410"/>
-      <c r="D9" s="408"/>
+      <c r="C9" s="408"/>
+      <c r="D9" s="410"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="334"/>
       <c r="B10" s="334"/>
-      <c r="C10" s="410"/>
-      <c r="D10" s="408"/>
+      <c r="C10" s="408"/>
+      <c r="D10" s="410"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="334"/>
       <c r="B11" s="334"/>
-      <c r="C11" s="410"/>
-      <c r="D11" s="408"/>
+      <c r="C11" s="408"/>
+      <c r="D11" s="410"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="334"/>
       <c r="B12" s="334"/>
-      <c r="C12" s="410"/>
-      <c r="D12" s="408"/>
+      <c r="C12" s="408"/>
+      <c r="D12" s="410"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="334"/>
       <c r="B13" s="334"/>
-      <c r="C13" s="410"/>
-      <c r="D13" s="408"/>
+      <c r="C13" s="408"/>
+      <c r="D13" s="410"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="334"/>
       <c r="B14" s="334"/>
-      <c r="C14" s="410"/>
-      <c r="D14" s="408"/>
+      <c r="C14" s="408"/>
+      <c r="D14" s="410"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="334"/>
       <c r="B15" s="334"/>
-      <c r="C15" s="410"/>
-      <c r="D15" s="408"/>
+      <c r="C15" s="408"/>
+      <c r="D15" s="410"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="334"/>
       <c r="B16" s="334"/>
-      <c r="C16" s="410"/>
-      <c r="D16" s="408"/>
+      <c r="C16" s="408"/>
+      <c r="D16" s="410"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="316"/>
       <c r="B17" s="316"/>
-      <c r="C17" s="411"/>
-      <c r="D17" s="409"/>
+      <c r="C17" s="409"/>
+      <c r="D17" s="411"/>
     </row>
     <row r="18" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="336"/>
@@ -9359,7 +9356,7 @@
       <c r="C18" s="403" t="s">
         <v>361</v>
       </c>
-      <c r="D18" s="408" t="s">
+      <c r="D18" s="410" t="s">
         <v>849</v>
       </c>
     </row>
@@ -9367,115 +9364,115 @@
       <c r="A19" s="336"/>
       <c r="B19" s="336"/>
       <c r="C19" s="403"/>
-      <c r="D19" s="408"/>
+      <c r="D19" s="410"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="336"/>
       <c r="B20" s="336"/>
       <c r="C20" s="403"/>
-      <c r="D20" s="408"/>
+      <c r="D20" s="410"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="336"/>
       <c r="B21" s="336"/>
       <c r="C21" s="403"/>
-      <c r="D21" s="408"/>
+      <c r="D21" s="410"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="336"/>
       <c r="B22" s="336"/>
       <c r="C22" s="403"/>
-      <c r="D22" s="408"/>
+      <c r="D22" s="410"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="336"/>
       <c r="B23" s="336"/>
       <c r="C23" s="403"/>
-      <c r="D23" s="408"/>
+      <c r="D23" s="410"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="336"/>
       <c r="B24" s="336"/>
       <c r="C24" s="403"/>
-      <c r="D24" s="408"/>
+      <c r="D24" s="410"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="336"/>
       <c r="B25" s="336"/>
       <c r="C25" s="403"/>
-      <c r="D25" s="408"/>
+      <c r="D25" s="410"/>
     </row>
     <row r="26" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="336"/>
       <c r="B26" s="336"/>
       <c r="C26" s="403"/>
-      <c r="D26" s="408"/>
+      <c r="D26" s="410"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="336"/>
       <c r="B27" s="336"/>
       <c r="C27" s="403"/>
-      <c r="D27" s="408"/>
+      <c r="D27" s="410"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="336"/>
       <c r="B28" s="336"/>
       <c r="C28" s="403"/>
-      <c r="D28" s="408"/>
+      <c r="D28" s="410"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="336"/>
       <c r="B29" s="336"/>
       <c r="C29" s="403"/>
-      <c r="D29" s="408"/>
+      <c r="D29" s="410"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="336"/>
       <c r="B30" s="336"/>
       <c r="C30" s="403"/>
-      <c r="D30" s="408"/>
+      <c r="D30" s="410"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="336"/>
       <c r="B31" s="336"/>
       <c r="C31" s="403"/>
-      <c r="D31" s="408"/>
+      <c r="D31" s="410"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="336"/>
       <c r="B32" s="336"/>
       <c r="C32" s="403"/>
-      <c r="D32" s="408"/>
+      <c r="D32" s="410"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="336"/>
       <c r="B33" s="336"/>
       <c r="C33" s="403"/>
-      <c r="D33" s="408"/>
+      <c r="D33" s="410"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="336"/>
       <c r="B34" s="336"/>
       <c r="C34" s="403"/>
-      <c r="D34" s="408"/>
+      <c r="D34" s="410"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="336"/>
       <c r="B35" s="336"/>
       <c r="C35" s="403"/>
-      <c r="D35" s="408"/>
+      <c r="D35" s="410"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="336"/>
       <c r="B36" s="336"/>
       <c r="C36" s="403"/>
-      <c r="D36" s="408"/>
+      <c r="D36" s="410"/>
     </row>
     <row r="37" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="317"/>
       <c r="B37" s="317"/>
       <c r="C37" s="404"/>
-      <c r="D37" s="409"/>
+      <c r="D37" s="411"/>
     </row>
     <row r="38" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="335"/>
@@ -9483,7 +9480,7 @@
       <c r="C38" s="403" t="s">
         <v>850</v>
       </c>
-      <c r="D38" s="408" t="s">
+      <c r="D38" s="410" t="s">
         <v>851</v>
       </c>
     </row>
@@ -9491,115 +9488,115 @@
       <c r="A39" s="335"/>
       <c r="B39" s="335"/>
       <c r="C39" s="403"/>
-      <c r="D39" s="408"/>
+      <c r="D39" s="410"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="335"/>
       <c r="B40" s="335"/>
       <c r="C40" s="403"/>
-      <c r="D40" s="408"/>
+      <c r="D40" s="410"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="335"/>
       <c r="B41" s="335"/>
       <c r="C41" s="403"/>
-      <c r="D41" s="408"/>
+      <c r="D41" s="410"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="335"/>
       <c r="B42" s="335"/>
       <c r="C42" s="403"/>
-      <c r="D42" s="408"/>
+      <c r="D42" s="410"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="335"/>
       <c r="B43" s="335"/>
       <c r="C43" s="403"/>
-      <c r="D43" s="408"/>
+      <c r="D43" s="410"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="335"/>
       <c r="B44" s="335"/>
       <c r="C44" s="403"/>
-      <c r="D44" s="408"/>
+      <c r="D44" s="410"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="335"/>
       <c r="B45" s="335"/>
       <c r="C45" s="403"/>
-      <c r="D45" s="408"/>
+      <c r="D45" s="410"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="335"/>
       <c r="B46" s="335"/>
       <c r="C46" s="403"/>
-      <c r="D46" s="408"/>
+      <c r="D46" s="410"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="335"/>
       <c r="B47" s="335"/>
       <c r="C47" s="403"/>
-      <c r="D47" s="408"/>
+      <c r="D47" s="410"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="335"/>
       <c r="B48" s="335"/>
       <c r="C48" s="403"/>
-      <c r="D48" s="408"/>
+      <c r="D48" s="410"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="335"/>
       <c r="B49" s="335"/>
       <c r="C49" s="403"/>
-      <c r="D49" s="408"/>
+      <c r="D49" s="410"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="335"/>
       <c r="B50" s="335"/>
       <c r="C50" s="403"/>
-      <c r="D50" s="408"/>
+      <c r="D50" s="410"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="335"/>
       <c r="B51" s="335"/>
       <c r="C51" s="403"/>
-      <c r="D51" s="408"/>
+      <c r="D51" s="410"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="335"/>
       <c r="B52" s="335"/>
       <c r="C52" s="403"/>
-      <c r="D52" s="408"/>
+      <c r="D52" s="410"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="335"/>
       <c r="B53" s="335"/>
       <c r="C53" s="403"/>
-      <c r="D53" s="408"/>
+      <c r="D53" s="410"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="335"/>
       <c r="B54" s="335"/>
       <c r="C54" s="403"/>
-      <c r="D54" s="408"/>
+      <c r="D54" s="410"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="335"/>
       <c r="B55" s="335"/>
       <c r="C55" s="403"/>
-      <c r="D55" s="408"/>
+      <c r="D55" s="410"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="335"/>
       <c r="B56" s="335"/>
       <c r="C56" s="403"/>
-      <c r="D56" s="408"/>
+      <c r="D56" s="410"/>
     </row>
     <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="318"/>
       <c r="B57" s="318"/>
       <c r="C57" s="404"/>
-      <c r="D57" s="409"/>
+      <c r="D57" s="411"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="337"/>
@@ -9607,7 +9604,7 @@
       <c r="C58" s="403" t="s">
         <v>852</v>
       </c>
-      <c r="D58" s="408" t="s">
+      <c r="D58" s="410" t="s">
         <v>853</v>
       </c>
     </row>
@@ -9615,85 +9612,85 @@
       <c r="A59" s="337"/>
       <c r="B59" s="337"/>
       <c r="C59" s="403"/>
-      <c r="D59" s="408"/>
+      <c r="D59" s="410"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="337"/>
       <c r="B60" s="337"/>
       <c r="C60" s="403"/>
-      <c r="D60" s="408"/>
+      <c r="D60" s="410"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="337"/>
       <c r="B61" s="337"/>
       <c r="C61" s="403"/>
-      <c r="D61" s="408"/>
+      <c r="D61" s="410"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="337"/>
       <c r="B62" s="337"/>
       <c r="C62" s="403"/>
-      <c r="D62" s="408"/>
+      <c r="D62" s="410"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="337"/>
       <c r="B63" s="337"/>
       <c r="C63" s="403"/>
-      <c r="D63" s="408"/>
+      <c r="D63" s="410"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="337"/>
       <c r="B64" s="337"/>
       <c r="C64" s="403"/>
-      <c r="D64" s="408"/>
+      <c r="D64" s="410"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="337"/>
       <c r="B65" s="337"/>
       <c r="C65" s="403"/>
-      <c r="D65" s="408"/>
+      <c r="D65" s="410"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="337"/>
       <c r="B66" s="337"/>
       <c r="C66" s="403"/>
-      <c r="D66" s="408"/>
+      <c r="D66" s="410"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="337"/>
       <c r="B67" s="337"/>
       <c r="C67" s="403"/>
-      <c r="D67" s="408"/>
+      <c r="D67" s="410"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="337"/>
       <c r="B68" s="337"/>
       <c r="C68" s="403"/>
-      <c r="D68" s="408"/>
+      <c r="D68" s="410"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="337"/>
       <c r="B69" s="337"/>
       <c r="C69" s="403"/>
-      <c r="D69" s="408"/>
+      <c r="D69" s="410"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="337"/>
       <c r="B70" s="337"/>
       <c r="C70" s="403"/>
-      <c r="D70" s="408"/>
+      <c r="D70" s="410"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="337"/>
       <c r="B71" s="337"/>
       <c r="C71" s="403"/>
-      <c r="D71" s="408"/>
+      <c r="D71" s="410"/>
     </row>
     <row r="72" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="319"/>
       <c r="B72" s="319"/>
       <c r="C72" s="404"/>
-      <c r="D72" s="409"/>
+      <c r="D72" s="411"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="339"/>
@@ -9701,7 +9698,7 @@
       <c r="C73" s="403" t="s">
         <v>854</v>
       </c>
-      <c r="D73" s="408" t="s">
+      <c r="D73" s="410" t="s">
         <v>855</v>
       </c>
     </row>
@@ -9709,97 +9706,97 @@
       <c r="A74" s="339"/>
       <c r="B74" s="339"/>
       <c r="C74" s="403"/>
-      <c r="D74" s="408"/>
+      <c r="D74" s="410"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="339"/>
       <c r="B75" s="339"/>
       <c r="C75" s="403"/>
-      <c r="D75" s="408"/>
+      <c r="D75" s="410"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="339"/>
       <c r="B76" s="339"/>
       <c r="C76" s="403"/>
-      <c r="D76" s="408"/>
+      <c r="D76" s="410"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="339"/>
       <c r="B77" s="339"/>
       <c r="C77" s="403"/>
-      <c r="D77" s="408"/>
+      <c r="D77" s="410"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="339"/>
       <c r="B78" s="339"/>
       <c r="C78" s="403"/>
-      <c r="D78" s="408"/>
+      <c r="D78" s="410"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="339"/>
       <c r="B79" s="339"/>
       <c r="C79" s="403"/>
-      <c r="D79" s="408"/>
+      <c r="D79" s="410"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="339"/>
       <c r="B80" s="339"/>
       <c r="C80" s="403"/>
-      <c r="D80" s="408"/>
+      <c r="D80" s="410"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="339"/>
       <c r="B81" s="339"/>
       <c r="C81" s="403"/>
-      <c r="D81" s="408"/>
+      <c r="D81" s="410"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="339"/>
       <c r="B82" s="339"/>
       <c r="C82" s="403"/>
-      <c r="D82" s="408"/>
+      <c r="D82" s="410"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="339"/>
       <c r="B83" s="339"/>
       <c r="C83" s="403"/>
-      <c r="D83" s="408"/>
+      <c r="D83" s="410"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="339"/>
       <c r="B84" s="339"/>
       <c r="C84" s="403"/>
-      <c r="D84" s="408"/>
+      <c r="D84" s="410"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="339"/>
       <c r="B85" s="339"/>
       <c r="C85" s="403"/>
-      <c r="D85" s="408"/>
+      <c r="D85" s="410"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="339"/>
       <c r="B86" s="339"/>
       <c r="C86" s="403"/>
-      <c r="D86" s="408"/>
+      <c r="D86" s="410"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="339"/>
       <c r="B87" s="339"/>
       <c r="C87" s="403"/>
-      <c r="D87" s="408"/>
+      <c r="D87" s="410"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="339"/>
       <c r="B88" s="339"/>
       <c r="C88" s="403"/>
-      <c r="D88" s="408"/>
+      <c r="D88" s="410"/>
     </row>
     <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="320"/>
       <c r="B89" s="320"/>
       <c r="C89" s="404"/>
-      <c r="D89" s="409"/>
+      <c r="D89" s="411"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="338"/>
@@ -9807,7 +9804,7 @@
       <c r="C90" s="403" t="s">
         <v>856</v>
       </c>
-      <c r="D90" s="408" t="s">
+      <c r="D90" s="410" t="s">
         <v>857</v>
       </c>
     </row>
@@ -9815,49 +9812,49 @@
       <c r="A91" s="338"/>
       <c r="B91" s="338"/>
       <c r="C91" s="403"/>
-      <c r="D91" s="408"/>
+      <c r="D91" s="410"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="338"/>
       <c r="B92" s="338"/>
       <c r="C92" s="403"/>
-      <c r="D92" s="408"/>
+      <c r="D92" s="410"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="338"/>
       <c r="B93" s="338"/>
       <c r="C93" s="403"/>
-      <c r="D93" s="408"/>
+      <c r="D93" s="410"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="338"/>
       <c r="B94" s="338"/>
       <c r="C94" s="403"/>
-      <c r="D94" s="408"/>
+      <c r="D94" s="410"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="338"/>
       <c r="B95" s="338"/>
       <c r="C95" s="403"/>
-      <c r="D95" s="408"/>
+      <c r="D95" s="410"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="338"/>
       <c r="B96" s="338"/>
       <c r="C96" s="403"/>
-      <c r="D96" s="408"/>
+      <c r="D96" s="410"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="338"/>
       <c r="B97" s="338"/>
       <c r="C97" s="403"/>
-      <c r="D97" s="408"/>
+      <c r="D97" s="410"/>
     </row>
     <row r="98" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="321"/>
       <c r="B98" s="321"/>
       <c r="C98" s="404"/>
-      <c r="D98" s="409"/>
+      <c r="D98" s="411"/>
     </row>
     <row r="99" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="340"/>
@@ -9865,7 +9862,7 @@
       <c r="C99" s="406" t="s">
         <v>858</v>
       </c>
-      <c r="D99" s="408" t="s">
+      <c r="D99" s="410" t="s">
         <v>859</v>
       </c>
     </row>
@@ -9873,73 +9870,73 @@
       <c r="A100" s="340"/>
       <c r="B100" s="340"/>
       <c r="C100" s="406"/>
-      <c r="D100" s="408"/>
+      <c r="D100" s="410"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="340"/>
       <c r="B101" s="340"/>
       <c r="C101" s="406"/>
-      <c r="D101" s="408"/>
+      <c r="D101" s="410"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="340"/>
       <c r="B102" s="340"/>
       <c r="C102" s="406"/>
-      <c r="D102" s="408"/>
+      <c r="D102" s="410"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="340"/>
       <c r="B103" s="340"/>
       <c r="C103" s="406"/>
-      <c r="D103" s="408"/>
+      <c r="D103" s="410"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="340"/>
       <c r="B104" s="340"/>
       <c r="C104" s="406"/>
-      <c r="D104" s="408"/>
+      <c r="D104" s="410"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="340"/>
       <c r="B105" s="340"/>
       <c r="C105" s="406"/>
-      <c r="D105" s="408"/>
+      <c r="D105" s="410"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="340"/>
       <c r="B106" s="340"/>
       <c r="C106" s="406"/>
-      <c r="D106" s="408"/>
+      <c r="D106" s="410"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="340"/>
       <c r="B107" s="340"/>
       <c r="C107" s="406"/>
-      <c r="D107" s="408"/>
+      <c r="D107" s="410"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="340"/>
       <c r="B108" s="340"/>
       <c r="C108" s="406"/>
-      <c r="D108" s="408"/>
+      <c r="D108" s="410"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="340"/>
       <c r="B109" s="340"/>
       <c r="C109" s="406"/>
-      <c r="D109" s="408"/>
+      <c r="D109" s="410"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="340"/>
       <c r="B110" s="340"/>
       <c r="C110" s="406"/>
-      <c r="D110" s="408"/>
+      <c r="D110" s="410"/>
     </row>
     <row r="111" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="322"/>
       <c r="B111" s="322"/>
       <c r="C111" s="407"/>
-      <c r="D111" s="409"/>
+      <c r="D111" s="411"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="336"/>
@@ -9947,7 +9944,7 @@
       <c r="C112" s="403" t="s">
         <v>860</v>
       </c>
-      <c r="D112" s="408" t="s">
+      <c r="D112" s="410" t="s">
         <v>861</v>
       </c>
     </row>
@@ -9955,67 +9952,67 @@
       <c r="A113" s="336"/>
       <c r="B113" s="336"/>
       <c r="C113" s="403"/>
-      <c r="D113" s="408"/>
+      <c r="D113" s="410"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="336"/>
       <c r="B114" s="336"/>
       <c r="C114" s="403"/>
-      <c r="D114" s="408"/>
+      <c r="D114" s="410"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="336"/>
       <c r="B115" s="336"/>
       <c r="C115" s="403"/>
-      <c r="D115" s="408"/>
+      <c r="D115" s="410"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="336"/>
       <c r="B116" s="336"/>
       <c r="C116" s="403"/>
-      <c r="D116" s="408"/>
+      <c r="D116" s="410"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="336"/>
       <c r="B117" s="336"/>
       <c r="C117" s="403"/>
-      <c r="D117" s="408"/>
+      <c r="D117" s="410"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="336"/>
       <c r="B118" s="336"/>
       <c r="C118" s="403"/>
-      <c r="D118" s="408"/>
+      <c r="D118" s="410"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="336"/>
       <c r="B119" s="336"/>
       <c r="C119" s="403"/>
-      <c r="D119" s="408"/>
+      <c r="D119" s="410"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="336"/>
       <c r="B120" s="336"/>
       <c r="C120" s="403"/>
-      <c r="D120" s="408"/>
+      <c r="D120" s="410"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="336"/>
       <c r="B121" s="336"/>
       <c r="C121" s="403"/>
-      <c r="D121" s="408"/>
+      <c r="D121" s="410"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="336"/>
       <c r="B122" s="336"/>
       <c r="C122" s="403"/>
-      <c r="D122" s="408"/>
+      <c r="D122" s="410"/>
     </row>
     <row r="123" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="317"/>
       <c r="B123" s="317"/>
       <c r="C123" s="404"/>
-      <c r="D123" s="409"/>
+      <c r="D123" s="411"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="335"/>
@@ -10023,7 +10020,7 @@
       <c r="C124" s="403" t="s">
         <v>862</v>
       </c>
-      <c r="D124" s="408" t="s">
+      <c r="D124" s="410" t="s">
         <v>863</v>
       </c>
     </row>
@@ -10031,31 +10028,31 @@
       <c r="A125" s="335"/>
       <c r="B125" s="335"/>
       <c r="C125" s="403"/>
-      <c r="D125" s="408"/>
+      <c r="D125" s="410"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="335"/>
       <c r="B126" s="335"/>
       <c r="C126" s="403"/>
-      <c r="D126" s="408"/>
+      <c r="D126" s="410"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="335"/>
       <c r="B127" s="335"/>
       <c r="C127" s="403"/>
-      <c r="D127" s="408"/>
+      <c r="D127" s="410"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="335"/>
       <c r="B128" s="335"/>
       <c r="C128" s="403"/>
-      <c r="D128" s="408"/>
+      <c r="D128" s="410"/>
     </row>
     <row r="129" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="318"/>
       <c r="B129" s="318"/>
       <c r="C129" s="404"/>
-      <c r="D129" s="409"/>
+      <c r="D129" s="411"/>
     </row>
     <row r="130" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="33"/>
@@ -10063,7 +10060,7 @@
       <c r="C130" s="403" t="s">
         <v>864</v>
       </c>
-      <c r="D130" s="408" t="s">
+      <c r="D130" s="410" t="s">
         <v>865</v>
       </c>
     </row>
@@ -10071,19 +10068,19 @@
       <c r="A131" s="33"/>
       <c r="B131" s="33"/>
       <c r="C131" s="403"/>
-      <c r="D131" s="408"/>
+      <c r="D131" s="410"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="33"/>
       <c r="B132" s="33"/>
       <c r="C132" s="403"/>
-      <c r="D132" s="408"/>
+      <c r="D132" s="410"/>
     </row>
     <row r="133" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="323"/>
       <c r="B133" s="323"/>
       <c r="C133" s="404"/>
-      <c r="D133" s="409"/>
+      <c r="D133" s="411"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="339"/>
@@ -10091,7 +10088,7 @@
       <c r="C134" s="403" t="s">
         <v>866</v>
       </c>
-      <c r="D134" s="408" t="s">
+      <c r="D134" s="410" t="s">
         <v>867</v>
       </c>
     </row>
@@ -10099,103 +10096,103 @@
       <c r="A135" s="339"/>
       <c r="B135" s="339"/>
       <c r="C135" s="403"/>
-      <c r="D135" s="408"/>
+      <c r="D135" s="410"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="339"/>
       <c r="B136" s="339"/>
       <c r="C136" s="403"/>
-      <c r="D136" s="408"/>
+      <c r="D136" s="410"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="339"/>
       <c r="B137" s="339"/>
       <c r="C137" s="403"/>
-      <c r="D137" s="408"/>
+      <c r="D137" s="410"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="339"/>
       <c r="B138" s="339"/>
       <c r="C138" s="403"/>
-      <c r="D138" s="408"/>
+      <c r="D138" s="410"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="339"/>
       <c r="B139" s="339"/>
       <c r="C139" s="403"/>
-      <c r="D139" s="408"/>
+      <c r="D139" s="410"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="339"/>
       <c r="B140" s="339"/>
       <c r="C140" s="403"/>
-      <c r="D140" s="408"/>
+      <c r="D140" s="410"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="339"/>
       <c r="B141" s="339"/>
       <c r="C141" s="403"/>
-      <c r="D141" s="408"/>
+      <c r="D141" s="410"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="339"/>
       <c r="B142" s="339"/>
       <c r="C142" s="403"/>
-      <c r="D142" s="408"/>
+      <c r="D142" s="410"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="339"/>
       <c r="B143" s="339"/>
       <c r="C143" s="403"/>
-      <c r="D143" s="408"/>
+      <c r="D143" s="410"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="339"/>
       <c r="B144" s="339"/>
       <c r="C144" s="403"/>
-      <c r="D144" s="408"/>
+      <c r="D144" s="410"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="339"/>
       <c r="B145" s="339"/>
       <c r="C145" s="403"/>
-      <c r="D145" s="408"/>
+      <c r="D145" s="410"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="339"/>
       <c r="B146" s="339"/>
       <c r="C146" s="403"/>
-      <c r="D146" s="408"/>
+      <c r="D146" s="410"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="339"/>
       <c r="B147" s="339"/>
       <c r="C147" s="403"/>
-      <c r="D147" s="408"/>
+      <c r="D147" s="410"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="339"/>
       <c r="B148" s="339"/>
       <c r="C148" s="403"/>
-      <c r="D148" s="408"/>
+      <c r="D148" s="410"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="339"/>
       <c r="B149" s="339"/>
       <c r="C149" s="403"/>
-      <c r="D149" s="408"/>
+      <c r="D149" s="410"/>
     </row>
     <row r="150" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="339"/>
       <c r="B150" s="339"/>
       <c r="C150" s="403"/>
-      <c r="D150" s="408"/>
+      <c r="D150" s="410"/>
     </row>
     <row r="151" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="320"/>
       <c r="B151" s="320"/>
       <c r="C151" s="404"/>
-      <c r="D151" s="409"/>
+      <c r="D151" s="411"/>
     </row>
     <row r="152" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="341"/>
@@ -10203,7 +10200,7 @@
       <c r="C152" s="403" t="s">
         <v>868</v>
       </c>
-      <c r="D152" s="408" t="s">
+      <c r="D152" s="410" t="s">
         <v>869</v>
       </c>
     </row>
@@ -10211,47 +10208,47 @@
       <c r="A153" s="341"/>
       <c r="B153" s="341"/>
       <c r="C153" s="403"/>
-      <c r="D153" s="408"/>
+      <c r="D153" s="410"/>
     </row>
     <row r="154" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="341"/>
       <c r="B154" s="341"/>
       <c r="C154" s="403"/>
-      <c r="D154" s="408"/>
+      <c r="D154" s="410"/>
     </row>
     <row r="155" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="324"/>
       <c r="B155" s="324"/>
       <c r="C155" s="404"/>
-      <c r="D155" s="409"/>
+      <c r="D155" s="411"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="24">
+    <mergeCell ref="C130:C133"/>
+    <mergeCell ref="D130:D133"/>
+    <mergeCell ref="C134:C151"/>
+    <mergeCell ref="D134:D151"/>
+    <mergeCell ref="C152:C155"/>
+    <mergeCell ref="D152:D155"/>
+    <mergeCell ref="C99:C111"/>
+    <mergeCell ref="D99:D111"/>
+    <mergeCell ref="C112:C123"/>
+    <mergeCell ref="D112:D123"/>
+    <mergeCell ref="C124:C129"/>
+    <mergeCell ref="D124:D129"/>
+    <mergeCell ref="C58:C72"/>
+    <mergeCell ref="D58:D72"/>
+    <mergeCell ref="C73:C89"/>
+    <mergeCell ref="D73:D89"/>
+    <mergeCell ref="C90:C98"/>
+    <mergeCell ref="D90:D98"/>
     <mergeCell ref="C2:C17"/>
     <mergeCell ref="D2:D17"/>
     <mergeCell ref="C18:C37"/>
     <mergeCell ref="D18:D37"/>
     <mergeCell ref="C38:C57"/>
     <mergeCell ref="D38:D57"/>
-    <mergeCell ref="C58:C72"/>
-    <mergeCell ref="D58:D72"/>
-    <mergeCell ref="C73:C89"/>
-    <mergeCell ref="D73:D89"/>
-    <mergeCell ref="C90:C98"/>
-    <mergeCell ref="D90:D98"/>
-    <mergeCell ref="C99:C111"/>
-    <mergeCell ref="D99:D111"/>
-    <mergeCell ref="C112:C123"/>
-    <mergeCell ref="D112:D123"/>
-    <mergeCell ref="C124:C129"/>
-    <mergeCell ref="D124:D129"/>
-    <mergeCell ref="C130:C133"/>
-    <mergeCell ref="D130:D133"/>
-    <mergeCell ref="C134:C151"/>
-    <mergeCell ref="D134:D151"/>
-    <mergeCell ref="C152:C155"/>
-    <mergeCell ref="D152:D155"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -54844,25 +54841,25 @@
     </row>
     <row r="4" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="118"/>
-      <c r="B4" s="412"/>
-      <c r="C4" s="412"/>
-      <c r="D4" s="412"/>
-      <c r="E4" s="412"/>
-      <c r="F4" s="412"/>
-      <c r="G4" s="412"/>
-      <c r="H4" s="412"/>
-      <c r="I4" s="412"/>
-      <c r="J4" s="412"/>
-      <c r="K4" s="412"/>
-      <c r="L4" s="412"/>
-      <c r="M4" s="412"/>
-      <c r="N4" s="412"/>
-      <c r="O4" s="412"/>
-      <c r="P4" s="412"/>
-      <c r="Q4" s="412"/>
-      <c r="R4" s="412"/>
-      <c r="S4" s="412"/>
-      <c r="T4" s="412"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="119"/>
+      <c r="M4" s="119"/>
+      <c r="N4" s="119"/>
+      <c r="O4" s="120"/>
+      <c r="P4" s="119"/>
+      <c r="Q4" s="119"/>
+      <c r="R4" s="119"/>
+      <c r="S4" s="119"/>
+      <c r="T4" s="119"/>
       <c r="U4" s="121"/>
       <c r="V4" s="122"/>
       <c r="W4" s="122"/>
@@ -54919,25 +54916,25 @@
     </row>
     <row r="5" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="118"/>
-      <c r="B5" s="412"/>
-      <c r="C5" s="412"/>
-      <c r="D5" s="412"/>
-      <c r="E5" s="412"/>
-      <c r="F5" s="412"/>
-      <c r="G5" s="412"/>
-      <c r="H5" s="412"/>
-      <c r="I5" s="412"/>
-      <c r="J5" s="412"/>
-      <c r="K5" s="412"/>
-      <c r="L5" s="412"/>
-      <c r="M5" s="412"/>
-      <c r="N5" s="412"/>
-      <c r="O5" s="412"/>
-      <c r="P5" s="412"/>
-      <c r="Q5" s="412"/>
-      <c r="R5" s="412"/>
-      <c r="S5" s="412"/>
-      <c r="T5" s="412"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
+      <c r="N5" s="119"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="119"/>
+      <c r="Q5" s="119"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="119"/>
+      <c r="T5" s="119"/>
       <c r="U5" s="121"/>
       <c r="V5" s="122"/>
       <c r="W5" s="122"/>
@@ -54994,25 +54991,25 @@
     </row>
     <row r="6" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="118"/>
-      <c r="B6" s="412"/>
-      <c r="C6" s="412"/>
-      <c r="D6" s="412"/>
-      <c r="E6" s="412"/>
-      <c r="F6" s="412"/>
-      <c r="G6" s="412"/>
-      <c r="H6" s="412"/>
-      <c r="I6" s="412"/>
-      <c r="J6" s="412"/>
-      <c r="K6" s="412"/>
-      <c r="L6" s="412"/>
-      <c r="M6" s="412"/>
-      <c r="N6" s="412"/>
-      <c r="O6" s="412"/>
-      <c r="P6" s="412"/>
-      <c r="Q6" s="412"/>
-      <c r="R6" s="412"/>
-      <c r="S6" s="412"/>
-      <c r="T6" s="412"/>
+      <c r="B6" s="117"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="119"/>
+      <c r="K6" s="119"/>
+      <c r="L6" s="119"/>
+      <c r="M6" s="119"/>
+      <c r="N6" s="119"/>
+      <c r="O6" s="120"/>
+      <c r="P6" s="119"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="119"/>
+      <c r="S6" s="119"/>
+      <c r="T6" s="119"/>
       <c r="U6" s="121"/>
       <c r="V6" s="122"/>
       <c r="W6" s="122"/>
@@ -55069,25 +55066,25 @@
     </row>
     <row r="7" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="118"/>
-      <c r="B7" s="412"/>
-      <c r="C7" s="412"/>
-      <c r="D7" s="412"/>
-      <c r="E7" s="412"/>
-      <c r="F7" s="412"/>
-      <c r="G7" s="412"/>
-      <c r="H7" s="412"/>
-      <c r="I7" s="412"/>
-      <c r="J7" s="412"/>
-      <c r="K7" s="412"/>
-      <c r="L7" s="412"/>
-      <c r="M7" s="412"/>
-      <c r="N7" s="412"/>
-      <c r="O7" s="412"/>
-      <c r="P7" s="412"/>
-      <c r="Q7" s="412"/>
-      <c r="R7" s="412"/>
-      <c r="S7" s="412"/>
-      <c r="T7" s="412"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="119"/>
+      <c r="L7" s="119"/>
+      <c r="M7" s="119"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="120"/>
+      <c r="P7" s="119"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="119"/>
+      <c r="S7" s="119"/>
+      <c r="T7" s="119"/>
       <c r="U7" s="121"/>
       <c r="V7" s="122"/>
       <c r="W7" s="122"/>
@@ -55144,25 +55141,25 @@
     </row>
     <row r="8" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="118"/>
-      <c r="B8" s="412"/>
-      <c r="C8" s="412"/>
-      <c r="D8" s="412"/>
-      <c r="E8" s="412"/>
-      <c r="F8" s="412"/>
-      <c r="G8" s="412"/>
-      <c r="H8" s="412"/>
-      <c r="I8" s="412"/>
-      <c r="J8" s="412"/>
-      <c r="K8" s="412"/>
-      <c r="L8" s="412"/>
-      <c r="M8" s="412"/>
-      <c r="N8" s="412"/>
-      <c r="O8" s="412"/>
-      <c r="P8" s="412"/>
-      <c r="Q8" s="412"/>
-      <c r="R8" s="412"/>
-      <c r="S8" s="412"/>
-      <c r="T8" s="412"/>
+      <c r="B8" s="117"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="119"/>
+      <c r="K8" s="119"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="119"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="120"/>
+      <c r="P8" s="119"/>
+      <c r="Q8" s="119"/>
+      <c r="R8" s="119"/>
+      <c r="S8" s="119"/>
+      <c r="T8" s="119"/>
       <c r="U8" s="121"/>
       <c r="V8" s="122"/>
       <c r="W8" s="122"/>
@@ -55219,25 +55216,25 @@
     </row>
     <row r="9" spans="1:73" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="118"/>
-      <c r="B9" s="412"/>
-      <c r="C9" s="412"/>
-      <c r="D9" s="412"/>
-      <c r="E9" s="412"/>
-      <c r="F9" s="412"/>
-      <c r="G9" s="412"/>
-      <c r="H9" s="412"/>
-      <c r="I9" s="412"/>
-      <c r="J9" s="412"/>
-      <c r="K9" s="412"/>
-      <c r="L9" s="412"/>
-      <c r="M9" s="412"/>
-      <c r="N9" s="412"/>
-      <c r="O9" s="412"/>
-      <c r="P9" s="412"/>
-      <c r="Q9" s="412"/>
-      <c r="R9" s="412"/>
-      <c r="S9" s="412"/>
-      <c r="T9" s="412"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="120"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="119"/>
+      <c r="R9" s="119"/>
+      <c r="S9" s="119"/>
+      <c r="T9" s="119"/>
       <c r="U9" s="121"/>
       <c r="V9" s="122"/>
       <c r="W9" s="122"/>
@@ -55308,7 +55305,7 @@
       <c r="M10" s="119"/>
       <c r="N10" s="119"/>
       <c r="O10" s="120"/>
-      <c r="P10" s="24"/>
+      <c r="P10" s="119"/>
       <c r="Q10" s="119"/>
       <c r="R10" s="119"/>
       <c r="S10" s="119"/>
@@ -55523,18 +55520,18 @@
       <c r="C13" s="117"/>
       <c r="D13" s="118"/>
       <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="119"/>
+      <c r="H13" s="119"/>
+      <c r="I13" s="119"/>
+      <c r="J13" s="119"/>
+      <c r="K13" s="119"/>
+      <c r="L13" s="119"/>
+      <c r="M13" s="119"/>
       <c r="N13" s="119"/>
       <c r="O13" s="120"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
+      <c r="P13" s="119"/>
+      <c r="Q13" s="119"/>
       <c r="R13" s="119"/>
       <c r="S13" s="119"/>
       <c r="T13" s="119"/>
@@ -55598,18 +55595,18 @@
       <c r="C14" s="117"/>
       <c r="D14" s="118"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="119"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="119"/>
       <c r="N14" s="119"/>
       <c r="O14" s="120"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
+      <c r="P14" s="119"/>
+      <c r="Q14" s="119"/>
       <c r="R14" s="119"/>
       <c r="S14" s="119"/>
       <c r="T14" s="119"/>
@@ -55673,18 +55670,18 @@
       <c r="C15" s="117"/>
       <c r="D15" s="118"/>
       <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="119"/>
+      <c r="L15" s="119"/>
+      <c r="M15" s="119"/>
       <c r="N15" s="119"/>
       <c r="O15" s="120"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
+      <c r="P15" s="119"/>
+      <c r="Q15" s="119"/>
       <c r="R15" s="119"/>
       <c r="S15" s="119"/>
       <c r="T15" s="119"/>
@@ -55748,18 +55745,18 @@
       <c r="C16" s="117"/>
       <c r="D16" s="118"/>
       <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="119"/>
       <c r="N16" s="119"/>
       <c r="O16" s="120"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="119"/>
       <c r="R16" s="119"/>
       <c r="S16" s="119"/>
       <c r="T16" s="119"/>
@@ -55823,18 +55820,18 @@
       <c r="C17" s="117"/>
       <c r="D17" s="118"/>
       <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="119"/>
+      <c r="K17" s="119"/>
+      <c r="L17" s="119"/>
+      <c r="M17" s="119"/>
       <c r="N17" s="119"/>
       <c r="O17" s="120"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
+      <c r="P17" s="119"/>
+      <c r="Q17" s="119"/>
       <c r="R17" s="119"/>
       <c r="S17" s="119"/>
       <c r="T17" s="119"/>
@@ -55895,21 +55892,21 @@
     <row r="18" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A18" s="118"/>
       <c r="B18" s="117"/>
-      <c r="C18" s="381"/>
+      <c r="C18" s="117"/>
       <c r="D18" s="118"/>
       <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="119"/>
+      <c r="K18" s="119"/>
+      <c r="L18" s="119"/>
+      <c r="M18" s="119"/>
       <c r="N18" s="119"/>
       <c r="O18" s="120"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="119"/>
       <c r="R18" s="119"/>
       <c r="S18" s="119"/>
       <c r="T18" s="119"/>
@@ -55973,18 +55970,18 @@
       <c r="C19" s="117"/>
       <c r="D19" s="118"/>
       <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="120"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="119"/>
       <c r="O19" s="120"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="119"/>
       <c r="R19" s="119"/>
       <c r="S19" s="119"/>
       <c r="T19" s="119"/>
@@ -56048,18 +56045,18 @@
       <c r="C20" s="117"/>
       <c r="D20" s="118"/>
       <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="120"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="119"/>
+      <c r="N20" s="119"/>
       <c r="O20" s="120"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
+      <c r="P20" s="119"/>
+      <c r="Q20" s="119"/>
       <c r="R20" s="119"/>
       <c r="S20" s="119"/>
       <c r="T20" s="119"/>
@@ -56123,18 +56120,18 @@
       <c r="C21" s="117"/>
       <c r="D21" s="118"/>
       <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="119"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="119"/>
       <c r="N21" s="119"/>
       <c r="O21" s="120"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
+      <c r="P21" s="119"/>
+      <c r="Q21" s="119"/>
       <c r="R21" s="119"/>
       <c r="S21" s="119"/>
       <c r="T21" s="119"/>
@@ -56198,18 +56195,18 @@
       <c r="C22" s="117"/>
       <c r="D22" s="118"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="119"/>
       <c r="N22" s="119"/>
       <c r="O22" s="120"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
+      <c r="P22" s="119"/>
+      <c r="Q22" s="119"/>
       <c r="R22" s="119"/>
       <c r="S22" s="119"/>
       <c r="T22" s="119"/>
@@ -56273,18 +56270,18 @@
       <c r="C23" s="117"/>
       <c r="D23" s="118"/>
       <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="119"/>
       <c r="N23" s="119"/>
       <c r="O23" s="120"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
+      <c r="P23" s="119"/>
+      <c r="Q23" s="119"/>
       <c r="R23" s="119"/>
       <c r="S23" s="119"/>
       <c r="T23" s="119"/>
@@ -56348,18 +56345,18 @@
       <c r="C24" s="117"/>
       <c r="D24" s="118"/>
       <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="120"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="119"/>
+      <c r="M24" s="119"/>
+      <c r="N24" s="119"/>
       <c r="O24" s="120"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
+      <c r="P24" s="119"/>
+      <c r="Q24" s="119"/>
       <c r="R24" s="119"/>
       <c r="S24" s="119"/>
       <c r="T24" s="119"/>
@@ -56423,18 +56420,18 @@
       <c r="C25" s="117"/>
       <c r="D25" s="118"/>
       <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="120"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="119"/>
+      <c r="N25" s="119"/>
       <c r="O25" s="120"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
+      <c r="P25" s="119"/>
+      <c r="Q25" s="119"/>
       <c r="R25" s="119"/>
       <c r="S25" s="119"/>
       <c r="T25" s="119"/>
@@ -56498,18 +56495,18 @@
       <c r="C26" s="117"/>
       <c r="D26" s="118"/>
       <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
-      <c r="N26" s="120"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="119"/>
+      <c r="N26" s="119"/>
       <c r="O26" s="120"/>
-      <c r="P26" s="24"/>
-      <c r="Q26" s="24"/>
+      <c r="P26" s="119"/>
+      <c r="Q26" s="119"/>
       <c r="R26" s="119"/>
       <c r="S26" s="119"/>
       <c r="T26" s="119"/>
@@ -56573,18 +56570,18 @@
       <c r="C27" s="117"/>
       <c r="D27" s="118"/>
       <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="120"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="119"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="119"/>
+      <c r="K27" s="119"/>
+      <c r="L27" s="119"/>
+      <c r="M27" s="119"/>
+      <c r="N27" s="119"/>
       <c r="O27" s="120"/>
-      <c r="P27" s="24"/>
-      <c r="Q27" s="24"/>
+      <c r="P27" s="119"/>
+      <c r="Q27" s="119"/>
       <c r="R27" s="119"/>
       <c r="S27" s="119"/>
       <c r="T27" s="119"/>
@@ -56648,18 +56645,18 @@
       <c r="C28" s="117"/>
       <c r="D28" s="118"/>
       <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="119"/>
+      <c r="J28" s="119"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="119"/>
       <c r="N28" s="119"/>
       <c r="O28" s="120"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
+      <c r="P28" s="119"/>
+      <c r="Q28" s="119"/>
       <c r="R28" s="119"/>
       <c r="S28" s="119"/>
       <c r="T28" s="119"/>
@@ -56723,18 +56720,18 @@
       <c r="C29" s="117"/>
       <c r="D29" s="118"/>
       <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="119"/>
+      <c r="J29" s="119"/>
+      <c r="K29" s="119"/>
+      <c r="L29" s="119"/>
+      <c r="M29" s="119"/>
       <c r="N29" s="119"/>
       <c r="O29" s="120"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
+      <c r="P29" s="119"/>
+      <c r="Q29" s="119"/>
       <c r="R29" s="119"/>
       <c r="S29" s="119"/>
       <c r="T29" s="119"/>
@@ -67586,12 +67583,6 @@
   </sheetData>
   <autoFilter ref="A2:BQ178" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="15">
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:U1"/>
-    <mergeCell ref="V1:Y1"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="BN1:BQ1"/>
     <mergeCell ref="BR1:BU1"/>
@@ -67601,6 +67592,12 @@
     <mergeCell ref="AX1:BA1"/>
     <mergeCell ref="BB1:BE1"/>
     <mergeCell ref="BF1:BI1"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:U1"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="AD1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -67636,19 +67633,19 @@
           <x14:formula1>
             <xm:f>datavalidation!$B$1:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>O3 O10:O1048576</xm:sqref>
+          <xm:sqref>O3:O1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000005000000}">
           <x14:formula1>
             <xm:f>datavalidation!$C$1:$C$8</xm:f>
           </x14:formula1>
-          <xm:sqref>N3 N10:N1048576</xm:sqref>
+          <xm:sqref>N3:N1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000006000000}">
           <x14:formula1>
             <xm:f>datavalidation!$E$1:$E$2</xm:f>
           </x14:formula1>
-          <xm:sqref>B10:C186 B3:C3</xm:sqref>
+          <xm:sqref>B3:C186</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -77939,6 +77936,13 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="14">
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="C2:C11"/>
+    <mergeCell ref="C12:C17"/>
+    <mergeCell ref="C18:C28"/>
+    <mergeCell ref="C44:C53"/>
+    <mergeCell ref="C29:C43"/>
     <mergeCell ref="C163:C176"/>
     <mergeCell ref="C61:C70"/>
     <mergeCell ref="C71:C94"/>
@@ -77946,13 +77950,6 @@
     <mergeCell ref="C99:C108"/>
     <mergeCell ref="C109:C115"/>
     <mergeCell ref="C116:C162"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="C2:C11"/>
-    <mergeCell ref="C12:C17"/>
-    <mergeCell ref="C18:C28"/>
-    <mergeCell ref="C44:C53"/>
-    <mergeCell ref="C29:C43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -77960,6 +77957,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="107e75b3-53cc-4838-92d2-ebc011bd4832">
@@ -77968,15 +77974,6 @@
     <TaxCatchAll xmlns="888ccf44-0d39-41a2-ab17-f7efb2bf6977" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -78229,6 +78226,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B21D61-7BBD-4BD3-A9A5-1E8F98F2F686}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2288FB7-E85A-4FE8-9E7A-FE572FF16064}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -78241,14 +78246,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="888ccf44-0d39-41a2-ab17-f7efb2bf6977"/>
     <ds:schemaRef ds:uri="107e75b3-53cc-4838-92d2-ebc011bd4832"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B21D61-7BBD-4BD3-A9A5-1E8F98F2F686}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
